--- a/referencias_con_topicos.xlsx
+++ b/referencias_con_topicos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I175"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,58 +478,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.1186/s40538-025-00751-9</t>
+          <t>10.1109/ACCESS.2023.3286730</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Discovery of antimicrobial peptides from Bacillus genomes against phytopathogens with deep learning models</t>
+          <t>Multi-Class Classification of Plant Leaf Diseases Using Feature Fusion of Deep Convolutional Neural Network and Local Binary Pattern</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>H., Su, Huan; M., Gu, Mengli; Z., Qu, Zechao; Q., Wang, Qiao; J., Jin, Jingjing; P., Lu, Peng; J., Zhang, Jianfeng; P., Cao, Peijian; X., Ren, Xueliang; J., Tao, Jiemeng</t>
+          <t>K. M. Hosny; W. M. El-Hady; F. M. Samy; E. Vrochidou; G. A. Papakostas</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chemical and Biological Technologies in Agriculture</t>
+          <t>IEEE Access</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6247495412826538</v>
+        <v>0.6024771332740784</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Background: Antimicrobial peptides (AMPs) have emerged as a potential novel class of antimicrobial agents due to their broad microbial targeting and low resistance risks. Although AMPs have limited applications in agriculture, their potential to replace chemical pesticides could address food security and environmental concerns. Members of Bacillus sp., abundant in soil and plant microbiomes, are recognized as important sources of AMPs for their resistance and strong antimicrobial properties, making them ideal candidates for biocontrol in sustainable agriculture. To harness this potential, this study employed deep learning models to predict AMPs derived from Bacillus genomes, aiming to identify candidates with high activity against phytopathogens. Subsequently, the antimicrobial efficacy of selected candidate AMPs was experimentally validated. Results: More than 6700 Bacillus genomes were collected to identify a broad range of short peptides (10–100 amino acids), which were analyzed using advanced deep learning models, including BERT, Mamba, CNN-LSTM, and CNN-Attention. These models demonstrated enhanced predictive accuracy and reliability over existing methods, and resulted in 4,993,389 potential AMPs from Bacillus genomes. Among these AMPs, two high-confidence AMPs (cAMP_1 and cAMP_2) were selected by cross-validation, and their structural stability and activity were evaluated and verified by molecular dynamics simulations and experimental assays, respectively. Both of them exhibited antimicrobial activity against Escherichia coli, Staphylococcus aureus, and various common agricultural fungal and bacterial pathogens. Conclusions: This high-throughput deep learning pipeline successfully uncovered novel AMPs from Bacillus genomes, which underscored the efficiency of deep learning models in identifying functional peptides. This approach could accelerate the discovery of potential AMPs for biocontrol applications in plant disease management, contributing to sustainable agriculture and reduced dependency on traditional antibiotics. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Plant diseases are one of the primary causes of decreased agricultural production quality and quantity. With ongoing changes in plant structure and cultivation techniques, new diseases are constantly arising on plant leaves. Thus, accurate classification and detection of plant leaf diseases in their early stages will limit the spread of the infection and support the healthy development of plant production. This work proposes a novel lightweight deep convolutional neural network (CNN) model for obtaining high-level hidden feature representations. The deep features are then fused with traditional handcrafted local binary pattern (LBP) features to capture local texture information in plant leaf images. The proposed model is trained and tested on three publicly available datasets (Apple Leaf, Tomato Leaf, and Grape Leaf). On the three datasets, the proposed approach achieves 99%, 96.6%, and 98.5% validation accuracies, respectively, and 98.8%, 96.5%, and 98.3% test accuracies, respectively. The results of the experiments show that the proposed approach can provide a better control solution for plant diseases.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.1186/s12870-025-07128-y</t>
+          <t>10.1109/ACCESS.2025.3545670</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Integrated phenotypic analysis, predictive modeling, and identification of novel trait-associated loci in a diverse Theobroma cacao collection</t>
+          <t>YOLO-RDM: Innovative Detection Methods for Eggplants and Stems in Complex Natural Environment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>I., Baek, Insuck; M., Cha, Min-hyeok; S., Lim, Seunghyun; B.M., Irish, Brian M.; S., Oh, Sookyung; J., Bhatt, Jishnu; R.K., Upadhyay, Rakesh Kumar; M., Kim, Moon-sung; L.W., Meinhardt, Lyndel W.; S., Park, Sunchung</t>
+          <t>Q. Liu; Z. Zhou; L. Xiong; M. Lu; J. Ouyang</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -537,122 +537,122 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BMC Plant Biology</t>
+          <t>IEEE Access</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7487729787826538</v>
+        <v>0.3577488660812378</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 6: gardening, management, specie</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Background: Cacao (Theobroma cacao L.) breeding and improvement rely on understanding germplasm diversity and trait architecture. This study characterized a cacao collection (173 accessions) evaluated in Puerto Rico, examining phenotypic diversity, trait interrelationships, and performing comparative analyses with published Trinidad and Colombia datasets. We also developed machine learning (ML) models for yield prediction and identified yield-associated SNP markers. Results: The cacao collection showed significant phenotypic variation and strong intra-collection trait correlations. Comparative analyses revealed conserved trait responses across environments, notably linking susceptibility to black pod rot in Puerto Rico with Witches' Broom Disease in Colombia, suggesting a broad-spectrum disease response mechanism. Machine learning models effectively modeled yield, quantifying a hierarchy of predictor importance, with ‘Total pods’, ‘Infection rate’, and ‘Pod weight’ being the most influential. Integrating existing SNP data for 28 common accessions, multiple SNPs were identified as significantly associated with key horticultural traits, including ‘Total pods’, ‘Infection rate’, and ‘Yield’ (FDR &lt; 0.01). Notably, a single genetic marker on chromosome 5 (TcSNP475), located within a putative zinc finger stress-associated protein gene (Tc05_t008610), was associated with both ‘Total pods’ and ‘Yield’, representing a prime target for marker-assisted selection. Conclusions: This research provides a detailed characterization of a wide germplasm collection, robust yield predictors, and a suite of novel trait-linked genetic markers, offering valuable resources for cacao breeding. These integrated findings will provide a solid foundation for targeted breeding strategies and deeper molecular investigations into the mechanisms underpinning yield and stress resilience in this vital global crop. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Accurate identification of eggplants and their stems in complex environments is crucial for the research on intelligent harvesting equipment for eggplants. Current object detection methods have limited and traditional approaches to eggplant research. To achieve rapid identification of eggplants and stems in complex environments and enhance overall accuracy, this study establishes a database for eggplants and stems and proposes an efficient detection model based on the YOLOv8n network. First, a lightweight Receptive-Field Attention Convolution (RFAConv) and Mixed Local Channel Attention (MLCA) attention mechanism are used to design the C2f_RM module, replacing the C2f module in YOLOv8n to create a lightweight yet effective model. Next, the DD-Head structure reparameterization detection head module is integrated, effectively merging deep and shallow information while retaining small-scale target feature information to improve detection accuracy. Finally, the loss function is substituted with the MPDIoU loss, optimizing the bounding box regression algorithm and enhancing convergence speed and regression accuracy. The proposed YOLO-RDM model (C2f_RM, DD-Head, MPDIoU) attains an average accuracy of 93.6% on the dataset, representing a 3.4% improvement over the original YOLOv8n model. Detection accuracies for eggplants and stems increased by 1.1% and 5.8%, respectively. Additionally, the F1 score improved by 4.96%, reaching 89.09%. This model demonstrates superior detection performance and robustness for both eggplants and their stems, providing valuable technical support for the automation of eggplant harvesting.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10.1007/s44211-025-00814-9</t>
+          <t>10.1109/ACCESS.2023.3311477</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mid-FTIR and machine learning for predicting fig leaf macronutrients content</t>
+          <t>Constructing and Optimizing RNN Models to Predict Fruit Rot Disease Incidence in Areca Nut Crop Based on Weather Parameters</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>L., Hssaini, Lahcen; R., Razouk, Rachid</t>
+          <t>R. Krishna; K. V. Prema</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Analytical Sciences</t>
+          <t>IEEE Access</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9131021499633789</v>
+        <v>0.6378465294837952</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Predicting leaf mineral composition is critical for monitoring plant health and optimizing agricultural practices. This study combines Fourier-transform infrared spectroscopy with attenuated total reflectance (FTIR-ATR) and machine learning (ML) to specific macronutrients, namely nitrogen (N), phosphorus (P), potassium (K), calcium (Ca), and magnesium (Mg), in fig leaves (Ficus carica L.). A dataset of 90 leaves was analyzed, with FTIR spectra (450–4000 cm⁻1) preprocessed via baseline correction and second-derivative transformations. Three ML models were evaluated using fivefold cross-validation including Random Forest (RF), Support Vector Regression (SVR), and Gradient Boosting (GB), with performance assessed via root mean square error (RMSE), coefficient of determination (R2), and ratio of performance to deviation (RPD). GB outperformed other models, achieving validation RMSE/RPD values of 0.133/1.60 (nitrogen, N), 0.0107/1.79 (phosphorus, P), 0.1328/1.65 (potassium, K), 0.0636/1.96 (magnesium, Mg), and 0.2657/1.60 (calcium, Ca). Predictions for Mg (validation R2 = 0.7351) and P (validation R2 = 0.6873) exhibited the highest accuracy, potentially attributed to their stronger or more distinct spectral features (e.g., Mg-O stretching around 1050– 1150 cm⁻1; P-O vibrations around 1240 cm⁻1). Cross-validation revealed robust generalization for GB; while mean training RMSE was very low (&lt; 0.01 for P and Mg), validation RMSE remained relatively low, underscoring the model’s utility for screening (RPD &gt; 1.5). Despite evidence of overfitting (training R2 ≈ 0.999 vs. validation R2 = 0.61–0.74), GB’s performance evaluated using both RMSE and RPD confirmed its superiority over RF and SVR, which showed higher errors (e.g., SVR for Ca: RMSE = 0.4574, RPD = 1.07). This study demonstrates that FTIR-ATR coupled with ML is a rapid, non-destructive alternative to conventional destructive chemical analysis and that GB’s reliability, as indicated by RPD values &gt; 1.5, offers actionable insights for precision nutrient management in sustainable agriculture. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>A farmer faces several challenges associated with fruit rot disease in the areca nut crop. Weather factors, including rainfall and temperature, largely influence the disease severity and spread of infection in crops. Significant growth has been achieved using RNN models for time series forecasting in the past few decades, but these models are not applied to fruit rot disease prediction. This study introduces Vanilla GRU, Stacked GRU, Bidirectional GRU, and Bidirectional LSTM models for the inaugural prediction of fruit rot disease scores using past weather data. The current investigation also involves the mitigation and comparison of forecast inaccuracies by utilising weight optimisation algorithms like Adam, Adagrad, RMSprop, and Genetic algorithms. Meteorological and disease score data are gathered from the Agricultural Research Station in Brahmavar, Karnataka, and CPCRI Kasargod, Kerala. These datasets are combined using a rule-based algorithm to train and evaluate the proposed model. Empirical outcomes reveal that the vanilla GRU model, when fine-tuned with the Adam algorithm, exhibits a diminished Mean Squared Error (MSE) value of 0.0009, an exceptionally minimal Mean Absolute Error (MAE) value of 0.02, and an elevated R-squared (R2) score of 0.99. Similarly, the Bidirectional LSTM model, optimised through RMSprop, yields an impressively low Root Mean Squared Error (RMSE) value of 0.033. Generally, the optimised Deep Learning (DL) models consistently demonstrate enhanced predictive precision compared to alternative models. In conclusion, the anticipation of areca nut disease, as facilitated by this study, stands to aid farmers in curtailing unnecessary fungicide application and achieving more favourable yields.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10.1016/j.bspc.2025.107761</t>
+          <t>10.1109/ACCESS.2024.3362230</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gaussian regressed generative adversarial network based hermitian extreme gradient boosting for plant leaf disease detection</t>
+          <t>A Review on Automated Detection and Assessment of Fruit Damage Using Machine Learning</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S., Prakadeswaran, S.; A.B., Banu, A. Bazila</t>
+          <t>Safari, Y.; Nakatumba-Nabende, J.; Nakasi, R.; Nakibuule, R.</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Biomedical Signal Processing and Control</t>
+          <t>IEEE Access</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6868104338645935</v>
+        <v>0.7949352264404297</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Identifying diseases from images of plant leaves is one of the most important research topics in the field of agriculture. Cassava is a rich plant in protein and vitamins, particularly in the leaves, and it is also employed as a substitute for rice. Since, the leaf is the most susceptible portion of a plant, it is said to be affected easily in comparison with the other parts. Therefore, the detection of plant leaf diseases may decrease the possibility that the plant will undergo additional damage. Many research works have been designed for Cassava plant leaf disease diagnosis, but the accuracy of leaf disease detection was not improved with the minimum amount of error and time. In this paper, a novel technique called Gaussian Regressed Generative Adversarial Networks based Hermitian Extreme Gradient Boosting (GRGAN-HEGB) is introduced for accurate cassava plant disease detection. The GRGAN-HEGB technique is composed of three parts: preprocessing, feature extraction, and classification. At first, the numbers of real cassava leaf images are collected from the Cassava Disease Classification dataset. Then, the collected cassava leaf images are preprocessed using the Gaussian Process Regressed Generative Adversarial Network (GPR-GAN) model. Feature extraction is performed by employing Continuous Hermitian Contingency Correlation (CH-CC) model to extract the most influential features such as texture, shape, and colour for disease pattern detection. Lastly, the Cophenetic Optimized Extreme Gradient Boosting classification process is performed to classify the input cassava leaf images with extracted features. As a result, the accuracy of leaf disease detection is improved with a short processing time. Experimental evaluation is carried out using the cassava disease classification dataset by considering different metrics such as disease detection accuracy, disease detection time, precision, and recall. The statistical results confirm that the proposed technique achieves higher accuracy by 12 %, precision by 2 %, and recall by 2 % with minimum disease detection processing time by 10 % than the conventional classification methods. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Automation improves the quality of fruits through quick and accurate detection of pest and disease infections, thus contributing to the country's economic growth and productivity. Although humans can identify the fruit damage caused by pests and diseases, the methods used are inconsistent, time-consuming, and variable. The surface features of fruits typically observed by consumers who seek their health benefits affect their market value. The issue of pest and disease infections further deteriorates fruits' quality, becoming a mounting stressor on farmers since they reduce the potential revenue from fruit production, processing, and export. This article reviews various studies on detecting and classifying damages in fruits. Specifically, we review articles where state-of-the-art approaches under segmentation, image processing, machine learning, and deep learning have proved effective in developing automated systems that address hurdles associated with manual methods of assessing damage using visual experiences. This survey reviews thirty-two journal and conference papers from the past thirteen years that were found electronically through Google Scholar, Scopus, IEEE, ScienceDirect, and standard online searches. This survey further presents a detailed discussion of previous research done in the past while emphasizing their strengths and limitations as well as outlining potential future research topics. It also reveals that much as the use of automated detection and classification of fruit damage has yielded promising results in the horticulture industry, more research is still needed with systems required to fully automate the detection and classification processes, especially those that are mobile phone-based towards addressing occlusion challenges. © 2013 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10.1007/s00122-025-04973-1</t>
+          <t>10.3389/fpls.2025.1558349</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>In silico prediction of variant effects: promises and limitations for precision plant breeding</t>
+          <t>IMNM: integrated multi-network model for identifying pepper leaf diseases</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>J., Sendrowski, Janek; T.M., Bataillon, Thomas M.; G.P., Ramstein, Guillaume P.</t>
+          <t>Cai, Z.; Farhana, N.; Karim, A.M.; Zhai, F.; Huang, W.; Guo, M.</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -660,122 +660,122 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Theoretical and Applied Genetics</t>
+          <t>Frontiers in Plant Science</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.784515380859375</v>
+        <v>0.6838383674621582</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Key message: Sequence-based AI models show great potential for prediction of variant effects at high resolution, but their practical value in plant breeding remains to be confirmed through rigorous validation studies. Abstract: Plant breeding has traditionally relied on phenotyping to select individuals with desirable traits—a process that is both costly and time-consuming. Increasingly, breeding strategies are shifting toward precision breeding, where causal variants are directly targeted based on their effects. To predict the effects of causal variants, in silico methods are emerging as efficient alternatives or complements to mutagenesis screens. Here, we review state-of-the-art machine learning methods for predicting variant effects in plants across both coding and noncoding regions, contrasting supervised approaches in functional genomics with unsupervised methods in comparative genomics. We discuss challenges in validating predictions, and compare these methods with traditional association and comparative genomics techniques. We argue that modern sequence models extend traditional methods by generalizing across genomic contexts, fitting a unified model across loci rather than a separate model for each locus. In doing so, they address inherent limitations of traditional quantitative and evolutionary comparative genetics techniques. However, the accuracy and generalizability of sequence models heavily depend on the training data, highlighting the need for validation experiments. We point to successful applications of sequence models, especially with protein sequences, and identify areas for further improvement, especially in modeling regulatory sequences. While not yet mature for in silico-driven precision breeding, sequence models show strong potential to become an integral part of the breeder’s toolbox. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>As a vegetable crop with high economic value, the yield of pepper is often significantly restricted by leaf diseases, and the spots formed by these diseases on the surface of leaves are highly complex in color and texture characteristics. To overcome the shortcomings of traditional manual identification methods, such as low efficiency, time-consuming, and labor-consuming, an integrated multi-network model (IMNM) was established by combining an improved ResNet, a dynamic convolution network (DCN), and a progressive prototype network (PPN), which was aimed at five typical pepper leaf samples (healthy, virus, leaf blight, brown spot, and phyllosticta). The experimental results show that IMNM achieves 98.55% accuracy in pepper disease identification, which is significantly better than the benchmark models such as Inception-V4, ShuffleNet-V3, and EfficientNet-B7. In the cross-species generalization verification, the average identification accuracy of the model for apple, wheat, and rice leaf diseases increased to 99.81%, and its four core indicators of specificity, precision, sensitivity, and accuracy were all stable over 98%. This demonstrates that IMNM can effectively analyze the color and texture characteristics of highly heterogeneous disease spots and possesses strong cross-crop generalization capabilities. Its technical path lays a theoretical foundation for the development of field mobile disease diagnosis equipment based on deep learning, and is of great value for promoting the engineering application of an intelligent monitoring system for crop diseases and insect pests. © © 2025 Cai, Farhana, Karim, Zhai, Huang and Guo.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10.1016/j.jmb.2025.169093</t>
+          <t>https://doi.org/10.1016/j.mattod.2023.07.002</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PlantPathoPPI: An Ensemble-based Machine Learning Architecture for Prediction of Protein-Protein Interactions between Plants and Pathogens</t>
+          <t>Microneedle technology as a new standpoint in agriculture: Treatment and sensing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>S., Murmu, Sneha; H., Chaurasia, Himanshushekhar; A.R., Ramakrishna Rao, Atmakuri Ramakrishna; A., Rai, Anil; S., Jaiswal, Sarika; A., Bharadwaj, Anshu; R.N., Yadav, Rajbir N.; S., Archak, Sunil</t>
+          <t>Emre Ece; Ismail Eş; Fatih Inci</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Journal of Molecular Biology</t>
+          <t>Materials Today</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7867923378944397</v>
+        <v>0.3988777995109558</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 6: gardening, management, specie</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>This study aimed to develop a machine learning-based tool for predicting protein–protein interactions (PPIs) between plant-pathogen systems, addressing the challenges of experimental PPI identification. Identifying PPIs in plant-pathogen interactions is crucial for understanding the molecular mechanisms underlying plant defense and pathogen virulence. However, experimental methods are time-consuming and labor-intensive, prompting the use of computational techniques to complement traditional approaches. A robust ensemble model was developed using multiple sequence encodings and diverse learning algorithms such as random forest, support vector machine, and artificial neural network. The features used included auto-covariance, conjoint triad, and local descriptor schemes, which were selected based on their performance. The top three performing models were combined into an ensemble model, improving prediction accuracy to approximately 97%. The PlantPathoPPI tool, developed through this approach, was compared with existing tools using an independent test dataset, showing promising potential for PPI prediction in plant-pathogen interactions. To facilitate broad accessibility, a web-based prediction server was developed, available at https://plantpathoppi.onrender.com/, alongside a Python package on https://pypi.org/project/plantpathoppi-ml/. This research contributes significantly to the field by offering an efficient tool for predicting PPIs in plant-pathogen systems, providing valuable insights into plant diseases and supporting hypothesis-driven research. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Preventing plant loss and improving their health status are essential for agricultural industry. Correspondingly, the deprivation of plants severely impacts our ecological system. As such, global efforts have been intensely made to promote the development of advanced sensing and treatment platforms to forestall plant loss. Existing technologies mainly encounter a number of challenges in providing results in a non-invasive, rapid turnaround, and affordable fashions. Accordingly, notable progressions in innovative approaches—particularly biosensing and delivery platforms, are vastly required for agriculture realm. In this regard, microneedles have emerged as a pivotal technological tool that plays multifaceted roles in biosensing and delivery systems, with attention of growing towards agriculture. Simply put, microneedles offer several advantages over conventional methods for being less invasive, rapid, and highly precise. In this review, recent advancements in microneedle technologies including their implementations in agriculture are highlighted coherently. In particular, extracting DNA from plant leaves and expressing transient genes using microneedles are elaborated in details. Microneedle-based sensing platforms for detecting essential compounds and secondary metabolites are discussed as well. Recent advances focusing the delivery of agrochemicals and nanotherapeutics via microneedles are elaborated. By this means, this review aims to bridge the existing gaps between microneedles and agriculture precisely.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10.1007/s11274-025-04442-3</t>
+          <t>10.3390/su13158600</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Monochromatic LeafAdaptNet (MLAN): an adaptive approach to spinach leaf disease detection using monochromatic imaging</t>
+          <t>Frontiers in the solicitation of machine learning approaches in vegetable science research</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>M., Elumalai, Meganathan; T.F., Fernandez, Terrance Frederick; R., Kaviarasan, Ramu; K., Suriyan, Kannadhasan</t>
+          <t>Sharma, M.; Kaushik, P.; Chawade, A.</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>World Journal of Microbiology and Biotechnology</t>
+          <t>Sustainability (Switzerland)</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5940303802490234</v>
+        <v>0.4134390652179718</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 2: approach, data, grape</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>A country's economic growth heavily relies on agricultural productivity, specifically nutrition derived from vegetables and leafy greens. Spinach, abundant in iron, vitamins, and other essential nutrients, plays a vital role in maintaining the health of human tissues, cartilage, and hair. However, extreme summer heat and plant diseases can significantly reduce spinach yields, making it less nutritious and harder to obtain. Implementing improved detection and classification of bacterial and fungal diseases affecting spinach leaves is crucial for minimizing pesticide use and enhancing agricultural output. A cutting-edge approach was introduced for identifying diseases in spinach leaves through deep learning object detection. To tackle these issues, the DenseNet-121-DO model served as the basis for developing the Custom Monochromatic LeafAdaptNet (MLAN). Spinach leaves were classified as Half-Spinach, Curry Leaves, Drumstick Leaves, and Lettuce, with the aid of Google-Colaboratory. This model displayed impressive results, achieving an accuracy of 99.10% and a mean Average Precision (mAP) of 98.16%. Such outcomes promote higher agricultural productivity and reduced pesticide costs by showcasing the system’s effectiveness in accurately identifying and classifying spinach leaf diseases. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Along with essential nutrients and trace elements, vegetables provide raw materials for the food processing industry. Despite this, plant diseases and unfavorable weather patterns continue to threaten the delicate balance between vegetable production and consumption. It is critical to utilize machine learning (ML) in this setting because it provides context for decision-making related to breeding goals. Cutting-edge technologies for crop genome sequencing and phenotyping, combined with advances in computer science, are currently fueling a revolution in vegetable science and technology. Additionally, various ML techniques such as prediction, classification, and clustering are frequently used to forecast vegetable crop production in the field. In the vegetable seed industry, machine learning algorithms are used to assess seed quality before germination and have the potential to improve vegetable production with desired features significantly; whereas, in plant disease detection and management, the ML approaches can improve decision-support systems that assist in converting massive amounts of data into valuable recommendations. On similar lines, in vegetable breeding, ML approaches are helpful in predicting treatment results, such as what will happen if a gene is silenced. Furthermore, ML approaches can be a saviour to insufficient coverage and noisy data generated using various omics platforms. This article examines ML models in the field of vegetable sciences, which encompasses breeding, biotechnology, and genome sequencing. © 2021 by the authors. Licensee MDPI, Basel, Switzerland.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10.1007/s00122-025-04948-2</t>
+          <t>https://doi.org/10.1016/j.ijfoodmicro.2025.111397</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Integrating multi-omics and machine learning for disease resistance prediction in legumes</t>
+          <t>A review on anthracnose disease caused by Colletotrichum spp. in fruits and advances in control strategies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>S., Mohamedikbal, Shameela; H.A., Al-Mamun, Hawlader Abdullah; M.S., Bestry, Mitchell S.; J., Batley, Jacqueline; D., Edwards, David</t>
+          <t>Cheng Xue Law; Norhashila Hashim; Siti Izera Ismail; Mahirah Jahari; Dimas Firmanda {Al Riza}</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -783,163 +783,163 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Theoretical and Applied Genetics</t>
+          <t>International Journal of Food Microbiology</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5551313757896423</v>
+        <v>0.5837229490280151</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 6: gardening, management, specie</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Key message: Multi-omics assisted prediction of disease resistance mechanisms using machine learning has the potential to accelerate the breeding of resistant legume varieties. Abstract: Grain legumes, such as soybean (Glycine max (L.) Merr.), chickpea (Cicer arietinum L.), and lentil (Lens culinaris Medik.) play an important role in combating micronutrient malnutrition in the growing human population. However, plant diseases significantly reduce grain yield, causing 10–40% losses in major food crops. The genetic mechanisms associated with disease resistance in legumes have been widely studied using genomic approaches. Multi-omics data encompassing various biological layers such as the transcriptome, epigenome, proteome, and metabolome, in addition to the genome, enables researchers to gain a deeper understanding of these complementary layers and their roles in complex legume-pathogen interactions. Genomic prediction, used to select the best genotypes with desirable traits for breeding, has largely relied on genome-wide markers and statistical approaches to estimate the breeding values of individuals. Integrating multi-omics data into genomic prediction can be achieved using machine learning models, which can capture nonlinear relationships prevalent in high-dimensional data better than traditional statistical methods. This integration may enable more accurate predictions and identification of resistance mechanisms for breeding resistant legumes. Despite its potential, multi-omics integration for disease resistance prediction in legumes has been largely unexplored. In this review, we explore omics studies focusing on disease resistance in legumes and discuss how machine learning models can integrate multi-omics data for disease resistance prediction. Such multi-omics assisted prediction has the potential to reduce the breeding cycle for developing disease-resistant legume varieties. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Fruits are a vital source of essential vitamins, minerals, and antioxidants necessary for human health and well-being. However, fruit production is often hampered by diseases that cause substantial yield losses and compromise fruit quality. Among these, anthracnose caused by various species of the Colletotrichum genus stands out as a particularly destructive disease, affecting a wide range of fruit crops and resulting in significant preharvest and postharvest losses worldwide. This review explores the impact of anthracnose across diverse fruit categories, including temperate fruits, berries, citrus, and tropical fruits. Furthermore, it provides a comprehensive overview of the life cycle and pathogenic mechanisms of Colletotrichum spp., emphasizing their remarkable adaptability to different host fruits. Advances in management strategies are also explored, emphasizing the need for sustainable approaches. While chemical fungicides remain widely used, their overuse has led to resistance development and environmental concerns. Promising alternatives include biological control agents and natural compounds like essential oils and chitosan-based coatings, and physical treatments, such as heat and UV-C irradiation, are also discussed. Future trends are also highlighted. This review provides a new insight of anthracnose across fruit categories, integrating current knowledge on pathogen biology, host-pathogen interactions, and innovative control measures. Future research should prioritize the development of integrated management strategies tailored to specific fruit categories, ensuring sustainable production, enhanced fruit quality, and reduced postharvest losses.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10.1016/j.dib.2025.111594</t>
+          <t>https://doi.org/10.1016/j.molp.2022.09.007</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cauliflower leaf diseases: A computer vision dataset for smart agriculture</t>
+          <t>Metabolomics-centered mining of plant metabolic diversity and function: Past decade and future perspectives</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>S.H., Durjoy, Sabbir Hossain; M.E., Shikder, Md Emon; M.M.H., Shoib, Md Mehedi Hasan; M.H.I., Bijoy, Md Hasan Imam</t>
+          <t>Shuangqian Shen; Chuansong Zhan; Chenkun Yang; Alisdair R. Fernie; Jie Luo</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data in Brief</t>
+          <t>Molecular Plant</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4917862117290497</v>
+        <v>0.2859475314617157</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Cauliflower is among the more well-known vegetables there are. Consumed all around the globe due to it being rich in nutrients such as vitamins, antioxidants, and for being high in fibre. These are nutritional qualities that help with digestion, immune-system, and minimizing inflammation. It is a common issue among farmers to have to deal with various diseases in cauliflower leaves that are difficult to diagnose in their early stages. These diseases have a tendency to propagate in a really swift pace throughout entire fields worth of crops. This in-turn causes heavy losses in the harvest, and makes it much more tedious and resource-intensive to protect the crops. As a result, farmers get more likely to use high amounts of pesticides and harmful chemicals to streamline the process of getting a more reliable yield on their crops. This is not only costly, but it is also harmful both to the quality of crops and to the well-being of the environment. In this publication, we are introducing a dataset containing a considerable number of images of cauliflower leaves. This is intended to drive development on this topic at a faster pace than it is now, and to help enhance disease monitoring, diagnosis, and precautionary techniques. We collected our dataset images between November 2024 and January 2025. In this dataset, cauliflower leaves were categorized into three classes: Healthy, Insect Holes, and Black Rot, each reflecting a specific condition that impacts plant health at different stages. This dataset consists of 2,661 images. The pictures were captured at different locations in Bangladesh, under different weather conditions, dates, temperatures, and with different devices. To enhance the data quality, we used several steps to process the dataset, making sure it would reflect real-world conditions and be ready for training. The images were resized to a standard size of 3000 × 3000 pixels, brightness was adjusted to make the images more easily discernible, and we removed duplicates and poor-quality images. These actions helped ensure the dataset was in the best possible shape for effective model training. This dataset will be highly effective for agricultural research, precision agriculture, and effective management of diseases. It should help develop highly accurate machine learning models for early detection of Cauliflower leaf diseases. The dataset is employed to train deep learning models to support automated monitoring and smart decision-making in precision agriculture. This data set also has immense potential for real-time and practical use. It can be utilized to develop applications like mobile apps or automated systems where farmers can easily identify diseases at early stages and take immediate action, without the requirement of expert on-site knowledge. This data set can also be utilized with smart farming equipment like drones and sensors to track big fields in real time. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Plants are natural experts in organic synthesis, being able to generate large numbers of specific metabolites with widely varying structures that help them adapt to variable survival challenges. Metabolomics is a research discipline that integrates the capabilities of several types of research including analytical chemistry, statistics, and biochemistry. Its ongoing development provides strategies for gaining a systematic understanding of quantitative changes in the levels of metabolites. Metabolomics is usually performed by targeting either a specific cell, a specific tissue, or the entire organism. Considerable advances in science and technology over the last three decades have propelled us into the era of multi-omics, in which metabolomics, despite at an earlier developmental stage than genomics, transcriptomics, and proteomics, offers the distinct advantage of studying the cellular entities that have the greatest influence on end phenotype. Here, we summarize the state of the art of metabolite detection and identification, and illustrate these techniques with four case study applications: (i) comparing metabolite composition within and between species, (ii) assessing spatio-temporal metabolic changes during plant development, (iii) mining characteristic metabolites of plants in different ecological environments and upon exposure to various stresses, and (iv) assessing the performance of metabolomics as a means of functional gene identification , metabolic pathway elucidation, and metabolomics-assisted breeding through analyzing plant populations with diverse genetic variations. In addition, we highlight the prominent contributions of joint analyses of plant metabolomics and other omics datasets, including those from genomics, transcriptomics, proteomics, epigenomics, phenomics, microbiomes, and ion-omics studies. Finally, we discuss future directions and challenges exploiting metabolomics-centered approaches in understanding plant metabolic diversity.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10.1007/s11240-025-03054-x</t>
+          <t>https://doi.org/10.1016/j.compag.2023.108265</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Revolutionizing in vitro cultivation: machine learning-based optimization of nutrients for superior morphology and biochemistry of Phalaenopsis orchids</t>
+          <t>High-throughput horticultural phenomics: The history, recent advances and new prospects</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Z., Mahdavi, Zahra; S., Dianati Daylami, Shirin; K., Asefpour Vakilian, Keyvan; K., Vahdati, Kourosh</t>
+          <t>Moran Zhang; Shengyong Xu; Yutong Han; Dongping Li; Shuo Yang; Yuan Huang</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Plant Cell, Tissue and Organ Culture</t>
+          <t>Computers and Electronics in Agriculture</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7995083928108215</v>
+        <v>0.6260955929756165</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tópico 4: yolov, increase, map</t>
+          <t>Tópico 8: horticultural, review, platform</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Growing Phalaenopsis orchids in vitro presents challenges for growers due to their prolonged growth period and extended juvenile stage. This study employed machine learning to optimize macronutrient concentrations during the cultivation of Phalaenopsis orchids. A dataset was generated by investigating the effects of various macronutrient levels on the morphological and biochemical traits of plantlets. An innovative iterative prediction scheme based on artificial neural networks (ANNs) was utilized to identify the optimal macronutrient levels necessary for enhancing plant morphology and biochemistry. The modeling results indicated that doubling the nitrate concentration, combined with a 2.2% increase in potassium and a 5.3% increase in phosphorus compared to the half-strength MS medium, yielded the most favorable morphological traits. Additionally, the model demonstrated that a twofold increase in nitrate, along with a 2.7% increase in potassium and a 4.7% increase in phosphorus, significantly improved biochemical characteristics, including chlorophyll a, chlorophyll b, total chlorophyll, and carotenoids. To investigate the possibility of introducing a single optimal point for the improvement of both morphological and biochemical traits, new plants were cultivated by doubling the nitrate content, a 2.5% increase in potassium, and a 5.0% increase in phosphorus, all compared with the control, i.e., half-strength MS medium. Remarkable enhancements were observed in plant physiology and biochemistry, achieving over a 50% increase in morphological traits and a 200% increase in biochemical traits. The proposed approach that effectively reduces the growth period of the orchid plantlets, can revolutionize the cultivation of plants with prolonged growth periods. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>With the development of advanced sensors, artificial intelligence, and computer vision, horticultural phenomics has made great progress in recent years. However, there is a lack of systematic reviews to discuss the horticultural phenomics and its applications at present. In this paper, we aim to fill this gap by providing a comprehensive review of the past developments, recent advances and existing challenges. Furthermore, we propose conception and give our prospects of high-throughput horticultural phenomics. We envision that horticultural phenomics will evolve towards multiscale, multidimension, multiperiod approach in the near future. This transformation will enable researchers to better realize the physiological processes, understand the genetic composition and develop new cultivars of horticultural plants that are better adapted to specific environments. Consequently, it will greatly promote the omics research in horticultural plants. In addition to advancing scientific research, high-throughput horticultural phenomics can also assist growers in efficient crop management, leading to improved yield and quality of horticultural products. However, it is important to acknowledge the challenges that need to be overcome. Once these challenges are addressed, high-throughput horticultural phenomics will become increasingly important in the fight against climate changes and maximizing profits.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10.1016/j.compbiomed.2025.109862</t>
+          <t>https://doi.org/10.1016/j.compag.2022.107096</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Identification of potent phytochemicals against Magnaporthe oryzae through machine learning aided-virtual screening and molecular dynamics simulation approach</t>
+          <t>Viable smart sensors and their application in data driven agriculture</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>S., Murmu, Sneha; A., Aravinthkumar, A.; M.K., Singh, Mahender Kumar; S., Sharma, Soumya; R., Das, Ritwika; G.K., Jha, Girish Kumar; G., Prakash, Ganesan; V.S., Rana, Virendra Singh; P., Kaushik, Parshant; M.S., Farooqi, Mohammad Samir</t>
+          <t>Kenny Paul; Sandeep S. Chatterjee; Puja Pai; Alok Varshney; Siddhi Juikar; Venkatesh Prasad; Bhaskar Bhadra; Santanu Dasgupta</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Computers in Biology and Medicine</t>
+          <t>Computers and Electronics in Agriculture</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5769309401512146</v>
+        <v>0.9740328192710876</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Magnaporthe oryzae stands as a notorious fungal pathogen responsible for causing devastating blast disease in cereals, leading to substantial reductions in grain production. Despite the usage of chemical fungicides to combat the pathogen, their effectiveness remains limited in controlling blast disease. Consequently, there exists a pressing need to discover a novel natural biofungicide for efficient blast disease management. To address this challenge, we combined machine learning-based bioactivity prediction with virtual screening, molecular docking, and molecular dynamics (MD) simulations to explore the molecular interactions between forty-eight plant-derived natural compounds and the effector protein, Avr-PikE, an avirulence protein from Magnaporthe oryzae. Among the evaluated phytochemicals, Calotropin, Lupeol, and Azadirachtin emerged as the top-ranking molecules based on their favourable affinity through molecular docking with the effector. MD simulations for 100 ns were conducted to ascertain the stability and reliability of these compounds. Through classical and steered MD simulations and free energy calculations, it was revealed that these selected compounds exhibit stable and favourable energies, thereby establishing strong binding interactions with Avr-PikE. These screened natural metabolites were also found to meet crucial criteria for fungicide-likeness. To support accessibility and broader applications, we also developed a bioactivity prediction app (http://login1.cabgrid.res.in:5260/), allowing users to predict bioactivity against fungi based on our model. The efficacy of one potent compound, Lupeol, was validated through in vitro experiments, confirming its significant antifungal activity against Magnaporthe oryzae. Such biofungicides hold promise for enhancing disease management strategies and mitigating the impact of blast disease on cereal crops. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Smart sensors are useful in professional farming approach by which one can use the digital technology to monitor, visualize, generate digital data, to control the application of resources, to improve quality and productivity of agriculture produce. Novel sensors add value in soil-less farming through automation and IoT (Internet of Things) based operation management digital tools. Data-driven technologies by using smart sensors can find a solution to many glitches in agriculture practices and it could improve new efficiencies. The principles of smart sensors as well as the most viable sensors that are used for monitoring soil and plant physicochemical parameters in field cultivation processes, greenhouse and indoor hydroponics are being discussed. Digital technologies in precision farming, automation in agro machinery, Precision Livestock Farming (PLF), TV White Spaces (TVWS) remote connectivity, Unmanned Aerial Vehicles (UAVs) based imagery, application of IoTs can help farming communities to use resources accurately based on real-time farm data acquired and improve crop yield without any wastage. Smart sensors helps the entire food value chain, the precision to productivity quest of growers and could enable new business models. This article provides a wide understanding of novel smart sensors, wireless sensor network architectures, and applications of these sensors to inculcate sustainable farming practices, value chain traceability and create secured income.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10.5812/ijp-148520</t>
+          <t>https://doi.org/10.1016/j.compag.2024.109704</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A Decision Support System for Machine Learning-Based Determination of Zinc Deficiency: A Study in Adolescent Patients</t>
+          <t>Advanced technologies for precision tree fruit disease management: A review</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>D., Orbatu, Dilek; Z.İ.P., Bulğan, Zeynep İzem Peker; E., Olmez, Emre; O., Er, Orhan</t>
+          <t>Yanqiu Yang; Priyanka Mali; Lawrence Arthur; Faezeh Molaei; Sena Atsyo; Jiarui Geng; Long He; Shirin Ghatrehsamani</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -947,40 +947,40 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Iranian Journal of Pediatrics</t>
+          <t>Computers and Electronics in Agriculture</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8011610507965088</v>
+        <v>0.3891785442829132</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Background: Over the past three years, zinc deficiency among adolescents has varied based on region and access to healthcare. Globally, zinc deficiency affects approximately 2 billion people, leading to serious issues such as immune problems and growth delays, particularly in developing countries. In the U.S., around 10% of adolescents experienced zinc deficiency in 2021, with a higher prevalence among teenage girls. In Europe, deficiency rates are generally low but can be significant in Eastern Europe and Central Asia. In Asia, particularly in rural and low-income areas, deficiency rates range from 20-30%. In Turkey, the prevalence is high due to poor nutrition. Objectives: This study aimed to develop a machine learning-based decision support system to determine zinc deficiency in children and adolescents aged 10-18 years. Methods: This machine learning-based study was conducted with 370 adolescents aged 10-18 years to assess their zinc deficiency. The dataset consists of 8 feature vectors and an output vector. The machine learning methods used in the analysis include logistic regression, naive bayes, decision tree (CART), K-nearest neighbors (K-NN), support vector machine (SVM), gradient boosting classifier, AdaBoost classifier, bagging classifier, random forest classifier, multilayer perceptron (MLP) classifier, and XGBoost (XGB) classifier. Evaluation metrics such as accuracy, precision, recall, and F1 score were used to assess the performance of these methods. Including specific values for these metrics, such as "SVM achieved 94.6% accuracy," would allow readers to quickly compare the effectiveness of the models. Different metrics serve various purposes: Accuracy provides an overall view of performance, precision and recall highlight specific aspects, and the F1 score balances precision and recall. Results: The mean age of the patients in the dataset was 13.79 ± 1.18 years. Of the children, 64.32% (n = 238) were female and 35.68% (n = 132) were male. It was found that 62.7% (n = 232) of the children had low zinc levels, while 37.3% (n = 138) did not require zinc supplementation. Thirteen different machine learning methods were applied to a 70% training and 30% testing set. As a result, the SVM method provided the most successful outcome with 94.6% accuracy. Implementing the SVM-based system in pediatric clinics could improve efficiency and patient care by automatically detecting high-risk zinc deficiency patients based on lab results, providing early intervention alerts for faster treatment, and improving health outcomes. Highlighting these practical applications could increase the study’s appeal to healthcare professionals by demonstrating its real-world benefits. Providing detailed information on these applications would enhance the study’s clarity and practical value, making it more valuable for researchers and healthcare providers interested in AI tools for adolescent health. Conclusions: This study concluded that machine learning methods can effectively determine zinc deficiency in children. The SVM method demonstrated superior classification performance compared to the other methods. An SVM-based decision support system could be integrated into pediatric outpatient clinics to enhance diagnostic accuracy and patient care. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Effective disease management in tree fruit cultivation is essential for ensuring crop health, improving yield, and minimizing economic losses. In recent years, the adoption of advanced technologies has revolutionized the approach to managing tree fruit diseases. This review explores the integration of precision agriculture tools, such as Unmanned Aerial Vehicles (UAVs), Unmanned Ground Vehicles (UGVs), and various sensor technologies, alongside sophisticated machine learning algorithms and predictive models. The effectiveness of these technologies in disease scouting, monitoring, detection, and prediction is evaluated, emphasizing their potential to enhance crop health, reduce economic losses, and minimize environmental impacts. Despite the promising advancements, challenges such as data quality, computational demands, and the need for robust, generalizable models persist. This review underscores the transformative potential of these technologies in promoting a resilient, efficient, and sustainable tree fruit industry, highlighting the need for continued research and development to fully realize their benefits.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10.1111/tpj.70169</t>
+          <t>10.1186/s12870-025-07128-y</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>In silico prediction method for plant Nucleotide-binding leucine-rich repeat- and pathogen effector interactions</t>
+          <t>Integrated phenotypic analysis, predictive modeling, and identification of novel trait-associated loci in a diverse Theobroma cacao collection</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A., Fick, Alicia; J.L.M., Fick, Jacobus Lukas Marthinus; V., Swart, Velushka; N., van den Berg, Noëlani</t>
+          <t>Baek, I.; Cha, M.; Lim, S.; Irish, B.M.; Oh, S.; Bhatt, J.; Upadhyay, R.K.; Kim, M.S.; Meinhardt, L.W.; Park, S.; Ahn, E.</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -988,40 +988,40 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Plant Journal</t>
+          <t>BMC Plant Biology</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9924077391624451</v>
+        <v>0.3863219916820526</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 2: approach, data, grape</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Plant Nucleotide-binding leucine-rich repeat (NLR) proteins play a crucial role in effector recognition and activation of Effector triggered immunity following pathogen infection. Genome sequencing advancements have led to the identification of a myriad of NLRs in numerous agriculturally important plant species. However, deciphering which NLRs recognize specific pathogen effectors remains challenging. Predicting NLR–effector interactions in silico will provide a more targeted approach for experimental validation, critical for elucidating function, and advancing our understanding of NLR-triggered immunity. In this study, NLR–effector protein complex structures were predicted using AlphaFold2-Multimer for all experimentally validated NLR–effector interactions reported in literature. Binding affinities- and energies were predicted using 97 machine learning models from Area-Affinity. We show that AlphaFold2-Multimer predicted structures have acceptable accuracy and can be used to investigate NLR–effector interactions in silico. Binding affinities for 58 NLR–effector complexes ranged between −8.5 and −10.6 log(K), and binding energies between −11.8 and −14.4 kcal/mol−1, depending on the Area-Affinity model used. For 2427 “forced” NLR–effector complexes, these estimates showed larger variability, enabling identification of novel NLR–effector interactions with 99% accuracy using an Ensemble machine learning model. The narrow range of binding energies- and affinities for “true” interactions suggest a specific change in Gibbs free energy, and thus conformational change, is required for NLR activation. This is the first study to provide a method for predicting NLR–effector interactions, applicable to all pathosystems. Finally, the NLR–Effector Interaction Classification (NEIC) resource can streamline research efforts by identifying NLRs important for plant–pathogen resistance, advancing our understanding of plant immunity. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Background: Cacao (Theobroma cacao L.) breeding and improvement rely on understanding germplasm diversity and trait architecture. This study characterized a cacao collection (173 accessions) evaluated in Puerto Rico, examining phenotypic diversity, trait interrelationships, and performing comparative analyses with published Trinidad and Colombia datasets. We also developed machine learning (ML) models for yield prediction and identified yield-associated SNP markers. Results: The cacao collection showed significant phenotypic variation and strong intra-collection trait correlations. Comparative analyses revealed conserved trait responses across environments, notably linking susceptibility to black pod rot in Puerto Rico with Witches' Broom Disease in Colombia, suggesting a broad-spectrum disease response mechanism. Machine learning models effectively modeled yield, quantifying a hierarchy of predictor importance, with ‘Total pods’, ‘Infection rate’, and ‘Pod weight’ being the most influential. Integrating existing SNP data for 28 common accessions, multiple SNPs were identified as significantly associated with key horticultural traits, including ‘Total pods’, ‘Infection rate’, and ‘Yield’ (FDR &lt; 0.01). Notably, a single genetic marker on chromosome 5 (TcSNP475), located within a putative zinc finger stress-associated protein gene (Tc05_t008610), was associated with both ‘Total pods’ and ‘Yield’, representing a prime target for marker-assisted selection. Conclusions: This research provides a detailed characterization of a wide germplasm collection, robust yield predictors, and a suite of novel trait-linked genetic markers, offering valuable resources for cacao breeding. These integrated findings will provide a solid foundation for targeted breeding strategies and deeper molecular investigations into the mechanisms underpinning yield and stress resilience in this vital global crop. © This is a U.S. Government work and not under copyright protection in the US; foreign copyright protection may apply 2025.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10.1111/sum.70063</t>
+          <t>https://doi.org/10.1016/j.plaphy.2025.110577</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Soil microbial variability in contrasting grown flue-cured tobacco under long-term continuous cropping</t>
+          <t>Development of multi-sensing technologies for high-throughput morphological, physiological, and biochemical phenotyping of drought-stressed watermelon plants</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>R., Jia, Rong; X., Qu, Xinyue; M., Chen, Min; Y., Xu, Yi; Z., Liu, Zhiyong; L.E.K., Peixoto, Leanne E.K.; Y., Lin, Yechun; Y., Guo, Yali; A., Kumar, Amit; J., Chen, Jie</t>
+          <t>Mohammad Akbar Faqeerzada; Eunsoo Park; Jinsu Lim; Kihyun Kim; Ramaraj Sathasivam; Sang Un Park; Hangi Kim; Byoung-Kwan Cho</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1029,122 +1029,122 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Soil Use and Management</t>
+          <t>Plant Physiology and Biochemistry</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3629493415355682</v>
+        <v>0.4252332746982574</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Soil microbial communities are directly impacted by agricultural management practices and play a crucial role in determining crop productivity. Therefore, we investigated how long-term continuous cropping would impact the composition of microbial communities and their feedback to flue-cured tobacco. We selected flue-cured tobacco with contrasting agronomic traits from three fields under continuous cultivation for over a decade, where well-grown plants had 1.45, 1.28, 1.17 and 1.25 times greater height, leaf number, length and width than poorly grown tobacco, respectively. The root zone soils of flue-cured tobacco with contrasting agronomic traits were collected to analyse the community structure and network characteristics of soil bacteria and fungi. Although bacterial and fungal diversity, dominated by stochastic processes, remained invariant between contrasting agronomic traits, community composition differed significantly at the order level. Specifically, the well-grown tobacco was enriched with Micrococcales, Xanthomonadales and Eurotiales groups known for their role in organic matter degradation. In contrast, poorly grown tobacco was uniquely enriched with bacteria typically involved in nitrate cycling, such as Nitrospira, Nocardioides and Betaproteobacteria. Bacterial function prediction based on Tax4Fun2 showed that functions related to amino acid cycling were enriched in the root zone of well-grown tobacco. Additionally, the rhizosphere of well-grown tobacco exhibited a more complex bacterial network with larger network hubs than that of poorly grown tobacco. In conclusion, the enrichment of organic matter decomposers and nitrate transformers in the root zones of continuously cropped flue-cured tobacco significantly impacts agronomic traits, with a complex soil bacterial network and key network hubs playing a crucial role in maintaining tobacco growth. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>High-throughput plant phenotyping (HTPP) technologies are rapidly transforming plant science by enabling real-time, non-invasive, and large-scale monitoring of complex morphological, physiological, and biochemical traits. However, existing platforms often lack integration across sensing modalities and analytical depth necessary for early and comprehensive phenotypic trait analysis. In this study, we developed a fully automated, multimodal HTPP system combining RGB, shortwave infrared (SWIR) hyperspectral, multispectral fluorescence imaging (MSFI), and thermal imaging to characterize drought-stressed watermelon (Citrullus lanatus) plants. RGB imaging facilitated detailed morphological analysis by extracting color-based traits, quantifying plant height and canopy area, and accurately distinguishing growth stages. SWIR hyperspectral imaging (HSI) enabled non-invasive biochemical assessment by detecting drought-responsive compounds, such as flavonoids, phenolics, and antioxidant activities, while also supporting the classification of stress severity. This spectral profiling revealed key biochemical alterations triggered by water deficit. MSFI liquid crystal tunable filter (LCTF-based) measured chlorophyll a (Chl-a), chlorophyll b (Chl-b), and total chlorophyll (t-Chl) levels, providing critical insights into photosynthetic performance under drought stress. Thermal imaging further enhanced drought assessment by capturing canopy temperature variations, which were used to derive thermal indices for indirect estimation of soil volumetric water content (SVWC). By integrating complementary imaging modalities, the proposed system captured comprehensive phenotypic responses with high predictive accuracy for early detection of drought stress and assessment of plant health. Advanced machine learning (ML) and deep learning (DL) models further enhanced trait extraction and classification, enabling robust analysis of complex, high-dimensional data. This automated, multimodal platform offers scalable, non-invasive crop monitoring, providing precise insights to support drought resilience and precision agriculture.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10.1002/pmic.202400261</t>
+          <t>https://doi.org/10.1016/j.sna.2023.114605</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Prediction of Plant Resistance Proteins Using Alignment-Based and Alignment-Free Approaches</t>
+          <t>Advancements in smart farming: A comprehensive review of IoT, wireless communication, sensors, and hardware for agricultural automation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>P.S., Gahlot, Pushpendra Singh; S., Choudhury, Shubham; N., Bajiya, Nisha; N., Kumar, Nishant; G.P.S., Raghava, Gajendra Pal Singh</t>
+          <t>Chander Prakash; Lakhwinder Pal Singh; Ajay Gupta; Shiv Kumar Lohan</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Proteomics</t>
+          <t>Sensors and Actuators A: Physical</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7002357244491577</v>
+        <v>0.8879760503768921</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Plant disease resistance (PDR) proteins are critical in identifying plant pathogens. Predicting PDR protein is essential for understanding plant–pathogen interactions and developing strategies for crop protection. This study proposes a hybrid model for predicting and designing PDR proteins against plant-invading pathogens. Initially, we tried alignment-based approaches, such as Basic Local Alignment Search Tool (BLAST) for similarity search and MERCI for motif search. These alignment-based approaches exhibit very poor coverage or sensitivity. To overcome these limitations, we developed alignment-free or machine learning (ML)-based methods using compositional features of proteins. Our ML-based model, developed using compositional features of proteins, achieved a maximum performance area under the receiver operating characteristic curve (AUROC) of 0.91. The performance of our model improved significantly from AUROC of 0.91–0.95 when we used evolutionary information instead of protein sequence. Finally, we developed a hybrid or ensemble model that combined our best ML model with BLAST and obtained the highest AUROC of 0.98 on the validation dataset. We trained and tested our models on a training dataset and evaluated them on a validation dataset. None of the proteins in our validation dataset are more than 40% similar to proteins in the training dataset. One of the objectives of this study is to facilitate the scientific community working in plant biology. Thus, we developed an online platform for predicting and designing plant resistance proteins, “PlantDRPpred” (https://webs.iiitd.edu.in/raghava/plantdrppred). © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Agriculture automation is a primary issue and a rapidly developing field for the nation. The global population is growing swiftly, so there is a severe need to fulfill food demand. Traditional farming methods are insufficient to meet the rising demand, so they pressure using fertilizers to increase crop productivity. That fall impacts agricultural activity; sometimes, land stays barren and lacks fertility. This paper is focused on the deep analysis of smart farming-related components such as the Internet of Things (IoT), wireless communication technology, sensors, and hardware. There is serious concern about selecting technology, sensors, and hardware in the different agriculture practices. This may result in an increase in mechanization among various agricultural practices in an easy way. This paper provides a systematic extensive review of the implication of automation in agriculture. And addressed how agricultural operations may benefit from modern sensors, wireless communication technologies, and hardware. Although, major challenges and components have been discussed. Moreover, future applications for crop health, human health, and machine health are also addressed in this study.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10.1371/journal.pcbi.1012503</t>
+          <t>https://doi.org/10.1016/j.envexpbot.2022.104912</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Computational studies reveal structural characterization and novel families of Puccinia striiformis f. sp. tritici effectors</t>
+          <t>The future of plant volatile organic compounds (pVOCs) research: Advances and applications for sustainable agriculture</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>R., Asghar, Raheel; N., Wu, Nan; N., Ali, Noman; Y., Wang, Yulei; M.S., Akkaya, Mahinur Sezener</t>
+          <t>Ramasamy Kanagaraj Murali-Baskaran; Palanisamy Mooventhan; Debanjan Das; Anil Dixit; Kailash Chander Sharma; Sengottayan Senthil-Nathan; Pankaj Kaushal; Probir Kumar Ghosh</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PLOS Computational Biology</t>
+          <t>Environmental and Experimental Botany</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9947812557220459</v>
+        <v>0.6158086657524109</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 2: approach, data, grape</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Understanding the biological functions of Puccinia striiformis f. sp. tritici (Pst) effectors is fundamental for uncovering the mechanisms of pathogenicity and variability, thereby paving the way for developing durable and effective control strategies for stripe rust. However, due to the lack of an efficient genetic transformation system in Pst, progress in effector function studies has been slow. Here, we modeled the structures of 15,201 effectors from twelve Pst races or isolates, a Puccinia striiformis isolate, and one Puccinia striiformis f. sp. hordei isolate using AlphaFold2. Of these, 8,102 folds were successfully predicted, and we performed sequence- and structure-based annotations of these effectors. These effectors were classified into 410 structure clusters and 1,005 sequence clusters. Sequence lengths varied widely, with a concentration between 101-250 amino acids, and motif analysis revealed that 47% and 5.81% of the predicted effectors contain known effector motifs [Y/F/W]xC and RxLR, respectively highlighting the structural conservation across a substantial portion of the effectors. Subcellular localization predictions indicated a predominant cytoplasmic localization, with notable chloroplast and nuclear presence. Structure-guided analysis significantly enhances effector prediction efficiency as demonstrated by the 75% among 8,102 have structural annotation. The clustering and annotation prediction both based on the sequence and structure homologies allowed us to determine the adopted folding or fold families of the effectors. A common feature observed was the formation of structural homologies from different sequences. In our study, one of the comparative structural analyses revealed a new structure family with a core structure of four helices, including Pst27791, PstGSRE4, and PstSIE1, which target key wheat immune pathway proteins, impacting the host immune functions. Further comparative structural analysis showed similarities between Pst effectors and effectors from other pathogens, such as AvrSr35, AvrSr50, Zt-KP4-1, and MoHrip2, highlighting a possibility of convergent evolutionary strategies, yet to be supported by further data encompassing on some evolutionarily distant species. Currently, our initial analysis is the most one on Pst effectors’ sequence, structural and annotation relationships providing a novel foundation to advance our future understanding of Pst pathogenicity and evolution. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Volatile organic compounds emitted by plants (pVOCs) protect themselves from abiotic and biotic stresses. Plants are under constant threats from biotic stress especially herbivores which facilitate plants to emit herbivore-induced plant volatiles (HIPVs), an inducible defense in plants against herbivores by communicating to herbivores’ natural enemies and neighboring plants. HIPVs are reported to act as feeding and/or oviposition deterrents to herbivores, belonging to four major groups including terpene/terpenoids, benzenoids and phenylpropanoids, the volatile fatty acid derivatives, and the volatile aminoacid derivatives. However, the plant volatile profiles induced by herbivores have been reported to be altered by silicon (Si)-fertilization, priming of plants with chemical elicitors and climate change which can induce plants to produce and emit novel plant volatiles that are not expressed by plants in response to damage by herbivory. Transgenic crops and/or sentinel crops with enhanced pVOCs emission profiles have been proposed to improve plant resistance, health and yields. Currently several technological advances in devices including field-portable electronic devices (e-Nose) and hand-held smartphone-based biosensors for in situ early detection of pVOCs profiles which are now available and supported by artificial intelligence (AI), to increase detection accuracy of these systems. The present review highlights the multi-dimension approaches emerging in pVOCs research for early and rapid detection of specific VOCs indicators as markers with associated plant biotic stressors.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10.1002/ps.8456</t>
+          <t>10.1016/j.postharvbio.2024.113281</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cassava disease detection using a lightweight modified soft attention network</t>
+          <t>YOLOv8-MDN-Tiny: A lightweight model for multi-scale disease detection of postharvest golden passion fruit</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A., Dosset, Arailym; D.M., Minh, Dang Minh; F.G., Alharbi, Faisal Ghazi; S., Habib, Shabana; N.A., Alam, Nur A.; H.Y., Park, Hanyong Young; H., Moon, Hyeonjoon</t>
+          <t>Chen, D.; Lin, F.; Lu, C.; Zhuang, J.; Su, H.; Zhang, D.; He, J.</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1152,163 +1152,172 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pest Management Science</t>
+          <t>Postharvest Biology and Technology</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3722582757472992</v>
+        <v>0.891001284122467</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>BACKGROUND: Cassava is a high-carbohydrate crop that is at risk of viral infections. The production rate and quality of cassava crops are affected by several diseases. However, the manual identification of diseases is challenging and requires considerable time because of the lack of field professionals and the limited availability of clear and distinct information. Consequently, the agricultural management system is seeking an efficient and lightweight method that can be deployable to edged devices for detecting diseases at an early stage. To address these issues and accurately categorize different diseases, a very effective and lightweight framework called CDDNet has been introduced. We used MobileNetV3Small framework as a backbone feature for extracting optimized, discriminating, and distinct features. These features are empirically validated at the early intermediate stage. Additionally, we modified the soft attention module to effectively prioritize the diseased regions and enhance significant cassava plant disease-related features for efficient cassava disease detection. RESULTS: Our proposed method achieved accuracies of 98.95%, 97.03%, and 98.25% on Cassava Image Dataset, Cassava Plant Disease Merged (2019–2020) Dataset, and the newly created Cassava Plant Composite Dataset, respectively. Furthermore, the proposed technique outperforms previous state-of-the-art methods in terms of accuracy, parameter count, and frames per second values, ultimately making the proposed CDDNet the best one for real-time processing. CONCLUSION: Our findings underscore the importance of a lightweight and efficient technique for cassava disease detection and classification in a real-time environment. Furthermore, we highlight the impact of modified soft attention on model performance. © 2024 The Author(s). Pest Management Science published by John Wiley &amp; Sons Ltd on behalf of Society of Chemical Industry. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Passion fruit, a commercially significant fruit crop, is easily infected by anthracnose and scab, which declines it economic value. However, at the present time, passion fruit quality grading is mainly judged by manual assessment, with strong subjectivity, poor efficiency and low accuracy. Intelligent classification of postharvest passion fruit is essential, with skin disease being a critical factor in grading fruit quality. In view of the shortcomings in traditional deep learning model, such as weak multi-scale detection ability and low accuracy, we propose a YOLOv8-MDN-Tiny model to improve the ability of passion fruit small-scale disease detection. The backbone layer is replaced by the self-made MFSO structure to expand the feature pixels of small target information and enrich their feature expression. An improved DyRep module is proposed to realize the interactive fusion of disease features at different scales and depths. NWD loss function is introduced to accurately measure the overlap of two bounding boxes. Finally, Slimming pruning and CWD are used to compress the model. Compared with YOLOv8s, our improved lightweight model achieves more accurate localization of small passion fruit targets. Specifically, the mAP&lt;inf&gt;50&lt;/inf&gt; is increased by 2.2–94.8 %, the precision and recall are improved by 1.5 % and 6.0 %. Meanwhile, the number of model parameters and memory usage are decreased by 90.1 % and 88.9 %. The results technically support the disease detection in postharvest passion fruit and real-time grading of their quality. © 2024 Elsevier B.V.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10.1007/978-981-96-1907-8_14</t>
+          <t>https://doi.org/10.1016/j.agsy.2023.103607</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A Prompt and Contrastive Learning-Based Model for Plant Antimicrobial Peptide Prediction</t>
+          <t>Autonomous field management – An enabler of sustainable future in agriculture</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Z., Qin, Zhaojing; J., Meng, Jun; H., Li, Haibin; Y., Tang, Youwei; Y., Luan, Yushi</t>
+          <t>David Gackstetter; Malte {von Bloh}; Veronika Hannus; Sebastian T. Meyer; Wolfgang Weisser; Claudia Luksch; Senthold Asseng</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Communications in Computer and Information Science</t>
+          <t>Agricultural Systems</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5466776490211487</v>
+        <v>0.5322385430335999</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Plant antimicrobial peptides (AMPs) are small peptides with low toxicity, essential roles in plant growth, and the ability to combat drug resistance. They show significant promise in agriculture and medicine. However, current AMP prediction methods often face shortcomings such as low efficiency, strong data dependence, and high computational costs. To address these issues, we propose PCLPAMP, a model incorporating prompt tuning and contrastive learning for plant AMP prediction. Continuous prompts guide the protein language model (LM) ProtT5 in extracting task-specific feature embeddings, while contrastive learning optimizes feature distribution to improve discrimination. PCLPAMP achieves an accuracy of 94.15%, outperforming the state-of-the-art (SOTA) model LMPred-T5XL UNI by 2.63%. Additionally, it outperforms the low-rank adaptation (LoRA) fine-tuning approach in both accuracy and computational efficiency. The complete code and datasets can be accessed at: https://github.com/Oliver4587/PCLPAMP. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>CONTEXT
+Technological innovations in agriculture are mainly driven by the maxim: increase productivity at any costs. Today, in the face of climate change and an unprecedented loss of biodiversity, this approach is reaching its limits. Meeting global nutrition needs while achieving sustainability is one of the greatest challenges for modern agriculture.
+OBJECTIVE
+Autonomous field management represents the next evolutionary step in agricultural technology. It is characterized by an end-to-end automation of agricultural production processes and by that – for the first time in history - independence from labor constraints. Although literature has provided solutions for individual components of these new technological systems, integrating those components into a common, fully autonomous process has not yet been achieved.
+METHODS
+We analyzed the technological, agronomic, environmental, and related, interdisciplinary literature in the context of automated, and digital field crop management.
+RESULTS AND CONCLUSION
+The review shows the disruptive potential of fully autonomous, labor-independent crop management systems to guarantee the required food security by simultaneously allowing sustainable factors to be equally incorporated into the agricultural decision-making process. The integration of multifaceted objectives into a common decision-making process poses a great challenge to human farmers and their capacities. Liberated from labor constraints, autonomous systems have the potential to align decisions with the complex requirements of multiple − even contradicting – goals more easily, and to execute them accordingly without exhaustion. We show barriers that explain, why fully autonomous crop management is not yet present in today's agricultural practice, despite the fact that the majority of technological sub-components has reached a maturity stage beyond the proof of concept. Substantial technological progress will still be required with respect to the robustness in varying application settings and the standardization of interfaces to integrate diverse subsystems. For the adoption of autonomous cropping systems, societal engagement will be required including extensive research and discussion on public acceptance, legal frameworks, and the human farmers' future role as crucial success factors.
+SIGNIFICANCE
+Aligning autonomous cropping systems to domain-overarching objectives can make these technological solutions not only another, next stage of more efficiently producing technologies, but a game changer for new, environmentally sustainable cropping systems. Field management practice can leave the currently persisting, oversimplified management strategies, characterized by large-scale, and standardized field arrangements, toward more complex approaches with small-scale, diversely structured fields, which consider local particularities and the heterogeneity of the natural landscape.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10.1016/bs.mim.2024.12.007</t>
+          <t>https://doi.org/10.1016/j.scienta.2024.113688</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Artificial intelligence in plant disease mitigation and nutrient acquisition</t>
+          <t>Navigating the landscape of precision horticulture: Sustainable agriculture in the digital Age</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>K., Nthebere, Knight; M.B.N., Yadav, Manikyala Bhargava Narasimha; G.R.V., Gowda, G. R.Vishwas; N.V., Kumar, Nallagatla Vinod; N.C., Joshi, Naveen Chandra; J.P., Tyagi, Jaagriti P.</t>
+          <t>Sanjeev Kumar; Ab Waheed Wani; Rupesh Kaushik; Harjinder Kaur; Djajadi Djajadi; Aniswatul Khamidah;  Saidah; Nada Alasbali; Maha Awjan Alreshidi; Mir Waqas Alam; Krishna Kumar Yadav; Atif Khurshid Wani</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Methods in Microbiology</t>
+          <t>Scientia Horticulturae</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9246030449867249</v>
+        <v>0.9284380674362183</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Agriculture plays a predominant role in boosting the economy of a country. However, plant infectious diseases pay significant challenges in declining both the quality and yield. Another key factor limiting crop growth worldwide is a lack of essential nutrients. Deficiencies in macronutrients (P, N, Ca, Mg and K) and micronutrients (Cu, Zn, and Mo) have a major impact on plant growth and development, ultimately leading to plant death. However, with artificial intelligence (AI), it is now possible to detect not only symptoms, but also identify the specific pathogens, understand plant–pathogen interactions, and even analyse nutrient deficiencies in both soil and plants. Thus, AI is necessitated to address these issues, which allows for real-time, accurate analysis of plant health using robots and probes, making it faster and more precise than traditional methods of plant tissue and soil testing. Advanced AI techniques—such as Naive Bayes, Random Forest, K-Nearest Neighbours (KNN), and Support Vector Machines (SVM)—are now being applied to detect infectious diseases and nutrient levels. This chapter explores the current role of AI in diagnosing plant infectious diseases and identifying nutrient needs that offering guidance for effective management practices. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Automation, autonomy, and precision play vital roles in modern technology and procedures, especially in response to the rising global population and the need for improved fruit production technologies. The quality criteria for fruit yield are becoming increasingly complex, necessitating fundamental upgrades. Sensor-based technologies pave the way for more rational and efficient soil usage. Precision farming, an advanced agricultural approach, employs software technologies and principles to optimize various aspects of horticultural production. Its goal is to enhance crop yields and promote environmental sustainability by managing spatial and temporal variations. Precision horticulture, a cutting-edge farming method, focuses on increasing crop yields and quality while minimizing environmental impact. This approach leverages advanced technology and data-driven decision-making. By utilizing sensors, robots, drones, and other innovative tools for yield mapping, irrigation control, robotic harvesting, nutrient and pesticide application, soil sensing, and crop growth analysis, growers can monitor plant growth and health, identify potential issues, and make informed crop management decisions. Tailoring practices to specific plant needs can lead to higher yields, improved product quality, and reduced environmental impact. Overall, precision horticulture holds significant promise for promoting sustainable agricultural practices while meeting the increasing demand for food production.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10.1111/tpj.17190</t>
+          <t>https://doi.org/10.1016/j.scienta.2021.110024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Identification, characterization, and design of plant genome sequences using deep learning</t>
+          <t>Remotely sensed real-time quantification of biophysical and biochemical traits of Citrus (Citrus sinensis L.) fruit orchards – A review</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Z., Wang, Zhenye; H., Yuan, Hao; J., Yan, Jianbing; J., Liu, Jianxiao</t>
+          <t>Ansar Ali; Muhammad Imran</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Plant Journal</t>
+          <t>Scientia Horticulturae</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8908332586288452</v>
+        <v>0.4593730568885803</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Due to its excellent performance in processing large amounts of data and capturing complex non-linear relationships, deep learning has been widely applied in many fields of plant biology. Here we first review the application of deep learning in analyzing genome sequences to predict gene expression, chromatin interactions, and epigenetic features (open chromatin, transcription factor binding sites, and methylation sites) in plants. Then, current motif mining and functional component design and synthesis based on generative adversarial networks, large models, and attention mechanisms are elaborated in detail. The progress of protein structure and function prediction, genomic prediction, and large model applications based on deep learning is also discussed. Finally, this work provides prospects for the future development of deep learning in plants with regard to multiple omics data, algorithm optimization, large language models, sequence design, and intelligent breeding. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Remote sensing provides accurate and cost-effective solution to quantify the biophysical and biochemical traits of citrus fruit orchards. Timely information on these traits can be used to design real-time computerized applications for site-specific orchard management, yield estimation, and scheduling precise and proper application of inputs thus growing net returns and optimizing resource utilization. Retrieval of these traits has been playing an important role during the last 30 years with steady improvement in remote sensing platforms and sensors and the techniques and methods forthwith. However, with dense canopy, variable illumination conditions and saturation effects caused by seasonal dynamics of leaf and canopy pigments combined with high year-round leaf density pose challenges for the accurate and precise inference of biophysical and biochemical traits in citrus fruit orchards. Concerning these challenges in the pursuit of earth observation, the present paper aims to provide a comprehensive and in-depth review of the remotely sensed technologies and applications for real-time and state-of-the-science retrieval of biophysical and biochemical traits of citrus fruit orchards. Establishing a database of citrus traits at leaf, canopy and orchard level is very important for future smart agriculture to help farmers for site-specific orchard management, plan farm management practices, selection of best cultivars, scheduling precise and proper application of inputs in citrus production paradigm; thus growing net returns and optimize resource utilization. Technical methods for different levels of remote sensing acquisition have also been elaborated highlighting the current situation of citrus traits acquired by remote sensing.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10.1155/js/5592225</t>
+          <t>https://doi.org/10.1016/j.phymed.2025.157303</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Real-Time Automatic Detection of Nutrient Deficiency in Lettuce Plants With New YOLOV12 model</t>
+          <t>SMART-HERBALOMICS: An innovative multi-omics approach to studying medicinal plants grown in controlled systems such as phytotrons</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ç., Bakir, Çiǧdem; A., Gezer, Ayberk</t>
+          <t>Kenneth Happy; Yeongjun Ban; Joyce Mudondo; Ariranur Haniffadli; Roggers Gang; Kyeong-OK Choi; Endang Rahmat; Denis Okello; Richard Komakech; Youngmin Kang</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1316,40 +1325,47 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Journal of Sensors</t>
+          <t>Phytomedicine</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9936512112617493</v>
+        <v>0.445985347032547</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tópico 4: yolov, increase, map</t>
+          <t>Tópico 2: approach, data, grape</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Healthy lettuce receives all the necessary nutrients, such as calcium, magnesium, nitrogen, phosphorus, and potassium for optimum growth. Deficiency of one of these vitamins causes growth retardation in plants. Vitamin deficiencies in lettuce grown in hydroponic systems can negatively affect plant development and create various problems. Therefore, it is critical to provide all the vitamin and mineral balances that plants need in hydroponic systems. In this study, the development of lettuce, which has an important place in daily life, was examined in detail. Deep learning techniques were applied to images of lettuce plants using various You Only Look Once (YOLO) models (YOLOV12 and YOLOV11). Various metrics were calculated for each YOLO version to evaluate performance. These metrics include precision, recall, mean average precision (mAP)50 (average accuracy), and mAP50–95 (average accuracy at different intersection over union [IoU]), thresholds). A balance was created between the classes on the lettuce images obtained using data augmentation techniques, which allowed the model to be trained more robustly. In the tests conducted with the augmented dataset, the mAP50 value of the YOLOV12 model was calculated as 0.984 and the mAP50–95 value as 0.957. This reveals the high performance of the model in correctly recognizing nutritional deficiencies. On the other hand, the YOLOV11 model achieved lower results, such as 0.975 mAP50 and 0.944 mAP50–95 in all classes. This study significantly improved the object detection performance by integrating novel attention modules into YOLOV11 and YOLOV12 models to detect nutrient deficiencies of lettuce plants early and accurately in soilless agriculture. Not only the comparison of models, but also the generalization and robustness of the model were strengthened with innovative modules that provide dynamic adaptation to environmental variables. This novel approach provides tangible contributions to both academic literature and practical applications in AI-supported early detection and yield optimization in sustainable hydroponic agriculture. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Background
+Traditional medicine has supported human health for centuries. However, its dependence on wild-sourced medicinal plants now poses serious threats to biodiversity, with over 90 % of these species harvested directly from their natural habitat. Overexploitation and increasing global demand have accelerated the depletion of medicinal plant genetic resources, raising concerns about extinction and long-term sustainability.
+Purpose
+This review introduces “Smart-Herbalomics (SH),” a novel interdisciplinary approach that merges traditional herbal knowledge with modern scientific methods. This review aims to ensure a sustainable use and conservation of medicinal plants while enhancing their therapeutic efficacy and safety. SH integrates advanced plant identification, propagation in controlled environments (e.g., phytotron and smart farms), and standardization protocols to maintain genetic integrity and bioactive compound consistency. Additionally, this novel approach incorporates cell-based assays for cytotoxicity and mechanistic evaluation, animal models for preclinical safety and efficacy assessment, and clinical trials for human validation. Additionally, multi-omics tools, including genomics, transcriptomics, metabolomics, and proteomics, help uncover the molecular basis of herbal actions.
+Method
+Data were collected through a comprehensive literature review using electronic databases such as PubMed, Google Scholar, Scopus, AMED, and the Cochrane Library. Key search terms included “Herbalomics,” “Pharmacology,” “Pharmacognosy,” “Multi-Omics,” “Botany,” “Safety and Toxicity,” “Herb Formulation,” and “Medicinal Plant Species.”
+Conclusion
+This article introduces SH for the first time as an integrative approach that offers a comprehensive and sustainable pathway to develop standardized, safe, and evidence-based herbal therapies. It bridges the fields of ethnopharmacology and pharmaceutical innovation, supporting the future of personalized, eco-conscious healthcare.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10.1109/ICIRCA65293.2025.11089838</t>
+          <t>10.3390/agronomy15071516</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A Novel Attention Mechanism for Disease Detection in Potatoes</t>
+          <t>Application of Hyperspectral Imaging for Early Detection of Pathogen-Induced Stress in Cabbage as Case Study</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>A.S.J., Sharmila, A. Supriya J.; K.S., Tamilselvan, Kumaravel Subramaniam; R., Monisha, R.; E.L., Dhivya Priya, E. L.; N., Gomathi, N.; V.R., Vinothini, V. R.</t>
+          <t>Szechynska-Hebda, M.; Hoĺownicki, R.; Doruchowski, G.; Sas, K.; Puławska, J.; Jarecka Boncela, A.; Ptaszek, M.; Włodarek, A.</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1357,122 +1373,122 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2022 4th International Conference on Inventive Research in Computing Applications (ICIRCA)</t>
+          <t>Agronomy</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5301912426948547</v>
+        <v>0.6909149289131165</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tópico 6: soybean, vegetable, learningbased</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>The potato plant is amongst the most significant vegetable crops farmed worldwide. It is rich in vitamin B12, considered to be the best ever compensation of vitamin B12 for vegetarians as it is abundantly present in non-veg foods. Potato is the most preferred vegetable to consume from kids to adults. The potato crop is prone to numerous infections like bacterial, fungal, and viral infections in its growing stages. The production is immensely affected by the diseases that occur in its sprout development stage. Diseases that occur in crops hinder the economy of agriculture as they lead to huge demands. The predominant devastating diseases influencing the growth and production of potatoes are late and early blight diseases. Detecting the diseases, especially the diseases that occurred in its initial stages, assists in preventing the loss in production and to improve the yield. A decrease in production results in increasing cost and demand. The proposed work incorporating the modified AttDenseNet architecture with the layers of Convolutional neural network layers proceeded by self-attention and co-attention mechanisms assist in predicting the disease in its earlier stages, proffers accuracy of 98.7 percent in detecting the diseases in potatoes in a maximum number of epochs. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Cabbage (Brassica oleracea L.) is a globally significant vegetable crop that faces productivity challenges due to fungal and bacterial pathogens. This review highlights the potential of spectral imaging techniques, specifically multispectral and hyperspectral methods, in detecting biotic stress in cabbage, with a particular emphasis on pathogen-induced responses. These non-invasive approaches enable real-time assessment of plant physiological and biochemical changes, providing detailed spectral data to identify pathogens before visible symptoms appear. Hyperspectral imaging, with its high spectral resolution, allows for distinctions among different pathogens and the evaluation of stress responses, whereas multispectral imaging offers broad-scale monitoring suitable for field-level applications. The work synthesizes research in the existing literature while presenting novel experimental findings that validate and extend current knowledge. Significant spectral changes are reported in cabbage leaves infected by Alternaria brassicae and Botrytis cinerea. Early-stage detection was facilitated by alterations in flavonoids (400–450 nm), chlorophyll (430–450, 680–700 nm), carotenoids (470–520 nm), xanthophyll (520–600 nm), anthocyanin (550–560 nm, 700–710 nm, 780–790 nm), phenols/mycotoxins (700–750 nm, 718–722), water/pigments content (800–900 nm), and polyphenols/lignin (900–1000). The findings underscore the importance of targeting specific spectral ranges for early pathogen detection. By integrating these techniques with machine learning, this research demonstrates their applicability in advancing precision agriculture, improving disease management, and promoting sustainable production systems. © 2025 by the authors.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10.1109/ACCESS.2025.3599359</t>
+          <t>10.1007/s11042-023-14372-7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A Dynamic Attention-guided Deep Learning Framework (D-PAN) with reduced complexity for fine grained Severity-Aware Classification of Micronutrient Deficiency and Disease detection in Banana and Coffee Leaves</t>
+          <t>An aggregated loss function based lightweight few shot model for plant leaf disease classification</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>M., Sudhakar, M.; S.P., Ramu, Swarna Priya</t>
+          <t>Garg, S.; Singh, P.</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IEEE Access</t>
+          <t>Multimedia Tools and Applications</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5336745977401733</v>
+        <v>0.3372700214385986</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Nutrition is a key factor in enabling crops to reach their optimal growth level. Farmers and agronomists often mistake nutrient deficiencies for diseases, leading to incorrect crop treatments. This study proposes a deep learning model for classifying micronutrient deficiencies (m-ND), evaluating their severity, and distinguishing them from diseases in banana and coffee crops. To address common classification challenges, the model is initially trained and validated on images of both nutritional deficiencies and visually similar disease symptoms. To assess its robustness, we also evaluated it on a coffee crop dataset from Mendeley. The proposed method, D-PAN - a modified Pyramid Attention Network (PAN) uses a dynamic attention mechanism to process multi-scale input images. Model performance was compared with various vision transformer (ViT) based channel attention methods and a weighted ensemble of Transformer models combined with a modified convolution neural network (CNN). The model achieved top accuracies of 98.80% for banana and 94.60% for coffee, with reduced misclassification errors. Experimental results show that the framework maintains low complexity, improves accuracy by an average of 2.9%, and reduces parameters by 1.64 to 3.83 times compared to other attention methods. Overall, the proposed model surpasses all evaluated state-of-the-art attention mechanisms, achieving strong performance across recall, accuracy, precision, and F1-score. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>In India, a significant portion of the annual crop is lost due to plant diseases. It is required to monitor agriculture’s growth and health status of plants to help farmers take prompt actions regarding any plant disease. An automatic plant disease classification algorithm is necessary to identify and prevent plant diseases at an early stage. This paper aims to classify plant diseases using a lightweight transfer learning model using only a few samples. Few-shot classification aims to identify unseen classes while training with small labeled data. The proposed work uses an aggregated loss function formed by the combination of triplet loss and cross-entropy loss with MobileNetV2 as a base model for the effective classification of plant disease using small samples. Two publicly available datasets (PlantVillage having 54,303 leaf samples and Plantdoc having 2598 Leaf samples) were considered for the evaluation of the proposed work. Different domain splits were considered to divide the dataset into the source, and target domains, and a large quantum of experimentation is conducted on the target dataset considering various sample sizes. For the analysis of plantvillage dataset, four domain splits were considered, and it is found that an average improvement in accuracy, when compared with recent work, is 1.49% for split-1, 16.25% for split-2, 2.9% for split-3, and 2.1%for split-4 using the proposed aggregated loss and the lightweight transfer learning model for the target domain data (K-ways, N-shot). Two domain splits were considered for the plantdoc dataset, and it gives an accuracy of around 81% using 30 samples and more than 40% using only 1 sample. The proposed work is compared with several state-of-the-art works using different evaluation metrics like, loss functions, execution time, model size, and model parameters. © 2023, The Author(s), under exclusive licence to Springer Science+Business Media, LLC, part of Springer Nature.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10.1109/ICICI65870.2025.11069612</t>
+          <t>10.2147/JMDH.S445549</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A Review on Deep Learning and Transfer Learning Models: Grape Leaf Disease Detection</t>
+          <t>Electrocardiogram Features in Non-Cardiac Diseases: From Mechanisms to Practical Aspects</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>P.G., Dhavane, P. G.; T.G., Mangave, Tejaswi G.; T.S., Deshmukh, Tejaswini S.; P.P., Kajale, Pooja P.</t>
+          <t>Ceasovschih, A.; Şorodoc, V.; Covantsev, S.; Balta, A.; Uzokov, J.; Kaiser, S.E.; Almaghraby, A.; Lionte, C.; Statescu, C.; Sascau, R.A.; Onofrei, V.; Haliga, R.E.; Stoica, A.; Bologa, C.; Ailoaei, Ș.; Sener, Y.Z.; Kounis, N.G.; Sorodoc, L.</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Journal of Multidisciplinary Healthcare</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5776461362838745</v>
+        <v>0.9699491262435913</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 8: horticultural, review, platform</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Grapes are the most significant fruit crops which contain several vitamins and minerals such as vitamins K, and B, as well as copper. Grape plants can be greatly affected by different diseases including grape esca, isariopsis leaf spot, black rot, powdery mildew or downy mildew, and so on. These diseases impact the entire grape's quality and yield. Early detection of grape leaf disease is essential to reduce economic costs and disease progression. However, various existing approaches pose certain challenges including computational cost, real-time detection, illumination, and occlusion as well as misclassification. This survey analyzes recent works using the machine learning, deep learning, and transfer learning techniques for grape leaf disease diagnosis in the form of dataset availability, disease severity estimation, and computational resources. Among other techniques, deep learning shows superior performance results and a better capability to extract features. Additionally, this research analyzes various performance metrics and the limitations of existing approaches. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Despite the noteworthy advancements and the introduction of new technologies in diagnostic tools for cardiovascular disorders, the electrocardiogram (ECG) remains a reliable, easily accessible, and affordable tool to use. In addition to its crucial role in cardiac emergencies, ECG can be considered a very useful ancillary tool for the diagnosis of many non-cardiac diseases as well. In this narrative review, we aimed to explore the potential contributions of ECG for the diagnosis of non-cardiac diseases such as stroke, migraine, pancreatitis, Kounis syndrome, hypothermia, esophageal disorders, pulmonary embolism, pulmonary diseases, electrolyte disturbances, anemia, coronavirus disease 2019, different intoxications and pregnancy. © 2024 Ceasovschih et al.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10.1109/ICPCSN65854.2025.11035612</t>
+          <t>10.1016/j.sciaf.2025.e03061</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Optimized CNN for Enhanced Cassava Leaf Disease Classification and Yield Improvement</t>
+          <t>Mango fruit disease detection and classification using MobileNetV3_large model</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>A., Yogitha, Akkineni; B.S.H.S., Singh, Bondili Sri Harsha Sai; N.P., Mikkili, Nissi Paul</t>
+          <t>Yehulu, G.T.; Walle, Y.M.; Haile, M.B.; Yohannes, S.T.; Tegegne, A.G.; Tesfaye, D.G.; Baye, G.A.</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1480,122 +1496,122 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Scientific African</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4962655901908875</v>
+        <v>0.8248141407966614</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa depends on cassava as its essential staple crop and carbohydrate foundation for its thousands of citizens. The cultivation of cassava faces severe risks because bacterial and viral infections cause yield decreases of as much as 70% within one season, which threatens the food security of smallholder farmers extensively. The research develops a modern deep learning-based diagnostic platform to demonstrate accurate disease classification of cassava leaf samples. ResNet50 and MobileNetV2 networks backed by boosting methods, including AdaBoost and Gradient Boosting, serve to improve classification outcomes from the proposed approach. A transfer learning approach and attention mechanisms enhance feature extraction within the system, which processes the 21,367 labeled images containing cassava leaf samples both in their healthy and diseased states using real-world image noise reduction methods. The proposed model produces classification outcomes with more than 99% precision for various disease categories, which surpasses conventional manual inspections and spreadsheet-based approaches. The conducted research established a mobile diagnosis tool that enables quick disease detection for cassava, thus empowering farmers to apply timely actions to promote sustainable agricultural growth and increase food security. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Mangoes are appreciated globally for their flavor, nutritional value, and economic significance, which are one of the most significant tropical fruit crops. Various fruit diseases also negatively impact mango production, decreasing yield and quality. This shows the critical necessity for precise and timely disease identification. This study targets the issue of a lack of effective automated diagnosis tools and a lack of research on diseases affecting the mango fruit rather than the leaves. To effectively identify and categorize the main diseases of mango fruit, such as Alternaria, Anthracnose, Black Mold Rot, and Stem-End Rot, a deep learning model had to be developed. A publicly available Kaggle dataset was used and augmented to 8297 samples to enhance generalization. The preprocessing phase involved background removal, image resizing, noise reduction, and z-score normalization to improve image quality and maintain consistency. Features were obtained using a customized MobileNetV3-Large architecture that significantly reduced the number of trainable parameters from 5507,432 to 566,325 and the model size from 21.8 MB to 6.29 MB, making it highly suitable for deployment on mobile and resource-constrained devices. Featured extracts were classified using the XGBoost algorithm, developing a hybrid MobileNetV3-Large–XGBoost model. Experiment results showed 98.95 % test accuracy, reflecting excellent reliability and precision in disease detection. Findings show that the proposed model not only enhances automatic fruit disease detection but also provides a viable solution for real-time disease monitoring and control. The deployment's potential helps farmers and agricultural experts with the capability to detect early infection, reduce crop loss, improve disease management approaches, and enhance sustainable mango growth. © 2025 The Authors</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10.1016/j.csbj.2025.06.048</t>
+          <t>10.1016/j.eij.2025.100877</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Learning the language of plant immunity: opportunities and challenges for AI-assisted modelling of fungal effector x host protein complexes</t>
+          <t>Channel-attentive YOLOv5 and capsule auto-encoder for pomegranate disease detection</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>C.J., Verdonk, Callum J.; K.K., Gagalova, Kristina Kirilova; S., Raffaele, Sylvain; M.C., Derbyshire, Mark C.</t>
+          <t>Sajitha, P.; A.; Anand, N.; Lublóy, E.</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Computational and Structural Biotechnology Journal</t>
+          <t>Egyptian Informatics Journal</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7229164242744446</v>
+        <v>0.296334832906723</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Phytopathogenic fungi cause substantial crop losses worldwide. They secrete proteins called effectors, which enable infection through interactions with diverse host proteins. These interactions are fundamentally important to plant disease and its practical control. New artificial intelligence (AI) techniques can predict many individual protein structures to near experimental accuracy. Although these techniques also predict protein complexes, they are not as accurate as single-protein models. Use of AI to study interactions between fungal pathogen effectors and plant proteins is currently limited. However, despite some challenges, early adoption of AI has highlighted its potential. General improvements in AI-assisted protein complex modelling may create more opportunities in future. This review focuses on recent research using AI to study the interactions between fungal effectors and plant proteins, outlining challenges and emerging opportunities. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Fruits are the most vital items of global diets because of their rich nutritional value, thereby providing very high demand and agricultural revenues to the economy. Among the fruit crops, pomegranate is a valuable one due to its highest antioxidant potential. However, most crops of pomegranate suffer from diseases, which greatly reduce agricultural yield and productivity. Thus, along with the increasing demand of the fruit, early detection as well as classification of diseases will prove very crucial in boosting the yield and taking appropriate measures for prevention. We propose a segmentation-based model using deep learning in this paper to conduct disease identification in pomegranates The process begins with pre-processing images that is primarily an activity of cropping and resizing of the images, followed by enhanced Wiener filtering, which eliminates noise and enhances the clarity of the images The preprocessed images are then further segmented using a CA_YV5GC algorithm, (Channel Attentive YOLOv5-based Grab Cut), which isolates diseased regions from the images. Then the optimized ResNet-152 network is applied to acquire the fundamental features embedding the texture along with the shape characteristics which could identify ailments related symptoms. Coati Optimization is applied to choose the most dominant features in the lower dimensional representation of the extracted information for the classification of the disease. Ultimately, classification is performed using a Deep Capsule Canonical Auto-encoder (DC_CAENet) to classify the disease type with higher accuracy. Adaptive Osprey Optimization is used to optimize the parameters of the model. The existing methods are compared with that results proved this technique to be more accurate and efficient as compared to traditional techniques. © 2025</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10.1016/j.csbj.2025.06.029</t>
+          <t>https://doi.org/10.1016/j.atech.2024.100481</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Predicting receptor-ligand pairing preferences in plant-microbe interfaces via molecular dynamics and machine learning</t>
+          <t>Early detection of Botrytis cinerea symptoms using deep learning multi-spectral image segmentation</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>É.T., Prates, Érica Teixeira; O.N.A., Demerdash, Omar N.A.; M.B., Shah, Manesh B.; T.A., Rush, Tomas Allen; U.C., Kalluri, Udaya C.; D.A., Jacobson, Dan A.</t>
+          <t>Nikolaos Giakoumoglou; Eleni Kalogeropoulou; Christos Klaridopoulos; Eleftheria Maria Pechlivani; Panagiotis Christakakis; Emilia Markellou; Nikolaos Frangakis; Dimitrios Tzovaras</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Computational and Structural Biotechnology Journal</t>
+          <t>Smart Agricultural Technology</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9932265877723694</v>
+        <v>0.3780460059642792</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Microbiome assembly, structure, and dynamics significantly influence plant health. Secreted microbial signaling molecules initiate and mediate symbiosis by binding to structurally compatible plant receptors. For example, lipo-chitooligosaccharides (LCOs), produced by nitrogen-fixing rhizobial bacteria and various fungi, are recognized by plant lysin motif receptor-like kinases (LysM-RLKs), which activate the common symbiotic pathway. Accurately predicting these molecular interactions could reveal complementary signatures underlying the initial stages of endosymbiosis. Despite the breakthrough in protein-ligand structure prediction with deep learning-based tools, such as AlphaFold3, the large size and highly flexible nature of signaling compounds like LCOs present major challenges for detailed structural characterization and binding-affinity prediction. Typical structure-/physics-based methods of ligand virtual screening are designed for small, drug-like molecules, often rely on high-resolution, experimentally determined structures of the protein receptors, and rarely achieve sufficient sampling to obtain converged thermodynamic quantities with large ligands. In this study, we developed a hybrid molecular dynamics/machine learning (MD/ML) approach capable of predicting binding affinity rankings with high accuracy in systems involving large, flexible ligands, despite limited experimental structural information. Using coarse initial structural models, the predictions using the MD/ML workflow achieved strong alignment with experimental trends, particularly in the top-affinity tier for four legume LysM-RLKs (LYR3) binding to LCOs and a chitooligosaccharide. Furthermore, the MD-based conformation selection protocol provided critical structural insights into substrate specificity and binding mechanisms. This study demonstrates a powerful method to screen for challenging cognate ligand-receptors and advance our understanding of the molecular basis of microbial colonization in plants. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Botrytis cinerea is an airborne plant pathogen that causes grey mould disease on horticultural crops, such as tomato, cucumber, pepper, and more. Early detection is crucial for timely and effective strategies for crop loss prevention. In this study, in planta assays were set up enabling a thorough assessment of grey mould progress on cucumber plants both artificially inoculated with two different inoculation methods, and naturally infected throughout the whole growing season of the host under controlled conditions simulating the environment typically prevailing in greenhouses. Multi-spectral imaging was used to capture a novel dataset across various spectral bands containing multiple stages of infection. Deep learning (DL) segmentation architectures, combined with Convolutional Neural Networks (CNNs) and Vision Transformers (ViTs) encoders, were employed to identify B. cinerea at various infection stages. The U-Net++ model with a MobileViT-S encoder performed best, achieving a Dice Coefficient (DC) of 0.677, an Intersection over Union (IoU) of 0.656, and a recall rate of 0.807, with a high overall accuracy of 90.1 %. In regards to early detection, the model achieves an IoU of 0.375 on 2nd day post inoculation (dpi), 0.230 on 1st dpi and 0.437 on the 6th dpi. The infection stages were compared to similar visible symptoms of physiological decline or plant responses to abiotic stress. The outcomes of this study demonstrate an important advance in the Artificial Intelligence (AI) plant health detection, for early crop disease diagnosis.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10.1007/978-981-96-2120-0_10</t>
+          <t>10.1016/j.atech.2025.101534</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Supplements and Herbal Remedies: An Exploration of Nutritional Supplements and Herbal Remedies for PCOS and AI’s Role in Personalized Recommendations</t>
+          <t>Advances in hyperspectral imaging-based non-destructive assessment of tomato quality attributes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>A., Gupta, Anshika; K., Katiyar, Kalpana</t>
+          <t>Zhang, J.; Zhang, Q.; Tan, Y.; Wang, M.; Zhang, X.; Li, H.; Zhao, R.; Yu, J.</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1603,40 +1619,40 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Smart Agricultural Technology</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7066919207572937</v>
+        <v>0.3284787535667419</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 6: gardening, management, specie</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Polycystic ovary syndrome (PCOS) is a multifaceted endocrine condition identified by cycles of menstruation that are irregular, polycystic ovaries and hormonal abnormalities, with symptoms including hirsutism, acne, and reproductive difficulties. Treatment usually includes lifestyle changes such as exercise, dietary changes, and vitamin supplementation, which is especially important for overweight people or those with metabolic issues. Natural supplements such as inositol, curcumin, vitamin D, N-acetylcysteine, D-chiro-inositol, omega-3 fatty acids, folate, and tocopherol have emerged as intriguing components in PCOS treatment, with possible therapeutic effects. Despite the success of traditional medications, many PCOS patients prefer alternative therapies owing to their perceived efficacy and fewer side effects. Phytochemicals derived from plants such as aloe vera, chamomile, cinnamon, ginseng, fennel, and licorice have received attention for their involvement in PCOS therapy and are frequently seen as a cost-effective and well-tolerated option. Furthermore, AI and machine learning (ML) techniques have demonstrated significant potential for improving PCOS diagnosis and classification accuracy. AI/ML models can help with early detection and personalized treatment methods by following standardized diagnostic criteria. AI-driven research must adhere to reporting criteria and maintain scientific rigor to achieve clinical relevance and diagnostic precision. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Tomato (Solanum lycopersicum L.), the world's second most economically significant horticultural crop, faces persistent quality assessment limitations due to conventional destructive methods and subjective inspections. Consequently, rapid non-destructive techniques for evaluating key quality attributes are essential to enhance postharvest management and market competitiveness. Hyperspectral imaging (HSI) addresses this need by acquiring spatially resolved spectral data across the biochemically critical 400–2500 nm range, capturing signatures of key attributes like lycopene and soluble solids. This technology demonstrates considerable potential for non-destructive agricultural assessment, enabling: high-accuracy maturity grading via pigment dynamics; ultra-early detection of asymptomatic diseases (e.g., latent fungal infections); quantitative nutritional component prediction; and reliable internal defect identification. These capabilities collectively enhance postharvest quality control. This review systematically evaluates advanced data preprocessing methods, feature extraction techniques, and deep learning models for their contributions to enhanced detection accuracy and system robustness. Nevertheless, challenges persist regarding hardware miniaturization, environmental resilience, model generalizability across diverse cultivars and growth environments, and real-time in-field implementation. Future efforts should prioritize developing integrated field-portable HSI platforms, multi-sensor fusion strategies, environmentally adaptive algorithms, and efficient AI architectures to bridge the gap between laboratory research and scalable industrial applications. Such advancements will critically underpin next-generation precision agriculture systems for robust tomato quality assurance and significant loss reduction. © 2025 The Authors. Published by Elsevier B.V. This is an open access article under the CC BY-NC license. http://creativecommons.org/licenses/by-nc/4.0/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10.1109/JIOT.2025.3578203</t>
+          <t>https://doi.org/10.1016/j.hpj.2023.09.005</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tech-Enhanced Forest Nursery Management: Harnessing Embedded Systems for Plant Health Monitoring and Growth Forecasting</t>
+          <t>Genomics, phenomics, and machine learning in transforming plant research: Advancements and challenges</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>M.R., Jena, Manas Ranjan; S., Misra, Sarita; B.P., Mishra, Bishnu Prasad; C., Sekhar Mishra, Chandra</t>
+          <t>Sheikh Mansoor; Ekanayaka M.B.M. Karunathilake; Thai Thanh Tuan; Yong Suk Chung</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1644,81 +1660,81 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IEEE Internet of Things Journal</t>
+          <t>Horticultural Plant Journal</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>0.992110550403595</v>
+        <v>0.5261374711990356</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>This study explores IoT-based forest nursery monitoring using Sony Picam 2 and Raspberry Pi B2 (8 GB RAM). The primary objective revolves around the measurement and continuous monitoring of plant leaf color, a crucial indicator of plant health and nutrient status. To accomplish this, a Python program has been developed to systematically monitor and analyze variations in plant leaf color within the same species, and even within individual plants. Additionally, the study extends its focus to nutrient deficiencies, encompassing essential elements like N, P, K, and 13 micronutrients, shedding light on the critical aspect of plant nutrition in nursery settings. To further enrich our comprehension of forest sapling growth, a growth model incorporating deep learning techniques has been meticulously designed. The development and refinement of this model were greatly facilitated by Google CoLab. The next phase of the research will involve thorough field testing of the developed model at a nursery in Bhubaneswar. This testing will include a variety of plant species. The primary objectives are to evaluate its accuracy and effectiveness in real-world scenarios and to explore its scalability for application in larger fields. This interdisciplinary study seamlessly bridges the realms of technology, biology, and agriculture, culminating in the creation of a robust system for efficient forest nursery management and early detection of plant health issues. By doing so, this research contributes significantly to the sustainable growth and conservation of forest ecosystems, ensuring their long-term vitality and resilience. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Advances in gene editing and natural genetic variability present significant opportunities to generate novel alleles and select natural sources of genetic variation for horticulture crop improvement. The genetic improvement of crops to enhance their resilience to abiotic stresses and new pests due to climate change is essential for future food security. The field of genomics has made significant strides over the past few decades, enabling us to sequence and analyze entire genomes. However, understanding the complex relationship between genes and their expression in phenotypes - the observable characteristics of an organism - requires a deeper understanding of phenomics. Phenomics seeks to link genetic information with biological processes and environmental factors to better understand complex traits and diseases. Recent breakthroughs in this field include the development of advanced imaging technologies, artificial intelligence algorithms, and large-scale data analysis techniques. These tools have enabled us to explore the relationships between genotype, phenotype, and environment in unprecedented detail. This review explores the importance of understanding the complex relationship between genes and their expression in phenotypes. Integration of genomics with efficient high throughput plant phenotyping as well as the potential of machine learning approaches for genomic and phenomics trait discovery.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10.1109/ICDT63985.2025.10986310</t>
+          <t>10.1016/j.atech.2024.100476</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AgriSynth: Machine Learning - Driven Crop Intelligence, Fertilizer Rationalization and Disease Diagnostics</t>
+          <t>Classification of mango disease using ensemble convolutional neural network</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B., Gupta, Bhoomika; S., Agarwal, Shivani; A., Srivastava, Aditya; Aaradhya; A., Agrahari, Anant</t>
+          <t>Bezabih, Y.A.; Ayalew, A.M.; Abuhayi, B.M.; Nigussie, T.N.; Awoke, E.A.; Mengistu, T.E.</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Smart Agricultural Technology</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9949524998664856</v>
+        <v>0.797835111618042</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Agriculture is important to feeding the world's growing population, especially in the face of climate change. Machine learning technology has the potential to greatly improve agriculture by helping farmers make more educated decisions. However, current systems have considerable limitations. Many fertilizer recommendations only address the key nutrients NPK: nitrogen, phosphorus, and potassium, fail to account for water availability, and rely on out-of-date historical data. This study would close these gaps by producing a machine learning system that can help farmers with crop recommendations, fertiliser guidance, and plant disease detection. The algorithm considers micronutrients and organic matter in addition to NPK when recommending fertiliser. It also incorporates water availability and real-time meteorological data to provide more precise crop suggestions, especially important for drought-prone areas. Deep learning methods analyze plant photos to detect diseases early on. Our findings indicate that by incorporating micro nutrients, water data, and real-time climate updates, the system can deliver more precise crop and fertilizer recommendations. The Random Forest and XGBoost models outperform, and the disease detection component helps to prevent crop losses by intervening early. The key takeaway from this study is that merging machine learning with large amounts of data can significantly improve farming techniques, raise crop yields, and provide farmers with reliable insights, thereby enhancing food security and sustainable agriculture. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Mango is a highly significant fruit crop that thrives in a variety of agro-ecologies around the world. Mangoes are rich in vitamins and minerals. However, its yield is currently severely constrained due to disease and pest infestations. Thus, in order to improve mango fruit quality and productivity, illnesses and insect pests must be detected early on. In this study, we conceived and constructed a mango leaf disease detection mechanism utilizing an ensemble convolutional neural network approach. Healthy and diseased mango leaf images were manually obtained from main producing locations in Amhara Region for Merawi fruit and vegetable research identification. To improve the datasets, several pre-processing procedures (such as image resizing, noise reduction, and image augmentation) were used. To improve classification performance and meet the study's purpose, various segmentation approaches such as k means and Mask R-CNN were applied. Furthermore, following pre-processing and segmentation, features of mango leaf images were retrieved using CNN to obtain important features. The classification model was then constructed using fully-connected layer classifiers on the retrieved features of mango leaf images. The ensemble proposed GoogLeNet and VGG16 based CNN model in the study encompasses various operations, including dataset collection, image preprocessing, noise removal, segmentation, data augmentation, feature extraction, and classification. Upon testing, the model demonstrated impressive performance with 99.87 % training classification accuracy, 99.72 % validation accuracy, and 99.21 % testing accuracy. This indicates the effectiveness of the ensemble approach in achieving high accuracy in image classification tasks. © 2024 The Authors</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10.1109/COMP-SIF65618.2025.10969966</t>
+          <t>https://doi.org/10.1016/j.stress.2025.100953</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Disease Detection in Finger Millet Plant Using Fine-Tuned Transfer Learning Models</t>
+          <t>Securing fruit trees future: AI-driven early warning and predictive systems for abiotic stress in changing climate</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B.R., Prajwal, B. R.; S., Mondal, Subhash; M., Raghu, M.; N., Shashank, N.</t>
+          <t>Muhammad Ahtasham Mushtaq; Muhammad Ateeq; Muhammad Ikram; Shariq Mahmood Alam; Muhammad Mohsin Kaleem; Muhammad Atiq Ashraf; Muhammad Asim; Khalid F. Almutairi; Mahmoud F. Seleiman; Fareeha Shireen</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1726,40 +1742,40 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Plant Stress</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>0.511612594127655</v>
+        <v>0.4463078379631042</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 6: gardening, management, specie</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Plant diseases are becoming one of the major threats to global food security, particularly in carbohydrate rich staple crops like finger millet (Eleusine coracana) which requires minimal water and can be grown in diverse climate conditions, highlighting the need for early disease detection to minimize yield losses and promote sustainable agriculture. We employed web scraping for data collection from different open source, data augmentation techniques like flip, rotation, zoom to enhance the model's performance and enhance generalization capabilities. This research focuses on developing an effective disease detection system for finger millet using Convolutional Neural Networks (CNNs) and transfer learning methodologies. We analyzed with pretrained CNN architectures, such as DenseNet121, VGG16, and VGG19, using a dataset of more than thousands of labelled images collected from diverse agricultural settings. Fine tuning these models ensures optimising model's performance and achieving better accuracy. Among the tested models, DenseNet121 achieved the highest accuracy, reaching 96.88%. Additionally, we developed a user-friendly real-time application to disease detection using Streamlit library helping the farmers to detect the disease in mobile for remote access. This study demonstrates the significant use of deep learning techniques like CNN architectures, particularly transfer learning, for developing better crop disease detection systems. By detecting the disease early and prevention at earlier stage will save tonnes of crops. This solves the major issues like food security and also malnutrition. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Horticultural fruit crops are important product for global food security as they provide important macro and micronutrients. Emerging abiotic stresses—drought, salinity, temperature extremes, and waterlogging—threaten crop productivity by disrupting key physiological processes, challenging sustainable agriculture under climate change. Traditionally, these challenges are tackled through physiological strategies and conventional breeding methods; which lacks scalability, adaptability, and real-time feedback. Advancement in technology, distinctly artificial intelligence (AI), and machine learning have revolutionized precision farming in agriculture. AI integrated approaches such as stress prediction, irrigation optimization, and image-based phenotyping have enhanced agriculture, while machine learning models like Random Forest and Gradient Boosting improve stress management. However, the acquiring of such AI based system in horticultural crops still faces numerous challenges. Specifically, multi-omics, data accessibility, algorithmic biases, the cost of implementation and requirements for robust training programs need to integrate for sustainable agriculture. Addressing these barriers is essential to enable the effective integration of AI technologies for resilient, carbon-neutral fruit production under climate stress. This review highlights recent developments in AI-driven stress detection, predictive modeling, remote sensing, and machine learning frameworks that support precision horticulture and climate-smart agriculture.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10.7717/PEERJ-CS.2733</t>
+          <t>10.1016/j.cpb.2025.100546</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Protein language model-based prediction for plant miRNA encoded peptides</t>
+          <t>Genetic algorithm enhanced deep learning with data augmentation for nitrogen and potassium deficiency detection in eggplant</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Y., Yue, Yishan; H., Fan, Henghui; J., Zhao, Jianping; J., Xia, Junfeng</t>
+          <t>Joshi, K.; Hooda, S.; Yadav, Y.; Singh, G.; Nehra, A.; Tuteja, N.; Gill, R.; Gill, S.S.</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1767,573 +1783,573 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PeerJ Computer Science</t>
+          <t>Current Plant Biology</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7227580547332764</v>
+        <v>0.7712940573692322</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 2: approach, data, grape</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Plant miRNA encoded peptides (miPEPs), which are short peptides derived from small open reading frames within primary miRNAs, play a crucial role in regulating diverse plant traits. Plant miPEPs identification is challenging due to limitations in the available number of known miPEPs for training. Existing prediction methods rely on manually encoded features, including miPEPPred-FRL, to infer plant miPEPs. Recent advances in deep learning modeling of protein sequences provide an opportunity to improve the representation of key features, leveraging large datasets of protein sequences. In this study, we propose an accurate prediction model, called pLM4PEP, which integrates ESM2 peptide embedding with machine learning methods. Our model not only demonstrates precise identification capabilities for plant miPEPs, but also achieves remarkable results across diverse datasets that include other bioactive peptides. The source codes, datasets of pLM4PEP are available at https://github.com/xialab-ahu/pLM4PEP. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>The quality of horticultural crops is significantly crucial for agricultural yield because of market demand, quality, and the priority of consumers. Macronutrients like nitrogen (N) and potassium (K) are crucial for the normal growth and development of crops. Thus, detecting nutritional deficiency in eggplant is very important for ensuring optimal growth and yield. The traditional approaches are time-consuming and require expert knowledge. The previously reported research in eggplant with a deep learning (DL) approach targeted disease detection and classification work. No work has been reported on eggplant nutritional deficiency detection using the genetic algorithm (GA) based tuning approach with data augmentation. This paper presents a YOLOv9 deep-learning model, optimized with a GA to find the best hyperparameters and data augmentation techniques to increase its robustness. The study used the OLID I dataset to detect nutritional deficiencies in eggplant leaves. The experimental results show that our approach achieved an accuracy of 94.52 %, mAP50 of 94.55 %, mAP50–95 of 93.23 %, Precision of 95.9 %, Recall of 92.8 %, and F1 Score of 94.32 %. These results suggest that the proposed approach is a significant step towards developing a practical application to support farmers in detecting nutrition deficiencies in the eggplant crop. © 2025 The Authors</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-80943-9_49</t>
+          <t>10.3390/agriengineering1030032</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A Hybrid Deep Learning and Natural Language Processing Model for Plant Ubiquitination Sites Prediction</t>
+          <t>Comparison of Image Texture Based Supervised Learning Classifiers for Strawberry Powdery Mildew Detection</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>T.X., Tran, Thi Xuan; T.T., Nguyen, Thi Tuyen; N.Q.K., Le, Nguyen Quoc Khanh; V.N., Nguyen, Van Nui</t>
+          <t>Chang, Y.K.; Mahmud, M.S.; Shin, J.; Nguyen-Quang, T.; Price, G.W.; Prithiviraj, B.</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lecture Notes in Networks and Systems</t>
+          <t>AgriEngineering</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5282415747642517</v>
+        <v>0.3314909338951111</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tópico 6: soybean, vegetable, learningbased</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Protein ubiquitination is a critical post-translational modification involved in numerous biological processes, playing a vital role in regulating both physiological and pathological mechanisms. Despite existing tools for predicting ubiquitination sites, variations in ubiquitination patterns among species remain inadequately understood. This study presents LBiPlantUbi, a novel hybrid deep learning model that incorporates Long Short-Term Memory (LSTM) and Bidirectional LSTM (Bi-LSTM) networks combined with natural language processing (NLP) techniques for predicting ubiquitination sites in plants. Our model uniquely learns features directly from raw protein sequences using word embedding and integrates feature extraction and prediction within a single architecture. LBiPlantUbi achieved superior performance with an accuracy of 84%, sensitivity of 88.9%, F1-score of 0.844, MCC of 0.675, and AUC of 0.902 on independent testing sets, outperforming existing methods. This advanced model opens new avenues for studying ubiquitination in plants and other species. The implementation is publicly accessible on GitHub at https://github.com/nuinvtnu/LBiPlantUbi. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Strawberry is an important fruit crop in Canada but powdery mildew (PM) results in about 30–70% yield loss. Detection of PM through an image texture-based system is beneficial, as it identifies the symptoms at an earlier stage and reduces labour intensive manual monitoring of crop fields. This paper presents an image texture-based disease detection algorithm using supervised classifiers. Three sites were selected to collect the leaf image data in Great Village, Nova Scotia, Canada. Images were taken under an artificial cloud condition with a Digital Single Lens Reflex (DSLR) camera as red-green-blue (RGB) raw data throughout 2017–2018 summer. Three supervised classifiers, including artificial neural networks (ANN), support vector machine (SVM), and k-nearest neighbors (kNN) were evaluated for disease detection. A total of 40 textural features were extracted using a colour co-occurrence matrix (CCM). The collected feature data were normalized, then used for training and internal, external and cross-validations of developed classifiers. Results of this study revealed that the highest overall classification accuracy was 93.81% using the ANN classifier and lowest overall accuracy was 78.80% using the kNN classifier. Results identified the ANN classifier disease detection having a lower Root Mean Square Error (RMSE) = 0.004 and Mean Absolute Error (MAE) = 0.003 values with 99.99% of accuracy during internal validation and 87.41%, 88.95% and 95.04% of accuracies during external validations with three different fields. Overall results demonstrated that an image texture-based ANN classifier was able to classify PM disease more accurately at early stages of disease development. © 2019 by the authors. Licensee MDPI, Basel, Switzerland.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10.1016/j.sab.2024.107072</t>
+          <t>10.3390/app122412557</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Characterization of the distribution of mineral elements in chromium-stressed rice (Oryza sativa L.) leaves based on laser-induced breakdown spectroscopy and data augmentation</t>
+          <t>Horticulture 4.0: Adoption of Industry 4.0 Technologies in Horticulture for Meeting Sustainable Farming</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>J., Peng, Jiyu; L., Ye, Longfei; Y., Liu, Yifan; F., Zhou, Fei; L., Xu, Linjie; F., Zhu, Fengle; J., Huang, Jing; F., Liu, Fei</t>
+          <t>Singh, R.; Singh, R.; Gehlot, A.; Akram, S.V.; Priyadarshi, N.; Twala, B.</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Spectrochimica Acta - Part B Atomic Spectroscopy</t>
+          <t>Applied Sciences (Switzerland)</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>0.790249764919281</v>
+        <v>0.4779257774353027</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tópico 6: soybean, vegetable, learningbased</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>The fast and precise visualization of mineral elements in contaminated plants is crucial for understanding nutrient dynamics, plant health, and environmental monitoring. In this study, a Wasserstein generative adversarial network (WGAN) is proposed to expand the data scale and combines laser-induced breakdown spectroscopy (LIBS) with three machine learning methods for mineral elements analysis in Cr-stressed rice (Oryza sativa L.) leaves. In the quantitative analysis of mineral elements, the proposed method improved the prediction performance for Cu, K, Mg, Mn, and Na, except for Ca and Fe, demonstrating the effectiveness of data augmentation in enhancing the quantitative models. Mapping the distribution of Ca, Fe, Mg, K, Mn, and Na in rice leaves shows higher concentrations towards the apical regions and approximately symmetrical distribution along the leaf vein. Additionally, Fe, K, and Mn concentrations are significantly lower in Cr-polluted leaves compared to uncontaminated leaves. These preliminary findings offer insights into the macro distribution of mineral elements in plants. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>The United Nations emphasized a significant agenda on reducing hunger and protein malnutrition as well as micronutrient (vitamins and minerals) malnutrition, which is estimated to affect the health of up to two billion people. The UN also recognized this need through Sustainable Development Goals (SDG 2 and SDG 12) to end hunger and foster sustainable agriculture by enhancing the production and consumption of fruits and vegetables. Previous studies only stressed the various issues in horticulture with regard to industries, but they did not emphasize the centrality of Industry 4.0 technologies for confronting the diverse issues in horticulture, from production to marketing in the context of sustainability. The current study addresses the significance and application of Industry 4.0 technologies such as the Internet of Things, cloud computing, artificial intelligence, blockchain, and big data for horticulture in enhancing traditional practices for disease detection, irrigation management, fertilizer management, maturity identification, marketing, and supply chain, soil fertility, and weather patterns at pre-harvest, harvest, and post-harvest. On the basis of analysis, the article identifies challenges and suggests a few vital recommendations for future work. In horticulture settings, robotics, drones with vision technology and AI for the detection of pests, weeds, plant diseases, and malnutrition, and edge-computing portable devices that can be developed with IoT and AI for predicting and estimating crop diseases are vital recommendations suggested in the study. © 2022 by the authors.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10.1038/s41598-024-75455-5</t>
+          <t>https://doi.org/10.1016/j.micpath.2025.107866</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Employing machine learning techniques for prediction of micronutrient supplementation status during pregnancy in East African Countries</t>
+          <t>Recent insights into potato dry rot an emerging Disease: Focusing on pathogen diversity, host-pathogen interactions, and management strategies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>H.S., Ngusie, Habtamu Setegn; E.B., Enyew, Ermias Bekele; A.D., Walle, Agmasie Damtew; B., Tilahun Assaye, Bayou; M.D., Kasaye, Mulugeta Desalegn; G.A., Tesfa, Getanew Aschalew; A.B., Zemariam, Alemu Birara</t>
+          <t xml:space="preserve"> Pooja; Prashant Chauhan; Ankit Kumar; Lellapalli Rithesh; Abhishek Kumar</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
+          <t>Microbial Pathogenesis</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6101933717727661</v>
+        <v>0.5760778784751892</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 2: approach, data, grape</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Micronutrient deficiencies, known as “hidden hunger” or “hidden malnutrition,” pose a significant health risk to pregnant women, particularly in low-income countries like the East Africa region. This study employed eight advanced machine learning algorithms to predict the status of micronutrient supplementation among pregnant women in 12 East African countries, using recent demographic health survey (DHS) data. The analysis involved 138,426 study samples, and algorithm performance was evaluated using accuracy, area under the ROC curve (AUC), specificity, precision, recall, and F1-score. Among the algorithms tested, the random forest classifier emerged as the top performer in predicting micronutrient supplementation status, exhibiting excellent evaluation scores (AUC = 0.892 and accuracy = 94.0%). By analyzing mean SHAP values and performing association rule mining, we gained valuable insights into the importance of different variables and their combined impact, revealing hidden patterns within the data. Key predictors of micronutrient supplementation were the mother’s education level, employment status, number of antenatal care (ANC) visits, access to media, number of children, and religion. By harnessing the power of machine learning algorithms, policymakers and healthcare providers can develop targeted strategies to improve the uptake of micronutrient supplementation. Key intervention components involve enhancing education, strengthening ANC services, and implementing comprehensive media campaigns that emphasize the importance of micronutrient supplementation. It is also crucial to consider cultural and religious sensitivities when designing interventions to ensure their effectiveness and acceptance within the specific population. Furthermore, researchers are encouraged to explore and experiment with various techniques to optimize algorithm performance, leading to the identification of the most effective predictors and enhanced accuracy in predicting micronutrient supplementation status. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Nowadays, global food safety and security are major concerns to mitigate global hunger. As, the world's population rising at an alarming rate and is expected to reach 10 billion by 2050, agriculturists have great responsibilities to grow more food from limited land. Crops are affected by several biotic and abiotic stresses in the field as well as during storage, this situation is drastic in developing countries. Potato belongs to the Solanaceae family, is considered a promising staple vegetable crop. To address the major issue of food safety and security, potatoes can be considered as a crucial non cereal food crop to combat this problem, as they can be grown under field conditions, and soilless medium (hydroponically, and aeroponically). The potato crop is also affected by various biotic stresses in both field and post-harvest conditions, significantly deteriorating its qualitative and quantitative yield. Among the biotic stresses, Fusarium dry rot (FDR) incited by the Fusarium species complex is considered a major problem in the present scenario. Dry rot of potato causes drastic quality and yield loss in cold stores. Moreover, Fusarium spp., producing mycotoxins like trichothecenes that contribute to the disease development. Fusarium spp. utilizes enzymes like pectinases and cellulases to break down plant cell walls, facilitating invasion and colonization. Therefore, implement crop rotation, use disease-resistant potato varieties, practice good sanitation, and employ fungicides to manage potato dry rot disease would be beneficial. Therefore, there is an urgent need to study the fungal species involved, pathogenicity, and to find the best management strategies for sustainable potato production. Although some reports on FDR of potato have been published previously, many recent studies have since offered new insights into diagnostic techniques, mycotoxin detection and quantification, and management strategies. Therefore, this review aims to integrate these recent findings, offering an updated outlook on FDR considering emerging research. Our objective is to provide a timely synthesis of the latest research developments that were not covered in previous reviews, making this article a valuable and necessary contribution to the agricultural field.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10.1016/j.jfca.2024.106824</t>
+          <t>10.1007/s42979-023-02262-6</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Comparative analysis of deep learning and machine learning-based models for simultaneous prediction of minerals in perilla (Perilla frutescens L.) seeds using near-infrared reflectance spectroscopy</t>
+          <t>An Efficient Approach to Detect and Predict the Tomato Leaf Disease Using Enhance Segmentation Neural Network</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>N., Singh, Naseeb; S., Kaur, Simardeep; A., Jain, Antil; A., Kumar, Amit; R., Bhardwaj, Rakesh; R.N., Pandey, Renu Nath; A.S., Riar, Amritbir Singh</t>
+          <t>Bajpai, A.; Tyagi, T.</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Journal of Food Composition and Analysis</t>
+          <t>SN Computer Science</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9941560626029968</v>
+        <v>0.7112112641334534</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Perilla seeds contain a rich array of essential minerals, thus having the potential to address multiple micronutrient deficiencies at a time. However, traditional methods of mineral estimation are complex, time-consuming, expensive, and require technical expertise. This study includes the development of Near-Infrared Reflectance Spectroscopy (NIRS)-based prediction models for predicting five important minerals (Calcium, Copper, Magnesium, Manganese, and Phosphorus) using machine learning and deep learning techniques. Four models, including 1D Convolutional Neural Networks (1D CNNs), Artificial Neural Networks (ANNs), Random Forests (RFs), and Support Vector Regression (SVR), were developed and evaluated. The developed 1D CNN model outperformed other considered models in predicting calcium, magnesium, and phosphorus content with RPD (Residual Prediction Deviation) values of 1.75, 1.83, and 2.96, respectively. Whereas, SVR performed best in predicting copper and manganese with an RPD of 1.82 and 2.2, respectively. The 1D CNN model demonstrated R2 (Coefficient of determination) values above 0.65 for all minerals, with a maximum of 0.88 for phosphorus. In addition, the developed models performed superior as compared to the Partial Least Square Regression method (R2= 0.32). The developed models provide efficient tools for rapidly screening perilla germplasm available in global repositories, thus aiding in the selection of mineral-rich genotypes to mitigate micronutrient deficiencies. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>The agricultural sector plays a crucial role in the Indian economy. According to the Economic Survey of India 2020–21 report, production in FY21 was recorded at 303.34 million tonnes. India is the world’s second-largest producer of tomatoes, both in terms of area and production. In India, tomato is one of the most important and highly consumed vegetable crops. Tomatoes are highly nutritional and thus good for human health. It makes a substantial contribution to the GDP. Being economically valuable, it is produced in large quantities. Because of adverse environmental conditions, several diseases are caused by bacteria, fungi and viruses in various parts of tomato plants. Diseases result in the loss of production and thus farmers have to face huge economic losses. In order to help the farmers, early detection of diseases is needed to be done using the latest and most accurate methods. In this paper, the ES-CNN model(Enhancement Seg- mentation CNN model) is proposed in which mean filtering and CLAHE are performed for the image enhancement step and K-means clustering is used for the image segmentation. ResNet-50, a CNN architecture, has been used for feature extraction and classification of images. © 2023, The Author(s), under exclusive licence to Springer Nature Singapore Pte Ltd.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10.1016/j.atech.2024.100575</t>
+          <t>10.3390/computers14110500</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AI based early identification and severity detection of nutrient deficiencies in coconut trees</t>
+          <t>Deep Learning-Based Citrus Canker and Huanglongbing Disease Detection Using Leaf Images</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>S.K., Manoharan, Sakthiprasad Kuttankulangara; R.K., Megalingam, Rajesh Kannan; G., A, Gopika; G., Jogesh, Govind; A., K, Aryan; A.R., Kunnambath, Akhil Revi</t>
+          <t>Devora-Guadarrama, M.; Luna-Benoso, B.; Alarcón-Paredes, A.; Martínez Perales, J.C.; Morales-Rodríguez, Ú.S.</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Smart Agricultural Technology</t>
+          <t>Computers</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9200223088264465</v>
+        <v>0.3090721964836121</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 2: approach, data, grape</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Coconut trees are vital in various agricultural and economic sectors. Their susceptibility to nutrient deficiencies poses a significant threat to growth and productivity. Traditional nutrient assessment methods are time and labour-intensive, relying on manual inspection and chemical testing. There has been no significant research on detecting nutrient deficiencies in coconut trees. Additionally, assessing deficiency, and severity automatically and recommending suitable fertilizers remain unexplored. This research leverages the YOLOv9 model to identify macro and micronutrient deficiencies in coconut trees and proposes an Image Analysis based Severity Detection (IASD), to determine the severity of these deficiencies. Along with these a Severity Index Calculation Model (SICM) is also introduced that calculates the Severity Index (SI) of these deficiencies. For each identified deficiency, the appropriate fertilizer and its application quantity are suggested. Four deep learning models—RetinaNet, Faster Regional Convolutional Neural Network (Faster R-CNN), You Only Look Once version 5 (YOLOv5), and version 9 (YOLOv9) —were compared for the prediction of nutrient deficiencies in coconut trees using a dataset of 5,720 images of nutrient-deficient coconut tree leaves. YOLOv9 outperformed other models with Accuracy, Precision, and Recall values of 80 %, 98.59 %, and 80.37 %, respectively. Manual verification ensured the correctness of IASD and SICM predictions during model creation, providing farmers and agricultural professionals with a precise, automated tool for managing coconut plantations. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Early detection of plant diseases is key to ensuring food production, reducing economic losses, minimizing the use of agrochemicals, and maintaining the sustainability of the agricultural sector. Citrus plants, an important source of vitamin C, fiber, and antioxidants, are among the world’s most significant fruit crops but face threats such as canker and Huanglongbing (HLB), incurable diseases that require management strategies to mitigate their impact. Manual diagnosis, although common, I s imprecise, slow, and costly; therefore, efficient alternatives are emerging to identify diseases from early stages using Artificial Intelligence techniques. This study evaluated four deep learning models, specifically convolutional neural networks. In this study, we evaluated four convolutional neural network models (DenseNet121, ResNet50, EfficientNetB0, and MobileNetV2) to detect canker and HLB in citrus leaf images. We applied preprocessing and data-augmentation techniques; transfer learning via selective fine-tuning; stratified k-fold cross-validation; regularization methods such as dropout and weight decay; and hyperparameter-optimization techniques. The models were evaluated by the loss value and by metrics derived from the confusion matrix, including accuracy, recall, and F1-score. The best-performing model was EfficientNetB0, which achieved an average accuracy of 99.88% and the lowest loss value of 0.0058 using cross-entropy as the loss function. Since EfficientNetB0 is a lightweight model, the results show that lightweight models can achieve favorable performance compared to robust models, models that can be useful for disease detection in the agricultural sector using portable devices or drones for field monitoring. The high accuracy obtained is mainly because only two diseases were considered; consequently, it is possible that these results do not hold in a database that includes a larger number of diseases. © 2025 by the authors.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10.1038/s41598-024-66281-w</t>
+          <t>10.24425/jppr.2025.153821</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Advancing common bean (Phaseolus vulgaris L.) disease detection with YOLO driven deep learning to enhance agricultural AI</t>
+          <t>Sweet pepper foliar diseases quantification and identification using an image analysis tool</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>D., Gomez, Daniela; M.G., Selvaraj, Michael Gomez; J.A., Casas, Jorge Andres; M., Kavino, M.; M., Rodriguez, Michael; T.M., Assefa, Teshale M.; A., Mlaki, Anna; G., Nyakunga, Goodluck; F., Kato, Fred; C.M., Mukankusi, Clare Mugisha</t>
+          <t>Rajamanickam, V.; Ramsubhag, A.; Jayaraman, J.</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
+          <t>Journal of Plant Protection Research</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4643924236297607</v>
+        <v>0.7164958715438843</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Common beans (CB), a vital source for high protein content, plays a crucial role in ensuring both nutrition and economic stability in diverse communities, particularly in Africa and Latin America. However, CB cultivation poses a significant threat to diseases that can drastically reduce yield and quality. Detecting these diseases solely based on visual symptoms is challenging, due to the variability across different pathogens and similar symptoms caused by distinct pathogens, further complicating the detection process. Traditional methods relying solely on farmers’ ability to detect diseases is inadequate, and while engaging expert pathologists and advanced laboratories is necessary, it can also be resource intensive. To address this challenge, we present a AI-driven system for rapid and cost-effective CB disease detection, leveraging state-of-the-art deep learning and object detection technologies. We utilized an extensive image dataset collected from disease hotspots in Africa and Colombia, focusing on five major diseases: Angular Leaf Spot (ALS), Common Bacterial Blight (CBB), Common Bean Mosaic Virus (CBMV), Bean Rust, and Anthracnose, covering both leaf and pod samples in real-field settings. However, pod images are only available for Angular Leaf Spot disease. The study employed data augmentation techniques and annotation at both whole and micro levels for comprehensive analysis. To train the model, we utilized three advanced YOLO architectures: YOLOv7, YOLOv8, and YOLO-NAS. Particularly for whole leaf annotations, the YOLO-NAS model achieves the highest mAP value of up to 97.9% and a recall of 98.8%, indicating superior detection accuracy. In contrast, for whole pod disease detection, YOLOv7 and YOLOv8 outperformed YOLO-NAS, with mAP values exceeding 95% and 93% recall. However, micro annotation consistently yields lower performance than whole annotation across all disease classes and plant parts, as examined by all YOLO models, highlighting an unexpected discrepancy in detection accuracy. Furthermore, we successfully deployed YOLO-NAS annotation models into an Android app, validating their effectiveness on unseen data from disease hotspots with high classification accuracy (90%). This accomplishment showcases the integration of deep learning into our production pipeline, a process known as DLOps. This innovative approach significantly reduces diagnosis time, enabling farmers to take prompt management interventions. The potential benefits extend beyond rapid diagnosis serving as an early warning system to enhance common bean productivity and quality. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Quantification and assessment of disease symptoms are important elements of plant disease management systems and are required to assist with making decisions on the choice of protective agents to be applied to crops or for screening plant genotypes for the development of resistant varieties. Traditional methods of identifying and quantifying disease severity are cumbersome, involving visual assessment tools or scales, and rating of plants at a point in time. Visual assessment is prone to human bias and error, thereby reducing the efficiency and accuracy of this method. In this study, we developed a smartphone camera-based image recording, processing, and assessment tool for measurement of symptoms of early and late blight, and bacterial leaf spot diseases in sweet pepper caused by Alternaria solani, Phytophthora infestans, and Xanthomonas campestris pv. vesicatoria, respectively. Sweet pepper or bell pepper is a major vegetable crop grown in the Caribbean region, but production is severely affected by plant diseases, most important of which include foliar infections by fungi and bacteria that cause major losses in fruit yield. This research utilized smartphone captured images of leaf specimens for severity measurement and classification of diseases. The steps involved were color space conversions, detection of leaf area by Otsu’s method, and thresholding for foliar diseased area detection and quantification. Gray-Level Co-occurrence Matrix (GLCM) extracted the texture features from the diseased area of leaves. These features are trained and classified by various machine learning classifiers including trees, rule-based and Bayes models. Application of decision trees and rule-based classifier models achieved 98% accuracy individually, while Bayes model achieved 86% accuracy. The image input into the above classifier models resulted in fast and accurate identification of the diseases by matching the features of trained images of disease symptoms. This method could work well for leaves collected from field-grown plants as well as from inoculated greenhouse plants. © 2025 Polska Akademia Nauk. All rights reserved.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10.1371/journal.pcbi.1012575</t>
+          <t>10.15586/qas.v15iSP1.1167</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Reliability of plastid and mitochondrial localisation prediction declines rapidly with the evolutionary distance to the training set increasing</t>
+          <t>Apple diseases: detection and classification using transfer learning</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>S.B., Gould, Sven Bernhard; J., Magiera, Jonas; C., García García, Carolina; P.K., Raval, Parth K.</t>
+          <t>Bhat, M.R.; Assad, A.; Dar, B.N.; Ahanger, A.N.; Kundroo, M.; Dar, R.A.; Ahanger, A.B.; Bhat, Z.A.</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PLOS Computational Biology</t>
+          <t>Quality Assurance and Safety of Crops and Foods</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.8757714629173279</v>
+        <v>0.8524230718612671</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tópico 4: yolov, increase, map</t>
+          <t>Tópico 2: approach, data, grape</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Mitochondria and plastids import thousands of proteins. Their experimental localisation remains a frequent task, but can be resource-intensive and sometimes impossible. Hence, hundreds of studies make use of algorithms that predict a localisation based on a protein’s sequence. Their reliability across evolutionary diverse species is unknown. Here, we evaluate the performance of common algorithms (TargetP, Localizer and WoLFPSORT) for four photosynthetic eukaryotes (Arabidopsis thaliana, Zea mays, Physcomitrium patens, and Chlamydomonas reinhardtii) for which experimental plastid and mitochondrial proteome data is available, and 171 eukaryotes using orthology inferences. The match between predictions and experimental data ranges from 75% to as low as 2%. Results worsen as the evolutionary distance between training and query species increases, especially for plant mitochondria for which performance borders on random sampling. Specificity, sensitivity and precision analyses highlight cross-organelle errors and uncover the evolutionary divergence of organelles as the main driver of current performance issues. The results encourage to train the next generation of neural networks on an evolutionary more diverse set of organelle proteins for optimizing performance and reliability. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Human diagnosis of horticultural diseases comes with added monetary costs in the shape of time, cost, and accessibility, with still considerable possibilities of misdiagnosis. Most common plant diseases present visually recognizable symptoms like change in color, shape, or texture. Deep learning is known to work with such accuracy and precision in recognizing patterns in such visual symptoms that rivals human diagnosis. We specifically designed a deep learning–based multi-class classification model AppleNet to include extra apple plant diseases, which has not been the case with other previously designed models. Our model takes advantage of transfer learning techniques by implementing ResNET 50 Convolutional Neural Network pretrained on image-net dataset. The knowledge of features learned by ResNET 50 is being used to extract features from our dataset. This technique takes advantage of knowledge learned on a larger and more diverse dataset and also saves precious computational resources and time in training on a relatively lesser data. The hyper-parameters were uniquely fine-tuned to maximize the model efficiency. We created our own dataset from the images taken directly from the trees, which, unlike the publicly available datasets created in a controlled setting with smooth (white) background, has been created in a real world environment and includes background noise as well. This helped us train our model in a more realistic way. The results of experimentation on a collected dataset of 2897 images with data augmentation demonstrated that AppleNet can be efficiently used for apple disease detection with a classification accuracy of 96.00%. To examine the effectiveness of our proposed approach, we compared our model with other pretrained models and a baseline model created from scratch. Results of the experiment demonstrate that transfer learning improves the performance of deep learning models and using pretrained models based on residual neural network architectures gives remarkable results as compared to other pretrained models. The mean difference in classification accuracies between our proposed model AppleNet and other experimental models was 21.54%. © 2023 Wageningen Academic Publishers. All rights reserved.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10.1111/tpj.17009</t>
+          <t>10.12694/SCPE.V22I3.1856</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bivariate GWA mapping reveals associations between aliphatic glucosinolates and plant responses to thrips and heat stress</t>
+          <t>BIG DATA ANALYTICS FOR ADVANCED VITICULTURE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B., Arouisse, Bader; M.P.M., Thoen, Manus P.M.; W., Kruijer, Willem; J.F., Kunst, Jonathan F.; M.A., Jongsma, Maarten A.; J.J., Keurentjes, Joost J.B.; R., Kooke, Rik; R.C.H., de Vos, Ric C.H.; R., Mumm, Roland; F.A., van Eeuwijk, Fred Antonis</t>
+          <t>Patel, J.; Patel, R.; Shah, S.; Patel, J.</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Plant Journal</t>
+          <t>Scalable Computing</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9375365972518921</v>
+        <v>0.451501876115799</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Although plants harbor a huge phytochemical diversity, only a fraction of plant metabolites is functionally characterized. In this work, we aimed to identify the genetic basis of metabolite functions during harsh environmental conditions in Arabidopsis thaliana. With machine learning algorithms we predicted stress-specific metabolomes for 23 (a)biotic stress phenotypes of 300 natural Arabidopsis accessions. The prediction models identified several aliphatic glucosinolates (GLSs) and their breakdown products to be implicated in responses to heat stress in siliques and herbivory by Western flower thrips, Frankliniella occidentalis. Bivariate GWA mapping of the metabolome predictions and their respective (a)biotic stress phenotype revealed genetic associations with MAM, AOP, and GS-OH, all three involved in aliphatic GSL biosynthesis. We, therefore, investigated thrips herbivory on AOP, MAM, and GS-OH loss-of-function and/or overexpression lines. Arabidopsis accessions with a combination of MAM2 and AOP3, leading to 3-hydroxypropyl dominance, suffered less from thrips feeding damage. The requirement of MAM2 for this effect could, however, not be confirmed with an introgression line of ecotypes Cvi and Ler, most likely due to other, unknown susceptibility factors in the Ler background. However, AOP2 and GS-OH, adding alkenyl or hydroxy-butenyl groups, respectively, did not have major effects on thrips feeding. Overall, this study illustrates the complex implications of aliphatic GSL diversity in plant responses to heat stress and a cell-content-feeding herbivore. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Big data analytics involve a systematic approach to find hidden patterns to help the organization grow from large volume and variety of data. In recent years big data analytics is widely used in the agricultural domain to improve yield. Viticulture (the cultivation of grapes) is one of the most lucrative farming in India. It is a subdivision of horticulture and is the study of wine growing. The demand for Indian Wine is increasing at about 27% each year since the 21st century and thus more and more ways are being developed to improve the quality and quantity of the wine products. In this paper, we focus on a specific agricultural practice as viticulture. Weather forecasting and disease detection are the two main research areas in precision viticulture. Leaf disease detection as a part of plant pathology is the key research area in this paper. It can be applied on vineyards of India where farmers are bereft of the latest technologies. Proposed system architecture comprises four modules: Data collection, data preprocessing, classification and visualization. Database module involves grape leaf dataset, consists of healthy images combined with disease leaves such as Black measles, Black rot, and Leaf blight. Models have been implemented on Apache Hadoop using map reduce programming framework. It applies feature extraction to extract various features of the live images and classification algorithm with reduced computational complexity. Gray Level Co-occurrence Matrix (GLCM) followed by K-Nearest Neighborhood (KNN) algorithm. The system also recommends the necessary steps and remedies that the viticulturists can take to assure that the grapes can be salvaged at the right time and in the right manner based on classification results. The overall system will help Indian viticulturists to improve the harvesting process. Accuracy of the model is 82%, and it can be increased as a future work by including deep learning with time-series grape leaf images. © 2020. All Rights Reserved.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10.1016/j.dib.2024.110822</t>
+          <t>10.17660/ActaHortic.2020.1296.124</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Unifying antimicrobial peptide datasets for robust deep learning-based classification</t>
+          <t>Current developments in greenhouse robotics and challenges for the future</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>S., Peng, Shuang; L., Rajjou, Loïc</t>
+          <t>Hemming, J.</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Data in Brief</t>
+          <t>Acta Horticulturae</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5971952080726624</v>
+        <v>0.8148910403251648</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 7: system, pesticide, solution</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Leguminous crops are vital to sustainable agriculture due to their ability to fix atmospheric nitrogen, improving soil fertility and reducing the need for synthetic fertilizers. Additionally, they are an excellent source of protein for both human consumption and animal feed. Antimicrobial peptides (AMPs), found in various leguminous seeds, exhibit broad-spectrum antimicrobial activity through diverse mechanisms, including interaction with microbial cell membranes and interference with cellular processes, making them valuable for enhancing crop resilience and food safety. In the field of plant sciences, computational biology methods have been instrumental in the discovery and optimization of AMPs. These methods enable rapid exploration of sequence space and the prediction of AMPs using deep learning technologies. Optimizing AMP annotations through computational design offers a strategic approach to enhance efficacy and minimize potential side effects, providing a viable alternative to conventional antimicrobial agents. However, the presence of overlapping sequences across multiple databases poses a challenge for creating a reliable dataset for AMP prediction. To address this, we conducted a comprehensive analysis of sequence redundancy across various AMP databases. These databases encompass a wide range of AMPs from different sources and with specific functions, including both naturally occurring and artificially synthesized AMPs. Our analysis revealed significant overlap, underscoring the need for a non-redundant AMP sequence database. We present the development of a new database that consolidates unique AMP sequences derived from leguminous seeds, aiming to create a more refined dataset for the binary classification and prediction of plant-derived AMPs. This database will support the advancement of sustainable agricultural practices by enhancing the use of plant-based AMPs in agroecology, contributing to improved crop protection and food security. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Horticultural production faces a growing demand for mechanization, automation and robotics as labour costs are increasing and the availability of skilled labour is decreasing. The modern consumer demands guaranteed and constant quality. Moreover, there are intensified hygiene, food safety and traceability demands. Automated production and quality assessment systems can contribute to fulfil these demands. Many highly automated systems are already applied in commercial high-tech greenhouses. This includes logistics and autonomous transport of plants and harvested product from the greenhouse to the sorting and packing facilities, spraying robots, machine vision based sorting systems for pot-plants and cut-flowers and robotic cutting, planting and grafting machines. Current research focus on automated crop scouting (e.g., insect and disease detection), phenotyping (e.g., monitoring and predicting fruit setting) and postharvest quality assessment. Many research activities are currently carried out on robotic systems that are capable to autonomously harvest crops and to conduct other repetitive and labour intensive operations. In most of these applications the success rate and cycle time are currently still too low to allow implementation in commercial practice. Human-robot collaboration and “human in the loop” applications are important stepping-stones towards full automation. These applications must also include the key issues of user safety and user acceptance. From the plant side, breeding crops with novel phenotypes and plant architectures, such as fruits which are easy to see and reach by robots, will simplify and accelerate the application of robotics in the horticultural field. Challenges involve the complex integration of multiple disciplines and technologies (e.g., navigation, safe operation, grasping, manipulation, perception, learning and adaptation). Current developments are supported by the worldwide rapid improvements in computing and sensor hardware, software and artificial intelligence. © 2020 International Society for Horticultural Science. All rights reserved.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10.1016/j.compag.2024.109351</t>
+          <t>10.1007/978-981-97-8031-0_10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MAIANet: Signal modulation in cassava leaf disease classification</t>
+          <t>Root Vegetable Crop Recommendation System Based on Soil Properties and Environmental Factors</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>J., Zhang, Jiayu; B., Zhang, Baohua; C., Qi, Chao; I., Nyalala, Innocent; P., Mecha, Peter; K., Chen, Kunjie; J., Gao, Junfeng</t>
+          <t>Ajagalla, M.; Pandey, M.; Choudhary, J.; Kumar, L.</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Computers and Electronics in Agriculture</t>
+          <t>Lecture Notes in Electrical Engineering</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5263422727584839</v>
+        <v>0.6517713665962219</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Cassava is the third largest source of carbohydrates for human consumption worldwide; however, it is highly susceptible to viral and bacterial diseases, which pose a significant threat to food security. The advancement of deep learning algorithms in precision agriculture holds the key to enabling the early classification of plant diseases, thereby leading to enhanced crop yields and ultimately stabilizing food security. In the coarse-grained label discrimination task of weak supervision learning, high-quality semantic features contain abundant semantic description information, which plays a crucial role in constructing a precise description of plant disease discrimination in tanglesome field circumstances and directly influences the performance of neural networks. Thus, a multiattention IBN anti-aliasing neural network (MAIANet) was proposed to improve the classification accuracy of cassava leaf disease classification by improving the feature quality in the coarseness label classification task. The proposed MAIANet neural network includes two innovative approaches. First, the multiattention method was designed to scale the feature signals twice to adjust the angular frequency of the feature signals in the residual branch for optimal feature fitting within the residual unit. Second, the anti-aliasing block extracts the high-frequency component feature and optimizes the quantization result of the pooling operation to depress the aliasing signal in the down-sampled feature maps. When the proposed method was tested and validated on the cassava dataset, the results showed that the prediction accuracy of the proposed method significantly improved, with an accuracy of 95.83 %, a loss of 1.720, and an F1-score of 0.9585, outperforming V2-ResNet-101, EfficientNet-B5, RepVGG-B3g4, and AlexNet with significant margins. Based on the above experimental results, the proposed algorithm is suitable for classifying cassava leaf diseases. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Traditional Agriculture has always involved the use of data. However, modern data challenges have become increasingly complex. As a result, data mining processes are now employed to construct machine learning models that analyze and extract valuable insights from this data. In the context of agriculture, data mining plays a crucial role in predicting crop yields, forecasting climate patterns and rainfall, optimizing seed and soil selections, and enhancing overall crop production efficiency. Agriculture serves as a cornerstone of India’s economic framework. Looking ahead to the next generation, the global population is projected to continue its growth. By 2050, the Earth will be home to an additional 9 billion people. Consequently, there is a pressing need to increase food production by 70%, all while utilizing less land. A common issue faced by numerous farmers is the challenge of selecting the appropriate crops based on their soil composition and local environment. This predicament leads to crop diseases, elevated production costs, and significant declines in productivity. Precision agriculture has emerged as a solution to this problem. Precision agriculture, rooted in traditional farming practices, leverages soil analysis, climate conditions, and temperature data to offer refined guidance on crop selection. This approach empowers farmers to enhance their output and productivity. In the context of this paper, we proposed a solution to address this challenge: the implementation of a recommendation system using a Random Forest classifier, which falls under the umbrella of Ensemble techniques. Additionally, the model is further refined by training it using Artificial Neural Network (ANN), employing the K-Fold Cross-validation technique through Keras. This strategy aims to augment the accuracy of model training, resulting in improved recommendations and outcomes. © The Author(s), under exclusive license to Springer Nature Singapore Pte Ltd. 2025.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10.3390/agronomy14091992</t>
+          <t>10.1007/978-981-19-7169-3_8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EFS-Former: An Efficient Network for Fruit Tree Leaf Disease Segmentation and Severity Assessment</t>
+          <t>Deep Learning Based Recognition of Plant Diseases</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>D., Jiang, Donghui; M., Sun, Miao; S., Li, Shulong; Z., Yang, Zhicheng; L., Cao, Liying</t>
+          <t>Parthiban, S.; Moorthy, S.; Sabanayagam, S.; Shanmugasundaram, S.; Naganathan, A.; Annamalai, M.; Sabitha, S.</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Agronomy</t>
+          <t>Lecture Notes in Electrical Engineering</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>0.6387072205543518</v>
+        <v>0.5539559125900269</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Fruit is a major source of vitamins, minerals, and dietary fiber in people’s daily lives. Leaf diseases caused by climate change and other factors have significantly reduced fruit production. Deep learning methods for segmenting leaf diseases can effectively mitigate this issue. However, challenges such as leaf folding, jaggedness, and light shading make edge feature extraction difficult, affecting segmentation accuracy. To address these problems, this paper proposes a method based on EFS-Former. The expanded local detail (ELD) module extends the model’s receptive field by expanding the convolution, better handling fine spots and effectively reducing information loss. H-attention reduces computational redundancy by superimposing multi-layer convolutions, significantly improving feature filtering. The parallel fusion architecture effectively utilizes the different feature extraction intervals of the convolutional neural network (CNN) and Transformer encoders, achieving comprehensive feature extraction and effectively fusing detailed and semantic information in the channel and spatial dimensions within the feature fusion module (FFM). Experiments show that, compared to DeepLabV3+, this method achieves 10.78%, 9.51%, 0.72%, and 8.00% higher scores for mean intersection over union (mIoU), mean pixel accuracy (mPA), accuracy (Acc), and F_score, respectively, while having 1.78 M fewer total parameters and 0.32 G lower floating point operations per second (FLOPS). Additionally, it effectively calculates the ratio of leaf area occupied by spots. This method is also effective in calculating the disease period by analyzing the ratio of leaf area occupied by diseased spots. The method’s overall performance is evaluated using mIoU, mPA, Acc, and F_score metrics, achieving 88.60%, 93.49%, 98.60%, and 95.90%, respectively. In summary, this study offers an efficient and accurate method for fruit tree leaf spot segmentation, providing a solid foundation for the precise analysis of fruit tree leaves and spots, and supporting smart agriculture for precision pesticide spraying. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Every country's primary requirement is agricultural products. Infected plants have an impact on the agricultural production and economic resources of a country. Early detection of plant diseases minimizes the risk of crop loss by allowing farmers to adopt curative and preventative actions to avoid further damage. Citrus is a large plant that is primarily grown in tropical areas of the world because of its high vitamin C and other key nutrient content. Citrus plant diseases play a vital role in causing a great financial loss to the farmers and affect the economy of the country. The tomato ranks among the most economically important vegetable crops, with a global production rate of around 200 million tonnes. But due to diseases occurring in the tomato plants, the farmers are facing a great loss. To prevent these losses and provide an immediate cure, we create a model to detect plant diseases. To get a better performance model, the data augmentation process is used, and we got 18,392 images. In our model, we used a convolutional neural network (CNN) to classify the citrus and tomato leaf diseases. The diseases are Mancha Graxa, Citrus Canker, Tomato Early Blight, Tomato Septoria Leafspot, Tomato Spider Mite Two-spotted spider mite (Tetranychus urticae), Tomato mosaic virus (Tobamovirus), Tomato yellow leaf curl virus (Begomovirus), Tomato Target Spot (Corynespora cassiicola). Convolution Neural Network (CNN) is stacked by multiple convolutions and pooling layers to detect plant leaf diseases. We train a model with augmented images. After the model gets trained, it is thoroughly tested to ensure that the results are accurate. Thereby we were able to achieve high validation accuracy with a rate of (97.02%) for this dataset used. As the results showed, applying the deep CNN model to identify diseases could greatly impact the accurate identification of diseases, and could even prove useful in detecting diseases in real-time agricultural systems. © 2023, The Author(s), under exclusive license to Springer Nature Singapore Pte Ltd.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10.1016/j.jmb.2024.168613</t>
+          <t>https://doi.org/10.1016/B978-0-12-822976-7.00012-0</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fungtion: A Server for Predicting and Visualizing Fungal Effector Proteins</t>
+          <t>Chapter 5 - Remote sensing for agriculture and resource management</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>J., Li, Jiahui; J., Ren, Jinzheng; W., Dai, Wei; C.J., Stubenrauch, Christopher James; R.D., Finn, Robert Daniel; J., Wang, Jiawei</t>
+          <t>Sandeep Kumar; Ram Swaroop Meena; Seema Sheoran; Chetan Kumar Jangir; Manoj Kumar Jhariya; Arnab Banerjee; Abhishek Raj</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Journal of Molecular Biology</t>
+          <t>Elsevier eBooks</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G45" t="n">
-        <v>0.991178035736084</v>
+        <v>0.797533392906189</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Fungal pathogens pose significant threats to plant health by secreting effectors that manipulate plant-host defences. However, identifying effector proteins remains challenging, in part because they lack common sequence motifs. Here, we introduce Fungtion (Fungal effector prediction), a toolkit leveraging a hybrid framework to accurately predict and visualize fungal effectors. By combining global patterns learned from pretrained protein language models with refined information from known effectors, Fungtion achieves state-of-the-art prediction performance. Additionally, the interactive visualizations we have developed enable researchers to explore both sequence- and high-level relationships between the predicted and known effectors, facilitating effector function discovery, annotation, and hypothesis formulation regarding plant-pathogen interactions. We anticipate Fungtion to be a valuable resource for biologists seeking deeper insights into fungal effector functions and for computational biologists aiming to develop future methodologies for fungal effector prediction: https://step3.erc.monash.edu/Fungtion/. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Exploitation of the infinitive natural resources is an alarming issue on the plate. Therefore, estimation and swift observation of the natural resources is a need of the hour. Geospatial technological development is playing an important role to collect the information from the targeted objectives. Geospatial technological is helpful to analyze the natural resources viz., land, water, air, energy, nutrients, forest, watershed, etc. for policy and planning toward their conservation in order to achieve food, nutritional, environmental, and economic security. Agriculture is a key sector on the planet for exploitation and interfere the natural resources. For collecting reliable and timely information about the nature, the extent and geographical boundaries, temporal behavior of natural resources is the first step in the way of their monitoring, management and efficient use of them in the agriculture. Remote sensing (RS) has emerged as a powerful geospatial tool for the identification, characterization, and land marking of these resources over a larger surface area in agricultural system. It provides valuable, accurate and timely information in high spatial and spectral resolutions about the agricultural urbanization, crop use patterns, soil, water, watersheds, desertification, agroforestry, rangelands, and climatic variations and their impact on agriculture. In crop production, RS provides the spatial information of crop type and area estimation followed by assessing the yield potential, ecosystem health and proper management of insect-diseases and weeds based on the spectral reflectance of the object by using modeling and vegetative indices. Moreover, RS has a potential to study the soil system like soil characteristics, types, spatial variability, assessment of land suitability, land capability, carbon dynamics, soil moisture, land use/land cover change, soil degradation, erosion identification, and remediation for agriculture applications. RS helps to generate a precise database in short time from the field. Predication for the advance planning, yield estimation of the covering areas, crop sections, drought management help in policymaking for the better production and reduce the risk from the aberrant weather conditions. It helps in proper use and sustainable management of the costly resources in agriculture. This chapter extensively discusses the potential of RS in management of agriculture and natural resources in a sustainable manner. In this context, in India, several programs/projects such as FASAL, CAPE, NNRMS, NADAMS, IMSD, CHAMAN, etc. are effectively running for management of agricultural system in one and another way. In this context, this chapter is useful for the policymaker students, scientists, producers for the agroecosystems management and promote the advance food and environmental security targeted as one of the United National Sustainable Development Goals.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10.1016/j.dib.2024.110763</t>
+          <t>https://doi.org/10.1016/B978-0-443-14072-3.00017-4</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A novel groundnut leaf dataset for detection and classification of groundnut leaf diseases</t>
+          <t>Chapter 2 - Geospatial applications for crop assessment</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B., Sasmal, Buddhadev; A., Das, Arunita; K.G., Dhal, Krishna Gopal; S.B., Saheb, Sk Belal; R.A., Abu Khurma, Ruba Abu; P.A., Castillo-Valdivieso, Pedro A.</t>
+          <t>V.M. Chowdary; Abhishek Chakraborty; Bhavana Sahay; Karun Kumar Choudhary; Anima Biswal; P. Srikanth; Mamta Kumari; B. Laxman; Varun Pandey; Parichay S. Raju; K. Sreenivas; Prakash Chauhan</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Data in Brief</t>
+          <t>Elsevier eBooks</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>4</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3967302441596985</v>
+        <v>0.6923701167106628</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Groundnut (Arachis hypogaea) is a widely cultivated legume crop that plays a vital role in global agriculture and food security. It is a major source of vegetable oil and protein for human consumption, as well as a cash crop for farmers in many regions. Despite the importance of this crop to household food security and income, diseases, particularly Leaf spot (early and late), Alternaria leaf spot, Rust, and Rosette, have had a significant impact on its production. Deep learning (DL) techniques, especially convolutional neural networks (CNNs), have demonstrated significant ability for early diagnosis of the plant leaf diseases. However, the availability of groundnut-specific datasets for training and evaluation of DL models is limited, hindering the development and benchmarking of groundnut-related deep learning applications. Therefore, this study provides a dataset of groundnut leaf images, both diseased and healthy, captured in real cultivation fields at Ramchandrapur, Purba Medinipur, West Bengal, using a smartphone camera. The dataset contains a total of 1720 original images, that can be utilized to train DL models to detect groundnut leaf diseases at an early stage. Additionally, we provide baseline results of applying state-of-the-art CNN architectures on the dataset for groundnut disease classification, demonstrating the potential of the dataset for advancing groundnut-related research using deep learning. The aim of creating this dataset is to facilitate in the creation of sophisticated methods that will aid farmers accurately identify diseases and enhance groundnut yields. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>With the ever-increasing global population and limited arable land for cultivation, sustainable management of the existing farming land become critical for future food security. Geospatial technologies, which combines satellite, aerial, ground-based mobile spatial/aspatial data involving advanced data processing techniques, can play an important role in the current aspect. This chapter provides a snapshot of these geospatial applications for crop assessment that includes spectral reflectance of crop and its relation with leaf and canopy parameters, and spectral separability of the crops and crop mapping. Popular spectral vegetation indices and its role in monitoring the crop health/condition are also discussed. Techniques to retrieve crop biophysical/biochemical parameters using satellite observations and different valued added products like crop phenology and cropping intensity were also presented. The chapter also deals with the crop yield modeling using different approaches like empirical, semiempirical (light use efficiency), and process-based simulation models. The critical geospatial inputs for crop insurance solutions such as climatic risk-based zonation, rate making, prevented sowing, mid-season adversity, crop damage due to weather extremes, objective crop cutting experiment through smart sampling, crop yield assessment, and timely claim settlement are presented in brief. Adoption of these technologies in crop management will be critical for sustainable growth under future climatic scenarios.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10.1007/s40031-024-01029-8</t>
+          <t>https://doi.org/10.1016/B978-0-323-90386-8.00139-X</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Intelligent Crop Recommender System for Yield Prediction Using Machine Learning Strategy</t>
+          <t>Urban Agriculture and Vertical Farming</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>A., Maheswary, A.; S., Nagendram, Sanam; U., Kiran, Uday; S.H., Hasane Ahammad, Sk Hasane; P.P., Priya, Putcha Poorna; M.A., Hossain, Md Amzad; A.N., Zaki Rashed, Ahmed Nabih</t>
+          <t>Chungui Lu; Steven Grundy; Gadelhag Mohmed; Katherine Hardy</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2341,327 +2357,327 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Journal of The Institution of Engineers (India): Series B</t>
+          <t>Elsevier eBooks</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>4</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9928716421127319</v>
+        <v>0.983501136302948</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>For most developed nations, agriculture is a significant economic force. The realm of contemporary agriculture is consistently growing with evolving farming techniques and agricultural innovations. Farmers face challenges in keeping pace with the evolving demands of the planet and meeting the requirements of profitable initiatives, characters, and various other stakeholders. Climate change brought on by industry emissions and soil erosion, soil's nutrient deficiency due to mineral's absence, which results in reduced crop growth, and the cultivation of the same crops repeatedly without trying out new varieties are a few of the difficulties farmers face. Without considering the lower quality or quantity, they arbitrarily infuse fertilizers. Using two separate metrics, entropy and Gini indexes, the study analyzes well-known procedures with K-nearest neighbor (KNN), decision tree (DT), and random forest (RF) classifier practices. Moreover, the precision under the agriculture paradigm, particularly “crop recommender systems,” includes these methods. Based on the outcomes, the random forest strategy outperforms the other approaches to model accuracy and reliability. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>World agriculture is undergoing a transition to new technological paradigms driven by innovations in sustainability and resource use efficiency. The development of this new paradigm is enabled by the ongoing “precision”, “info” and “smart” revolutions, and new demands of the markets. This article is intended to introduce a novel agricultural practice - vertical farming/urban agriculture that can help deliver, in environmentally and socially sustainable ways, safe and nutritious food for a growing world population - improving global food security and citizen health and wellbeing. An effect of this new agricultural revolution is a notable increase in crop yields and quality.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10.3390/nu16142226</t>
+          <t>https://doi.org/10.1016/B978-0-443-27324-7.00007-0</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Predicting Recurrent Deficiency and Suboptimal Monitoring of Thiamin Deficiency in Patients with Metabolic and Bariatric Surgery</t>
+          <t>Chapter 7 - Genomic assisted breeding approaches for biotic stress tolerance in horticultural crops</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>J.M., Parrott, Julie M.; A.J., Parrott, Austen J.; J.S., Parrott, James Scott; N.N., Williams, Noël N.; K.R., Dumon, Kristoffel R.</t>
+          <t>Priti Upadhyay; Manish Kumar Vishwakarma</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nutrients</t>
+          <t>Elsevier eBooks</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6912403106689453</v>
+        <v>0.849856972694397</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tópico 6: soybean, vegetable, learningbased</t>
+          <t>Tópico 2: approach, data, grape</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Introduction: Vitamin B1 (thiamine) deficiency (TD) after metabolic and bariatric surgery (MBS) is often insidious and, if unrecognized, can lead to irreversible damage or death. As TD symptoms are vague and overlap with other disorders, we aim to identify predictors of recurrent TD and failure to collect B1 labs. Methods: We analyzed a large sample of data from patients with MBS (n = 878) to identify potential predictors of TD risk. We modeled recurrent TD and failure to collect B1 labs using classical statistical and machine learning (ML) techniques. Results: We identified clusters of labs associated with increased risk of recurrent TD: micronutrient deficiencies, abnormal blood indices, malnutrition, and fluctuating electrolyte levels (aIRR range: 1.62–4.68). Additionally, demographic variables associated with lower socioeconomic status were predictive of recurrent TD. ML models predicting characteristics associated with failure to collect B1 labs achieved 75–81% accuracy, indicating that clinicians may fail to match symptoms with the underlying condition. Conclusions: Our analysis suggests that both clinical and social factors can increase the risk of life-threatening TD episodes in some MBS patients. Identifying these indicators can help with diagnosis and treatment. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Fruits, vegetables, and ornamentals are examples of horticultural crops that are essential to the economies and food security of the world. Biologic stressors like illnesses and insect infestations, however, drastically lower quality and productivity. Conventional resistance breeding techniques are labour-intensive and constrained by genetics. By utilizing cutting-edge genomic technologies, genomic-assisted breeding (GAB) provides a quicker and more accurate substitute. Resistance genes have been identified thanks to high-throughput sequencing, quantitative trait locus (QTL) mapping, and genome-wide association studies (GWAS). Breeding is accelerated by the integration of these genes into top cultivars through marker-assisted selection (MAS) and genomic selection (GS). Furthermore, specific alterations to improve plant immunity are possible with genome editing techniques like CRISPR-Cas9.While machine learning and big data analytics enhance the prediction of resistance traits, omics techniques like as transcriptomics, proteomics, and metabolomics provide deeper insights into plant defense processes. Even with these developments, problems still exist. Widespread adoption is constrained by the genetic complexity and heterozygosity of many horticulture crops, as well as regulatory obstacles and consumer apprehensions regarding genome-edited plants. To improve breeding efficiency, future studies should combine multi-omics datasets, improve gene-editing methods, and provide affordable genotyping tools. A revolutionary method for creating horticultural crops that can withstand biotic stress is genomic-assisted breeding. The development of genomic tools for enhancing crop varieties with improved quality and stress tolerance is covered in this chapter. By combining state-of-the-art genomic technology, breeders may increase disease and pest resistance while preserving productivity and quality. To fully realize its promise in sustainable horticulture, scientists, breeders, and legislators must continue to work together.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10.3390/ijms25136932</t>
+          <t>https://doi.org/10.1016/B978-0-443-27324-7.00014-8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Integrated Assays of Genome-Wide Association Study, Multi-Omics Co-Localization, and Machine Learning Associated Calcium Signaling Genes with Oilseed Rape Resistance to Sclerotinia sclerotiorum</t>
+          <t>Chapter 14 - Advanced technological innovations for mitigating biotic stresses in horticulture: From remote sensing to AI-Driven solutions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>X., Wang, Xinyao; C., Ren, Chunxiu; Q., Fan, Qingwen; Y., Xu, Youping; L., Wang, Luwen; Z.L., Mao, Zhou Lu; X., Cai, Xinzhong</t>
+          <t>Reetesh Kumar; Dilip Kumar Chaurasiya; Sarvesh Singh</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>International Journal of Molecular Sciences</t>
+          <t>Elsevier eBooks</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9924727082252502</v>
+        <v>0.3683551251888275</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Sclerotinia sclerotiorum (Ss) is one of the most devastating fungal pathogens, causing huge yield loss in multiple economically important crops including oilseed rape. Plant resistance to Ss pertains to quantitative disease resistance (QDR) controlled by multiple minor genes. Genome-wide identification of genes involved in QDR to Ss is yet to be conducted. In this study, we integrated several assays including genome-wide association study (GWAS), multi-omics co-localization, and machine learning prediction to identify, on a genome-wide scale, genes involved in the oilseed rape QDR to Ss. Employing GWAS and multi-omics co-localization, we identified seven resistance-associated loci (RALs) associated with oilseed rape resistance to Ss. Furthermore, we developed a machine learning algorithm and named it Integrative Multi-Omics Analysis and Machine Learning for Target Gene Prediction (iMAP), which integrates multi-omics data to rapidly predict disease resistance-related genes within a broad chromosomal region. Through iMAP based on the identified RALs, we revealed multiple calcium signaling genes related to the QDR to Ss. Population-level analysis of selective sweeps and haplotypes of variants confirmed the positive selection of the predicted calcium signaling genes during evolution. Overall, this study has developed an algorithm that integrates multi-omics data and machine learning methods, providing a powerful tool for predicting target genes associated with specific traits. Furthermore, it makes a basis for further understanding the role and mechanisms of calcium signaling genes in the QDR to Ss. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Climate change and population expansion are posing a growing challenge to global food security, which calls for creative and sustainable farming methods to boost crop yields. Horticultural yields and quality are greatly impacted by biotic stressors, including as pests, diseases, and weeds, which are typically controlled using chemical inputs like pesticides and herbicides. However, over usage of these pesticides has resulted in negative impacts on non-target organisms, environmental deterioration, and pesticide resistance. Advanced technical advancements like drone-based monitoring, hyperspectral imaging, and remote sensing are transforming biotic stress management in order to meet these problems. Real-time, high-resolution crop monitoring is made possible by these state-of-the-art instruments, which also make it easier to identify biotic hazards early and implement focused, accurate responses. Furthermore, combining machine learning and artificial intelligence (AI) improves decision-making and predictive modeling, maximizing resource utilization while reducing environmental effect. The potential of emerging technologies to enhance sustainability, efficiency, and resilience in agricultural systems is highlighted in this chapter, which examines their function in horticulture's mitigation of biotic stress.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10.1063/5.0197883</t>
+          <t>https://doi.org/10.1016/B978-0-443-40584-6.00005-X</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>An IOT based low cost intelligent irrigation system using deep learning model</t>
+          <t>Chapter 16 - New frontiers in soil chemistry research innovations and discoveries</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>V.P., Sakthivel, V. Prithika; P., Prakash, P.</t>
+          <t>Khizar Hayat; Shehzad Ahmad; Nazima Wahid;  Karishma; Amjad Ali; Alevcan Kaplan; Muhammad Nauman Khan; Shah Fahad; Majid Iqbal</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AIP Conference Proceedings</t>
+          <t>Elsevier eBooks</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>4</v>
       </c>
       <c r="G50" t="n">
-        <v>0.8176574110984802</v>
+        <v>0.656091570854187</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Water scarcity starts affecting the world and the trend remains the same even worse over the time due to the increasing global population which is expected to be more than 9 billion by 2050. The major portion of the fresh water was consumed by agriculture sector predominantly on irrigation. India has 4% of world's freshwater resources to assist 18% of world population. Unlike USA and China, India takes 2-4 % more water for its agricultural production. Continuous harvesting without the sufficient measurement and provisioning of the soil nutrient may endanger the sustainability of the agriculture. The amount of macro and micronutrients, pH level and water is used to measure the fertility of the soil. In case of soil nutrient deficiency, fertilizers to be added to the soil to maintain the nutrient levels. Most of the farmers apply the fertilizers manually. The right amount of nutrient to be maintained or else it may affect the plant life cycle and reduce the yield. Therefore, there is a need to adopt the advanced technologies in agro irrigation system by applying intelligent systems and services for the effective usage of fresh water and to maintain soil nutrient. Intelligent Irrigation System (IIS) which schedules the irrigation dynamically based on the soil features. Deep learning model for soil moisture and nutrient prediction, the same model can be deployed into other domains such textile and home automation. Mobile application to the farmers to know the status of the irrigation and soil fertility information. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Soil chemistry is critical to the long-term viability of agriculture, the environment, and ecosystems. Recent advances in soil chemistry research have revealed new boundaries, owing to technical developments, multidisciplinary methods, and a better knowledge of soil dynamics. This chapter investigates developing trends, such as nanotechnology applications for soil remediation, biochar and organic additions to improve soil fertility, and the importance of molecular spectroscopy in soil nutrient analysis. Furthermore, advances in soil microbial interactions, carbon sequestration processes, and sustainable land management options are discussed. The merging of artificial intelligence and big data analytics is changing soil chemistry research by allowing more accurate soil health evaluations and predictive modeling. These advances not only enhance soil management methods but also help to ensure global food security and mitigate climate change. This chapter covers significant findings and future perspectives in soil chemistry, highlighting the necessity for ongoing study and long-term uses in agriculture and environmental protection.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10.1063/5.0189928</t>
+          <t>10.1117/12.836944</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optimization based hybrid approach for grape leaf disease classification and pesticide detection</t>
+          <t>Cucumber diseases diagnosis using multispectral images</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>N., Malarvizhi, N.; V.S., Bajait, Vaishali Sukhadeo</t>
+          <t>Feng, J.; Li, H.; Shi, J.; Yang, W.; Liao, N.</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2024</v>
+        <v>2009</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AIP Conference Proceedings</t>
+          <t>Proceedings of SPIE - The International Society for Optical Engineering</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9920365214347839</v>
+        <v>0.5395429134368896</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tópico 2: tomato, fruit, grape</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Grape is one of the most cultivated fruit crops in India and widely used to produce the food items. Among the world, grapes are considered as most significant fruit and it comprises various nutrients, namely Vitamin C. However, grape plants suffer with diseases which extremely affect good quality grape yield. The major six general grape leaf disease and pests are brown spot, leaf blight, downy mildew, anthracnose, and black rot, which produces severe economic suffers to grape commerce. Thus, the early detection of grape leaf disease is highly needed to produce healthy grape yield. Moreover, computer vision driven approaches have been employed effectively in modern years for detecting and classifying plants diseases. In this paper, hybrid approach with fuzzy logic and neural network has been proposed to classify the grape leaf disease. The work is further extended to identify whether leaf is affected with pesticide or not and percentages of pesticide is calculated if it is affected with pesticides. Optimization approach has been used to find accurate results. This optimization based deep learning approach achieved the accuracy of pesticide identification 93.43%. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>In this paper, multispectral imaging technique for plant diseases diagnosis is presented. Firstly, multispectral imaging system is designed. This system utilizes 15 narrow-band filters, a panchromatic band, a monochrome CCD camera, and standard illumination observing environment. The spectral reflectance and color of 8 Macbeth color patches are reproduced between 400nm and 700nm in the process. In addition, spectral reflectance angle and color difference is obtained through measurements and analysis of color patches using spectrometer and multispectral imaging system. The result shows that 16 narrow-bands multispectral imaging system realizes good accuracy in spectral reflectance and color reproduction. Secondly, a horticultural plant, cucumber' familiar disease are the researching objects. 210 multispectral samples are obtained by multispectral and are classified by BP artificial neural network. The classification accuracies of Sphaerotheca fuliginea, Corynespora cassiicola, Pseudoperonospora cubensis are 100%. Trichothecium roseum and Cladosporium cucumerinum are 96.67% and 90.00%. It is confirmed that the multispectral imaging system realizes good accuracy in the cucumber diseases diagnosis. © 2009 SPIE.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10.11591/ijeecs.v33.i3.pp1748-1759</t>
+          <t>https://doi.org/10.1016/bs.agron.2025.10.005</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Virtual analysis of machine learning models for diseases prediction in muskmelon</t>
+          <t>Operational and analytical frameworks of Unoccupied Aerial Vehicles (UAV) for precision agriculture applications</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>K., Deeba, K.; B., Amutha, B.; D., Sattianadan, Dasarathan; D., Rosy Salomi Victoria, D.; V., Maheshkar, Vikas; R., Ramkumar, R.; D., Karthikeyan, D.</t>
+          <t>Gaurav Jha; Sourajit Dey; Prasad Deshpande</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Indonesian Journal of Electrical Engineering and Computer Science</t>
+          <t>Advances in agronomy</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G52" t="n">
-        <v>0.4786550104618073</v>
+        <v>0.7572234869003296</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Muskmelon, a crop prized for its economic potential, has a relatively brief growth cycle. Disease susceptibility during this period can have a profound impact on yields, posing challenges for farmers. Environmental conditions are pivotal in disease occurrence. Unfavorable conditions reduce the likelihood of pathogens infecting vulnerable host plants as temperature and humidity influence pathogen behavior, including toxin synthesis, virulence protein production, and reproduction. Pathogens can lie dormant in the soil until suitable conditions activate them. When the right environment and host plants align, these dormant pathogens can cause outbreaks. Disease prediction becomes possible by analyzing environmental variables. Real-time data collected via strategically placed sensors focused on viral, fungal, and bacterial infections. Results indicated that the extreme gradient boosting (XGBoost) algorithm, with a maximum tree depth of 4 and 30 trees per iteration, achieved remarkable performance, yielding an accuracy of 97%. For comparison, the XGBoost model outperformed an 8-layer Backpropagation network with 7 nodes per layer, which achieved 95% accuracy. These findings underscore XGBoost's efficacy in forecasting and mitigating muskmelon plant diseases, offering the potential for improved crop yields and agricultural sustainability. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Agricultural systems are entering an era defined not just by mechanization but by real-time, spatially aware, data driven production practices. This shift which has rapidly evolved from novelty to necessity in precision agriculture. At the center of this shift Unoccupied Aerial Vehicles (UAV) or drones have operationalized high-resolution aerial data into sustainable agricultural outcomes. This chapter provides an application-focused roadmap for integrating UAV into modern agronomic workflows as pre, during, and post flight operations for agronomic flight planning. It bridges the engineering of flight platforms and sensors with the applications in crop stress detection, variable-rate input application, and predictive yield modeling. We explore UAV architecture and their implications for data resolution, field scale, and operational complexity. Sensor systems use the portions of electromagnetic spectrum (RGB, multispectral, hyperspectral, thermal, LiDAR) and are examined through their applications for plant physiology and soil interactions. Ground sampling distance, spectral calibration, geospatial accuracy and photogrammetry are not treated as ancillary steps, but as critical determinants of agronomic utility. We describe the full data pipeline from FAA (Federal Aviation Administration) regulations to machine learning-driven analytics, acquisition, orthomosaic generation, digital surface modeling, vegetation index extraction, and the development of actionable prescription maps. In the context of AI evolution, we emphasize how AI-ML methods classification, regression, clustering, and dimensionality reduction help with integrating complex patterns in time-series UAV imagery, enabling early and precise management of nutrients, water, weeds, and disease. By synthesizing global regulatory frameworks and field-based use cases, the chapter concludes UAV as tools that transforms data into agronomic decisions.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10.5614/j.eng.technol.sci.2024.56.1.5</t>
+          <t>10.1016/j.procs.2023.01.225</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Comparison Study of Corn Leaf Disease Detection based on Deep Learning YOLO-v5 and YOLO-v8</t>
+          <t>A Systematic Review of Citrus Disease Perceptions and Fruit Grading Using Machine Vision</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>N., Chitraningrum, Nidya; L., Banowati, Lies; D., Herdiana, Dina; B., Mulyati, Budi; I., Sakti, Indra; A., Fudholi, Ahmad; H., Saputra, Huzair; S., Farishi, Salman; K., Muchtar, Kahlil; A., Andria, Agus</t>
+          <t>Palei, S.; Behera, S.K.; Sethy, P.K.</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Journal of Engineering and Technological Sciences</t>
+          <t>Procedia Computer Science</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.3863027095794678</v>
+        <v>0.9912382364273071</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tópico 4: yolov, increase, map</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Corn is one of the primary carbohydrate-rich food commodities in Southeast Asian countries, among which Indonesia. Corn production is highly dependent on the health of the corn plant. Infected plants will decrease corn plant productivity. Usually, corn farmers use conventional methods to control diseases in corn plants. Still, these methods are not effective and efficient because they require a long time and a lot of human labor. Deep learning-based plant disease detection has recently been used for early disease detection in agriculture. In this work, we used convolutional neural network algorithms, namely YOLO-v5 and YOLO-v8, to detect infected corn leaves in the public data set called ‘Corn Leaf Infection Data set’ from the Kaggle repository. We compared the mean average precision (mAP) of mAP 50 and mAP 50-95 between YOLO-v5 and YOLO-v8. YOLO-v8 showed better accuracy at an mAP 50 of 0.965 and an mAP 50-95 of 0.727. YOLO-v8 also showed a higher detection number of 12 detections than YOLO-v5 at 11 detections. Both YOLO algorithms required about 2.49 to 3.75 hours to detect the infected corn leaves. This all-trained model could be an effective solution for early disease detection in future corn plantations. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Citrus is one of the most commonly farmed and popular fruit crops globally. Citrus fruits are high in vitamins, minerals, and dietary fibre, which are essential for overall health. Oranges are the most widely traded citrus fruit, accounting for more than half of global citrus production. Tangerines, lemons, and mandarins are the next most commonly farmed varieties. Citrus production and export have steadily expanded over the previous three decades, though slower than competing items like mangoes, avocados, and melons. The production of citrus fruit is heavily hampered due to diseases in its growth stages. Again, the diseases not only appear in leaves but also in fruits. So, the quality of fruits is degraded due to the appearance of flaws. The citrus fruits are graded in two ways: first based on their skin tone and second on their size. So, there is a requirement to assess citrus diseases to avoid the degradation of production. Further, there is a need to grade citrus fruit to make easy packaging concerning its quality; so that the proper values of Citrus fruits be generated. This article studied and analysed different methodologies reported for citrus disease prediction and grading of citrus fruit in the postharvest stage based on machine vision between 2010 and 2021. This paper outlines the current achievements, limitations, and suggestions for future research on citrus diseases and their fruit grading. © 2022 Elsevier B.V.. All rights reserved.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10.1016/j.compag.2023.108571</t>
+          <t>10.1016/j.procs.2017.11.323</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hyperspectral imaging detects biological stress of wheat for early diagnosis of crown rot disease</t>
+          <t>Identification of plant disease infection using soft-computing: Application to modern botany</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Y., Xie, Yiting; D.C., Plett, Darren Craig; M.L., Evans, Margaret L.; T., Garrard, Tara; M., Butt, Mark; K.D., Clarke, Kenneth D.; H., Liu, Huajian</t>
+          <t>Kiani, E.; Mamedov, T.</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Computers and Electronics in Agriculture</t>
+          <t>Procedia Computer Science</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6947838068008423</v>
+        <v>0.8805938959121704</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Crown rot, caused by a stubble-soil fungal pathogen, threatens wheat production, leading to significant yield losses. The challenge lies in the absence of early visible symptoms for timely detection and management. While hyperspectral imaging technologies have been successfully applied to improve screening for some plant health indicators and diseases, they have not yet been successfully used for crown rot disease detection. This study endeavoured to harness hyperspectral imaging technologies for early-stage, high-throughput, accurate, economical, and non-destructive detection of crown rot disease. Four common Australian commercial wheat varieties with different resistance levels were chosen for study, including Aurora, Yitpi, Emu Rock and Trojan. Three different hyperspectral cameras, covering various wavelength ranges, were tested from both side-view and top-view. Four types of input data for support vector machine classification were tested, including reflectance and the other three derived forms namely hyper-hue, standard normal variate, and principal components. The experimental results showed that hyperspectral imaging technologies can successfully diagnose infected plants in a greenhouse approximately 30 days after infection when there were no visible symptoms on shoots, and the hyper-hue and standard normal variate data transformation methods achieved high F1 scores above 0.75. By discovering key wavelengths, we found that hyperspectral imaging achieved early detection by uncovering biological stress related to photosynthetic activities, and limited absorption of water, protein and starch synthesis. These findings represent a critical advance towards establishing a hyperspectral imaging system for crown rot detection, thereby facilitating disease management and breeding resistant varieties. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Botany is the scientific examination of plants characters. Plant disease can be caused either by living organisms having wide range as harmful or benign ones which grow specifically on the horticultural plant leaves or deficiency of minerals e.g. iron, phosphate, nitrogen, etc. Modern agriculture requires smart and feasible techniques to replace the human intelligence with machine intelligence. Whereas a human identifies the disease infected leaves by his eye, the machine should also be capable of vision-based disease identification. The objective of this paper is to practically verify the applicability of a new computer-vision method for discrimination between the healthy and disease infected strawberry leaves which does not require neural network or time consuming trainings. The proposed method was tested under outdoor lighting condition using a regular DLSR camera without any particular lens. Since the type and infection degree of disease is approximated a human brain a fuzzy decision maker classifies the leaves over the images captured on-site having the same properties of human vision. Optimizing the fuzzy parameters for a typical horticultural field at a mid-day summer Mediterranean day in produced 96% accuracy for segmented iron deficiency and 93% accuracy for segmented using a typical human instant classification approximation as the benchmark holding higher accuracy than a human eye identifier. The fuzzy-base classifier provides approximate result for decision making on the leaf status as if it is healthy or not. © 2018 The Authors. Published by Elsevier B.V.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10.1145/3672758.3672780</t>
+          <t>10.1063/5.0189928</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BelncRNA-Deep: plant lncRNA prediction using BERT and neural networks</t>
+          <t>Optimization based hybrid approach for grape leaf disease classification and pesticide detection</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>H., Yang, Huaizhou; S., Fu, Shikun; Z., Lei, Zhang</t>
+          <t>Malarvizhi, N.; Bajait, V.</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2669,778 +2685,778 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>AIP Conference Proceedings</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6322852373123169</v>
+        <v>0.6627197861671448</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 2: approach, data, grape</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>With the rapid development of biotechnology, the number of biological sequences is growing explosively. This provides a rich data base for the application of deep learning in biological sequence classification. For predicting and analyzing the biological functions of DNA, RNA, proteins and peptides, sequence-based prediction and analysis play a crucial role. Especially in the field of RNA, long noncoding RNAs (lncRNAs) play an indispensable role in regulating biological activities, and thus their identification and prediction are important for a deeper understanding of biological processes. In order to achieve more accurate predictions, an improved deep learning model is proposed in this study. The model treats plant lncRNA sequences as natural text, utilizes the BERT model for pre-training, and combines with convolutional neural network (CNN) for feature extraction and prediction. The experimental results show that the CNN model trained by BERT exhibits higher accuracy and stability in lncRNA prediction compared with traditional machine learning methods such as SVM, LR, and K-NN. This fully demonstrates the great potential of deep learning methods in biological sequence analysis. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Grape is one of the most cultivated fruit crops in India and widely used to produce the food items. Among the world, grapes are considered as most significant fruit and it comprises various nutrients, namely Vitamin C. However, grape plants suffer with diseases which extremely affect good quality grape yield. The major six general grape leaf disease and pests are brown spot, leaf blight, downy mildew, anthracnose, and black rot, which produces severe economic suffers to grape commerce. Thus, the early detection of grape leaf disease is highly needed to produce healthy grape yield. Moreover, computer vision driven approaches have been employed effectively in modern years for detecting and classifying plants diseases. In this paper, hybrid approach with fuzzy logic and neural network has been proposed to classify the grape leaf disease. The work is further extended to identify whether leaf is affected with pesticide or not and percentages of pesticide is calculated if it is affected with pesticides. Optimization approach has been used to find accurate results. This optimization based deep learning approach achieved the accuracy of pesticide identification 93.43%. © 2024 Author(s).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10.1109/DELCON64804.2024.10866614</t>
+          <t>10.4018/978-1-7998-2736-8.ch005</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A Review on Fungal Diseases Detection in Apple Plant using Machine Learning</t>
+          <t>Fusion approach-based horticulture plant diseases identification using image processing</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>S., Gupta, Shivani; P., Rani, Pooja</t>
+          <t>Balakrishna, K.</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Advances in computational intelligence and robotics book series</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>0.7513718008995056</v>
+        <v>0.7255992889404297</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Apple is a common fruit rich in antioxidants, dietary fiber, several vitamins, and a large range of macro and micronutrients. All these features make it a healthy addition to a balanced diet. Apples come in a large range of colors, flavors, and varieties. There are several types of diseases both bacterial and fungal along with other types of nutritional and soil diseases that hamper the production of apple crops. A few common types of fungal diseases include Apple rot, rust, and scab. Timely identification and proper treatment can save apple crops in early stages of disease progression, saving the crop and not digging a hole in the pocket of the farmer. Until last century manual identification methods were more popular but they were very laborious, time-consuming, and the accuracy was not up to the mark. 21st century marks the use of machine learning and deep learning in almost all aspects of human life including early identification of disease in several plants including Apple. In this paper authors analyze and evaluate what are the current trends in detection of fungal diseases of Apple plants. Out of several types of Apple diseases three main types were chosen to conduct this review and those diseases are rust, scab, and rot. The primary aim of this review article is to analyze the use of various machine learning tools like CNN (convolutional neural network), support vector machine, and k nearest neighbor for the detection of fruit and leaf diseases under these three plant disease categories of Apple. An early detection will ensure early curative and remedial measures which will save the crop from getting destroyed due to the above diseases and will save the farmer from huge losses. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Plant disease is the major threat to the productivity of the plants. Identification of the plant diseases is the key to prevent the losses in the productivity and quality of the yield. It is a very challenging task to identify diseases detection on the plant for sustainable agriculture, where it requires a tremendous amount of work, expertise in the plant disease, and also requires excessive processing time. Hence, image processing is used here for detection of diseases in multi-horticulture plants such as alternaria alternata, anthracnose, bacterial blight, and cercospora leaf spot and also addition with the healthy leaves. In the first stage, the leaf is classified as healthy or unhealthy using the KNN approach. In the second stage, they classify the unhealthy leaf using PNN, SVM, and the KNN approach. The features are like GLCM, Gabor, and color are used for classification purposes. Experimentation is conducted on the authors own dataset of 820 healthy and unhealthy leaves. The experimentation reveals that the fusion approach with PNN and SVM classifier outperforms KNN methods. © 2022 by IGI Global. All rights reserved.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10.1109/ICPECTS62210.2024.10780166</t>
+          <t>10.35940/ijitee.J9802.0981119</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Smart Model for Recognizing Hydroponic Lettuce Shortages Utilizing Higher Level Efficient Algorithms and Consensus Multi-Dilated Adaptive Networks</t>
+          <t>Diagnosis of plant diseases using artificial neural network</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>T., Prabahar Godwin James, T.; K., Bala, Kiran</t>
+          <t>Chavan, M.S.</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>International Journal of Innovative Technology and Exploring Engineering</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.6681990623474121</v>
+        <v>0.5338223576545715</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>The evolution that never stops, especially in smart agriculture, especially hydroponic farming has bought a great change for efficiencies and productivities. Nevertheless, identification and categorization of nutrient deficiencies in hydroponic lettuce are still challenging, specifically, when training deep learning models for low power 'Edge' IoT devices such as smart mobile phones and Raspberry Pi. Current methods are challenging due to high computational complexity, high power consumption, and inadequate utilization of resources, which hinders real-life implementation in embedded systems. To overcome these challenges, this paper presents an intelligent, highly efficient approach for the identification of nutrient deficiencies in hydroponic lettuce using advanced algorithms and a Consensus Multi-Dilated Adaptive Network (CMDA-Net). The proposed model harnesses or combines many of the current best-known or best performing approaches to yield a proper feature extraction and classification. This approach takes advantage of deep neural networks including VGG-16, Residual Attention Network (RAN) and Convolutional Neural Networks (CNNs) with a multi-dilated convolutional network to improve spatial feature learning while at the same time reducing computational cost. These features are then passed through LSTM network that help capture temporal information control and ensure that lettuce deficiencies are correctly classified. The entire system structure is enhanced through the new Improvised Honey Badger Algorithm (I-HBA), which adjusts specific networks' parameters for maximum effectiveness with minimal resource consumption. Many experiments were carried out on Lettuce NPK dataset which contains test images of Fully Nutritional, Nitrogen Deficient, Phosphorus Deficient and Potassium Deficient lettuce. It respectively assessed the accuracy, specificity rate, precision, NPV, FPR, and MCC of the model. We also gained compelling improvements in terms of both computational time and model accuracy with exactly terminal prediction accuracy 96% and specificity 95%. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Pomegranate is one of India's most commonly cultivated fruit crops. manual expert observations are being used to detect leaf diseases that take longer time for further prevention. Fruit diseases are causing devastating disadvantages in worldwide agricultural business economic losses in production in this journal, the answer is proposed and valid by experiment for the identification and classification of fruit disorders. The objective of proposed work is to analyze the illness utilizing picture preparing and artificial intelligence techniques on pictures of pomegranate plant leaf. In the proposed framework, pomegranate leaf picture with complex foundation is taken as input. Then pomegranate leaf ailment division is finished utilizing K-means clustering. The infected segment from portioned pictures is recognized. Best results have been seen when neural networks with a RBFN is used for a classification. © BEIESP.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10.1109/ICCCNT61001.2024.10724678</t>
+          <t>10.1109/ICSSIT48917.2020.9214159</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The smart Multispectral Image Processing for system based Vision Applications</t>
+          <t>Disease Detection in Plants using Convolutional Neural Network</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>S., Sivamurugan, S.; A., Akila, A.; N., Sakthi Saravanan, N.; P.S., Niji, P. S.; R., Ramya, R.</t>
+          <t>D. M. Sharath; S. A. Kumar; M. G. Rohan; Akhilesh; K. V. Suresh; C. Prathap</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2022 13th International Conference on Computing Communication and Networking Technologies (ICCCNT)</t>
+          <t>2020 Third International Conference on Smart Systems and Inventive Technology (ICSSIT)</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9892328977584839</v>
+        <v>0.4398524165153503</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Multispectral picture Processing for gadgets primarily based on imaginative and prescient programs is a generation that permits green and correct picture processing for numerous vision packages. It uses more than one mild spectral band in the seen and non-seen stages to seize and analyze pictures with high decision and accuracy. The gadget comprises advanced sensors, algorithms, and software that collectively extract meaningful records from the captured photos. The sensors use an aggregate of filters and lenses to capture photographs in unique spectral bands, which are then processed using specialized algorithms to identify and decorate the precise capabilities of the hobby. This era has several programs in various industries, including agriculture, environmental monitoring, scientific imaging, and defense. Agriculture may be used to discover illnesses and improve crop yield via reading about plant health and vitamins. Environmental tracking can help pick out pollutants and tune modifications in ecosystems. In medical imaging, it may assist in the early detection of sicknesses and guide treatment plans. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Majority population of the world depends on agriculture as their primary occupation to earn their income. If any problems occur in that primary sector, it is going to affect the livelihood of the population adversely. Hence, it is necessary to maintain the proper balance in the agriculture sector by preventing the same from adverse effects like drought, plant diseases etc. In agriculture sector, especially horticulture yield more income to the farmers than other crops. These crops are prone to many diseases very easily and manual detection of disease in crops is very much difficult in the early stage. To avoid errors due to manual detection of diseases, Machine learning methods are used. Image processing is done by capturing the infected region of image. The infected image is provided for enhancement followed by image segmentation. then, the segmented image is given as input for the classification using convolutional neural network. This entire process is going to take place over an Android platform. This Android application helps the farmers to identify the disease easily. This paper proposes the techniques involved in the detection of diseases in the very early stage using image processing and the classification is made using convolutional neural network. After the identification a proper solution are going to provide to combat the infection in a very early stage to the farmers. This will increase the income of the farmers.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10.34133/plantphenomics.0260</t>
+          <t>10.1109/ICPCSI.2017.8392162</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Multi-Scale Attention Network for Vertical Seed Distribution in Soybean Breeding Fields</t>
+          <t>Pomogranite disease detection and classification</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>T., Li, Tang; P.M., Blok, Pieter M.; J., Burridge, James; A., Kaga, Akito; W., Guo, Wei</t>
+          <t>R. Pawar; A. Jadhav</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Plant Phenomics</t>
+          <t>2017 IEEE International Conference on Power, Control, Signals and Instrumentation Engineering (ICPCSI)</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9935283064842224</v>
+        <v>0.5086567401885986</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tópico 6: soybean, vegetable, learningbased</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>The increase in the global population is leading to a doubling of the demand for protein. Soybean (Glycine max), a key contributor to global plant-based protein supplies, requires ongoing yield enhancements to keep pace with increasing demand. Precise, on-plant seed counting and localization may catalyze breeding selection of shoot architectures and seed localization patterns related to superior performance in high planting density and contribute to increased yield. Traditional manual counting and localization methods are labor-intensive and prone to error, necessitating more efficient approaches for yield prediction and seed distribution analysis. To solve this, we propose MSANet: a novel deep learning framework tailored for counting and localization of soybean seeds on mature field-grown soy plants. A multi-scale attention map mechanism was applied to maximize model performance in seed counting and localization in soybean breeding fields. We compared our model with a previous state-of-the-art model using the benchmark dataset and an enlarged dataset, including various soybean genotypes. Our model outperforms previous state-of-the-art methods on all datasets across various soybean genotypes on both counting and localization tasks. Furthermore, our model also performed well on in-canopy 360° video, dramatically increasing data collection efficiency. We also propose a technique that enables previously inaccessible insights into the phenotypic and genetic diversity of single plant vertical seed distribution, which may accelerate the breeding process. To accelerate further research in this domain, we have made our dataset and software publicly available: https://github.com/UTokyo-FieldPhenomics-Lab/MSANet. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>In country like India, agriculture is the backbone of the overall GDP. Horticulture has become one of the important source of economy for the country and even the farmers. Formers will face much losses because of the not identifying the diseases at early stage. Relying on pure naked-eye observation to detect and classify diseases can be expensive for various plant diseases such as Pomegranate. It poses a great threat to the agricultural sector by reducing the life of the plants. In Agriculture field also image processing plays a very important role in identifying any disease of the plant or in grading of the quality of the fruit. Identification of the plant diseases is the key to preventing the losses in the yield and quantity of the agricultural product. The studies of the plant diseases mean the studies of visually observable patterns seen on the plant. Health monitoring and disease detection on plant is very critical for sustainable agriculture. It is very difficult to monitor the plant diseases manually. In this paper, we have implemented the methods for the detection of Pomegranate plant diseases using the images of the leaves.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10.6041/j.issn.1000-1298.2024.09.025</t>
+          <t>10.1109/ICSCAN.2019.8878753</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Detection Method of Chlorophyll Content in Canopy of Kiwifruit Orchard Based on UAV; 基于无人机多光谱的猕猴桃园冠层叶绿素含量检测方法</t>
+          <t>Retracted: Plant disease analysis using image processing in MATLAB</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Y., Huo, Yingqiu; S., Zhao, Shichao; G., Zhao, Guoqi; J., Sun, Jianghao; S., Hu, Shaojun</t>
+          <t>H. Krishnan; K. Priyadharshini; M. Gowsic; N. Mahesh; S. Vijayananth; P. Sudhakar</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nongye Jixie Xuebao/Transactions of the Chinese Society for Agricultural Machinery</t>
+          <t>2019 IEEE International Conference on System, Computation, Automation and Networking (ICSCAN)</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9966049194335938</v>
+        <v>0.9705628752708435</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 6: gardening, management, specie</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Digitalization and intelligence play a crucial role in facilitating the high-quality development of the kiwifruit industry. Unlike other fruit trees, kiwi trees are vine plants that require abundant mineral nutrients during their key growth period. Inadequate management can easily lead to nutrient deficiencies, which not only affect the health of the trees but also impact the yield and quality of kiwis. Therefore, real-time monitoring of tree growth health is essential. To achieve fast and large-scale monitoring of overall growth and health in kiwi orchards, the drone was used to capture multispectral images of orchards, and then Pix4Dmapper software was utilized to splice UAV multispectral images for orthophoto maps and radiation correction on canopy leaves. The segmented orthophoto images were used as samples from 420 regions. The maximum inter-class variance (Otsu) method was employed to segment canopy leaves from soil backgrounds in the sample images, enabling measurement of canopy SPAD values for constructing a multispectral dataset. Firstly, outliers within the dataset were detected by using box plot analysis and subsequently removed as abnormal samples. Next, based on data characteristics derived from multi-channel images, feature values such as change rates between adjacent channels and 23 kinds of common vegetation indices were extracted, as well as their combination, to serve as sample feature values. Then three feature screening algorithms, including CARS, LARS, and IRIV were applied to optimize these features accordingly. Eight modeling methods, partial least square regression (PLSR) , support vector regression ( SVR ) , ridge regression ( RR ) , multiple linear regression ( MLR ) , extreme gradient boosting ( XGBoost) , least absolute shrinkage and selection operator regression ( Lasso ) , random forest regression ( RFR) , and Gaussian process regression ( GPR) , were employed to construct models for identifying canopy chlorophyll content in macaque peach orchards. Finally, the performance of the 24 models constructed with different sample features was compared and analyzed. The experimental results showed that GPR model had the best performance among the models based on the change rate of adjacent channels, R2 and RMSE were 0. 770 and 3. 044, respectively. Among the models based on the combination of vegetation index and adjacent channel change rate, GPR model also had the best performance, R2 and RMSE were 0.783 and 2.957, respectively. The XGBoost model based on vegetation index was the best among all models, R2 and RMSE were 0.787 and 2.933, respectively. Consequently, the intelligent detection model utilizing UAV remote sensing enabled accurate assessment of orchard canopy chlorophyll content while facilitating analysis of orchard health status to provide decision support for subsequent intelligent orchard management. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Recognizable proof of plant ailment is troublesome in horticulture field. In the event that recognizable proof is mistaken, at that point there is an enormous misfortune on the generation of yield and efficient estimation of market. Leaf infection recognition requires tremendous sum of work, information in the plant sicknesses, and furthermore require the additionally preparing time. So we can utilize picture handling for recognizable proof of leaf infection in MATLAB. Recognizable proof of ailment pursues the means like stacking the picture, differentiate upgrade, changing over RGB to HSI, extricating of highlights and SVM.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10.7717/PEERJ-CS.2149</t>
+          <t>10.1109/ICSCAN46389.2019.10702764</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Early detection of abiotic stress in plants through SNARE proteins using hybrid feature fusion model</t>
+          <t>Retraction Notice: Plant disease analysis using image processing in MATLAB</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>T., Bhargavi, T.; D., Sumathi, D.</t>
+          <t>H. Krishnan; K. Priyadharshini; M. Gowsic; N. Mahesh; S. Vijayananth; P. Sudhakar</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PeerJ Computer Science</t>
+          <t>2019 IEEE International Conference on System, Computation, Automation and Networking (ICSCAN)</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5148641467094421</v>
+        <v>0.9705590605735779</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Tópico 2: tomato, fruit, grape</t>
+          <t>Tópico 6: gardening, management, specie</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Agriculture is the main source of livelihood for most of the population across the globe. Plants are often considered life savers for humanity, having evolved complex adaptations to cope with adverse environmental conditions. Protecting agricultural produce from devastating conditions such as stress is essential for the sustainable development of the nation. Plants respond to various environmental stressors such as drought, salinity, heat, cold, etc. Abiotic stress can significantly impact crop yield and development posing a major threat to agriculture. SNARE proteins play a major role in pathological processes as they are vital proteins in the life sciences. These proteins act as key players in stress responses. Feature extraction is essential for visualizing the underlying structure of the SNARE proteins in analyzing the root cause of abiotic stress in plants. To address this issue, we developed a hybrid model to capture the hidden structures of the SNAREs. A feature fusion technique has been devised by combining the potential strengths of convolutional neural networks (CNN) with a high dimensional radial basis function (RBF) network. Additionally, we employ a bi-directional long short-term memory (Bi-LSTM) network to classify the presence of SNARE proteins. Our feature fusion model successfully identified abiotic stress in plants with an accuracy of 74.6%. When compared with various existing frameworks, our model demonstrates superior classification results. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Recognizable proof of plant ailment is troublesome in horticulture field. In the event that recognizable proof is mistaken, at that point there is an enormous misfortune on the generation of yield and efficient estimation of market. Leaf infection recognition requires tremendous sum of work, information in the plant sicknesses, and furthermore require the additionally preparing time. So we can utilize picture handling for recognizable proof of leaf infection in MATLAB. Recognizable proof of ailment pursues the means like stacking the picture, differentiate upgrade, changing over RGB to HSI, extricating of highlights and SVM.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10.1109/I2CT61223.2024.10544287</t>
+          <t>10.1049/icp.2022.0368</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Multiclass Classification of Tomato Leaf Diseases using a Hybrid of LSTM and CNN Model</t>
+          <t>Detection of plant diseases and nutritional deficiencies from unhealthy plant leaves using machine learning techniques</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>A., Kaur, Arshleen; V., Kukreja, Vinay; S.R., Singh, Sartaj Rakesh; A., Choudhary, Ankur; R., Sharma, Rishabh</t>
+          <t>D. Nath; P. K. Dutta; A. K. Bhattacharya</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2022 IEEE 7th International conference for Convergence in Technology (I2CT)</t>
+          <t>4th Smart Cities Symposium (SCS 2021)</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" t="n">
-        <v>0.993289589881897</v>
+        <v>0.3528182506561279</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Tópico 2: tomato, fruit, grape</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Identifying diseases on tomato leaves is very important as tomatoes contain a rich amount of vitamins and other essential compounds for the human body. It helps keep crops healthy and makes farming last longer. Tomato leaf diseases are big problems for farmers and the farming business. Some of the key challenges associated with tomato leaf diseases include: Plant diseases in the leaves of tomato plants directly lead to a decrease in crop production. Diseases like early blight, late blight and bacterial wilt cause leaves to fall off too soon. This results in the plant's ability to grow fruit properly. Diseases in leaves can affect tomatoes by decreasing fruit production with weird shapes and marks. This not only makes the food look bad but can also result in people saying no to buying it and making its worth lower. In the proposed work, we proposed a strong ensemble model that uses Long Short-Term Memory (LSTM) and Convolutional Neural Network (CNN). This helps to accurately identify ten different types of tomato leaf diseases using a learning rate of 0.015, our hybrid model gets an accuracy at 99.8%. The model's performance is shown more by a loss value of 0.032, showing how good it is at finding complicated patterns in the data set. This smart method not only shows the strength of mixing LSTM and CNN designs, but it also helps in improving the classification accuracy of tomato leaf disease detection. It provides a trustworthy tool for farmers and scientists working on growing plants for many kinds of disease detection in tomato plants. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>In countries like India, which are majorly dependent on an agricultural economy, detection of crop-disease and classification has immense significance. To support agriculture, automatic disease detection and classification of plant/crop disease has become an important aspect today. Manual disease detection requires enormous amount of labour and involves too much processing-time. Therefore, image-processing plays important role for the detection of crop/plant disease from images of diseased leaves. The proposed method is based on the automatic segmentation and classification of different diseased regions of leaf from the plant/crop images, which works in three steps: In the first step, pre-processing is applied to the captured leaf image that is subjected to median filters and contrast stretching in order to remove the digitization noise and enhance the contrast of the image, respectively. In the second step, K-means clustering algorithm is employed on L*a*b* colour model of leaf image that segments pixels into uniform sets. These segments then are converted into HSV colour model and the segment that has maximum hue value among other segments are extracted as a disease segment. Finally, to the extracted diseased segment we will apply machine learning, i.e., Multi SVM classifier to classify crop image into various categorises of diseases. The same methodology is used to predict the Chlorophyll-Nitrogen content of the leaf and use the SVM classifier to show whether there is an ‘efficiency’ or ‘deficiency’ of nutrients in the crop.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10.3389/fnut.2024.1397399</t>
+          <t>10.1109/ICAECA52838.2021.9675529</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Employing advanced supervised machine learning approaches for predicting micronutrient intake status among children aged 6–23 months in Ethiopia</t>
+          <t>Foliar Disease Classification in Apple Trees</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>A.B., Zemariam, Alemu Birara; M.A., Adisu, Molalign Aligaz; A.A., Habesse, Aklilu Abera; B.B., Abate, Biruk Beletew; M., Azmeraw, Molla; W.T., Wondie, Wubet Tazeb; A.W., Alamaw, Addis Wondmagegn; H.S., Ngusie, Habtamu Setegn</t>
+          <t>R. Dhivya Praba.; R. Vennila.; G. Rohini.; S. Mithila.; K. Kavitha</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Frontiers in Nutrition</t>
+          <t>2021 International Conference on Advancements in Electrical, Electronics, Communication, Computing and Automation (ICAECA)</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G63" t="n">
-        <v>0.6559443473815918</v>
+        <v>0.7291356325149536</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Background: Although micronutrients (MNs) are important for children’s growth and development, their intake has not received enough attention. MN deficiency is a significant public health problem, especially in developing countries like Ethiopia. However, there is a lack of empirical evidence using advanced statistical methods, such as machine learning. Therefore, this study aimed to use advanced supervised algorithms to predict the micronutrient intake status in Ethiopian children aged 6–23 months. Methods: A total weighted of 2,499 children aged 6–23 months from the Ethiopia Demographic and Health Survey 2016 data set were utilized. The data underwent preprocessing, with 80% of the observations used for training and 20% for testing the model. Twelve machine learning algorithms were employed. To select best predictive model, their performance was assessed using different evaluation metrics in Python software. The Boruta algorithm was used to select the most relevant features. Besides, seven data balancing techniques and three hyper parameter tuning methods were employed. To determine the association between independent and targeted feature, association rule mining was conducted using the a priori algorithm in R software. Results: According to the 2016 Ethiopia Demographic and Health Survey, out of 2,499 weighted children aged 12–23 months, 1,728 (69.15%) had MN intake. The random forest, catboost, and light gradient boosting algorithm outperformed in predicting MN intake status among all selected classifiers. Region, wealth index, place of delivery, mothers’ occupation, child age, fathers’ educational status, desire for more children, access to media exposure, religion, residence, and antenatal care (ANC) follow-up were the top attributes to predict MN intake. Association rule mining was identified the top seven best rules that most frequently associated with MN intake among children aged 6–23 months in Ethiopia. Conclusion: The random forest, catboost, and light gradient boosting algorithm achieved a highest performance and identifying the relevant predictors of MN intake. Therefore, policymakers and healthcare providers can develop targeted interventions to enhance the uptake of micronutrient supplementation among children. Customizing strategies based on identified association rules has the potential to improve child health outcomes and decrease the impact of micronutrient deficiencies in Ethiopia. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Apple is commercially the most important temperate fruit and is third among the most widely produced fruits in the world. Jammu and Kashmir are one of the leading apple producers accounting for about 60% of production in our country and Himachal Pradesh apple accounts for about 90% of horticulture production. The diseases like apple scab, apple rust, and brown rot affect apple trees. During wet cool weather between 55- and 75-degrees Fahrenheit in the spring and early summer, the fungal spores are dispersed by wind and rain. Apple scab is the most important disease of apple which results in a 70% yield loss or even more if not managed properly. Currently, crop disease diagnosis mainly relies on farmer scouting, which is time-consuming, expensive, and ineffective due to the difference in diagnosing experience. The proposed method uses Deep Learning algorithms like VGG16, Dense Net121 and ResNetlS to classify images into four classes healthy leaves, apple scab leaves, apple rust leaves, and multiple diseases leaves. Model performance is evaluated by comparing the prediction accuracy and confusion matrix and finds the best model for this classification</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10.1109/IC457434.2024.10486737</t>
+          <t>10.1109/GCAT55367.2022.9972186</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VGG16-based Multiclass Classification of Grapevine Leaf Diseases for Precision Viticulture</t>
+          <t>Disease Detection in Tomato Plants Using CNN</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>G., Singh, Gurpreet; K., Guleria, Kalpna; S., Sharma, Shagun</t>
+          <t>K. S. Rekha; H. D. Phaneendra; B. C. S. Gandha; H. Rohan; B. N. S. Niranjan; C. Badrinat</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>2022 IEEE 3rd Global Conference for Advancement in Technology (GCAT)</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G64" t="n">
-        <v>0.4008100926876068</v>
+        <v>0.7795026302337646</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Tópico 6: soybean, vegetable, learningbased</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Grape is one of the fruit which contains a rich amount of minerals including manganese, potassium, and other vitamins namely C, B, and K, which are essential to prevent osteoporosis. With the increase in world population, the fruit demand has also increased. However, there are various diseases which affect the health of the grapevine leading to loss in its production. In the present study, a pre-trained and fine-tuned VGG16 model has been implemented for precise and accurate grape leaf disease identification. It is crucial to determine the health and growth of grapevines, but the use of advanced computer vision methods can speed up this process. The VGG16 model extracts deep features from the images and allows a faster and non-invasive performance evaluation. In the proposed work, the significance of grape leaf disease detection in viticulture is examined. The study implements the fine-tuned VGG16 model on a Kaggle-based dataset and examines the performance outcomes. The model's performance results have been identified in terms of accuracy and loss on different numbers of epochs. The results show that with the increase in the epoch count, the accuracy has also increased and reached 98% at epoch 25. The proposed VGG16 model for grape leaf disease recognition is a significant step forward for the viticulture sector, offering a potential approach for automating the evaluation of grape plant health. The proposed work also discusses about the training and testing loss and results that at epoch count 25, the lowest training and testing loss of 0.1466, and 0.1051 have been identified. These findings demonstrate the VGG16 model's effectiveness in identifying grape leaf diseases by demonstrating its precision and potential to improve both the effectiveness and quality of grapevine management. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Tomato is one of the highest yield cash crops in the World and is produced in large quantity to fulfil the huge market demand. In India tomato season prevails throughout the year and has high commercial value, it is harvested four times a year based on the geo location. Diseases indirectly affect the quality and yield of the crops. In this regard always prevention is better than cure is the best way to go, so early diseases detection plays a crucial role for high quality yielding and plays a crucial role in scientific agricultural practice with proper pesticides for specific category of disease. The objective of the study is to categorise tomato diseases using deep hidden layers of Convolution Neural Network (CNN),for the identification and classifying 8different classes of diseases in tomato leaf with an accuracy around 94.17%, our model which uses CNN allows the farmers to get an accurate disease prediction based on the photo uploaded by them and remedies for the diseases is suggested, the processing of image is done by using feature extraction methods where feature such as shape, colour, and texture are taken in consideration.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-51195-0_16</t>
+          <t>10.1109/ICCISc52257.2021.9484860</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Crop and Fertiliser Recommendation System for Sustainable Agricultural Development</t>
+          <t>Application of discrete orthonormal Stockwell transform and local neighborhood patterns for leaf disease classification in banana</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>K., Sankareswari, K.; G., Sujatha, G.</t>
+          <t>D. Mathew; C. S. Kumar; K. A. Cherian</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Signals and Communication Technology</t>
+          <t>2021 International Conference on Communication, Control and Information Sciences (ICCISc)</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G65" t="n">
-        <v>0.9957056045532227</v>
+        <v>0.681675136089325</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Agriculture is the main source of income for the people living in India and vital to our Indian economy. In recent years, agriculture struggles to meet the demand of population of our country which grows rapidly, and various agricultural problems such as pest detection, plant disease detection and classification, soil classification, cultivation of right crops, crop yield prediction, weed detection, environmental prediction, seed quality prediction and classification and animal intrusion detection are the major threats to farmers. An efficient system is required for monitoring agricultural problems and supporting farmers to identify the crops to be cultivated. Soil is the most important for the living of people on our earth which is a root source for agriculture. Farmers are depending on soil for growing crops which is a warehouse of minerals. Soil is of different types in India. Soil properties and the nature of the soil can vary from one location to another location. The same soil properties cannot be found even within a few distances. Each soil can have different levels of minerals, nutrients and organic matter and can have different characteristics based on the location. So, farmers need to know the soil types and features of various kinds of soils to understand which crops are to be cultivated in that particular soil type in different climate conditions and what kind of pesticides and fertilisers can be used for better crop yield. IoT, machine learning and deep learning techniques are emerging techniques and support smart farming. This study analysed articles on soil classification and crop recommendation systems to classify the soil based on the macro- and micronutrients available in the soil and predict the suitable crop to be grown in different types of soil based on soil data. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Among fruit crops, banana is a significant fruit in agricultural production and trade. However, global banana production is severely affected by diseases, leading to substantial declination in the yield. Hence, timely detection and control of these diseases is necessary. Diagnosis of diseases by manual inspection of initial symptoms is quite challenging for farmers. This paper demonstrates a novel machine learning approach towards classification of three major foliar fungal diseases, Sigatoka, Deightoneilla and Cordana, using discoloration patterns appearing on the leaf blade. The images, after pre-processing and segmentation, are transformed to frequency domain using discrete orthonormal Stockwell transform (DOST). Feature vectors based on local neighborhood patterns such as local binary pattern (LBP), elliptic LBP (ELBP) and its variants, are extracted from DOST transformed images and classified using five prominent image classifiers. A comparative analysis of performance metrics through a ten-fold cross validation procedure is done. Classification accuracy of 95.9% is obtained for ELBP features when classified with artificial neural network classifier (ANN). The technique of integrating DOST with LBP based features has achieved significant accuracy compared to contemporary methods of disease classification in plants.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10.3389/fmicb.2024.1304044</t>
+          <t>10.1109/AIC55036.2022.9848867</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AGRAMP: machine learning models for predicting antimicrobial peptides against phytopathogenic bacteria</t>
+          <t>IOT Assisted Smart Farming using Data Science Techniques</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>J.Y., Shao, Jonathan Y.; Y., Zhao, Yan; W., Wei, Wei; I.I., Vaisman, Iosif I.</t>
+          <t>Verma, V.; Ramakant, n.; Mathur, H.; Agarwal, N.</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Frontiers in Microbiology</t>
+          <t>2022 IEEE World Conference on Applied Intelligence and Computing (AIC)</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G66" t="n">
-        <v>0.5935820937156677</v>
+        <v>0.9936811923980713</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Introduction: Antimicrobial peptides (AMPs) are promising alternatives to traditional antibiotics for combating plant pathogenic bacteria in agriculture and the environment. However, identifying potent AMPs through laborious experimental assays is resource-intensive and time-consuming. To address these limitations, this study presents a bioinformatics approach utilizing machine learning models for predicting and selecting AMPs active against plant pathogenic bacteria. Methods: N-gram representations of peptide sequences with 3-letter and 9-letter reduced amino acid alphabets were used to capture the sequence patterns and motifs that contribute to the antimicrobial activity of AMPs. A 5-fold cross-validation technique was used to train the machine learning models and to evaluate their predictive accuracy and robustness. Results: The models were applied to predict putative AMPs encoded by intergenic regions and small open reading frames (ORFs) of the citrus genome. Approximately 7% of the 10,000-peptide dataset from the intergenic region and 7% of the 685,924-peptide dataset from the whole genome were predicted as probable AMPs. The prediction accuracy of the reported models range from 0.72 to 0.91. A subset of the predicted AMPs was selected for experimental test against Spiroplasma citri, the causative agent of citrus stubborn disease. The experimental results confirm the antimicrobial activity of the selected AMPs against the target bacterium, demonstrating the predictive capability of the machine learning models. Discussion: Hydrophobic amino acid residues and positively charged amino acid residues are among the key features in predicting AMPs by the Random Forest Algorithm. Aggregation propensity appears to be correlated with the effectiveness of the AMPs. The described models would contribute to the development of effective AMP-based strategies for plant disease management in agricultural and environmental settings. To facilitate broader accessibility, our model is publicly available on the AGRAMP (Agricultural Ngrams Antimicrobial Peptides) server. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>The rising global population demands a high yield of crop production. At present, farmers grow crops for all the people, but in case of contracting horticultural grounds and exhaustion of limited regular assets due to many reasons, and a massive increase in population, the need to improve ranch yield has turned out to be essential. Nowadays, there are various startups, technology innovators, and steps taken by the government that work to enhance total crop production. All those innovations taken for the farming framework are called smart Farming (SF). Smart Farming includes consolidating data and correspondence advances into apparatus, hardware, and sensors in the rural creation framework. The advancement of technologies must be reduced to convey meaningful information. The economy of nations like India is highly dependent on agricultural production. So disease detection in plants using an efficient algorithm is supposed to be a vital job in the farming field. This research paper is presented in three-fold:(1) Efficient way to detect disease and find cavity area; It presents Image Segmentation Algorithm (2) Using data analysis in different ways which will work for crops in a better way. The paper also presents two analysis methodologies, one is based on using an optical transducer for detecting the presence of Nitrogen (N), Phosphorous (P), and Potash (K) in soil, and the other analysis is based on the moisture content of the soil using sensors. (3)using machine learning algorithms to predict the number of fertilizers based on the collected features of soil samples, which will help farmers in amount prediction. © 2022 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10.2174/1574893618666230417104543</t>
+          <t>10.1109/ICCSEA54677.2022.9936100</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SVM-Root: Identification of Root-Associated Proteins in Plants by Employing the Support Vector Machine with Sequence-Derived Features</t>
+          <t>Early Blight and Late Blight Disease Prediction using CNN for Potato Leaves</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>P.K., Meher, Prabina Kumar; S., Hati, Siddhartha; T.K., Sahu, Tanmaya Kumar; U.K., Pradhan, Upendra Kumar; A., Gupta, Ajit; S.N., Rath, Surya Narayan</t>
+          <t>Krishna, K.S.; Narayana, G.V.S.</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Current Bioinformatics</t>
+          <t>2022 Second International Conference on Computer Science, Engineering and Applications (ICCSEA)</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>0.6031487584114075</v>
+        <v>0.4982307255268097</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 2: approach, data, grape</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Background: Root is a desirable trait for modern plant breeding programs, as the roots play a pivotal role in the growth and development of plants. Therefore, identification of the genes governing the root traits is an essential research component. With regard to the identification of root-associated genes/proteins, the existing wet-lab experiments are resource intensive and the gene expression studies are species-specific. Thus, we proposed a supervised learning-based computational method for the identification of root-associated proteins. Methods: The problem was formulated as a binary classification, where the root-associated proteins and non-root-associated proteins constituted the two classes. Four different machine learning algorithms such as support vector machine (SVM), extreme gradient boosting, random forest, and adaptive boosting were employed for the classification of proteins of the two classes. Sequence-derived features such as AAC, DPC, CTD, PAAC, and ACF were used as input for the learning algorithms. Results: The SVM achieved higher accuracy with the 250 selected features of AAC+DPC+CTD than that of other possible combinations of feature sets and learning algorithms. Specifically, SVM with the selected features achieved overall accuracies of 0.74, 0.73, and 0.73 when evaluated with single 5-fold cross-validation (5F-CV), repeated 5F-CV, and independent test set, respectively. Conclusions: A web-enabled prediction tool SVM-Root (https://iasri-sg.icar.gov.in/svmroot/) has been developed for the computational prediction of the root-associated proteins. Being the first of its kind, the proposed model is believed to supplement the existing experimental methods and high throughput GWAS and transcriptome studies. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>A well-known vegetable crop farmed all throughout the world is the potato. The possibility of a large number of diseases, however, could also impair the harvest. In order to quickly deal with the crop, it is vital for the planter to recognise the type of contamination. It had been determined that the leaves were a simple indicator of many diseases. Many Machine Learning (ML) techniques as well as Convolution Neural Network (CNN) models are superior in the literature for the detection of tomato crop diseases. CNN models rely on deep learning and neural networks, which are superior than traditional machine learning methods like decision trees and kNN. Although well before CNN creates beautiful artwork, the wide range of subjects they cover renders them operationally intensive. This painting suggests a less complex CNN model with eight convolution layer At the publicly accessible dataset PlantVillage, the recommended compact model performs better than the standard machine learning techniques and pre-trained fashions with an accuracy of 98.4%. The PlantVillage dataset includes 39 classes of different crops, including tomato diseases. These crops include apple, potato, maize, grapes, and more. In comparison to VGG16, which has an amazing accuracy of 93% 5% in pretrained patterns, k-NN has the absolute best accuracy of 94% in conventional ML approaches. After image augmentation, picture pre-processing was used to improve the suggested CNN's overall performance by having the ability to modify the brightness of the image using the knowledge of a prospective variable involving a randomized width of the image. The suggested model, which has a 98% accuracy rate, is also incredibly effective with datasets other than PlantVillage. © 2022 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10.1080/15427528.2023.2285827</t>
+          <t>10.1109/ICDSIS55133.2022.9915830</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Potato disease prediction using machine learning, image processing and IoT–a systematic literature survey</t>
+          <t>Plant Health Monitoring System and Smart Gardening using IoT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>A., Gupta, Ayushi; A., Chug, Anuradha; A.P., Singh, Amit Prakash</t>
+          <t>R. N. D; A. R; D. G; G. P. S</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Journal of Crop Improvement</t>
+          <t>2022 IEEE International Conference on Data Science and Information System (ICDSIS)</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G68" t="n">
-        <v>0.6631643176078796</v>
+        <v>0.4312544763088226</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Potato is one of the most nutritious foods rich in fiber and essential vitamins and minerals. However, potato plants may suffer from diseases such as early blight, late blight, septoria leaf spot or skin diseases such as greening, silver scurf, common scab, black rot etc. These diseases may lead to huge losses in the potato yield annually. Hence, an early prediction of such diseases is required so that they can be controlled at an early stage. Several machine learning, IoT based and image processing techniques have been utilized for this purpose, and this paper aims to survey all such methods and prediction models. A total of 116 studies were analyzed, and out of them, 77 relevant studies belonging to (60%) journals, (34%) conferences and (6%) other sources have been surveyed. It has been observed that most of the selected studies (64%) have used RGB image data (proprietary or PlantVillage dataset). Also, majority of the studies (48%) have worked with imbalanced data. Late blight and early blight are the two diseases that have gained the most attention by the researchers, being included in 58% and 34% of the studies. Moreover, feature extraction/selection has been used only with image data (RGB and hyperspectral). Convolutional Neural Network is the most widely used classifier, followed by Support Vector Machines. This review will help the researchers gain an insight into the work done for disease detection in potato crop and what techniques or diseases need intervention so that yield losses can further be minimized. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Plant heath is the scientific framework associated with controlling pest infection and pathogen intervention. This in large scale could be helpful in managing effectiveness of field or forest. The food we eat in and the cattle we grow all have close correlation with plant health. The plant health monitoring system includes chlorophyll analysis, crop density or growth analysis and nutrient analysis using image processing technique. The proposed method monitors the plant health by Chlorophyll meter is used for identifying nutrient deficiency in plants. The existing chlorophyll meter is expensive and has many disadvantages. A low-cost chlorophyll meter is implemented and it has combined assistance of internet of things. The results are compared with that of spectrophotometer and all its enhancements are highlighted. The objective is satisfied there by introduction of low cost and less complexity. The ultrasonic sensors transmit and receives waves from the target it hits. This is mounted at the top of the crop or field there by continuously monitoring the growth and indicating the periodical growth updation. The nutrition of the plant is monitored by the image processing technique, using plant image acquired from the camera. The raspberry pi board is the heart of the entire system where it controls the entire experimentation.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10.1007/s11042-023-14808-0</t>
+          <t>10.1109/ASIANCON55314.2022.9908820</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>A comparative study of grape crop disease classification using various transfer learning techniques</t>
+          <t>Tomato Blight Classification Using Transfer Learning and Fine Tuning</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>S., Sood, Shivani; H., Singh, Harjeet</t>
+          <t>O. Chougule; D. Katheria; K. Jain; S. Shinde</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Multimedia Tools and Applications</t>
+          <t>2022 2nd Asian Conference on Innovation in Technology (ASIANCON)</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G69" t="n">
-        <v>0.2826882600784302</v>
+        <v>0.6330949664115906</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tópico 2: tomato, fruit, grape</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Grapes are one of the fruits, which provides a significant source of Vitamin C. Like the other plant diseases, grapes plants are also affected some diseases. In order to protect the grapes crop from such diseases, time-to-time monitoring is required. Moreover, some remedies actions can be used at early stages for disease detection. Hence, it is a challenging task to detect grape leaf diseases in their early stages. In this article, deep Convolutional Neural Networks (CNNs) are used to identify different types of diseases in grape crops. Thereafter, a Gaussian noise features are included during the training, by which an improvement in the training accuracy has been observed. Therefore, an attempt is made to remove overfitting from deep learning model for detecting different grape diseases. Moreover, for training the proposed model, a publicly online available dataset i.e., PlantVillage has been utilized. This dataset is also used for transfer learning or pre-trained CNN models i.e., VGG16, ResNet50, InceptionV3, and DenseNet121. Thereafter, the proposed model results are compared with other transfer learning models. Eventually, the proposed model achieved an accuracy rate of 99.88%, higher than other transfer learning models. This study concludes that adding the Gaussian noise feature during model training contributes in increasing the accuracy of the deep learning model. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Plant diseases are a huge hazard to the world’s food supply. Farms are frequently exposed to pest and disease outbreaks. Tomatoes are the second-largest vegetable crop grown worldwide. Early identification of plant blight helps farmers to take proper care of tomato plants hence they can secure their agricultural income. Farmers need a quick, consistent, and reliable method to identify plant diseases early. So, we have prepared a React Native Mobile application through which farmers can take a picture of their tomato crop leaf, and our CNN model predicts the type of blight leaf has, if any, or shows it is healthy. CNN deep learning models are widely used for image classification. Lightweight Pre-trained models are readily available and are trained on ImageNet data. We have prepared different models with pre-trained models using transfer learning and fine-tuning techniques. We have selected MobileNetV2, NASNetMobile, and EfficientNetV2B0 pre-trained models for the study as these are lightweight models and which was the basic requirement as we have built the mobile application. We have compared the performance of the models for different learning rates, batch size, and dropout with different metrics such as accuracy, loss, precision, recall, f1-score, and AUC for the 100 epochs. The best classification performance is shown by the model using EfficientNetV2B0 with a training accuracy of 99.95%, validation accuracy of 98.12%, and testing accuracy of 97.58% and the size of the model is 30.6 MB which is easily deployable for the mobile application.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10.1109/ICAICCIT64383.2024.10912316</t>
+          <t>10.1109/ICCST55948.2022.10040394</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Plant Disease Detection using Machine Learning</t>
+          <t>Hybrid Model of K-Means Clustering and SVM to Detect Ailments in Vegetables</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>A., Batra, Ashmit; P.S., Kang, Prabaldeep Singh; S., Setia, Sambhav; Aparna; Menka; V., Dagar, Vivek; A., Sharma, Anshu; K., Kumar, Kapila</t>
+          <t>J. J. Amarnath; V. V; S. M. D</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>2022 1st International Conference on Computational Science and Technology (ICCST)</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3637583255767822</v>
+        <v>0.4390957653522491</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>This research explores the use of machine learning approaches for accurate identification and detection of major diseases in pulse crops, targeting improvements in early diagnosis and management of infections such as downy mildew, Ascochyta blight, rust, powdery mildew, and anthracnose. These diseases trigger diverse signalling pathways. Specific genes and proteins, are upregulated in response to pathogen invasion, enabling plants to mount targeted defence responses. Understanding these mechanisms highlights opportunities for enhancing disease resistance through breeding and genetic research in legume crops. This paper outlines a procedure for identification of diseases in pulse crops using modern image processing technologies and machine learning techniques. The objective is to build a system that can recognize the common ailments of pulses which would otherwise lead to a huge loss in case of the weeds not being controlled. The system uses a data set of diseased and healthy plants and applies CNN's to classify and predict disease. The findings achieved very encouraging Level of accuracy thus suggesting further work could extend to practical use by farmers in assessing the health of the crops more conveniently. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>Agriculture is the backbone of Indian Economy, which is true because 70% of India's population are engaged in agriculture and raw material for industrial sectors like food processing. As the population increased, the demand for food also increased. However, disease infection of agricultural goods such as vegetables leads in a decrease in both quality and quantity. Farmers' livelihoods and public health are directly impacted as a result of this. Because of this, early diagnosis of illnesses in vegetable crops reduces the loss of productivity and product quality. Viral and microbial infections as well as environmental stressors are the primary causes of most vegetable-related disorders. Image processing techniques such as K-means clustering and Support Vector Machines (SVM) will be used to identify and diagnose vegetable illnesses, according to the suggested model (SVM). For categorization, it uses supervised leaning. In this paradigm, there are many steps involved in acquiring and processing images, including image segmentation, feature extraction, classification, and illness classification. Alerts are sent via a buzzer if a sickness has been detected. Farmers would have been able to avoid the problem if they had been alerted early. In other words, if breakouts are caught early and dealt with quickly, the farmer stands to lose very little money.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10.1371/journal.pcbi.1011651</t>
+          <t>10.1109/ICEARS64219.2025.10940749</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>A computational model of Pseudomonas syringae metabolism unveils a role for branched-chain amino acids in Arabidopsis leaf colonization</t>
+          <t>Artificial Intelligence-Powered Internet of Things for Farming and Plant Research</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>P.J., Tubergen, Philip J.; G.L., Medlock, Gregory L.; A.K., Moore, Anni K.; X., Zhang, Xiaomu; J.A., Papin, Jason A.; C.H., Danna, Cristian H.</t>
+          <t>Padma, A.; Suresh, P.; Narsimlu, G.; Amarnath, M.; Sreedhar, B.R.</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PLOS Computational Biology</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G71" t="n">
-        <v>0.8396974802017212</v>
+        <v>0.9912109375</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Bacterial pathogens adapt their metabolism to the plant environment to successfully colonize their hosts. In our efforts to uncover the metabolic pathways that contribute to the colonization of Arabidopsis thaliana leaves by Pseudomonas syringae pv tomato DC3000 (Pst DC3000), we created iPst19, an ensemble of 100 genome-scale network reconstructions of Pst DC3000 metabolism. We developed a novel approach for gene essentiality screens, leveraging the predictive power of iPst19 to identify core and ancillary condition-specific essential genes. Constraining the metabolic flux of iPst19 with Pst DC3000 gene expression data obtained from naïve-infected or pre-immunized-infected plants, revealed changes in bacterial metabolism imposed by plant immunity. Machine learning analysis revealed that among other amino acids, branched-chain amino acids (BCAAs) metabolism significantly contributed to the overall metabolic status of each gene-expression-contextualized iPst19 simulation. These predictions were tested and confirmed experimentally. Pst DC3000 growth and gene expression analysis showed that BCAAs suppress virulence gene expression in vitro without affecting bacterial growth. In planta, however, an excess of BCAAs suppress the expression of virulence genes at the early stages of infection and significantly impair the colonization of Arabidopsis leaves. Our findings suggesting that BCAAs catabolism is necessary to express virulence and colonize the host. Overall, this study provides valuable insights into how plant immunity impacts Pst DC3000 metabolism, and how bacterial metabolism impacts the expression of virulence. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>The wearable fiber optic sensors for plants to monitor microenvironment and growth wearable fiber optic plant sensors for microclimate and growth monitoring. The plant agricultural sectors are facing challenges because to population expansion and climate change.AI-powered computer vision-based plant growth monitoring system the goal of this research project is to use computer vision to create an AI-based plant growth monitoring system. The technology will allow for automatic and real-time evaluation of plant growth and health by utilizing computer vision algorithms and artificial intelligence approaches. Conventional techniques for tracking plant growth require a lot of work and time. By employing image processing techniques to analyze plant photos and extract pertinent features leaf area, plant height, and width, the suggested solution will overcome these drawbacks. Using the collected information, machine learning methods will be used to train models that can identify patterns and forecast plant development. The system will be made to adapt to various plant species and environmental circumstances. This AI-based plant growth monitoring system will help farmers, researchers, and plant enthusiasts by offering precise and timely insights into plant health and growth. This will allow them to make well-informed decisions about plant care and optimize growth conditions. By providing an economical, scalable, and effective system with numerous applications in horticulture, agriculture, and environmental research, this research project seeks to transform plant growth monitoring. © 2025 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10.1016/j.geodrs.2023.e00731</t>
+          <t>10.1109/ICISC65841.2025.11188291</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Predictive geochemical mapping using machine learning in western Kenya</t>
+          <t>Classification and Detection of Apple Leaf Disease Using DenseNet201 and YOLOV8</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>O.S., Humphrey, Olivier S.; M.R., Cave, Mark R.; E.M., Hamilton, Elliott M.; O., Osano, Odipo; D.M., Menya, Diana M.; M.J., Watts, Michael J.</t>
+          <t>V. Parisae; D. Yushmanth; N. M. Sree; G. Manyasri; C. Jannu; G. S. S. Rao</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Geoderma Regional</t>
+          <t>2025 9th International Conference on Inventive Systems and Control (ICISC)</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G72" t="n">
-        <v>0.6541068553924561</v>
+        <v>0.3675290048122406</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Digital soil mapping techniques represent a cost-effective method for obtaining detailed information regarding the spatial distribution of chemical elements in soils. Machine learning (ML) algorithms using random forest (RF) models have been developed for classification, pattern recognition and regression tasks, they are capable of modelling non-linear relationships using a range of datasets, identifying hierarchical relationships, and determining the importance of predictor variables. In this study, we describe a framework for spatial prediction based on RF modelling where inverse distance weighted (IDW) predictors are used in conjunction with ancillary environmental covariates. The model was applied to predict the total concentration (mg kg−1) and assess the prediction uncertainty of 56 elements, soil pH and organic matter content using 466 soil samples in western Kenya; the results of iodine (I), selenium (Se), zinc (Zn) and soil pH are highlighted in this work. These elements were selected due to contrasting biogeochemical cycles and widespread dietary deficiencies in sub-Saharan Africa, whilst soil pH is an important parameter controlling soil chemical reactions. Algorithm performance was evaluated determining the relative importance of each predictor variable and the model's response using partial dependence profiles. The accuracy and precision of each RF model were assessed by evaluating out-of-bag predicted values. The models R2 values range from 0.31 to 0.64 whilst CCC values range from 0.51 to 0.77. The IDW predictor variables had the greatest impact on assessing the distribution of soil properties in the study area, however, the inclusion of ancillary environmental data improved model performance for all soil properties. The results presented in this paper highlight the benefits of ML algorithms which can incorporate multiple layers of data for spatial prediction, uncertainty assessment and attributing variable importance. Additional research is now required to ensure health practitioners and the agri-community utilise the geochemical maps presented here for assessing the relationship between environmental geochemistry, endemic diseases and preventable micronutrient deficiency. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>Globally, plant diseases severely reduce crop output, consequently affecting agricultural productivity. Lots of specialist expertise makes it tough to detect those issues. The usage of leaf pictures, deep learning-primarily based models present interesting answers; despite the fact that, problems including the call for more extensive training sets and computational complexity remain unresolved. We propose a convolutional neural network (CNN) with much less layers to address this, consequently lowering computational load. The training set is expanded using augmentation methods along with shift, shear, scaling, zoom, and flipping without gathering fresh snap shots. Since about half of the world's populace relies upon on agriculture, raising production by way of 50–60 % is absolutely crucial, mainly in areas experiencing fast population growth. Apple crop output in India suffers no matter an increasing location of cultivation yield has hardly ever modified. A chief apple-producing state, Himachal Pradesh, suffers significantly in fruit quality from fungal infections. Our work tackles those issues via the use of YOLO series models for effective disease detection in apples and deep learning models together with pre-trained ones to handle timeliness and accuracy of disease diagnosis is guaranteed through using picture processing and artificial intelligence. This era should rework apple plant disease detection, consequently improving food security all round. Brief intervention facilitates farmers protect their plants and guarantee higher yields, there-fore contributing to the general meals security for the rising world population.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10.1016/j.envres.2023.116753</t>
+          <t>10.1109/ICAECT60202.2024.10468676</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Proximal sensing provides clean, fast, and accurate quality control of organic and mineral fertilizers</t>
+          <t>Deep Insights into Mango Scab: An AI-Powered Approach for Detection and Classification</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>R., Andrade, Renata; S.H.G., Silva, Sérgio Henrique Godinho; L., Benedet, Lucas; M., Mancini, Marcelo; G.J.E.O.O., Lima, Geraldo Jânio Eugênio O.Oliveira; K., Nascimento, Kauan; F.H.C., Amaral, Francisco Hélcio Canuto; D.R., Guelfi, Douglas Ramos; M.V., Ottoni, Marta Vasconcelos; M.A.C., Carneiro, Marco Aurélio Carbone</t>
+          <t>Kaur, A.; Kukreja, V.; Rana, D.S.; Garg, A.; Sharma, R.</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Environmental Research</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.9010332226753235</v>
+        <v>0.992514431476593</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Farms use large quantities of fertilizers from many sources, making quality control a challenging task, as the traditional wet-chemistry analyses are expensive, time consuming and not environmentally-friendly. As an alternative, this work proposes the use of portable X-ray fluorescence (pXRF) spectrometry and machine learning algorithms for rapid and low-cost estimation of macro and micronutrient contents in mineral and organic fertilizers. Four machine learning algorithms were tested. Whole (i.e., as delivered by the manufacturer) (CP) and ground (AQ) samples (429 in total) were analyzed to test the effect of fertilizer granulometry in prediction performance. Model validation indicated highly accurate predictions of macro (N: R2 = 0.92; P: 0.97; K: 0.99; Ca: 0.94, Mg: 0.98; S: 0.96) and micronutrients (B: 0.99; Cu: 0.99; Fe: 0.98; Mn: 0.91; Zn: 0.94) for both organic and mineral fertilizers. RPD values ranged from 2.31 to 9.23 for AQ samples, and Random Forest and Cubist Regression were the algorithms with the best performances. Even samples analyzed as they were received from the manufacturer (i.e., no grinding) provided accurate predictions, which accelerate the confirmation of nutrient contents contained in fertilizers. Results demonstrated the potential of pXRF data coupled with machine learning algorithms to assess nutrient composition in both mineral and organic fertilizers with high accuracy, allowing for clean, fast and accurate quality control. Sensor-driven quality assessment of fertilizers improves soil and plant health, crop management efficiency and food security with a reduced environmental footprint. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>The mango, which comes from the plant genus Mangifera indica L., is a fruit crop that is well-regarded all over the world due to its scrumptious flavor and noteworthy nutritional profile. The illness known as mango scab, which is brought on by the fungus Elsinoe mangiferae, is a serious obstacle for the mango business. This disease causes the mango fruit to develop scaly lesions, which in turn results in decreased market value and yield losses. To effectively manage a disease, timely discovery and correct assessment of the severity of the condition are both essential. This study provides a hybrid deep learning (DL) model that combines a Convolutional Neural Network (CNN) for the detection of disease with a Support Vector Machine (SVM) for the categorization of the severity of the disease. The model was trained and tested using a broad dataset of mango photos that included a range of disease severity levels as well as different varieties of mango. The model's performance in illness detection resulted in an overall accuracy of 95.93%, with scores of best precisions of 97.17% and best recall of 96.28%, respectively. When it came to the classification of severity, the SVM classifier was able to achieve an accuracy of 95.93%. These findings provide evidence that the model is capable of precisely identifying the degree of mango scab illness and demonstrating its usefulness in detecting the condition. To provide mango farmers with a flexible instrument, the hybrid method makes use of the capability of CNNs to extract features as well as the SVM's skill in classifying data. This research provides growers with up-to-date information that enables targeted disease management. As a result, mango crop yields are increased, and economic losses are decreased. © 2024 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10.1016/j.fochx.2023.100851</t>
+          <t>10.1109/SMARTGENCON60755.2023.10442719</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>An early asymptomatic diagnosis method for cork spot disorder in ‘Akizuki’ pear (Pyrus pyrifolia Nakai) using micro near infrared spectroscopy</t>
+          <t>Advancing Pear Disease Recognition: A Hybrid CNN-Random Forest Approach</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>L., Liu, Li; H., Zhang, Hanhan; L., Wu, Lin; S., Gu, Shangfeng; J., Xu, Jing; B., Jia, Bing; Z., Ye, Zhengfeng; W., Heng, Wei; X., Jin, Xiu</t>
+          <t>Yashu, n.; Kukreja, V.; Madan, K.; Singh, A.; Kumar, D.</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3448,163 +3464,163 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Food Chemistry: X</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>0.9882709383964539</v>
+        <v>0.2611232101917267</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 6: gardening, management, specie</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>The early symptoms of cork spot disorder in 'Akizuki' pear (Pyrus pyrifolia Nakai) are challenging to distinguish from those in healthy fruits, hindering early identification in production. In this study, samples of cork-browned 'Akizuki' pears, asymptomatic fruits and healthy fruits were examined to determine the content of relevant mineral elements. A micro near-infrared spectrometer collected spectral information, and various pretreatment methods were applied to the near-infrared spectral data. Support vector machine (SVM) modelling using the original data achieved the highest overall recognition accuracy of 84.65% and an F1 value of 84.06%. For identifying fruits without cork spot disease, Autokeras modelled data processed with the SG method, achieving the best accuracy of 90%. These findings establish a reliable basis for the early identification and diagnosis of cork spot disorder in 'Akizuki' pear, enhancing pear production management. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>The pear is a key fruit in the horticultural sector, renowned for its adaptability and nutritional value. In recent years, the effects of climate change have increased dramatically. It is influencing all stages of plant production and compelling farmers to adopt new technologies based on data analytics to modify and adapt their crop management practices. Every year, plant diseases are proven to cause significant economic losses. This study introduces a novel method for automating the recognition of pear disease using a synergistic combination of Convolutional Neural Networks (CNN) and Random Forest. A meticulously collected and annotated dataset containing 3,150 high-resolution images of pear leaves in various disease states was compiled. The proposed system's exceptional accuracy of 77.2% signifies a significant advance in agricultural technology. The CNN module is optimised for robust feature extraction, which enables the model to recognise intricate patterns and textures that are characteristic of various pear diseases. Utilising the collective intelligence of a collection of decision trees, a Random Forest classifier is used to refine classification. This study demonstrates the potential of deep learning-based models in the detection and handling of pear disease, which can result in substantial enhancements to pear production and food security. © 2023 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10.1007/s00521-023-08943-w</t>
+          <t>10.1109/ICITEICS61368.2024.10625429</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A deep feature fusion network using residual channel shuffled attention for cassava leaf disease detection</t>
+          <t>Fruitful Fusion: CNN-Random Forest Synergy in Banana Ripeness Detection</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>R., Karthik, R.; R., Menaka, R.; M.V., Siddharth, M. V.; S., Hussain, Sameeha; M.S., Balamurugan, M. S.; D., Won, Daehan</t>
+          <t>Yashu; V. Kukreja; P. Srivastava; A. Garg</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Neural Computing and Applications</t>
+          <t>2024 IEEE International Conference on Information Technology, Electronics and Intelligent Communication Systems (ICITEICS)</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.3946555554866791</v>
+        <v>0.3800880014896393</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Cassava is a significant source of carbohydrates for tropical populations. However, diseases caused by agents such as bacteria, viruses, fungi, and phytoplasmas cause considerable economic damage to these crops. Existing methods for cassava disease detection require farmers to seek the assistance of agricultural experts for visual inspection and diagnosis, which is challenging and laborious. Most studies have employed pre-trained convolutional neural networks to detect diseases in cassava leaves. Also, it is essential to design customized deep neural networks specific to the target domain for precise classification. This research proposes a novel deep fusion of two networks, residual channel shuffled attention network and Efficientnet. The first network, RCSANet, was presented to capture contextual information using depthwise separable convolution effectively. It also integrates significant inter-spatial and inter-channel information using the triplet attention module and employs shuffled group convolution to capture features from distinct filter groups. As a result of incorporating the above architectural enhancements, the proposed feature fusion network exhibited better performance than the existing studies. The proposed network was trained on the Kaggle cassava leaf disease dataset with 21,367 samples and yielded a classification accuracy of 93.25%. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>This research paper introduces a new methodology for detecting the maturity of bananas by combining Convolutional Neural Networks (CNN) with Random Forest. The objective is to tackle the pressing need for automated evaluation of fruit quality in the field of agriculture. The experimental configuration included the use of Windows 11 as the operating system, an i5 processor as the central processing unit, and the Colab platform, which together facilitated efficient testing. The model had a notable overall accuracy rate of 86.97%, indicating its strong categorization skills. Additionally, the F1 score, which is calculated as the harmonic mean of accuracy and recall, exhibited an average value of 87.00, therefore emphasising the model's well-balanced performance. The precision scores showed a range of 81.97% to 91.37%, which signifies the level of accuracy in positive forecasts across various ripeness categories. The use of a hybrid strategy efficiently leveraged the feature extraction capabilities of Convolutional Neural Networks (CNN) and the ensemble learning technique of Random Forest to achieve accurate and dependable classification. The findings indicate a significant development in the precise identification of fruit maturity, showcasing potential implications in enhancing harvest procedures and reducing post-harvest wastage. This research establishes a foundation for the development of enhanced and automated techniques for evaluating the quality of fruits, hence offering potential advantages to the agriculture sector.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10.1007/s10705-023-10303-y</t>
+          <t>10.1109/ICISAA62385.2024.10828973</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Spatial prediction of soil micronutrients using machine learning algorithms integrated with multiple digital covariates</t>
+          <t>Roses Plant Disease Detection using DenseNet121 Model</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>A., Keshavarzi, Ali; F., Kaya, Fuat; L., Başayiǧit, Levent; Y., Gyasi-Agyei, Yeboah; J., Rodrigo-Comino, Jesús; A., Caballero-Calvo, Andrés</t>
+          <t>L. R. Chaudhari; A. V. Tidke; P. S. Gupta; P. Patel; S. Hudnurkar</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nutrient Cycling in Agroecosystems</t>
+          <t>2024 International Conference on Intelligent Systems and Advanced Applications (ICISAA)</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>0.925505518913269</v>
+        <v>0.8185207843780518</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 2: approach, data, grape</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>The design and application of multiple tools to map soil micronutrients is key to efficient land management. While collecting a representative number of soil samples is time consuming and expensive, digital soil mapping could provide maps of soil properties fast and reliably. The objective of this research was to predict the spatial distribution of soil micronutrients within the piedmont plain in northeastern Iran using random forest (RF) and support vector regression (SVR) algorithms. Sixty-eight locations with different land uses were sampled to determine the content of iron, manganese, zinc and copper in the topsoil (0–20 cm). Forty-one digital covariates were used as input to the models and were derived from a digital elevation model, open-source remote sensing (RS) data (Landsat 8 OLI and Sentinel 2A MSI images), WorldClim climate database and maps of soil properties. Covariates were grouped into 11 scenarios: I–III, based on RS data; IV–VI, including RS, topographic, climate and soil covariates; VII, VIII and IX, based only on topographic, climate and soil covariates, respectively; X and XI, based on recursive feature elimination and expert opinion, respectively. The RF algorithm gave 91, 94, 91 and 108% normalized root mean squared error values for iron, manganese, zinc and copper, respectively, for the validation dataset with scenario XI. The most important digital covariates for micronutrients prediction with both RF and SVR models were precipitation seasonality, mean annual temperature and the mean saturation index based on Sentinel 2A MSI data. Digital maps produced at 30 m spatial resolution using scenario XI could be used to effectively identify micronutrient deficiencies and excess hotspots. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>Roses diseases pose a significant threat to horticultural productivity, necessitating early detection and intervention for effective management. This research proposes the development of a web-based application leveraging Deep Learning (DL) methodologies to facilitate rapid and accurate disease identification in roses. The application will employ a pre-trained Convolutional Neural Network (CNN) model, DenseNet121, fine-tuned on a curated dataset of rose disease images through transfer learning. Users will be able to upload images of their plants via the web interface, which will then be analyzed by the DenseNet121 model to identify potential diseases. This DL-powered tool aims to empower gardeners and horticulturists with a user-friendly platform for early disease detection and proactive management, ultimately contributing to healthier rose cultivation practices. The research will investigate the effectiveness of DenseNet121 for detecting rose diseases, assess the accuracy of the web application across various disease types, and explore the practical implications of integrating such a tool into real-world horticultural settings.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10.1007/s10142-023-01172-3</t>
+          <t>10.1109/IGARSS39084.2020.9323679</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Structural diversity and stress regulation of the plant immunity-associated CALMODULIN-BINDING PROTEIN 60 (CBP60) family of transcription factors in Solanum lycopersicum (tomato)</t>
+          <t>Modeling Early Indicators of Grapevine Physiology Using Hyperspectral Imaging and Partial Least Squares Regression (PLSR)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>V., Shivnauth, Vanessa; S., Pretheepkumar, Sonya; E.J.R., Marchetta, Eric J.R.; C.A.M., Rossi, Christina A.M.; K., Amani, Keaun; C.D.M., Castroverde, Christian Danve M.</t>
+          <t>M. Maimaitiyiming; M. Maimaitijiang; P. Sidike; V. Sagan; Z. Migicovsky; D. H. Chitwood; P. Cousins; N. Dokoozlian; A. J. Miller; M. Kwasniewski</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Functional and Integrative Genomics</t>
+          <t>IGARSS 2020 - 2020 IEEE International Geoscience and Remote Sensing Symposium</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>2</v>
       </c>
       <c r="G77" t="n">
-        <v>0.7359481453895569</v>
+        <v>0.9854222536087036</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Cellular signaling generates calcium (Ca2+) ions, which are ubiquitous secondary messengers decoded by calcium-dependent protein kinases, calcineurins, calreticulin, calmodulins (CAMs), and CAM-binding proteins. Previous studies in the model plant Arabidopsis thaliana have shown the critical roles of the CAM-BINDING PROTEIN 60 (CBP60) protein family in plant growth, stress responses, and immunity. Certain CBP60 factors can regulate plant immune responses, like pattern-triggered immunity, effector-triggered immunity, and synthesis of major plant immune-activating metabolites salicylic acid (SA) and N-hydroxypipecolic acid (NHP). Although homologous CBP60 sequences have been identified in the plant kingdom, their function and regulation in most species remain unclear. In this paper, we specifically characterized 11 members of the CBP60 family in the agriculturally important crop tomato (Solanum lycopersicum). Protein sequence analyses revealed that three CBP60 homologs have the closest amino acid identity to Arabidopsis CBP60g and SARD1, master transcription factors involved in plant immunity. Strikingly, AlphaFold deep learning–assisted prediction of protein structures highlighted close structural similarity between these tomato and Arabidopsis CBP60 homologs. Conserved domain analyses revealed that they possess CAM-binding domains and DNA-binding domains, reflecting their potential involvement in linking Ca2+ signaling and transcriptional regulation in tomato plants. In terms of their gene expression profiles under biotic (Pseudomonas syringae pv. tomato DC3000 pathogen infection) and/or abiotic stress (warming temperatures), five tomato CBP60 genes were pathogen-responsive and temperature-sensitive, reminiscent of Arabidopsis CBP60g and SARD1. Overall, we present a genome-wide identification of the CBP60 gene/protein family in tomato plants, and we provide evidence on their regulation and potential function as Ca2+-sensing transcriptional regulators. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>In this contribution, we use field-based hyperspectral imaging (HSI) and partial least squares regression (PLSR) to estimate early indicators of grapevine physiological indicators, and analyze identified significant spectral regions for fast and accurate plant health monitoring. HSI and physiological measurements were carried out at two commercial vineyards in California, USA. The PLSR models were developed between reflectance spectra extracted from hyperspectral images and four vine physiological parameters, including stomatal conductance (Gs) photosynthetic CO2 rate (A), intercellular CO2 concentration (Ci) and transpiration rate (E). The results demonstrate PLSR models to predict physiological parameters ( R2 ≥ 0.6), and the best model was found for Gs (R2=0.7). The identified significant spectral regions overlap with most commonly used remote sensing stress indicator, suggesting that HSI coupled with PLSR has great potential for upscaling and broader agricultural applications.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10.1016/j.seta.2023.103355</t>
+          <t>10.1109/AIC57670.2023.10263945</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Duck optimization with enhanced capsule network based citrus disease detection for sustainable crop management</t>
+          <t>An Overall Disease Analysis of Mango Using Neural Network with Hybrid Feature model</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>A., Arthi, A.; N., Sharmili, N.; S.A., Althubiti, Sara A.; E., Laxmi Lydia, E.; M.G., Alharbi, Meshal Ghalib; A.H.R., Alkhayyat, Ahmed Hussein R.; D.K., Gupta, Deepak Kumar</t>
+          <t>J. Kaur; A. K. Sharma; M. Kaushal; A. Badhoutiya; N. Reddy; A. Alkhayyat</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3612,245 +3628,245 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sustainable Energy Technologies and Assessments</t>
+          <t>2023 IEEE World Conference on Applied Intelligence and Computing (AIC)</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.9295258522033691</v>
+        <v>0.8519370555877686</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tópico 2: tomato, fruit, grape</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Sustainable agriculture methodology seeks to apply natural resources whereby they could reconstruct their productive capacity and minimise adverse effects on the ecosystem beyond a field edge. In agriculture, plant diseases are mainly responsible for production degradation, which causes economic loss. In plants, citrus is widely utilized as a critical resource of nutrients such as vitamin C. But Citrus disease negatively impacts the quality and production of citrus fruits. Over the last few years, image processing and computer vision technologies have been extensively applied to detect and classify diseases in plants. Mostly, plant disease has clear signs, and today's recognized model is for an expert plant diagnostician to recognize the disease by observing a diseased plant leaf through a microscope. Manual disease detection can be labour-intensive and the efficiency of the diagnoses is associated with the pathologist's skills, which makes this a greater application field for computer-aided diagnosis systems. This work develops an effectual Duck Optimization with Enhanced Capsule Network Based Citrus Disease Detection for Sustainable Crop Management (DOECN-CDDCM) technique. The presented technique majorly focuses on the detection and classification of citrus diseases. In the presented approach, several stages of preprocessing are performed. In addition, the duck optimization algorithm (DOA) with the Enhanced Capsule Network (ECN) model is exploited as a feature extractor, and the optimal hyperparameter tuning process helps obtain enhanced performance. Finally, the deep stacked sparse autoencoder (DSSAE) model is utilized for citrus disease detection and classification. A series of simulations were performed to ensure the enhanced disease detection performance of the DOECN-CDDCM algorithm. The simulation results demonstrate the improvised outcomes of the DOECN-CDDCM algorithm than other current techniques. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>Mango is a highly valued fruit crop, with arable land covering about 36% of the total fruit area. With roughly 23% of the total area under mango, Uttar Pradesh and Andhra Pradesh lead the way, followed by Tamil Nadu, Karnataka, Gujarat, and Bihar. Global food security is affected a lot due to crop plant diseases. These diseases directly affect the quality of food, fruits, etc., resulting in a fall in agricultural productivity. Farmers must assess the leaf, fruit, or tree through visual interpretation to determine whether any fruit crop part is contaminated or blooming properly. But this traditional technique has its limitations; it is inconsistent, unreliable, and prone to mistakes. Researchers have proposed a variety of techniques for resolving the above-stated issues. Most of them preferred the modelling of convolutional neural network models according to problem areas by giving low-resolution images as input, resulting in low disease detection accuracy. In this work, we use an artificial neural network (ANN) technique with the objective of early detection of disease in any part of the fruit crop with tiny disease blobs that can only be seen with better resolution images. All the contaminated blobs are segmented for the entire dataset after a pre-processing phase using a contrast enhancement approach.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10.1094/MPMI-11-22-0236-TA</t>
+          <t>10.1109/CIS-RAM47153.2019.9095778</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EffectorO: Motif-Independent Prediction of Effectors in Oomycete Genomes Using Machine Learning and Lineage Specificity</t>
+          <t>Tomato Fruit Image Dataset for Deep Transfer Learning-based Defect Detection</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>M., Nur, Munir; K.J., Wood, Kelsey J.; R.W., Michelmore, Richard W.</t>
+          <t>R. G. de Luna; E. P. Dadios; A. A. Bandala; R. R. P. Vicerra</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Molecular Plant-Microbe Interactions</t>
+          <t>2019 IEEE International Conference on Cybernetics and Intelligent Systems (CIS) and IEEE Conference on Robotics, Automation and Mechatronics (RAM)</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G79" t="n">
-        <v>0.6701561808586121</v>
+        <v>0.4662255644798279</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Oomycete plant pathogens cause a wide variety of diseases, including late blight of potato, sudden oak death, and downy mildews of plants. These pathogens are major contributors to loss in numerous food crops. Oomycetes secrete effector proteins tomanipulate their hosts to the advantage of the pathogen. Plants have evolved to recognize effectors, resulting in an evolutionary cycle of defense and counter-defense in plant-microbe interactions. This selective pressure results in highly diverse effector sequences that can be difficult to computationally identify using only sequence similarity. We developed a novel effector prediction tool, EffectorO, that uses two complementary approaches to predict effectors in oomycete pathogen genomes: i) amachine learning-based pipeline that predicts effector probability based on the biochemical properties of the N-Terminal amino-Acid sequence of a protein and ii) a pipeline based on lineage specificity to find proteins that are unique to one species or genus, a sign of evolutionary divergence due to adaptation to the host.We tested EffectorO on Bremia lactucae, which causes lettuce downymildew, and Phytophthora infestans,which causes late blight of potato and tomato, and predicted many novel effector candidates while recovering the majority of known effector candidates. EffectorO will be useful for discovering novel families of oomycete effectors without relying on sequence similarity to known effectors. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>Tomato is considered as one of the vegetable crops with highest demand in the Philippines. Job of the farmers does not end after harvesting since the harvested tomatoes needed to be sorted according to its size. Manual sorting is the most widely recognized strategy in sorting but is very dependent on human interpretation and thus, very prone to error. This research proposed a solution that provides sorting of tomato fruit by detection of presence of defect. The study presented the generation of image dataset for a deep learning approach detection of defects based from a single tomato fruit image. Models were implemented using OpenCV libraries and Python programming. A total of 1200 tomato images classified as no defect and with defect are gathered using the improvised image capturing box. These images are used for the training, validation, and testing of the three deep learning models namely; VGG16, InceptionV3, and ResNet50. From this, 240 images are used as testing images to assess independently the performance of the trained models using accuracy and F1-score as performance metrics. Experiment results shown that VGG16 has 95.75-95.92-98.75 training-validation-testing accuracy percentage performance, 56.38-59.24-58.33 for the InceptionV3 model, and 90.58-58.46-64.58 for the ResNet50. Comparative analysis revealed that VGG16 is the best deep learning model to be used in the detection of presence of defect in the tomato fruit based from the dataset gathered.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10.1016/j.scitotenv.2022.160545</t>
+          <t>10.1109/ISCON47742.2019.9036158</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Fast detection of minerals in rice leaves under chromium stress based on laser-induced breakdown spectroscopy</t>
+          <t>A Data Repository of Leaf Images: Practice towards Plant Conservation with Plant Pathology</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>J., Peng, Jiyu; Y., Liu, Yifan; L., Ye, Longfei; J., Jiang, Jiandong; F., Zhou, Fei; F., Liu, Fei; J., Huang, Jing</t>
+          <t>S. S. Chouhan; U. P. Singh; A. Kaul; S. Jain</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Science of the Total Environment</t>
+          <t>2019 4th International Conference on Information Systems and Computer Networks (ISCON)</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G80" t="n">
-        <v>0.649029552936554</v>
+        <v>0.4101784825325012</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Minerals in rice leaves is a crucial indicator of plant health, and their concentrations can be used to guide plant management. It is important to predict mineral content in contaminated rice rapidly. In this study, laser-induced breakdown spectroscopy (LIBS) was applied to quantify minerals (Ca, Cu, Fe, K, Mg, Mn, and Na) in rice leaves under chromium (Cr) stress. Two feature extraction methods, including principal component analysis (PCA) and extreme gradient boosting (XGBoost), were compared to identify important variables that related to mineral concentrations. Results showed that partial least square regression (PLSR) achieved good performance in Ca, Fe Mg, K, Mn, and Na, with correlation coefficient of 0.9782, 0.8712, 0.8933, 0.9206, 0.9856, and 0.9865, root mean square error of 219.25, 14.78, 1192.47, 385.12, 9.56, and 124.32 mg/kg, respectively. In addition, the correlation between different spectral lines were further analyzed. Cr exhibited a positive correlation with Ca, Mg, and Na, and a negative correlation with Mn, Cu, and K. The proposed method provides a high-accuracy and fast approach for minerals prediction in rice leaves under Cr stress, which is important for environmental protection and food safety. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>The relationship between the plants and the environment is multitudinous and complex. They help in nourishing the atmosphere with diverse elements. Plants are also a substantial element in regulating carbon emission and climate change. But in the past, we have destroyed them without hesitation. For the reason that not only we have lost a number of species located in them, but also a severe result has also been encountered in the form of climate change. However, if we choose to give them time and space, plants have an astonishing ability to recover and re-cloth the earth with varied plants and species that we have, so recently, stormed. Therefore, a contribution has been made in this article towards the study of plant growth and its management. Twelve economically and environmentally beneficial plants have been selected for this purpose. Leaf images of these plants in healthy and unhealthy conditions have been acquired and alienated among two separate classes. We have collected about 4503 images of which contain 2278 images of healthy leaf and 2225 images of the diseased leaf. Further, we hope that this study can be beneficial for researchers and academicians in developing methods for plant identification, plant classification, plant growth monitoring, leaf disease diagnosis, etc. Finally, the anticipated impression is towards a better understanding of the plants to be planted and their appropriate management.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10.3390/bios13020278</t>
+          <t>10.1109/InCACCT61598.2024.10551189</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Detection of Rice Fungal Spores Based on Micro- Hyperspectral and Microfluidic Techniques</t>
+          <t>Feature Fusion Approach with Inception-RestNet and Canonical Correlation Analysis for Strawberry Leaf Disease Detection</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>X., Zhang, Xiaodong; H., Song, Houjian; Y., Wang, Yafei; L., Hu, Lian; P., Wang, Pei; H., Mao, Hanping</t>
+          <t>Gautam, V.; Maheshwari, H.; Tiwari, R.G.; Agarwal, A.K.; Kumar Trivedi, N.K.; Garg, N.</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Biosensors</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G81" t="n">
-        <v>0.4267955720424652</v>
+        <v>0.2805809378623962</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>As rice is one of the world’s most important food crops, protecting it from fungal diseases is very important for agricultural production. At present, it is difficult to diagnose rice fungal diseases at an early stage using relevant technologies, and there are a lack of rapid detection methods. This study proposes a microfluidic chip-based method combined with microscopic hyperspectral detection of rice fungal disease spores. First, a microfluidic chip with a dual inlet and three-stage structure was designed to separate and enrich Magnaporthe grisea spores and Ustilaginoidea virens spores in air. Then, the microscopic hyperspectral instrument was used to collect the hyperspectral data of the fungal disease spores in the enrichment area, and the competitive adaptive reweighting algorithm (CARS) was used to screen the characteristic bands of the spectral data collected from the spores of the two fungal diseases. Finally, the support vector machine (SVM) and convolutional neural network (CNN) were used to build the full-band classification model and the CARS filtered characteristic wavelength classification model, respectively. The results showed that the actual enrichment efficiency of the microfluidic chip designed in this study on Magnaporthe grisea spores and Ustilaginoidea virens spores was 82.67% and 80.70%, respectively. In the established model, the CARS-CNN classification model is the best for the classification of Magnaporthe grisea spores and Ustilaginoidea virens spores, and its F1-core index can reach 0.960 and 0.949, respectively. This study can effectively isolate and enrich Magnaporthe grisea spores and Ustilaginoidea virens spores, providing new methods and ideas for early detection of rice fungal disease spores. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>Strawberries are one of the most demanding horticulture crops due to their flavor and nutritional value. Therefore, the demand for strawberries growing yearly and production of the same is very low. The prime factor of low production is leaf disease because the crop is susceptible to various types of leaf diseases. This causes huge financial losses every year to the farmers. Therefore, adequate action is needed to save strawberry crops from diseases and effectively manage their spread. Farmers were completely dependent on expert skilled personnel to identify crop diseases that may be the reason for the loss of crop yield. Therefore, this research proposed a novel deep-learning method to recognize plant leaf disease to optimize losses. However, with the invention of this method, it is easy to recognize different disease patterns within the plant leaf. The research proposed a feature fusion-based deep learning model named FFIR (Feature Fusion with Inception-RestNet) for recognizing leaf diseases. The features were extracted with a composition of the Inception-RestNet model. Later, the extracted features are fused in a fusion matrix using canonical correlation analysis (CCA). Afterward, the classification was performed with a Convolution Neural network. The proposed model outperformed with an accuracy of 99.34%. © 2024 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10.1111/tpj.16071</t>
+          <t>10.1109/ICACCS51430.2021.9441714</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Early detection of late blight in potato by whole-plant redox imaging</t>
+          <t>Literature Review of Disease Detection in Tomato Leaf using Deep Learning Techniques</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>M., Hipsch, Matanel; Y., Michael, Yaron; N., Lampl, Nardy; O., Sapir, Omer; Y.R., Cohen, Yigal R.; D., Helman, David; S., Rosenwasser, Shilo</t>
+          <t>H. E. David; K. Ramalakshmi; H. Gunasekaran; R. Venkatesan</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Plant Journal</t>
+          <t>2021 7th International Conference on Advanced Computing and Communication Systems (ICACCS)</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.79137122631073</v>
+        <v>0.3490220010280609</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 2: approach, data, grape</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Late blight caused by the oomycete Phytophthora infestans is a most devastating disease of potatoes (Solanum tuberosum). Its early detection is crucial for suppressing disease spread. Necrotic lesions are normally seen in leaves at 4 days post-inoculation (dpi) when colonized cells are dead, but early detection of the initial biotrophic growth stage, when the pathogen feeds on living cells, is challenging. Here, the biotrophic growth phase of P. infestans was detected by whole-plant redox imaging of potato plants expressing chloroplast-targeted reduction–oxidation sensitive green fluorescent protein (chl-roGFP2). Clear spots on potato leaves with a lower chl-roGFP2 oxidation state were detected as early as 2 dpi, before any visual symptoms were recorded. These spots were particularly evident during light-to-dark transitions, and reflected the mislocalization of chl-roGFP2 outside the chloroplasts. Image analysis based on machine learning enabled systematic identification and quantification of spots, and unbiased classification of infected and uninfected leaves in inoculated plants. Comparing redox with chlorophyll fluorescence imaging showed that infected leaf areas that exhibit mislocalized chl-roGFP2 also showed reduced non-photochemical quenching and enhanced quantum PSII yield (ΦPSII) compared with the surrounding leaf areas. The data suggest that mislocalization of chloroplast-targeted proteins is an efficient marker of late blight infection, and demonstrate how it can be utilized for non-destructive monitoring of the disease biotrophic stage using whole-plant redox imaging. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>Tomatoes are the most common vegetable crop widely cultivated in the agricultural fields in India. The tropical climate is ideal for its growth, however certain climatic conditions and various other factors affect the normal growth of tomato plants. Apart from these climatic conditions and natural disasters, plant disease is a major crisis in crop production and results in economic loss. The traditional disease detection methods for tomato crops could not produce the expected outcome and the detection period for diseases was slow. The early detection of diseases can give better results than the existing detection models. Thus, computer vision-based technology deep learning techniques could be implemented for earlier disease detection. This paper introduces a comprehensive analysis of the disease classification and detection techniques implied for tomato leaf disease identification. This paper also reviews the merits and drawbacks of the methodologies proposed. This paper finally proposes the early disease detection technique to identify tomato leaf disease using hybrid deep-learning architecture.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10.1007/s00500-022-07446-5</t>
+          <t>10.1109/FIT63703.2024.10838453</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Image-based disease classification in grape leaves using convolutional capsule network</t>
+          <t>Wheat Fusarium Head Blight Disease Severity Estimation using UAS Multispectral Imagery and Machine Learning</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>A.D., Andrushia, A. Diana; T., Mary Neebha, T.; A., Trephena Patricia, A.; S., Umadevi, S.; N., Anand, N.; A., Varshney, Atul</t>
+          <t>U. u. R. Janjua; M. Maimaitijiang; B. Millett; D. Yabwalo; K. Dilmurat; M. M. Billah; S. N. Khan; M. Shires; S. K. Sehgal; S. Ali</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Soft Computing</t>
+          <t>2024 International Conference on Frontiers of Information Technology (FIT)</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G83" t="n">
-        <v>0.4137524962425232</v>
+        <v>0.5846612453460693</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Crop protection is the prime hindrance to food security. Plant diseases destroy the overall quality and quantity of agricultural products. Grape is an important fruit and a major source of vitamin C nutrients. The automatic decision-making system plays a paramount role in agricultural informatics. This paper aims to detect the diseases in grape leaves using convolutional capsule networks. The capsule network is a promising neural network in deep learning. This network uses a group of neurons as capsules and effectively represents spatial information of features. The novelty of the proposed work relies on the addition of convolutional layers before the primary caps layer, which indirectly decreases the number of capsules and speeds up the dynamic routing process. The proposed method has experimented with augmented and non-augmented datasets. It effectively detects the diseases of grape leaves with an accuracy of 99.12%. The method's performance is compared with state-of-the-art deep learning methods and produces reliable results. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>Wheat is an important primary crop that feeds billions of people worldwide. Wheat diseases, particularly Fusarium Head Blight (FHB), often have severe effects on yield quality and the health of humans and livestock. Traditional field-based methods for monitoring wheat diseases are time-consuming and inefficient. Remote sensing approach, particularly the use of aerial imaging via Uncrewed Aircraft Systems (UAS) has become an essential tool for fine-scale and rapid field scouting and crop disease monitoring in recent years. This study investigates the potential of combining high-resolution UAS multispectral imagery with machine learning (ML) methods to detect FHB disease severity. Two experimental wheat fields were set up in Brookings, South Dakota, USA, in 2022. The severity of FHB disease was assessed periodically through visual observation, with synchronous UAS flights collecting multispectral imagery. UAS-based canopy spectral and texture features were derived and used as input variables to develop ML-based classification and regression models to estimate FHB disease severity. Conventional ML methods such as Support Vector Machine (SVM) and Random Forest (RF), along with deep learning models like Deep Neural Network (DNN) and One-Dimensional Convolutional Neural Network (1D-CNN), were employed. SVM demonstrated superior performance in both classification and regression analyses for predicting FHB disease severity levels, achieving an overall accuracy of 0.80 using texture features in classification and an R2 of 0.73 using spectral features in regression. The results show that both spectral and texture features are important features for estimating wheat FHB disease severity. UAS remote sensing, coupled with ML-based approaches, provides a rapid and accurate method to assess FHB disease severity at a fine scale over large areas.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10.1109/CCEM60455.2023.00044</t>
+          <t>10.1109/ICSPIS60075.2023.10343735</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Multi – Stage Canker Disease Detection in Lime Leaves</t>
+          <t>An Extensive Evaluation of Plant Disease Detection Using Diverse Machine Learning Approaches</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>R., Akshay, R.; B.R., Pushpa, B. R.; N.S., Rani, N. Shobha; M.A., Sangamesha, M. A.</t>
+          <t>F. Suthar; K. Padhya; R. Joshi; S. Parikh; A. Panthakkan; W. Mansoor</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3858,40 +3874,40 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>2023 6th International Conference on Signal Processing and Information Security (ICSPIS)</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.8859900236129761</v>
+        <v>0.763390064239502</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Tópico 2: tomato, fruit, grape</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>The whole economic status of the country depends on the agricultural and the types of crops that provides the good yield, more than 500 varieties of crops are grown in India. Lime plant is one of the major crop in the field of agriculture that provides vitamin and it is grown in more than 30 countries. Various research clarifies that by consuming lime provides greater immunity. Plant disease is the greatest adversity that provides loss during the time of yield. Detection of the plant disease is very important in order to prevent the yield losses. Lime plants also getting affected by various types of diseases and one of them is canker. The dataset used in this work are the images that are affected by the canker disease in different stages. In this work, the detection of canker disease in different stages is carried out and yolov7 object detection model is considered for disease detection. The model is trained using different number of epochs and the appropriate results are acquired. The proposed model delivers 70% of accuracy in the detection of canker diseases. The proposed work for identification of the disease in the lime leaves at different stages would guide in using proper fertilizer to the particular staged disease to treat the leaves. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Plant sicknesses fundamentally affect horticultural efficiency and food security. In order to minimize widespread damage and maximize crop yield, it is essential to detect these diseases promptly and accurately. Automating the process of detecting plant diseases has been shown to be a promising application of machine learning techniques in recent years. This study presents a comprehensive analysis of various machine learning techniques applied to the task of plant disease detection. This study investigates the use of different AI procedures for plant illness recognition. Convolutional neural networks (CNNs), support vector machines (SVMs), random forests, and k-nearest neighbors (KNNs) are just a few of the algorithms that are compared in this study. Feature extraction from diseased plant images is the first step in our experiment, followed by model training and validation. The results demonstrate the efficacy of machine learning in accurately identifying plant diseases based on visual symptoms. The findings provide insights into the strengths and limitations of each technique, paving the way for further research in automated and precise plant disease diagnosis to enhance agricultural sustainability.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10.1109/SMARTGENCON60755.2023.10442288</t>
+          <t>10.1109/IGARSS52108.2023.10282890</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DeepLeafNet: Multiclass Classification of Soybean Plant Leaves with ResNet50V2 for Enhanced Crop Monitoring and Disease Detection</t>
+          <t>Hyperspectral Detection of Fusarium Wilt in Tomato Plants Using Machine Learning-Based Approaches</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>G., Shandilya, Gunjan; V., Anand, Vatsala; S., Malhotra, Sonal; S., Kukreti, Sanjeev; S., Gupta, Sheifali</t>
+          <t>Sivaganesh; C. H; M. K. C. V. S. S.; M. Kaushik; R. G. Sharathchandra; R. Rao Nidamanuri</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3899,40 +3915,40 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>IGARSS 2023 - 2023 IEEE International Geoscience and Remote Sensing Symposium</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G85" t="n">
-        <v>0.6794548034667969</v>
+        <v>0.5249166488647461</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>The soybean, which is a fundamental component of worldwide agriculture, plays a crucial role in meeting the global need for protein and oil. Nevertheless, the spread of many diseases poses a significant risk to both the quantity and quality of soybean harvests. The timely and accurate categorization of diseases is crucial for the successful implementation of crop management strategies. This study aims to enhance the categorization of soybean diseases by addressing ten different disease classes using the ResNet50V2 deep learning model. In order to accomplish this objective, the Soybean Disease Leaf Image Classification Dataset has been employed for both the purposes of training as well as evaluating the model. The ResNet50V2 model's architectural depth and inclusion of skip connections augment its capacity to grasp complicated patterns present in leaf images, hence bolstering its efficacy in performing robust categorization. The experimental findings provide evidence for the effectiveness of our methodology since the model attains a notable training accuracy of 97% and validation accuracy rate of 96% when diagnosing illnesses in soybean plant leaves with a minimum loss of 0.05 and 0.38. Moreover, this research endeavor makes a valuable contribution to the expanding domain of computer vision in the agricultural sector, facilitating the automation and enhancement of plant disease diagnosis processes. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Crop health is vital in agricultural nations like India. One of India's most important crops, tomato, is farmed and consumed globally. Bacteria, viruses, and fungi may damage tomato plants and other food and vegetable crops. Fusarium wilt is a seed-borne fungal infection that causes severe damage in the growth and yield of tomato crop. The objective of this research is the assessment of spectral discriminability and classification of health and Fusarium wilt diseased-tomato plants using hyperspectral data. In-situ reflectance measurements of healthy and infected plants over a tomato growing region (Tumkur, Karnataka, India) have been collected, processed, and analyzed to spectrally differentiate diseased and healthy plants. Various statistical and machine-learning approaches have been applied for assessing the spectral discrimination of diseased plants with sensitivity to five different levels of disease severity. Results suggest the existence of stable spectral features which differentiate healthy and diseases plants at distinct levels of disease severity. The discrimination has substantial variance with the method used. Amongst the methods used, Linear Discriminant Analysis (LDA), Gradient Boosting, and XGBoost methods offer spectral discrimination of about 80% accuracy.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10.1109/ICCIT60459.2023.10441449</t>
+          <t>10.1109/ICRASET59632.2023.10420037</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>A vision transformer-based approach for recognizing seven prevalent mango leaf diseases</t>
+          <t>Intelligent Recognition of Leaf Abnormalities Using Deep Learning Method</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>M.E., Rayed, Md Eshmam; Abdullah-Al-Akib; N., Alfaz, Nazia; S.I., Niha, Sadia Islam; S.M.S., Islam, Showrov M.Sajibul</t>
+          <t>A. M N; P. P S; P. K; D. R H; Kiran; S. C N</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3940,249 +3956,249 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>2023 International Conference on Recent Advances in Science and Engineering Technology (ICRASET)</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G86" t="n">
-        <v>0.3512542843818665</v>
+        <v>0.3777965307235718</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Tópico 6: soybean, vegetable, learningbased</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Plant diseases, particularly affecting fruit crops, pose a significant challenge to the worldwide supply of fresh food due to their direct impact on the quality of fruits, resulting in an overall decline in agricultural production. The traditional approach of detecting leaf diseases in fruit plants requires farmers to undertake manual inspection which exhibits a lack of reliability and consistency. Moreover, the manual inspection procedure is prone to errors due to its reliance on the farmer's knowledge and skill. Mango referred to as the "king of all fruits", is renowned for its rich composition of various vitamins and vital nutrients. Mangoes are susceptible to many diseases that adversely damage their visual appeal, and flavor, and have significant implications on the overall economy. The identification of diseases affecting mango plant leaves using automated recognition remains a challenge due to the diverse range of symptoms and limited availability of data. There have been several deep learning-based research studies focused on identifying diseases in mango leaves; however, the majority of these studies have employed a convolutional neural network (CNN) trained on a small number of data. This study presents a Vision Transformer (ViT) based approach to detect diseases in mango leaves using publicly available data namely MangoLeafBD. The ViT model has been selected as the detection model due to its parameter efficiency compared to deep CNN models. The ViT has produced remarkable overall classification accuracy of 100%, precision of 100%, recall of 100%, and f1-score of 100% for disease detection on mango leaves which is better than the existing CNN approaches on the MangoLeafBD dataset. This demonstrates that our approach has the potential to assist farmers in the field by providing automated, simple, and more reliable mango leaf disease diagnosis. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Deep Neural Networks (DNNs) have significantly improved the detection of different diseases affecting plants. The impact of unidentified and untreated plant diseases is to reduce crop yield significantly, as they negatively affect the quality and quantity of horticultural and agricultural products. Therefore, early recognition of plant diseases is essential for improving crop quality and reducing production losses. To this end, a modern framework has been developed that incorporates image acquisition and analysis, utilizing DNN models to calculate various evaluation metrics such as Recall, F1 scaling, accuracy, and precision. By diversifying the results, it becomes possible to differentiate between healthy and bacterial plant leaves. The proposed methodology has been tested on two types of plants - pepper, and potato - and can determine the percentage of infection on plant leaves.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10.1109/ISAS60782.2023.10391530</t>
+          <t>10.1109/AICDMB64359.2025.11277487</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>An Automation Perception for Cotton Crop Disease Detection Using Machine Learning</t>
+          <t>Stage-Wise Late Blight Disease Detection in Tomato Plants Using Deep Learning Models along with Treatment Recommendation</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>R., Aggarwal, Ritu; E., Aggarwal, Eshaan; A., Jain, Anurag; T., Choudhury, Tanupriya; K.V., Kotecha, Ketan V.</t>
+          <t>G. S. Prajwal; A. Deepak; K. R. Sharath Kumar; J. Varshini; V. Ravi Kumar; S. Gagana; L. V. Kumar; G. Manjunath</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>2025 Annual International Conference on Data Science, Machine Learning and Blockchain Technology (AICDMB)</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G87" t="n">
-        <v>0.4628013074398041</v>
+        <v>0.8021979928016663</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Cotton crop disease detection and classification based on images of leaves is a significant objective in agriculture. Cotton crops play a vital role in India. Every year, due to the attack of diseases, cotton production is decreasing. The main reasons for disease in plants are the pests, insects, and pathogens used; if they are not controlled on time, they affect productivity. In advancing digital image processing technologies, machine learning and other techniques that identify early disease detection in plants are proposed. This paper focuses on improving disease detection in cotton crop plants and leaves. Machine learning is used to identify and predict cotton plant disease using images and leaves collected in an uncontrolled environment. This study uses machine learning to review the different problems identified regarding plant disease. Various experimental configurations are investigated to analyze the impacts of different leaf classes, plant disease combinations, and their categories. Cotton crops are detected to classify the various types of cotton plants. Cotton plant diseases have a wide range of illnesses, from bacterial deficiency to bacterial, fungal, viral, and vitamin and nutrient deficiency. The proposed approach indicates the cotton crop plant in the leaf disease by their implementation results. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>This work introduces a novel method for stage-wise disease detection in tomato plants through deep learning architecture called InceptionV3, which gave better results compared to EfficientNetB0 and MobileNetV2 whose accuracy was $38.23 \%$ and $92.74 \%$ respectively. Here we concentrated on late blight disease, which is a widespread problem in Indian agriculture, and manually annotated a dataset of 4,648 images divided into three stages depending on the level of leaf damage (Stage 1, Stage 2, Stage 3) and healthy leaves. The dataset was divided into $80 \%$ training and $20 \%$ test sets. The model obtained a training accuracy of $93.68 \%$ and testing accuracy of $95.56 \%$. The system also offers stage-wise medication recommendations for disease management. When given multiple photos from the same plant with different disease stages, the model predicts the stage for each leaf and finally highlights the highest stage along with suggesting the treatment for that highest stage. A simple web application was implemented to support image uploads, detection of disease stages, and tracking of history. The uniqueness of this project is the stage-wise detection of disease in tomato plants, similar to cancer staging, which presents a new contribution to precision agriculture.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10.3389/fnut.2023.1277048</t>
+          <t>10.1109/STSIVA.2014.7010156</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Predictors of micronutrient deficiency among children aged 6–23 months in Ethiopia: a machine learning approach</t>
+          <t>An image retrieval system for tomato disease assessment</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>L.G., Gebeye, Leykun Getaneh; E.Y., Dessie, Eskezeia Yihunie; J.A., Yimam, Jemal Ayalew</t>
+          <t>Baquero, D.; Molina, J.; Gil, R.; Bojacá Aldana, C.; Franco, H.; Gómez, F.</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Frontiers in Nutrition</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G88" t="n">
-        <v>0.5343393087387085</v>
+        <v>0.2583999633789062</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Introduction: Micronutrient (MN) deficiencies are a major public health problem in developing countries including Ethiopia, leading to childhood morbidity and mortality. Effective implementation of programs aimed at reducing MN deficiencies requires an understanding of the important drivers of suboptimal MN intake. Therefore, this study aimed to identify important predictors of MN deficiency among children aged 6–23 months in Ethiopia using machine learning algorithms. Methods: This study employed data from the 2019 Ethiopia Mini Demographic and Health Survey (2019 EMDHS) and included a sample of 1,455 children aged 6–23 months for analysis. Machine Learning (ML) methods including, Support Vector Machine (SVM), Logistic Regression (LR), Random Forest (RF), Neural Network (NN), and Naïve Bayes (NB) were used to prioritize risk factors for MN deficiency prediction. Performance metrics including accuracy, sensitivity, specificity, and Area Under the Receiver Operating Characteristic (AUROC) curves were used to evaluate model prediction performance. Results: The prediction performance of the RF model was the best performing ML model in predicting child MN deficiency, with an AUROC of 80.01% and accuracy of 72.41% in the test data. The RF algorithm identified the eastern region of Ethiopia, poorest wealth index, no maternal education, lack of media exposure, home delivery, and younger child age as the top prioritized risk factors in their order of importance for MN deficiency prediction. Conclusion: The RF algorithm outperformed other ML algorithms in predicting child MN deficiency in Ethiopia. Based on the findings of this study, improving women’s education, increasing exposure to mass media, introducing MN-rich foods in early childhood, enhancing access to health services, and targeted intervention in the eastern region are strongly recommended to significantly reduce child MN deficiency. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Tomato represents an important vegetable crop worldwide. During cropping cycle several diseases and abnormal conditions may affect tomato plants resulting on considerable losses of production. A precise identification of these pathologies in early phases is fundamental for the implementation of control strategies. Nevertheless, the right identification of symptoms of plants diseases require highly specialized knowledge and facilities, which are not available for small growers. Recently, computer vision tools have been proposed as an alternative for tomato diseases characterization. These works mainly focus on identification of affected regions and classification tasks. Nevertheless, non-specialists may lack of clarity about what they are looking for during the assessment. In these cases, Content Based Image Retrieval (CBIR) systems can be helpful as a complementary strategy to improve the quality of the search by allowing exploration of databases with supplementary information. This work presents a novel strategy for image retrieval of tomato leaves for greenhouse crops suitable to support disease diagnosis. The strategy is based on color structure descriptors and nearest neighbors. Experimental results show that the proposed approach can successfully characterize in several abnormal conditions, such as, chlorosis, sooty moulds and early blight. © 2014 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10.1117/12.3006157</t>
+          <t>10.1109/ATNT61688.2024.10719249</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deep learning based secreted protein prediction</t>
+          <t>Effect of Hyperparameter Tuning to Fruit Quality Detection Using Convolutional Neural Network</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>C., Liu, Chaoyang; B., Wang, Bo; X., Zhang, Xinhong; F., Zhang, Fan</t>
+          <t>M. H. Z. Ariffin; M. Harun; H. H. Amizi; R. A. Rashid</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Proceedings of SPIE - The International Society for Optical Engineering</t>
+          <t>2024 IEEE International Conference on Advanced Telecommunication and Networking Technologies (ATNT)</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G89" t="n">
-        <v>0.5130228400230408</v>
+        <v>0.4878039360046387</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Proteins secreted by various cells and tissues into different body fluids can signal several physiological disorders. However, the degree of complexity in different body fluids and the presence of a large number of proteins in fluids can make studying them with existing proteomics techniques complex and result in large discrepancies between experimental studies. To address this, we developed a deep learning framework called SecBert that identifies secreted proteins in two human body fluids. SecBert uses a sequence-based approach with end-To-end automatic feature extraction for protein classification. Our results show that SecBert performs well, achieving an average area under the ROC curve of 0.94-0.95 on each fluid test dataset. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>Malaysia's agricultural sector plays a crucial role in the nation's economy and food security. One of the most pressing issues is the difficulty in identifying and addressing fruit damage early in the production cycle. Current manual inspection methods are labor-intensive, time-consuming, and prone to human error. Convolutional Neural Network (CNN) is a useful tool that help in automatically learning and recognizing pattern in image and to determine the quality of the fruit in agriculture industry. This project is focusing on building CNN machine learning for image classification and detection of fruit quality. The CNN model is being trained with 3 different data sets which are apple, damage apple and potato. The model is trained for two-class-set (apple, damage_apple) and three-class-set (apple, damage_apple and potato) with 1000 and 1500 images consecutively. The experimental results in this study demonstrate that the hyperparameter adjustment of machine learning algorithms has varying effects on fruit quality detection.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-35641-4_28</t>
+          <t>10.1109/CICN63059.2024.10847513</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Identification of Potato Leaf Diseases Using Hybrid Convolution Neural Network with Support Vector Machine</t>
+          <t>PepperShield: Disease Detection with Hyper Tuned Precision</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>T., Sultana, Tasleem; M., Reza, Motahar</t>
+          <t>Julian, A.; Jaiganesh, V.; Thirumurugan, O.T.; Isreal Moses, B.</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Communications in Computer and Information Science</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G90" t="n">
-        <v>0.5654139518737793</v>
+        <v>0.350147008895874</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Agriculture has long been a vital source of sustenance. More over 60% of the world’s population relies mostly on agricultural sources for food, according to linked statistics. Plant infections, however, are a catastrophic issue that seriously hampers agriculture productivity. Plant diseases cause a loss of agriculture productivity of about 25% per year. Potato crops have many benefits for human life. One of the most valuable benefits of potatoes for humans is their carbohydrate content; carbohydrates are the leading food for humans. The development of potato crop agriculture is significant for the sustainability of human life. There are several obstacles to developing potato farming, including a disease that attacks potato leaves. Infestans only the diseases early Blight (Alternia Solani) and late Blight (Phytophthora infestans de Bary) are among the most harmful to potato crops. However, the percentage of crops that fail to grow grows due to the erroneous and tardy identification of plant diseases. Using a diagnostic and detection system based on the Hybrid CNN (Convolutional neural network) with SVM (Support vector machine) presently deep learning (DL) technology, we offer an efficient and accurate way to identify early plant illnesses to reduce the plant output losses. Potato leaf disease detection issues can be resolved with the use of informatics technology and digital image processing. From the input photos of the supported training dataset, we utilised CNN to extract best feature of the illness characteristics, and then we used SVM to those features to do classification. 1900 photos of potato leaves were used to train the deep learning model, and about 950 images were utilised for testing. We suggested the CNN model and trained a strong accuracy data set. In addition, we employed ResNET50, a transfer learning model, and obtained accuracy that was superior to our suggested CNN model. It’s interesting that the accuracy of our suggested Hybrid CNN (ResNet 50) with SVN is 97.3% and that it was trained using the same Potato lead picture dataset and test data accuracy is 95.6. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>A popular vegetable crop, bell peppers (Capsicum annuum) are prized for both their economic significance and nutritional advantages. Bell peppers, like many other crops, are prone to a number of illnesses brought on by bacteria, fungi, viruses, and environmental conditions. These diseases can drastically lower the harvest's quality and output. Preventing crop losses and guaranteeing food security depends on the early identification and precise classification of these diseases. Conventional plant disease detection techniques usually entail professional manual inspection, which can be expensive, time-consuming, and prone to human mistakes. Recent developments in machine learning and artificial intelligence (AI) have opened new possibilities for automating agricultural disease diagnosis. By contrasting two different models, one created from scratch and the other improved with hyperparameter tuning, this effort seeks to utilize CNNs' potential for bell pepper disease prediction and classification. The main goal is to investigate how CNN model performance is affected by adjusting important hyperparameters like learning rate, batch size, and the number of training epochs. Metrics including accuracy, precision, recall, and F1-score will be used to train and assess the models using preprocessed picture data of both healthy and diseased bell peppers. By providing a scalable, AI-driven method for real-time disease diagnosis in bell pepper crops, this research holds significance for precision agriculture. © 2024 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>10.1109/ACCESS57397.2023.10199392</t>
+          <t>10.1109/ICDSAAI55433.2022.10028790</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tomato Plant Health Management Using AI</t>
+          <t>Deep Learning Approach for Recognition and Classification of Tomato Fruit Diseases</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>N.A., Aswathy, N. A.; J.J., Poovely, Jaimy James; A., Surendran, Abhijith; S.S., Thomas, Samuel Sabu</t>
+          <t>A. S. Nagesh; G. N. Balaji</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>2022 International Conference on Data Science, Agents &amp; Artificial Intelligence (ICDSAAI)</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G91" t="n">
-        <v>0.5699195861816406</v>
+        <v>0.4337250590324402</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>India is a country whose economy is heavily reliant on agriculture. The agriculture sector accounts for a significant portion of the country's overall economy. Plant diseases are particularly important because they can have a negative impact on the quality and quantity of crops. Viruses, bacteria, fungi, and other microorganisms can cause plant diseases. The majority of farmers are completely unaware of such diseases. In India, the tomato crop is a common staple due to its high commercial value and strong production potential. In tomatoes, the three most potent antioxidants are vitamin E, vitamin C, and beta-carotene. The main focus of the proposed article is to create a more accurate and time-efficient automatic method for detecting tomato plant leaf diseases. This work aims to create a system that captures images with a Raspberry Pi camera and classifies them using Convolutional Neural Network. In neural network models, automatic feature extraction is utilized to help classify input photos into appropriate illness categories. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>Diseases devastate food crops, causing significant losses for farmers and jeopardising food security, resulting in a low production rate. Health monitoring and disease detection are critical for sustainable agriculture. Monitoring the fruit diseases manually is extremely difficult. It necessitates a significant amount of work, knowledge of fruit diseases, and an extended processing time. Hence, deep learning is used to detect fruit diseases with high accuracy. This paper proposes the method to detect the tomato fruit diseases in color images. In the proposed method, convolutional neural network is used for extracting the features and classification. Further, the augmentation strategy is applied on existing samples to create the dataset with large number of samples. The convolutional neural network method based on VGG16 will be used to train augmented data for recognition and classification of tomato diseases. The results of the CNN after testing affirms that the tomato disease can be predicted efficiently, and it can be utilised for early detection purpose.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>10.1109/ICESC57686.2023.10193447</t>
+          <t>10.1109/ICECSP61809.2024.10698492</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Classification and Segmentation of Leaf Images based on Deep Learning for Peanut Plant Disease Detection</t>
+          <t>Deep Learning Based Fruit Crop Disease Classification Using Plants Leaf Imagery</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>V., Ebenezer, V.; A.A., Daniel, Arsha Anna; G.J.L., Paulraj, Getzi Jeba Leelipushpam; B., Edwin, Bijolin; M., Roshni Thanka, M.; R., Devassy, Rosebel</t>
+          <t>Joshi, A.; Badola, A.; Saini, R.</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -4193,238 +4209,238 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>0.7834851741790771</v>
+        <v>0.3924592435359955</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Tópico 2: tomato, fruit, grape</t>
+          <t>Tópico 2: approach, data, grape</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Peanut is a key food commodity, and diseases of its leaves can have a negative impact on the quantity and quality of the product. The seed has high levels of potassium, magnesium, calcium, riboflavin, niacin, folic acid, vitamin E, resveratrol, and amino acids. It also contains 36% to 54% oil, 16% to 36% protein, and 10% to 20% carbs. Early, late, and rusty leaf spots, among other frequent illnesses, are recognized by this equipment. Techniques for image augmentation have been used, such as twisting, rotating, and scaling. The variant employs a Multi Class Convolutional neural network with 5 output which include Normal Leaf, Images Without Leaf and the images with the leaf been infected by the diseases. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>Agriculture plays an important role in the economy, providing nutrition, food, and livelihoods to billions of people in this world. Fruits are a vital component of a balanced diet, acting as a rich source of antioxidants, vitamins, minerals, and fibres. To ensure its proper supply to the market, early diagnosis and treatment of fruit crop disease can play a significant role. In order to make this process quicker and more accurate, Deep learning (DL) techniques can be of immense help. In the proposed study, the implementation of four DL models: Visual Geometry Group VGG16, VGG19, EfficientNet-B0, and MobileNet is done on a subset of the Plant Village database, constituting 7,233 leaf images of apples and grapes divided into 8 different classes. Evaluation is done through various metrics, namely Precision, Recall, F1-score and Specificity. All the DL models performed well by attaining accuracy above 95%. MobileNet performed best among all DL models by achieving an accuracy of 99.38%, while VGG16, VGG19, and EfficientNet-B0 achieved an accuracy of 96.75%, 98.69% and 98.76% respectively. © 2024 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>10.1007/978-981-99-1946-8_38</t>
+          <t>10.1109/ICGTSPICC.2016.7955315</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>A Deep Learning-Based InceptionResNet V2 Model for Cassava Leaf Disease Detection</t>
+          <t>Fusion classification technique used to detect downy and Powdery Mildew grape leaf diseases</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>R., Singh, Rahul; A.K., Sharma, Avinash Kumar; N., Sharma, Neha; K., Sharma, Kulbhushan; R., Gupta, Rupesh</t>
+          <t>Padol, P.B.; Sawant, S.D.</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Lecture Notes in Networks and Systems</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G93" t="n">
-        <v>0.7319851517677307</v>
+        <v>0.5827574133872986</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>A tropical root vegetable called cassava can make flour, bread, tapioca, and alcohol. After rice and maize, cassava ranks third among common food sources of carbohydrates. Over half a billion people in the developing world rely on cassava as a staple crop for daily nutrition. It is one of the crops that can grow on poor soils and is one of the most drought-tolerant. Cassava is produced extensively in Nigeria, and cassava starch is exported most widely from Thailand. Even though the deep convolution neural network technique had respectable results for classifying cassava photos. The proposed work identifies Cassava leaf disease using a CNN-based pre-trained deep learning algorithm. Several cassava leaf diseases are included in the dataset, including Cassava Bacterial Blight (CBB), Cassava Brown Steak Disease (CBSD), Cassava Green Mite (CGM), Cassava Mosaic Disease (CMD), and Healthy. The InceptionResNetV2 was used to test the CNN model, and the predictions for the model were run for 20 epochs. Performance indicators like Precision, Recall, F1-Score, and Accuracy were used for the CNN model study. The maximum accuracy of the proposed model is 87%. The suggested methodology yields precise and prompt results, which may assist farmers in saving their plants and making healthier growth, and helping farmers boost their economy. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>Grape constitutes one of the most widely grown fruit crop in the India. Manual observation of experts is used in practice for detection of leaf diseases, which takes more time for further control action. Without accurate disease diagnosis, proper control actions cannot be taken at appropriate time. This is where modern agriculture technique is required to detect and prevent the leaf from different diseases. This paper aims to introduce a new approach for detection of grape leaf diseases using image processing, which will minimize the loss and increase its profit due to automation. In this system, classification is done using Support Vector Machine (SVM) and Artificial Neural Network (ANN) classifies separately. A new classifier is proposed using fusion classification technique which ensembles classifiers from SVM and ANN to regenerate base classifier for grape leaf disease detection. Based on detection of disease the proper mixture of fungicides will be provided to the grape farmers. © 2016 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>10.1007/978-981-99-0769-4_1</t>
+          <t>10.1109/RCTFC.2016.7893419</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Impact of Data Centric Approach to Improve the Performance of Leaf Disease Classification</t>
+          <t>Design and simulation of crop monitoring robot for green house</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>D., Prajapati, Dharv; N.M., Bhatt, Nikita M.; A.R., Thakkar, Amit R.; D., Bhoi, Dhaval</t>
+          <t>K. R. Aravind; P. Raja</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lecture Notes in Networks and Systems</t>
+          <t>2016 International Conference on Robotics: Current Trends and Future Challenges (RCTFC)</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G94" t="n">
-        <v>0.4867905378341675</v>
+        <v>0.4361766278743744</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Cassava is the third highest carbohydrate food after rice and maize. Due to various plant diseases found in Cassava, security threat is posed in developing countries. To stop spoiling the whole plant, a lot of effort has been made by researchers to identify early leaf disease as agricultural farming is closely associated with every country’s economy. Recently, Machine Learning (ML) models have achieved a lot of success with big data, available resources and improvement in learning algorithms. However, there are invalid instances in big data like ambiguous or mislabelled or irrelevant. Though the performance of ML model is not degraded if such instances are small as the effect of the average gradient is small during the training. But the performance of system is degraded if quantity of invalid instances is large. The existing work for leaf disease detection is performed using Model Centric approach, where hyperparameter tuning is performed to enhance the performance of the system. Recently, focus in changed from Model Centric to Data Centric approach, where model is fixed but quality of dataset is enhanced by considering the consistency of labels, systematic sampling of training data and selection of appropriate batches. This is an invaluable step towards improvement of any system. In this work, noise label detection and correction are performed on Cassava Leaf Disease Classification dataset using confidence learning. The generated quality data is given to the model, and performance comparison is made between model centric and data centric approaches, which concludes that the performance of data centric is improved by 6.33%. The conclusion of this work is not to downgrade the significance of model centric, but to showcase the neglected potential of enhancing the performance of such systems using data centric approach. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>Incidence of disease in horticultural crops is one of the important problems affecting the production of fruits, vegetables and flowers. Regular monitoring of crops for early diagnosis and treatment with pesticides or removal of the affected crop is some of the solution to minimize the crop loss. Monitoring of the crops by human labour is costly, time consuming, error prone due to insufficient knowledge of the disease and highly repetitive at different stages of crop growth. These needs have motivated to design a line following mobile robot with vision sensors for navigation across the field for disease identification in a green house. The robot has been designed and simulated in an open source software known as Virtual Robot Experimental Platform (V-REP) with experimental field of 40 crops. Programming for navigation is done in Lua scripting tool which is embedded with the V-REP software. Capturing of images has been performed using camera. Processing of images for identification of disease and its representation in a Graphical User Interface (GUI) has been done using an algorithm in MATLAB R2011B which interacts with V-REP tool through socket communication. Texture based analysis has been done to identify the diseased crops among the healthy crops in the simulated field setup.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>10.1007/978-981-99-0981-0_54</t>
+          <t>10.1109/ICCIC.2014.7238283</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Prediction of Nitrogen Deficiency in Paddy Leaves Using Convolutional Neural Network Model</t>
+          <t>Identification and classification of fungal disease affected on agriculture/horticulture crops using image processing techniques</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>S.N., Bhagirath, Swami Nisha; V., Bhatnagar, Vaibhav; L., Raja, Linesh</t>
+          <t>J. D. Pujari; R. Yakkundimath; A. S. Byadgi</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Lecture Notes in Networks and Systems</t>
+          <t>2014 IEEE International Conference on Computational Intelligence and Computing Research</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G95" t="n">
-        <v>0.8926389217376709</v>
+        <v>0.3151417076587677</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>At various stages of development, including flowering and fruit production, plants need a variety of minerals and nutrients to grow. The phenotype, quality, and yield of crops are all influenced by the nitrogen level in precision agriculture. In the future, it won’t be possible to achieve without the application of nitrogen fertilizer. A useful and cutting edge technique for diagnosing the nitrogen nutrition of crops is needed for an effective and appropriate nitrogen fertilizer management system. Plant diseases that have a substantial impact on agricultural output are brought on by nutrient deficiency. Rice producers can reduce output loss significantly by taking essential measures with the help of early disease identification. Deep learning, an effective machine learning method, has recently demonstrated considerable potential in the task of classifying images. The convolutional neural network has been trained after classification of the affected leaf regions. In this study, the lack of nitrogen in the paddy crop was identified and predicted using leaf data. The model achieved 95% of accuracy for identifying nitrogen deficiency in leaves from available dataset. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>This paper presents a study on the image processing techniques used to identify and classify fungal disease symptoms affected on different agriculture/horticulture crops. Many diseases exhibit general symptoms that are be caused by different pathogens produced by leaves, roots etc. Images Often do not possess sufficient details to assist in diagnosis, resulting in waste of time, misshaping the diagnostician to arrive at incorrect diagnosis. Farmers experience great difficulties and also in changing from one disease control policy to another i.e. intensive use of pesticides. Farmers are also concerned about the huge costs involved in these activities and severe loss. The cost intensity, automatic correct identification and classification of diseases based on their particular symptoms is very useful to farmers and also agriculture scientists. Early detection of diseases is a major challenge in horticulture / agriculture science. Development of proper methodology, certainly of use in these areas. Plant diseases are caused by bacteria, fungi, virus, nematodes, etc., of which fungi is the main disease causing organism. The present study has been focused on early detection and classification of fungal disease and its related symptoms.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>10.1109/ICAAIC56838.2023.10141055</t>
+          <t>10.1109/IATMSI64286.2025.10985113</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nutrient Deficiency Detection in Mobile Captured Guava Plants using Light Weight Deep Convolutional Neural Networks</t>
+          <t>Indoor Greenery Identification: A ResNet-50 and SVM-Based Approach for Plant Species Recognition</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>S., Haris, Sona; K.S., Sai, Keshav Shesha; N.S., Rani, N. Shobha; B.R., Pushpa, B. R.</t>
+          <t>J. Kaur; G. Singh; S. Jagadish; Z. A. Salami</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>2025 IEEE International Conference on Interdisciplinary Approaches in Technology and Management for Social Innovation (IATMSI)</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G96" t="n">
-        <v>0.4911169111728668</v>
+        <v>0.4391982853412628</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 6: gardening, management, specie</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Nutrition deficiency in plants is a major problem that affects their growth, yield, and nutritional value. Over the past few years, there has been a significant growth in the application of machine learning and computer vision techniques, in early detection and classification of plant disorders. This study, proposes a deep learning-based approach for detecting nutritional deficiencies in guava leaf images. A dataset of guava leaf images captured using mobile devices, containing various nutritional deficiencies including magnesium and phosphorous, was acquired for training the model. A pre-trained deep CNN model is employed to extract convolved features and detect the affected regions, categorizing them as nutritional deficient or non-nutritional deficient Experimental results show that the proposed method achieved an accuracy of 87% in detecting nutritional deficiencies in guava leaf images. These outcomes demonstrate that the proposed approach provides a reliable and accurate method for early detection of nutritional deficiencies in guava leaves. This approach has the potential to be deployed in the agricultural domain for the effective diagnosis of plant nutrient deficiencies, ultimately increasing crop productivity and nutritional quality. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>The accurate identifications of houseplant species are very important applications in horticulture, biodiversity conservation, and plant disease management. This research paper presents an approach for classification of house-plant species by focusing on the identification of various plants commonly found in indoor environments. In the model, a hybrid architecture is used in which ResNet-50 is combined with an SVM classifier implemented using the PyTorch deep learning (DL) framework. It utilizes the Adam optimizer to train efficiently. The dataset consists of images of various house plants, categorized into 47 classes with a total of 15,131 images. The ResNet-50 DL architecture has been used and, as an SVM classifier, has performed multi-class classification. The dataset has been divided into training (80%) and testing (20%) sets. The model has been trained for 10 epochs. The proposed model has achieved an impressing accuracy of 98.80%, thereby proving to identify plant species in a more precise manner. As shown by the loss curve, training and validation loss decreased steadily throughout the process. This apparently indicates that the model converged appropriately. The results demonstrate how the SVM-ResNet-50 hybrid is capable of alleviating complex image classification tasks. The major challenge for this experiment was the model’s insensitivity to changes caused in images by lighting and angles. Further work in the future will focus on enriching the model through more augmentation techniques and data augmentation to enhance generalization and robustness. Another possible improvement of the model is to implement attention mechanisms to better concentrate on important features.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>10.1080/21681163.2023.2228914</t>
+          <t>10.1109/IATMSI64286.2025.10985542</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Non-invasive method for the prediction of micronutrient deficiency using sequential learning techniques</t>
+          <t>Indoor Greenery Identification: A ResNet-50 and SVM-Based Approach for Plant Species Recognition</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>T., Kalavathi Devi, T.; K.N., Baluprithviraj, K. N.; M.M., Mohan, M. Madhan; S., Umadevi, S.; P.K., Sakthivel, Prakash Kumar; P., Rajeshwari, P.; B., Vinodha, B.</t>
+          <t>J. Kaur; G. Singh; S. Jagadish; Z. A. Salami</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Computer Methods in Biomechanics and Biomedical Engineering: Imaging and Visualization</t>
+          <t>2025 IEEE International Conference on Interdisciplinary Approaches in Technology and Management for Social Innovation (IATMSI)</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G97" t="n">
-        <v>0.328843891620636</v>
+        <v>0.4462177157402039</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 6: gardening, management, specie</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Study data from World Health Organization indicate that 2.8% of the disease around the world is caused by micronutrient insufficiency due to improper consumption of a balanced diet. The micronutrient deficiency is detected from the individual’s blood sample which is an invasive technique. Such techniques are quite in comfort for the persons and also painful. This proposed method involves the micronutrient deficiency identification using the non-invasive method of image processing. In this work, images of the anterior conjunctiva of eye, tongue and nail bed are used to detect the deficiency. Convolutional neural network models are used in the proposed deep learning model to extract the features of the parts of eye, nail and tongue. CNN-LSTM and CNN-GRU architectures are used to predict the deficiency in the images by extracting the features and perform the classification. A collection of 140 images were used as a dataset in this system. The real-time images are used to train the model, which is then validated with sample images for increased accuracy. The simulation of the CNN network with CNN-GRU has very low MSEs with 0.22%, results show that the proposed system achieved an accuracy of 99.6%, specificity of 99.7% and sensitivity of 99.4%. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>The accurate identifications of houseplant species are very important applications in horticulture, biodiversity conservation, and plant disease management. This research paper presents an approach for classification of house-plant species by focusing on the identification of various plants commonly found in indoor environments. In the model, a hybrid architecture is used in which ResNet-50 is combined with an SVM classifier implemented using the PyTorch deep learning (DL) framework. It utilizes the Adam optimizer to train efficiently. The dataset consists of images of various house plants, categorized into 47 classes with a total of 15,131 images. The ResNet-50 DL architecture has been used and, as an SVM classifier, has performed multi-class classification. The dataset has been divided into training (80%) and testing (20%) sets. The model has been trained for 10 epochs. The proposed model has achieved an impressing accuracy of 98.80%, thereby proving to identify plant species in a more precise manner. As shown by the loss curve, training and validation loss decreased steadily throughout the process. This apparently indicates that the model converged appropriately. The results demonstrate how the SVM-ResNet-50 hybrid is capable of alleviating complex image classification t asks. The major challenge for this experiment was the model’s insensitivity to changes caused in images by lighting and angles. Further work in the future will focus on enriching the model through more augmentation techniques and data augmentation to enhance generalization and robustness. Another possible improvement of the model is to implement attention mechanisms to better concentrate on important features.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>10.3389/fpls.2023.1155341</t>
+          <t>10.1109/ICCC57789.2023.10165629</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Complete genome sequence of an Israeli isolate of Xanthomonas hortorum pv. pelargonii strain 305 and novel type III effectors identified in Xanthomonas</t>
+          <t>Classification of leaf spot diseases in banana using pre-trained convolutional neural networks</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>N., Wagner, Naama; D., Ben-Meir, Daniella; D.D., Teper, Doron Dov; T., Pupko, Tal</t>
+          <t>D. Mathew; C. S. Kumar; K. Anita Cherian</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -4432,286 +4448,286 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Frontiers in Plant Science</t>
+          <t>2023 International Conference on Control, Communication and Computing (ICCC)</t>
         </is>
       </c>
       <c r="F98" t="n">
         <v>2</v>
       </c>
       <c r="G98" t="n">
-        <v>0.8389540314674377</v>
+        <v>0.4572099447250366</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Xanthomonas hortorum pv. pelargonii is the causative agent of bacterial blight in geranium ornamental plants, the most threatening bacterial disease of this plant worldwide. Xanthomonas fragariae is the causative agent of angular leaf spot in strawberries, where it poses a significant threat to the strawberry industry. Both pathogens rely on the type III secretion system and the translocation of effector proteins into the plant cells for their pathogenicity. Effectidor is a freely available web server we have previously developed for the prediction of type III effectors in bacterial genomes. Following a complete genome sequencing and assembly of an Israeli isolate of Xanthomonas hortorum pv. pelargonii - strain 305, we used Effectidor to predict effector encoding genes both in this newly sequenced genome, and in X. fragariae strain Fap21, and validated its predictions experimentally. Four and two genes in X. hortorum and X. fragariae, respectively, contained an active translocation signal that allowed the translocation of the reporter AvrBs2 that induced the hypersensitive response in pepper leaves, and are thus considered validated novel effectors. These newly validated effectors are XopBB, XopBC, XopBD, XopBE, XopBF, and XopBG. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>Banana is a leading fruit crop in the global market and is grown all over the world. However, its production and trade are severely affected by the diseases caused by fungi, bacte- ria and viruses. Early diagnosis and management of such diseases are essential to avoid the yield loss. This paper demonstrates a deep learning based automated algorithm for the classification of three important leaf spot diseases in banana namely, Sigatoka, Cordana and Deightoneilla. Images of banana leaves infected with these diseases have been applied to four augmented pre-trained convolutional neural networks and their performance in disease classification is compared. An accuracy of 91.7% is achieved on the model with DenseNet 121 backbone.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>10.1007/978-981-19-9876-8_25</t>
+          <t>10.1109/ICIRCA65293.2025.11089838</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Soil Classification Using Machine Learning, Deep Learning, and Computer Vision: A Review</t>
+          <t>A Novel Attention Mechanism for Disease Detection in Potatoes</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>A., Kumar, A.; J., Kaur, Jagdeep</t>
+          <t>S. A; K. S. Tamilselvan; M. R; D. P. E L; N. Gomathi; V. V R</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lecture Notes in Electrical Engineering</t>
+          <t>2025 6th International Conference on Inventive Research in Computing Applications (ICIRCA)</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G99" t="n">
-        <v>0.796586275100708</v>
+        <v>0.6815060377120972</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 7: system, pesticide, solution</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>The goal of this work is to examine the primary soil variables that impact crop development, such as organic matter, vital plant nutrients, and micronutrients, and to determine the appropriate connection proportion among those qualities using ML and DL models. Agriculture relies heavily on the soil. Different kinds of dirt can be found in various locations. Each type of soil can have unique characteristics to develop crops. To cultivate crops in diverse soil types, we need to know which kind of soil is best. Accurate soil moisture and temperature forecast are beneficial to agriculture planting factors. According to the review articles, machine learning approaches, deep learning prediction models, and computer vision are helpful in this instance. The external temperature and humidity and soil moisture and temperature are used to train and test to anticipate soil moisture and temperature. A deep learning model was developed based on the extended short-term memory network (LSTM). Machine learning models such as k-nearest neighbor, SVM, and RF methods are utilized for soil classification. Several contributions of computer vision models in fields like planting, harvesting, enhanced weather analysis, weeding, and plant health detection and monitoring have been shown in the application of computer vision in soil categorization. This paper presents a review of soil classification and various challenges associated with it using machine learning, deep learning, and computer vision. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>The potato plant is amongst the most significant vegetable crops farmed worldwide. It is rich in vitamin B12, considered to be the best ever compensation of vitamin B12 for vegetarians as it is abundantly present in non-veg foods. Potato is the most preferred vegetable to consume from kids to adults. The potato crop is prone to numerous infections like bacterial, fungal, and viral infections in its growing stages. The production is immensely affected by the diseases that occur in its sprout development stage. Diseases that occur in crops hinder the economy of agriculture as they lead to huge demands. The predominant devastating diseases influencing the growth and production of potatoes are late and early blight diseases. Detecting the diseases, especially the diseases that occurred in its initial stages, assists in preventing the loss in production and to improve the yield. A decrease in production results in increasing cost and demand. The proposed work incorporating the modified AttDenseNet architecture with the layers of Convolutional neural network layers proceeded by self-attention and co-attention mechanisms assist in predicting the disease in its earlier stages, proffers accuracy of 98.7 percent in detecting the diseases in potatoes in a maximum number of epochs.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>10.1109/ICAECT57570.2023.10117860</t>
+          <t>10.1109/CGiV.2016.34</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>A Comparative Study of Deep Learning Models for Guava Leaf Disease Detection</t>
+          <t>Automatic Recognition of the Damages and Symptoms on Plant Leaves Using Parallel Combination of Two Classifiers</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>R., Thangaraj, R.; M.R., Mohan, M. Raj; M., Moulik, M.; A., Logeshwari, A.; T., Loganathan, T.; P., Koushika, P.</t>
+          <t>I. El Massi; Y. Es-Saady; M. El Yassa; D. Mammass; A. Benazoun</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>2016 13th International Conference on Computer Graphics, Imaging and Visualization (CGiV)</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G100" t="n">
-        <v>0.7037473320960999</v>
+        <v>0.486023336648941</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Plant diseases are regarded as one of the major variables affecting food production and reducing production losses. Early identification and disease diagnosis of fruit crops are essential for the food industry to increase production. The development of the healthy fruit sector is highly dependent on plant diseases. Guava fruit is a good source of fiber, calcium, pectins, and vitamin C. Guava disease has become a major issue for guava production, which has a negative impact on farmers' socioeconomic growth. Infections that harm guava plants and fruits pose the greatest obstacles, although they can be avoided by early identification. Deep learning has recently been widely used to automatically identify a variety of diseases that cannot be seen with the human eye. In this study, convolution neural models are suggested to use leaf images to detect guava disease. The presented models can be used to categorize the main guava leaf diseases, including Canker, Dot, Healthy, Mummification and Rust. The kaggle dataset is used to gather images of guava with the disease Canker, Dot, Healthy, Mummification and Rust. In our work, CNN models like DenseNet121, DenseNet169, InceptionV3, and Xception are used to categorize the diseases that affect guava leaves. The experimental findings indicate that, with an accuracy of 96.12%, the DenseNet169 model outperformed other models. When the model's effectiveness is assessed using performance metrics like precision, recall, and F1 score, the results demonstrate that DenseNet169 gives excellent results. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>This study presents a multiple classifier system for automatic recognition of the damages and symptoms on plant leaves from images. The proposed approach is based on parallel combination of two kinds of classifiers, one is a neural network classifier that uses texture, color and shape features to distinguish between the damages and symptoms, then the other is a support vector machine (SVM) classifier that uses texture and shape features. In order to design our system, we have based on some existing approaches in the field that adopt a single classifier. The tests of this study were carried out on six classes including the damages of three pest insects (Leaf miners, Thrips and Tuta absoluta) and symptoms of three fungal diseases (Early blight, Late blight and Powdery mildew). The experimental results show the efficiency of our approach compared to the pervious approaches based on single classifier. The proposed approach is more effective and has the highest rate of recognition.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>10.7717/PEERJ.15147</t>
+          <t>10.1109/INCIP64058.2025.11020033</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Enhanced reptile search optimization with convolutional autoencoder for soil nutrient classification model</t>
+          <t>Performance Analysis of Machine and Deep Learning Techniques for Pomegranate Fruit Disease Detection and Classification</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>R., Prabavathi, R.; B.J., Chelliah, Balika J.</t>
+          <t>Narayana, D.V.; B․, B.; Reddy, Y.V.; Chikmurge, A.; Mayur, R.; Lokesh, T.</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>PeerJ</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G101" t="n">
-        <v>0.9951870441436768</v>
+        <v>0.3165832161903381</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Background: Soil nutrients play an important role in soil fertility and other environmental factors. Soil testing is an effective tool for evaluating soil nutrient levels and calculating the appropriate quantitative of soil nutrients based on fertility and crop requirements. Because traditional soil nutrient testing models are impractical for real-time applications, efficient soil nutrient and potential hydrogen (pH) prediction models are required to improve overall crop productivity. Soil testing is an effective method to evaluate the presence of nutrient status of soil and assists in determining appropriate nutrient quantity. Methods: Various machine learning (ML) models proposed, predict the soil nutrients, soil type, and soil moisture. To assess the significant soil nutrient content, this study develops an enhanced reptile search optimization with convolutional autoencoder (ERSOCAE-SNC) model for classifying and predicting the fertility indices. The model majorly focuses on the soil test reports. For classification, CAE model is applied which accurately determines the nutrient levels such as phosphorus (P), available potassium (K), organic carbon (OC), boron (B) and soil pH level. Since the trial-and-error method for hyperparameter tuning of CAE model is a tedious and erroneous process, the ERSO algorithm has been utilized which in turn enhances the classification performance. Besides, the ERSO algorithm is derived by incorporating the chaotic concepts into the RSO algorithm. Results: Finally, the influence of the ERSOCAE-SNC model is examined using a series of simulations. The ERSOCAE-SNC model reported best results over other approaches and produces an accuracy of 98.99% for soil nutrients and 99.12% for soil pH. The model developed for the ML decision systems will help the Tamil Nadu government to manage the problems in soil nutrient deficiency and improve the soil health and environmental quality. Also reduces the input expenditures of fertilizers and saves time of soil experts. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>Pomegranate (Punica granatum) is a fruit crop with great nutritional and economic values; it has been touted in various parts of the world, especially the Mediterranean, Middle East, and South Asia, for health benefits. However, with more intense effort to increase yield and production, the production of the pomegranate crop is threatened by many diseases caused by pathogens such as fungi, bacteria, and viruses. Traditional diagnosis methodologies are based on the visual inspection of farmers and experts in agriculture, which takes a longer time and also rely on human judgment and may lead to some mistakes. To overcome these challenges this research utilizes the ML and DL methods like SVM, KNN, and CNN for the automatic identification and classification of diseases related to pomegranate. Dataset contains five classes such as Healthy, Anthracnose, Bacterial Blight, Cercospora, and Alternaria. We performed many task in this research like pre-processing, feature extraction to improve the model performance. Each model is trained and tested for detection and classification. KNN got 82% accuracy, which is pretty good but struggles a bit with similar disease traits. SVM performed the best and outwitted KNN with an outstanding accuracy of 93%. The SVM model classified the diseases efficaciously with high sensitivity and specificity in the ROC curve. The CNN model achieved about 98% after it had passed over 10-50 epochs, which had improved incrementally with every epoch. The results confirm that DL is a promising solution for pomegranate disease detection, offering more efficiency and reliability than traditional methods. It supports early disease identification, aiding farmers and experts in better crop management and productivity. © 2025 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>10.1007/978-981-19-8136-4_35</t>
+          <t>10.1109/ICNC.2008.371</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Disease Detection in Tomato Leaves Using Raspberry Pi-Based Machine Learning Model</t>
+          <t>Prediction and early warning method for flea beetle based on semi-supervised learning algorithm</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>J., Rahul, Jagdeep; L.D., Sharma, Lakhan Dev; R., Bhardwaj, Rishav; R.S., Singh, Ram Sewak</t>
+          <t>Li, T.; Yang, J.; Peng, X.; Chen, Z.; Luo, C.</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2023</v>
+        <v>2008</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Lecture Notes in Electrical Engineering</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0.4780805110931396</v>
+        <v>0.8136895895004272</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 2: approach, data, grape</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>The income of farmers is very low, mostly all over the world, as compared to other professions. They are the primary producers of our food, but they still live in poverty. There are many reasons for this, but one of these is damage caused to their crops by different diseases, either caused by some bacteria, viruses, or some mineral deficiency diseases. They have a deleterious impact on crops, lowering both quality and quantity. In this paper, we have used image processing and k-nearest neighbours (KNN)-based algorithm to detect plant disease with an implementation on the Raspberry Pi. At first, the leaf image is segmented, and later features such as area, entropy, and aspect ratio are extracted. These features are fed to the KNN classifier to get the desired result. Using this technology, it will have a significant impact on farming. The cost of fertilizers and excessive or wrong use of pesticides can be reduced, and hence, it can lead to an increase in productivity. The accuracy we have achieved is 96%. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>The prediction and early warning for vegetable crop diseases and insect pests commonly based on experts' knowledge of plant protection while math modeling methods are used to analyze the associated data quantitatively scarcely. This paper takes advantage of labeled historical data to extract association rules as the supervised information, and combining with the use of the unsupervised learning method iterative self- organizing data analysis techniques algorithm (ISODATA) to establish the model semi-supervised learning algorithm for predicting and early warning vegetable pest flea beetle. Semi-supervised learning algorithm not only obtains a high accuracy of supervised learning method, but also takes advantage of the flexibility of unsupervised learning method, which is significative for both research and practice. The experimental results of Guangdong vegetable pest flea beetle show the prediction and early warning accuracy of semi-supervised learning method provides a higher accuracy rate than that of k-mean clustering, support vector machine and RBF neural network in the same condition. © 2008 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>10.2196/45332</t>
+          <t>10.1109/GCAT62922.2024.10923907</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Predicting Unreported Micronutrients from Food Labels: Machine Learning Approach</t>
+          <t>Branching Out: A Simple 5-Level Classification of Magnolia Scale Diseases Using a Combination of CNN and DT Models</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>R., Razavi, Rouzbeh; G., Xue, Guisen</t>
+          <t>R. Sharma; M. Nagpal</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Journal of Medical Internet Research</t>
+          <t>2024 5th IEEE Global Conference for Advancement in Technology (GCAT)</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>0.5302886962890625</v>
+        <v>0.4898054003715515</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Background: Micronutrient deficiencies represent a major global health issue, with over 2 billion individuals experiencing deficiencies in essential vitamins and minerals. Food labels provide consumers with information regarding the nutritional content of food items and have been identified as a potential tool for improving diets. However, due to governmental regulations and the physical limitations of the labels, food labels often lack comprehensive information about the vitamins and minerals present in foods. As a result, information about most of the micronutrients is absent from existing food labels. Objective: This paper aims to examine the possibility of using machine learning algorithms to predict unreported micronutrients such as vitamin A (retinol), vitamin C, vitamin B1 (thiamin), vitamin B2 (riboflavin), vitamin B3 (niacin), vitamin B6, vitamin B12, vitamin E (alpha-tocopherol), vitamin K, and minerals such as magnesium, zinc, phosphorus, selenium, manganese, and copper from nutrition information provided on existing food labels. If unreported micronutrients can be predicted with acceptable accuracies from existing food labels using machine learning predictive models, such models can be integrated into mobile apps to provide consumers with additional micronutrient information about foods and help them make more informed diet decisions. Methods: Data from the Food and Nutrient Database for Dietary Studies (FNDDS) data set, representing a total of 5624 foods, were used to train a diverse set of machine learning classification and regression algorithms to predict unreported vitamins and minerals from existing food label data. For each model, hyperparameters were adjusted, and the models were evaluated using repeated cross-validation to ensure that the reported results were not subject to overfitting. Results: According to the results, while predicting the exact quantity of vitamins and minerals is shown to be challenging, with regression R2 varying in a wide range from 0.28 (for magnesium) to 0.92 (for manganese), the classification models can accurately predict the category (“low,” “medium,” or “high”) level of all minerals and vitamins with accuracies exceeding 0.80. The highest classification accuracies for specific micronutrients are achieved for vitamin B12 (0.94) and phosphorus (0.94), while the lowest are for vitamin E (0.81) and selenium (0.83). Conclusions: This study demonstrates the feasibility of predicting unreported micronutrients from existing food labels using machine learning algorithms. The results show that the approach has the potential to significantly improve consumer knowledge about the micronutrient content of the foods they consume. Integrating these predictive models into mobile apps can enhance their accessibility and engagement with consumers. The implications of this research for public health are noteworthy, underscoring the potential of technology to augment consumers’ understanding of the micronutrient content of their diets while also facilitating the tracking of food intake and providing personalized recommendations based on the micronutrient content and individual preferences. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>Checking and sorting Magnolia Scale diseases is very important for keeping plants healthy and making sure they get the best crop output in farming. In this work, introduce a new mix using Convolutional Neural Networks (CNN) and Decision Trees (DT). It helps to sort Magnolia Scale diseases into five agreed severity levels. The mix of CNN and DT models does well. It gets 96 out of 100 right at guessing how bad the infestation with the Magnolia Scale is. Using what’s known as transfer learning, the CNN part takes important features from an existing deep learning system. Then it adjusts these learned features to special traits of a set of Magnolia Scale images for disease identification after fine-tuning. After that, adding the results from a process called CNN into a group of choices helps make the model better. It also makes it strong and gives exact levels for how serious something is. Accuracy measurements such as precision, recall, and F1-scores above 90% across all disease severity levels show that the model is dependable and accurate in spotting different stages of illnesses. The research shows that the mixed model can be very important in disease control plans for gardening. It provides accurate and sure evaluation skills needed to find diseases early on so action can be taken quickly. This study sets the building blocks for improving ways of checking diseases and it looks promising to change disease control methods in plants outside Magnolia. This could improve plant health and make farming more sustainable without just thinking about Magnolia flowers.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>10.1007/978-981-19-7169-3_8</t>
+          <t>10.1109/ICSET65917.2025.11283911</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deep Learning Based Recognition of Plant Diseases</t>
+          <t>Machine Learning (ML) and Deep Learning (DL) Based Detection of Bacterial Heart Rot (BHR) in Pineapple Leaves</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>S., Parthiban, Swetha; S., Moorthy, Sneha; S., Sabanayagam, Sribalaji; S., Shanmugasundaram, Shobana; A., Naganathan, Athishwaran; M., Annamalai, Mohan; B., Sabitha, B.</t>
+          <t>Z. Zaludin; N. S. Khalid; N. D. B. N. Danial; M. N. Ayob; M. Z. Hasan; I. I. Ibrahim</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Lecture Notes in Electrical Engineering</t>
+          <t>2025 IEEE 15th International Conference on System Engineering and Technology (ICSET)</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G104" t="n">
-        <v>0.5277950167655945</v>
+        <v>0.695757269859314</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Tópico 2: tomato, fruit, grape</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Every country's primary requirement is agricultural products. Infected plants have an impact on the agricultural production and economic resources of a country. Early detection of plant diseases minimizes the risk of crop loss by allowing farmers to adopt curative and preventative actions to avoid further damage. Citrus is a large plant that is primarily grown in tropical areas of the world because of its high vitamin C and other key nutrient content. Citrus plant diseases play a vital role in causing a great financial loss to the farmers and affect the economy of the country. The tomato ranks among the most economically important vegetable crops, with a global production rate of around 200 million tonnes. But due to diseases occurring in the tomato plants, the farmers are facing a great loss. To prevent these losses and provide an immediate cure, we create a model to detect plant diseases. To get a better performance model, the data augmentation process is used, and we got 18,392 images. In our model, we used a convolutional neural network (CNN) to classify the citrus and tomato leaf diseases. The diseases are Mancha Graxa, Citrus Canker, Tomato Early Blight, Tomato Septoria Leafspot, Tomato Spider Mite Two-spotted spider mite (Tetranychus urticae), Tomato mosaic virus (Tobamovirus), Tomato yellow leaf curl virus (Begomovirus), Tomato Target Spot (Corynespora cassiicola). Convolution Neural Network (CNN) is stacked by multiple convolutions and pooling layers to detect plant leaf diseases. We train a model with augmented images. After the model gets trained, it is thoroughly tested to ensure that the results are accurate. Thereby we were able to achieve high validation accuracy with a rate of (97.02%) for this dataset used. As the results showed, applying the deep CNN model to identify diseases could greatly impact the accurate identification of diseases, and could even prove useful in detecting diseases in real-time agricultural systems. © 2024 Elsevier B.V., All rights reserved.</t>
+          <t>Bacterial Heart Rot (BHR) is a major disease affecting pineapple (Ananas comosus) cultivation, with detrimental impacts on agricultural sustainability and productivity. Conventional or traditional detection methods are often hindered by inconsistency and subjectivity. BHR infected fruits, even when harvested, exhibit accelerated spoilage, reduced shelf life, and increased post-harvest losses. Consequently, growers and farmers experience significant economic losses due to decreased marketable yield and the necessity for additional disease management interventions. Hence, this study investigates the possibility using Artificial Intelligence (AI) techniques for the detection and classification of BHR severity in pineapple leaves. A comparative analysis is conducted between a deep learning model utilizing Convolutional Neural Networks (CNN) and a traditional machine learning algorithm employing K-Nearest Neighbors (KNN). Both models are trained and tested on image-based datasets and evaluated using standard performance metrics, including accuracy, precision, recall, and confusion matrices. Experimental results indicate that while both models demonstrate reasonable classification performance, the CNN-based approach achieves superior accuracy and generalization capability. These findings proved the potential of AI-driven systems in supporting precision agriculture by facilitating timely, scalable, and reliable disease detection in crop management practices.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>10.1007/s10661-022-10561-3</t>
+          <t>10.1109/ICCUBEA58933.2023.10391966</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mobile application using DCDM and cloud-based automatic plant disease detection</t>
+          <t>Machine Learning for Accurate and Efficient Pomegranate Fruit Disease Detection: A Novel Approach to Improve Crop Yield and Quality</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>P., Kumar, Parasuraman; S., Raghavendran, Srinivasan; K., Silambarasan, K.; K.S., Kannan, K. Senthamarai; N., Krishnan, Nallaperumal</t>
+          <t>Wakhare, P.; Neduncheliyan, S.; Mane, P.B.</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4719,40 +4735,40 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Environmental Monitoring and Assessment</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G105" t="n">
-        <v>0.5543388724327087</v>
+        <v>0.4315369129180908</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Farming has a plethora of difficult responsibilities, and plant monitoring is one of them. There is also an urgent need to increase the number of alternative techniques for detecting plant diseases, which is now lacking. The agriculture and agricultural support sectors in India provide employment for the great majority of the country’s people. In India, the agricultural production of the country is directly connected to the country’s economic growth rate. In order to sustain healthy plant development, a variety of processes must be followed, including consideration of environmental factors and water supply management for the optimal production of crops. It is inefficient and uncertain in its outcomes to use the traditional method of watering a lawn. The devastation of more than 18% of the world’s agricultural produce is caused by disease attacks on an annual basis. Because it is difficult to execute these activities manually, identifying plant diseases is essential to decreasing losses in the agricultural product business. In addition to diagnosing a wide range of plant ailments, our method also includes the identification of infections as a prophylactic step. Below is a detailed description of a farm-based module that includes numerous cloud data centers and data conversion devices for accurately monitoring and managing farm information and environmental elements. This procedure involves imaging the plant’s visually obvious signs in order to identify disease. It is recommended that the therapy be used in conjunction with an application to minimize any harm. Increased productivity as a result of the suggested approach would help both the agricultural and irrigation sectors. The plant area module is fitted with a mobile camera that captures images of all of the plants in the area, and all of the plants’ information is saved in a database, which is accessible from any computer with Internet access. It is planned to record information on the plant’s name, the type of illness that has been afflicted, and an image of the plant. In a wide range of applications, bots are used to collect images of various plants as well as to prevent disease transmission. To ensure that all information given is retained on the Internet, data is collected and stored in cloud storage as it becomes essential to regulate the condition. According to our findings from our research on wide images of healthy and ill fruit and plant leaves, real-time diagnosis of plant leaf diseases may be done with 98.78% accuracy in a laboratory environment. We utilized 40,000 photographs and then analyzed 10,000 photos to construct a DCDM deep learning model, which was then used to train additional models on the data set. Using a cloud-based image diagnostic and classification service, consumers may receive information about their condition in less than a second on average, with the process requiring only 0.349 s on average. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>This paper presents a web-based tool for identifying diseases in fruit crops to address the negative impact of climate change on agriculture. With the increase in population, there is a growing demand for more food production, which puts pressure on farmers to increase crop yields. However, climate change is causing uneven weather conditions, leading to decreased crop yields. This paper proposes a solution that allows farmers to upload an image of a fruit to a system that has a trained dataset of fruit images. The system uses several image processing steps, including feature extraction based on parameters such as color, morphology, and CCV, followed by clustering using CNN Algorithm and classification using SVM to determine if the fruit is infected or not. An intent search technique is used to find the user intention from the features extracted. The experimental evaluation of the approach shows that it is effective, with a 98.38% accuracy rate in identifying diseases in fruit crops. The proposed tool can be used to identify the diseases that affect fruit crops and provide farmers with timely and accurate information, enabling them to take preventive measures to protect their crops, improve crop yields, and contribute to the overall agricultural economy. The recommendations for the application of the developed machine learning model for pomegranate fruit disease detection include using high-quality data, regularly updating the model, integrating with other detection methods, providing an easy-to-use interface, and providing technical support to growers. © 2023 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>10.3390/app122412557</t>
+          <t>10.1109/ICAC3N56670.2022.10074491</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Horticulture 4.0: Adoption of Industry 4.0 Technologies in Horticulture for Meeting Sustainable Farming</t>
+          <t>Disease Detection in Plants Using KNN Algorithm</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>R., Singh, Rajat; R., Singh, Rajesh; A.N., Gehlot, Anita N.; S.V., Akram, Shaik Vaseem; N., Priyadarshi, Neeraj; B., Twala, Bhekisipho</t>
+          <t>S. Garg; D. Dixit; S. S. Yadav</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4760,696 +4776,696 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Applied Sciences (Switzerland)</t>
+          <t>2022 4th International Conference on Advances in Computing, Communication Control and Networking (ICAC3N)</t>
         </is>
       </c>
       <c r="F106" t="n">
         <v>4</v>
       </c>
       <c r="G106" t="n">
-        <v>0.4738219678401947</v>
+        <v>0.7418451905250549</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>The United Nations emphasized a significant agenda on reducing hunger and protein malnutrition as well as micronutrient (vitamins and minerals) malnutrition, which is estimated to affect the health of up to two billion people. The UN also recognized this need through Sustainable Development Goals (SDG 2 and SDG 12) to end hunger and foster sustainable agriculture by enhancing the production and consumption of fruits and vegetables. Previous studies only stressed the various issues in horticulture with regard to industries, but they did not emphasize the centrality of Industry 4.0 technologies for confronting the diverse issues in horticulture, from production to marketing in the context of sustainability. The current study addresses the significance and application of Industry 4.0 technologies such as the Internet of Things, cloud computing, artificial intelligence, blockchain, and big data for horticulture in enhancing traditional practices for disease detection, irrigation management, fertilizer management, maturity identification, marketing, and supply chain, soil fertility, and weather patterns at pre-harvest, harvest, and post-harvest. On the basis of analysis, the article identifies challenges and suggests a few vital recommendations for future work. In horticulture settings, robotics, drones with vision technology and AI for the detection of pests, weeds, plant diseases, and malnutrition, and edge-computing portable devices that can be developed with IoT and AI for predicting and estimating crop diseases are vital recommendations suggested in the study. © 2022 Elsevier B.V., All rights reserved.</t>
+          <t>India is widely acknowledged as the world's fundamental producer of spices, grains, rice harvests etc. The characteristics of theyield, that defined by the plants growth and harvest. As a result, disease identification in plants is critical in the sector of cultivation. Plants are highly prone to infections, that disturb the plant's progress &amp;, as a result, disrupt the natural balance of the agronomist. The need for an automatic disease detection process is advantageous in identifying a plant disease at an early stage.Pre-processing, feature extraction, segmentation, and classification are all steps in plant disease detection algorithms.The performance of the KNN classifier is examined, and it is discovered that the KNN classifier has higher accuracy and less fault detection than other techniques.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>10.1186/s13007-022-00871-5</t>
+          <t>10.1109/ICTBIG59752.2023.10456200</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Predictive modeling of Persian walnut (Juglans regia L.) in vitro proliferation media using machine learning approaches: a comparative study of ANN, KNN and GEP models</t>
+          <t>Smart Environment and Plant Disease Monitoring with Analysis System in Agricultural Field</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>M., Sadat Hosseini Grouh, Mohammad; M.M., Arab, Mohammad Mehdi; M., Soltani, Mohammad; M., Eftekhari, Maliheh; A., Soleimani, Amanollah; K., Vahdati, Kourosh</t>
+          <t>M. Kavitha; S. Senthilkumar; K. Kalaivani; E. Saranya; P. Arunkumar; V. Malu</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Plant Methods</t>
+          <t>2023 IEEE International Conference on ICT in Business Industry &amp; Government (ICTBIG)</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G107" t="n">
-        <v>0.4689224064350128</v>
+        <v>0.9892768859863281</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Background: Optimizing plant tissue culture media is a complicated process, which is easily influenced by genotype, mineral nutrients, plant growth regulators (PGRs), vitamins and other factors, leading to undesirable and inefficient medium composition. Facing incidence of different physiological disorders such as callusing, shoot tip necrosis (STN) and vitrification (Vit) in walnut proliferation, it is necessary to develop prediction models for identifying the impact of different factors involving in this process. In the present study, three machine learning (ML) approaches including multi-layer perceptron neural network (MLPNN), k-nearest neighbors (KNN) and gene expression programming (GEP) were implemented and compared to multiple linear regression (MLR) to develop models for prediction of in vitro proliferation of Persian walnut (Juglans regia L.). The accuracy of developed models was evaluated using coefficient of determination (R2), root mean square error (RMSE) and mean absolute error (MAE). With the aim of optimizing the selected prediction models, multi-objective evolutionary optimization algorithm using particle swarm optimization (PSO) technique was applied. Results: Our results indicated that all three ML techniques had higher accuracy of prediction than MLR, for example, calculated R2 of MLPNN, KNN and GEP vs. MLR was 0.695, 0.672 and 0.802 vs. 0.412 in Chandler and 0.358, 0.377 and 0.428 vs. 0.178 in Rayen, respectively. The GEP models were further selected to be optimized using PSO. The comparison of modeling procedures provides a new insight into in vitro culture medium composition prediction models. Based on the results, hybrid GEP-PSO technique displays good performance for modeling walnut tissue culture media, while MLPNN and KNN have also shown strong estimation capability. Conclusion: Here, besides MLPNN and GEP, KNN also is introduced, for the first time, as a simple technique with high accuracy to be used for developing prediction models in optimizing plant tissue culture media composition studies. Therefore, selection of the modeling technique to study depends on the researcher’s desire regarding the simplicity of the procedure, obtaining clear results as entire formula and/or less time to analyze. © 2022 Elsevier B.V., All rights reserved.</t>
+          <t>Agriculture is deemed to be the most significant segment in India. The main objective of this research work is to monitor plant diseases and analyze the system using a smartphone. The remote monitoring framework, including temperature, stickiness and soil humidity sensors, a microcontroller, an ultrasonic sensor, a camera, and a GSM module is validated for effective environment observation. The technology could offer a fresh method for farming to obtain information related to agriculture. In this monitoring system of agricultural diseases, the main aim is to achieve disease monitoring information and collections of the results are detected by Android application through GSM. ARM processor is used for analog to digital converter (ADC) and sends the gathered information to portable through GSM. An IP web camera is occasionally empowered to catch the plant leaf picture for disease checking and an ultrasonic sensor is utilized with the end goal of plant development checking. It uses a soil battery to drive the temperature sensor to foster plant development checking framework and plant infection observation, likewise adaptive android application to screen such circumstances by utilizing this innovation to accomplish a green hardware framework.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10.1609/aaai.v36i11.21512</t>
+          <t>10.1109/InCACCT65424.2025.11011320</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Micronutrient Deficiency Prediction via Publicly Available Satellite Data</t>
+          <t>Deep Learning-based Mango Leaf Disease Detection using Yolov8</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>E., Bondi-Kelly, Elizabeth; H., Chen, Haipeng; C.D., Golden, Christopher D.; N., Behari, Nikhil; M., Tambe, Milind</t>
+          <t>G. O. S; P. Perugu; J. S; R. Mahajan; J. G. M. A; R. Sheeja; AhilanAppathurai; Aarti</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Proceedings of the AAAI Conference on Artificial Intelligence</t>
+          <t>2025 3rd International Conference on Advancement in Computation &amp; Computer Technologies (InCACCT)</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>0.457623302936554</v>
+        <v>0.5632565021514893</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Micronutrient deficiency (MND), which is a form of malnutrition that can have serious health consequences, is difficult to diagnose in early stages without blood draws, which are expensive and time-consuming to collect and process. It is even more difficult at a public health scale seeking to identify regions at higher risk of MND. To provide data more widely and frequently, we propose an accurate, scalable, low-cost, and interpretable regional-level MND prediction system. Specifically, our work is the first to use satellite data, such as forest cover, weather, and presence of water, to predict deficiency of micronutrients such as iron, Vitamin B12, and Vitamin A, directly from their biomarkers. We use real-world, ground truth biomarker data collected from four different regions across Madagascar for training, and demonstrate that satellite data are viable for predicting regional-level MND, surprisingly exceeding the performance of baseline predictions based only on survey responses. Our method could be broadly applied to other countries where satellite data are available, and potentially create high societal impact if these predictions are used by policy makers, public health officials, or healthcare providers. © 2025 Elsevier B.V., All rights reserved.</t>
+          <t>The mango holds a significant position in India's fruit crop rotation and plays a major part in the nation's economy. The best strategy to avoid losing money and time is to recognize diseases in crops earlier. Obtaining a comprehensive dataset can be challenging and time-consuming. Additionally, deep learning models may struggle with detecting early-stage symptoms of diseases. In this work, a novel deep learning-based model is proposed for the early detection of mango leaf disease (MLD). An adaptive unsharp mask-guided (AUG) filter is used as a pre-processing step to improve the input pictures from the collected dataset. The enhanced images are fed into the YOLOV8 model for detecting mango leaf disease (MLD) and classifying the different kinds of disease. According to the experimental result, the proposed model attains a 99.29% success rate for the classification of disease in mango leaf. The proposed approach is compared to DL methods such as SSD, Mask RCNN, and YOLO v8. The detection accuracy is improved by the YOLO network over SSD, Mask R-CNN, and Yolo v8 by 7.57%, 4.89%, and 2.36%, respectively. In comparison to SVM, ANN, and CNN-HOG, the proposed approach advances the overall accuracy range by 4.72%, 0.73%, 13.18%, and 5.44%, respectively.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>10.3389/fpls.2022.884903</t>
+          <t>10.1109/ICICCS56967.2023.10142319</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>A Caps-Ubi Model for Protein Ubiquitination Site Prediction</t>
+          <t>An Organized Examination of Image Processing for Detection and Diagnosis of Plant Diseases</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Y., Luo, Yin; J., Jiang, Jiulei; J., Zhu, Jiajie; Q., Huang, Qiyi; W., Li, Weimin; Y., Wang, Ying; Y., Gao, Yamin</t>
+          <t>M. Naveenkumar; M. Akila</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Frontiers in Plant Science</t>
+          <t>2023 7th International Conference on Intelligent Computing and Control Systems (ICICCS)</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.9478254318237305</v>
+        <v>0.4503737986087799</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Ubiquitination, a widespread mechanism of regulating cellular responses in plants, is one of the most important post-translational modifications of proteins in many biological processes and is involved in the regulation of plant disease resistance responses. Predicting ubiquitination is an important technical method for plant protection. Traditional ubiquitination site determination methods are costly and time-consuming, while computational-based prediction methods can accurately and efficiently predict ubiquitination sites. At present, capsule networks and deep learning are used alone for prediction, and the effect is not obvious. The capsule network reflects the spatial position relationship of the internal features of the neural network, but it cannot identify long-distance dependencies or focus on amino acids in protein sequences or their degree of importance. In this study, we investigated the use of convolutional neural networks and capsule networks in deep learning to design a novel model “Caps-Ubi,” first using the one-hot and amino acid continuous type hybrid encoding method to characterize ubiquitination sites. The sequence patterns, the dependencies between the encoded protein sequences and the important amino acids in the captured sequences, were then focused on the importance of amino acids in the sequences through the proposed Caps-Ubi model and used for multispecies ubiquitination site prediction. Through relevant experiments, the proposed Caps-Ubi method is superior to other similar methods in predicting ubiquitination sites. © 2022 Elsevier B.V., All rights reserved.</t>
+          <t>Agriculture is one of the most important and necessary sources of national wealth. Plant and crop diseases are one of the major factors that affect output quality and quantity. Lack of quality and quantity in food production creates a negative impact on the economy as well. Hence, it is crucial to identify plant diseases. Studies reveal a wide range of plant diseases occurring in different parts of the world. Various components of plants exhibit symptoms of plant diseases especially, the leaves. Extensive research is conducted across the globe and many horticulture specialists in liaison with technological experts apply computer vision and soft computing methods to automatically detect plant diseases from leaf photos. This article provides a summary of several aspects of such studies, along with their benefits and drawbacks. The authors addresses common infections as well as the state of such detection systems’ research at various stages. The current feature extraction methods are examined in order to determine which one seems to function best across a variety of crop categories. This study will aid researchers in their understanding of the use of computer vision for identifying and categorizing plant diseases.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>10.3390/computers11050082</t>
+          <t>10.1109/ICAISS58487.2023.10250558</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Botanical Leaf Disease Detection and Classification Using Convolutional Neural Network: A Hybrid Metaheuristic Enabled Approach</t>
+          <t>Machine Learning and Internet of Things for infection Prediction in Fruits and Vegetables</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>M., Mohapatra, Madhumini; A.K., Parida, Ami Kumar; P.K., Mallick, Pradeep Kumar; M.L., Zymbler, Mikhail L.; S., Kumar, Sachin</t>
+          <t>B. Manjunatha; K. S. Moorthy; V. Srinivasan; M. Awasthi; M. Ashok; M. Suresh</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Computers</t>
+          <t>2023 Second International Conference on Augmented Intelligence and Sustainable Systems (ICAISS)</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G110" t="n">
-        <v>0.7388099431991577</v>
+        <v>0.7326192855834961</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Tópico 2: tomato, fruit, grape</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Botanical plants suffer from several types of diseases that must be identified early to improve the production of fruits and vegetables. Mango fruit is one of the most popular and desirable fruits worldwide due to its taste and richness in vitamins. However, plant diseases also affect these plants’ production and quality. This study proposes a convolutional neural network (CNN)-based metaheuristic approach for disease diagnosis and detection. The proposed approach involves preprocessing, image segmentation, feature extraction, and disease classification. First, the image of mango leaves is enhanced using histogram equalization and contrast enhancement. Then, a geometric mean-based neutrosophic with a fuzzy c-means method is used for segmentation. Next, the essential features are retrieved from the segmented images, including the Upgraded Local Binary Pattern (ULBP), color, and pixel features. Finally, these features are given into the disease detection phase, which is modeled using a Convolutional Neural Network (CNN) (deep learning model). Furthermore, to enhance the classification accuracy of CNN, the weights are fine-tuned using a new hybrid optimization model referred to as Cat Swarm Updated Black Widow Model (CSUBW). The new hybrid optimization model is developed by hybridizing the standard Cat Swarm Optimization Algorithm (CSO) and Black Widow Optimization Algorithm (BWO). Finally, a performance evaluation is undergone to validate the efficiency of the projected model. © 2022 Elsevier B.V., All rights reserved.</t>
+          <t>Future agriculture will depend heavily on connected devices, detectors and the Internet of Things (IoT) to be more productive and sustainable. WSNs Technology-based communications and data can be used to solve the majority of the critical challenges in economics, technology, and environmental protection. Increasing the number of connected devices produces a significant amount of data in many different modalities. Additionally, geographical and temporal factors contribute to the rise in the number of networked devices. After being carefully processed and analyzed, this enormous volume of data will offer a deeper understanding that motivation enhances future forecasting, executive, and management of sensor compulsion.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>10.1371/journal.pone.0267650</t>
+          <t>10.1109/ICCE-Taiwan66881.2025.11208032</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Maize leaf disease identification based on WG-MARNet</t>
+          <t>Application of Deep Learning-Based Visual Recognition for the Prevention of Rose Leaf Mite Damage</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Z., Li, Zongchen; G., Zhou, Guoxiong; Y., Hu, Yaowen; A., Chen, Aibin; C., Lu, Chao; M., He, Mingfang; Y., Hu, Yahui; Y., Wang, Yanfeng</t>
+          <t>K. -T. Zhang; C. -H. Su; J. -H. Tang</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>PLOS ONE</t>
+          <t>2025 IEEE International Conference on Consumer Electronics - Taiwan (ICCE-Taiwan)</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0.3819758296012878</v>
+        <v>0.8259888291358948</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 2: approach, data, grape</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>In deep learning-based maize leaf disease detection, a maize disease identification method called Network based on wavelet threshold-guided bilateral filtering, multi-channel ResNet, and attenuation factor (WG-MARNet) is proposed. This method can solve the problems of noise, background interference, and low detection accuracy of maize leaf disease images. To begin, a processing layer called Wavelet threshold guided bilateral filtering (WT-GBF) based on the WG-MARNet model is employed to reduce image noise and perform high and low-frequency decomposition of the input image using WT-GBF. This increases the input image’s resistance to environmental interference and feature extraction capability. Secondly, for the multiscale feature fusion technique, an average down-sampling and tiling method is employed to increase feature representation and limit the risk of overfitting. Then, on high and low-frequency multi-channel, an attenuation factor is introduced to optimize the performance instability during training of the deep network. Finally, when the convergence and accuracy are compared, PRelu and Adabound are used instead of the Relu activation function and the Adam optimizer. The experimental results revealed that our method’s average recognition accuracy was 97.96%, and the detection time for a single image was 0.278 seconds. The average detection accuracy has been increased. The method lays the groundwork for the precise control of maize diseases in the field. © 2022 Elsevier B.V., All rights reserved.</t>
+          <t>This study applies Convolutional Neural Networks (CNNs) to detect two-spotted spider mite (Tetranychus urticae) infestations on rose leaves in Taiwan. Rose cultivation, a vital component of Taiwan’s horticultural industry, is frequently threatened by these infestations, which cause leaf chlorosis and substantial yield losses.A dataset comprising 1,051 images of both healthy and infested rose leaves was constructed, and AlexNet and VGG16 models were employed for classification. K-Fold cross-validation was used to enhance model robustness and the reliability of evaluation. Experimental results show that the VGG16 model achieved superior performance, with 90.11% accuracy and a standard deviation of 1.39%, outperforming AlexNet, which attained 88.11% accuracy.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>10.1093/bib/bbac015</t>
+          <t>10.1109/ICMNWC63764.2024.10872206</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Predicting protein phosphorylation sites in soybean using interpretable deep tabular learning network</t>
+          <t>Deep Learning Based Classification and Prediction on Vegetable Crop Leaf</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>E., Khalili, Elham; S., Ramazi, Shahin; F., Ghanati, F.; S., Kouchaki, Samaneh</t>
+          <t>Pushpa, P.; Priyanka, M.; Somu, C.S.; Venitha, E.; Savija, J.; Mohanaprakash, T.A.</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Briefings in Bioinformatics</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G112" t="n">
-        <v>0.4609563052654266</v>
+        <v>0.7563869953155518</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Tópico 6: soybean, vegetable, learningbased</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Phosphorylation of proteins is one of the most significant post-translational modifications (PTMs) and plays a crucial role in plant functionality due to its impact on signaling, gene expression, enzyme kinetics, protein stability and interactions. Accurate prediction of plant phosphorylation sites (p-sites) is vital as abnormal regulation of phosphorylation usually leads to plant diseases. However, current experimental methods for PTM prediction suffers from high-computational cost and are error-prone. The present study develops machine learning-based prediction techniques, including a high-performance interpretable deep tabular learning network (TabNet) to improve the prediction of protein p-sites in soybean. Moreover, we use a hybrid feature set of sequential-based features, physicochemical properties and position-specific scoring matrices to predict serine (Ser/S), threonine (Thr/T) and tyrosine (Tyr/Y) p-sites in soybean for the first time. The experimentally verified p-sites data of soybean proteins are collected from the eukaryotic phosphorylation sites database and database post-translational modification. We then remove the redundant set of positive and negative samples by dropping protein sequences with &gt;40% similarity. It is found that the developed techniques perform &gt;70% in terms of accuracy. The results demonstrate that the TabNet model is the best performing classifier using hybrid features and with window size of 13, resulted in 78.96 and 77.24% sensitivity and specificity, respectively. The results indicate that the TabNet method has advantages in terms of high-performance and interpretability. The proposed technique can automatically analyze the data without any measurement errors and any human intervention. Furthermore, it can be used to predict putative protein p-sites in plants effectively. The collected dataset and source code are publicly deposited at https://github.com/Elham-khalili/Soybean-P-sites-Prediction. © 2022 Elsevier B.V., All rights reserved.</t>
+          <t>Globally speaking, India is a country that is growing quickly. Crop diseases pose a severe danger to food security, yet they are still hard to identify. Due to their reliance on a manually created feature extraction process, these systems' accuracy has reached its peak. This approach classification method needs to incorporate CNN to surpass grading accuracy for tomato leaf pestilence. To properly describe and categorize tomato infections, the Deep Learning algorithm is used. Using a sample of 3000 frames of tomato leaves with nine various pestilences and a better and healthier leaf, the full simulation was carried out using Google Colab. The targeted area of the input photographs is first segregated from the genuine snaps after preprocessing the input images. Second, the frames are further processed using various CNN model hyper-parameters. CNN also extracts additional qualities from frames, such as colours, borders, and textures. The results reveal that the predictions made by the demonstrated replica are 98.49% precise. © 2024 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>10.3390/plants11060717</t>
+          <t>10.1109/EPSCICON.2018.8379584</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Salt Stress in Plants and Mitigation Approaches</t>
+          <t>Detection of unhealthy plant leaves using image processing and genetic algorithm with Arduino</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>G., Ondrasek, Gabrijel; S., Rathod, Santosha; K.K., Manohara, Kallakeri Kannappa; C., Gireesh, Channappa; M.S., Anantha, Madhyavenkatapura Siddaiah; A.S., Sakhare, Akshay Sureshrao; B., Parmar, Brajendra; B.K., Yadav, Brahamdeo Kumar; N., Bandumula, Nirmala; F., Raihan, Farzana</t>
+          <t>Arya, M.S.; Anjali, K.; Unni, D.</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Plants</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F113" t="n">
         <v>4</v>
       </c>
       <c r="G113" t="n">
-        <v>0.7144461870193481</v>
+        <v>0.5904638767242432</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Salinization of soils and freshwater resources by natural processes and/or human activities has become an increasing issue that affects environmental services and socioeconomic relations. In addition, salinization jeopardizes agroecosystems, inducing salt stress in most cultivated plants (nutrient deficiency, pH and oxidative stress, biomass reduction), and directly affects the quality and quantity of food production. Depending on the type of salt/stress (alkaline or pH-neutral), specific approaches and solutions should be applied to ameliorate the situation on-site. Various agro-hydrotechnical (soil and water conservation, reduced tillage, mulching, rainwater harvesting, irrigation and drainage, control of seawater intrusion), biological (agroforestry, multi-cropping, cultivation of salt-resistant species, bacterial inoculation, promotion of mycorrhiza, grafting with salt-resistant rootstocks), chemical (application of organic and mineral amendments, phytohormones), bio-ecological (breeding, desalination, application of nano-based products, seed biopriming), and/or institutional solutions (salinity monitoring, integrated national and regional strategies) are very effective against salinity/salt stress and numerous other constraints. Advances in computer science (artificial intelligence, machine learning) provide rapid predictions of salinization processes from the field to the global scale, under numerous scenarios, including climate change. Thus, these results represent a comprehensive outcome and tool for a multidisciplinary approach to protect and control salinization, minimizing damages caused by salt stress. © 2022 Elsevier B.V., All rights reserved.</t>
+          <t>India is an agricultural country and about seventy percent of our population depends on agriculture. One-third of our national income comes from agriculture. So the disease detection of plants plays an important role in the agricultural field. Majority of the plant diseases are caused by the attack of bacteria, fungi, virus etc. If proper care is not taken in this area, it may lead to serious effects on plants and adversely affects the productivity and quality. To detect, the plant diseases we need a fast automatic way. The main approach adopted in practice for detection and identification of plant diseases is naked eye observation through experts. The decision making capability of an expert also depends on his/her physical condition, such as fatigue and eye sight, work pressure, climate etc. So this method is time consuming and less efficient. Here, a project is proposed with an idea of detecting plant diseases using image processing. Image processing toolbox of Matlab is used for measuring affected area of disease and to determine the difference in the color of the disease affected area. This concept can be extended to detect the symptoms of any type of plant diseases that is affected on different horticulture crops. The algorithm can be used to classify the leaves and the classified outcomes are separated using Arduino based conveyor belt system. This reduces an important task of monitoring of farms crops at very early stage itself to detect the symptom of diseases appear on plant leaves. © 2018 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>10.1094/MPMI-08-21-0201-R</t>
+          <t>10.1109/SPICES62143.2024.10779961</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EffectorP 3.0: Prediction of Apoplastic and Cytoplasmic Effectors in Fungi and Oomycetes</t>
+          <t>Identification of Paddy Leaf Disease using Machine Learning Methods</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>J., Sperschneider, Jana; P.N., Dodds, Peter N.</t>
+          <t>N. K. S; S. P; R. R</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Molecular Plant-Microbe Interactions</t>
+          <t>2024 IEEE International Conference on Signal Processing, Informatics, Communication and Energy Systems (SPICES)</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>0.8713313341140747</v>
+        <v>0.5021934509277344</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 2: approach, data, grape</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Many fungi and oomycete species are devasting plant pathogens. These eukaryotic filamentous pathogens secrete effector proteins to facilitate plant infection. Fungi and oomycete pathogens have diverse infection strategies and their effectors generally do not share sequence homology. However, they occupy similar host environments, either the plant apoplast or plant cytoplasm, and, therefore, may share some unifying properties based on the requirements of these host compartments. Here, we exploit these biological signals and present the first classifier (EffectorP 3.0) that uses two machine-learning models: one trained on apoplastic effectors and one trained on cytoplasmic effectors. EffectorP 3.0 accurately predicts known apoplastic and cytoplasmic effectors in fungal and oomycete secretomes with low estimated false-positive rates of 3 and 8%, respectively. Cytoplasmic effectors have a higher proportion of positively charged amino acids, whereas apoplastic effectors are enriched for cysteine residues. The combination of fungal and oomycete effectors in training leads to a higher number of predicted cytoplasmic effectors in biotrophic fungi. EffectorP 3.0 expands predicted effector repertoires beyond small, cysteine-rich secreted proteins in fungi and RxLR-motif containing secreted proteins in oomycetes. We show that signal peptide prediction is essential for accurate effector prediction, because EffectorP 3.0 recognizes a cytoplasmic signal also in intracellular, nonsecreted proteins. © 2022 Elsevier B.V., All rights reserved.</t>
+          <t>The skill of growing fruits and vegetables is known as horticulture, and it is the foundation of both business and well-being. Crop observation and disease detection have even taken precedence over conventional methods of modern farming, despite those techniques being rendered outdated by ignorance of plant illnesses, which can result in financial losses. Plant disease detection and treatment strategies are becoming more sophisticated as horticulture moves toward the Industrial Internet of things (IIoT) 5.0. This effort focuses on creating a model that can precisely diagnose rice leaf disease by examining the leaves of rice plants in order to accomplish this aim. Utilizing a logistic regression classification algorithm, the ResNet50 model based on R-CNN has been evaluated with a dataset of plant leaf image information. 97% accuracy is attained with the Resnet-50 model when compared with other models namely, DenseNet-161 and Inception Net V3 +RCNN.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>10.1088/1742-6596/2161/1/012033</t>
+          <t>10.1109/ICSTSDG61998.2024.11026485</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Crop prediction using machine learning</t>
+          <t>PlantMed - An Automated App for Monitoring the Tasks of Farmers</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>M.S., Rao, Madhuri Shripathi; A., Singh, Arushi; N.V.S.A., Reddy, Nagireddypally Veerappareddy Subba Anvesh; U., Dinesh Acharya, U.</t>
+          <t>S. B; M. S; A. R</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Journal of Physics: Conference Series</t>
+          <t>2024 International Conference on Smart Technologies for Sustainable Development Goals (ICSTSDG)</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G115" t="n">
-        <v>0.9934973120689392</v>
+        <v>0.3164848983287811</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 7: system, pesticide, solution</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>For most developing countries, agriculture is their primary source of revenue. Modern agriculture is a constantly growing approach for agricultural advances and farming techniques. It becomes challenging for the farmers to satisfy our planet's evolving requirements and the expectations of merchants, customers, etc. Some of the challenges the farmers face are-(i) Dealing with climatic changes because of soil erosion and industry emissions (ii) Nutrient deficiency in the soil, caused by a shortage of crucial minerals such as potassium, nitrogen, and phosphorus can result in reduced crop growth. (iii) Farmers make a mistake by cultivating the same crops year after year without experimenting with different varieties. They add fertilizers randomly without understanding the inferior quality or quantity. The paper aims to discover the best model for crop prediction, which can help farmers decide the type of crop to grow based on the climatic conditions and nutrients present in the soil. This paper compares popular algorithms such as K-Nearest Neighbor (KNN), Decision Tree, and Random Forest Classifier using two different criterions Gini and Entropy. Results reveal that Random Forest gives the highest accuracy among the three. © 2022 Elsevier B.V., All rights reserved.</t>
+          <t>Farmers and terrace gardeners use PlantMed, a sophisticated mobile application, to track ailments and monitor plant health through the use of machine learning and computer vision. The API focuses on various plants, and users can upload pictures of their plants to diagnose diseases quickly using K-means and CNN network (KNN) algorithms. The application utilizes an open API (Application Programming Interface) for well-being and a linear regression model to forecast production figures for various climatic conditions, including rainfall, temperature, humidity, and wind, while also integrating current weather information. The application offers suggestions for managing agro-health care, such as using pesticides, linking GP (Gram Panchayat) outage measures with government schemes, and registering the soil condition in their vicinity using the Google Maps API. Eva, the integrated multilingual Chabot, encourages users across languages by teaching them how to grow plants, prevent them from diseases, and use the app. Additionally, the application provides educational content in the form of articles, videos, and news about current agricultural trends. Some upcoming enhancements include the incorporation of market demand, the implementation of growing crops where there is a demand for them, and the ability to search nearby locations for agricultural equipment and supplies, thereby transforming plant medicine into a remedy for enhancing crop productivity.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>10.1109/ICOSST57195.2022.10016854</t>
+          <t>10.1109/ICITSI.2018.8696087</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Diagnosis Of Cassava Leaf Diseases and Classification Using Deep Learning Techniques</t>
+          <t>Identification of Tomato Plant Diseases by Leaf Image Using Squeezenet Model</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>S.M., Riaz, Syed Morsleen; M., Ahsan, Muhammad; M.U., Akram, M. Usman</t>
+          <t>A. Hidayatuloh; M. Nursalman; E. Nugraha</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>2018 International Conference on Information Technology Systems and Innovation (ICITSI)</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G116" t="n">
-        <v>0.5492375493049622</v>
+        <v>0.8801521062850952</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>The plants disease diagnosis is very challenging research in the field of agriculture. Cassava is a second most provider of carbohydrates in Africa. It is a key food for people of Africa in very harsh conditions. According to United Nations (FAO) almost eighty percent farmers of sub Saharan Africa are growing cassava roots, but due to a variety of viral diseases the production of cassava is very low from last two years. With the help of data science, it is possible to diagnose and classify these types of viral diseases. Existing methods of disease detection require farmers to solicit the help of government-funded agricultural experts to visually inspect and diagnose the plants. Moreover, this process is labor-intensive, time taken, costly and impacting the production and supply cycle. As an added challenge, effective solutions for farmers must perform well under significant constraints since African farmers may only have access to mobile-quality cameras with low-bandwidth. The dataset which we use in this research is taken from Kaggle competition 2020. Dataset contains 21397 images of cassava plants which belongs to five different classes i.e., Cassava Bacterial Blight, Cassava Brown Streak Disease, Cassava Green Mottle, Cassava Mosaic Disease and Healthy leaves. In this work we have used augmentation technique to increase the samples for classification and balancing the uneven distribution of data for all classes and used deep learning model efficiennetB3 for identification classification of diseases and got 83.03% overall accuracy on test dataset with more than 90% individual accuracy of each class. We have developed a graphical user interface for using the model in more efficient way with the aim to help the industry for prediction of diseases during its initial stages. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>One of the problems in the field of agriculture is regarding plant diseases. Plant diseases can cause a decrease in agricultural production. Therefore, early detection and diagnosis of plant diseases is very important. Plant diseases often appear on the leaves, and the characteristics of the affected leaves can be varied and difficult to distinguish. This makes it difficult to identify the disease automatically. Increased smartphone usage and advances in the field of computer vision through deep learning have made it possible to connect smartphones as a tool in diagnosing diseases. Plants used as case studies in this study were tomato plants. The method used is Convolutional Neural Network (CNN). This CNN method has many types based on the architecture it builds, one of which is squeezenet architecture. Squeezenet architecture can produce a model with a relatively small size, so that the model can be implemented on smartphone devices, server computing, and microcontroller devices. This research will focus on building a model based on squeezenet architecture to classify seven types of tomato plant diseases on the leaves including healthy leaves. The model is built using the help of Keras deep learning frameworks. The data used in this study is the image of tomato plant leaves obtained from the Vegetable Crops Research Institute (Balitsa) in Lembang, West Java. With 200 classes for each class. This study has successfully detected tomato plant disease through its leaf image automatically with an average accuracy of identification of 86.92%.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>10.1109/ICTACS56270.2022.9988660</t>
+          <t>10.1109/GCAT59970.2023.10353399</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Leaf Disease Detection using Deep Learning Models</t>
+          <t>Deep learning based Automatic Indoor Plant Management System using Arduino</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>M.K., Dharani, M. K.; R., Thamilselvan, R.; S.P., Gudadhe, Smita P.; M.A., Joshi, Manasi Arvindrao; V., Yadav, Vipul</t>
+          <t>S. Prasad; K. Umme Haniya; S. Zeenathunnisa; M. Tahir; M. Sulaiman</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2022 2nd International Conference on Technological Advancements in Computational Sciences (ICTACS)</t>
+          <t>2023 4th IEEE Global Conference for Advancement in Technology (GCAT)</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G117" t="n">
-        <v>0.7204647064208984</v>
+        <v>0.8539389967918396</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Cassava plant is the most widely planted cash and food crop around the world. It has various mineral contents and vitamins so it is taken as a nutritive supplement food in the period of drought. So these types of plant have to be cultivated at most care for the survival of people. The cassava plant production is very easy with the tropical climate but with the sudden change in the climate level and watering issues there may be a infection caused by fungus. So far the fungal infections are identified using a manual method because it will occur in the root and leaves. Inorder to identify the level and variety of fungal or viral disease manual examination have to be made. However, this is time-consuming, costly, and lacks the knowledge to recognize the disease at the proper time. This leads the farmers to apply preventive strategies to non-infected cassava plants and affects the yields. This have been done to identify and categorize few kinds of disease infected on the cassava plant as it will be easy for the farm workers to take a preventive measure on time. This work mainly focuses on three different viral diseases of cassava plant namely Cassava Bacterial Blight, Cassava Mosaic Disease, Cassava Green Mite, Cassava Brown streak Disease and a healthy plant in order to expedite disease identification. In this project, there are 21,375 images of Cassava plants that will be used to train a disease classification model and we give different images to test the model using convolutional neural network (CNN). The model has been trained with two different CNN model architecture called EfficientNetB4 and Inception-Resnet-V2. The accuracy have been calculated and analysed that Inception-Resnet-V2 outperforms other model. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>Normal plant management systems relies majorly on human monitoring and care. Some of the disadvantages are uneven watering, inadequate nutrition supply to the plants, time consuming, lack in precision of plant health parameters, not having real time visibility, inefficient resource usage of water and energy. In order to overcome these drawbacks, a deep learning-based Plant management system is proposed in this work. By automating the system, there are several advantages. In this project, an Arduino Based Plant Automation System that waters plants automatically based on the amount of soil moisture detected by the sensors is designed. The device provide fertilizer based on detecting plant diseases through image processing software. Some advantages of the proposed system include Accurate Monitoring of plants health parameters. Automated watering, fertilizing, providing real time alerts and notifications, improved plant health and growth, energy and resource efficiency, remote access and control etc. Some areas where this system can be deployed are Smart homes, Indoor gardening, Horticulture research, Sustainable Agriculture and Vertical Farming.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>10.1109/ICCCNT54827.2022.9984351</t>
+          <t>10.1109/ICIICS59993.2023.10421635</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Analysis on Cassava leaf disease prediction using pre-trained models</t>
+          <t>Mulberry Leaves Diseases and Disease Identification Techniques</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>M.K., Dharani, M. K.; R., Thamilselvan, R.; R., Rajadevi, R.; K., Logeswaran, K.; J., Arunesh, J.; S., Deepan Raj, S.</t>
+          <t>S. Sandeep Kumar; U. Divakarla</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2022 13th International Conference on Computing Communication and Networking Technologies (ICCCNT)</t>
+          <t>2023 International Conference on Integrated Intelligence and Communication Systems (ICIICS)</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G118" t="n">
-        <v>0.7564964294433594</v>
+        <v>0.5765791535377502</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Cassava plant is the most widely planted cash and food crop around the world. It has various mineral contents and vitamins so it is taken as a nutritive supplement food in the period of drought. The cassava plant production is very easy with the tropical climate but with the sudden change in the climate level and watering issues there may be a infection caused by fungus. Inorder to identify the level and variety of fungal or viral disease manual examination have to be made. However, this is time-consuming, costly, and lacks the knowledge to recognize the disease at the proper time. This leads the farmers to apply preventive strategies to non-infected cassava plants and affects the yields. This have been done to identify and categorize few kinds of disease infected on the cassava plant as it will be easy for the farm workers to take a preventive measure on time. This work mainly focuses on three different viral diseases of cassava plant namely Cassava Bacterial Blight, Cassava Mosaic Disease, Cassava Green Mite, Cassava Brown streak Disease and a healthy plant in order to expedite disease identification. In this project, there are 21,375 images of Cassava plants that will be used to train a disease classification model and we give different images to test the model using convolutional neural network (CNN). The model has been trained with two different CNN model architecture called EfficientNetB4 and Inception-Resnet-V2. The accuracy have been calculated and analysed that Inception-Resnet-V2 outperforms other model. © 2023 Elsevier B.V., All rights reserved.</t>
+          <t>In sericulture, the young caterpillars of the common silk moth, also known as ”Bombyx Mori,” are the most widely used species of silkworm. For the purpose of raising silkworms, mulberry plants are grown. Mulberry leaves are the main source of food for silkworms. Mulberry leaves are an important economic factor in sericulture because they directly influence the quality and quantity of cocoons produced per unit area. Mulberry leaf diseases cause both a loss in leaf quality and a reduction in leaf yield. Feeding silkworms diseased leaves has an effect on both the quality of the silk produced and the number of cocoons formed. Traditional techniques have been used to detect diseases. However, plant pathologists or agricultural professionals have traditionally used empty-eye observation to find leaf diseases. It takes a lot of labour and in-depth understanding of plant illnesses to detect diseases in plant leaves using this approach, which may be unreliable, time-consuming, and lucrative. Therefore, it is crucial to maintain regular watchfulness and employ effective disease diagnosis methods to safeguard mulberry leaves from various disease attacks.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10.1007/978-981-19-5037-7_39</t>
+          <t>10.1109/TIAR.2016.7801208</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Plant Disease Detection Using Image Processing and Machine Learning</t>
+          <t>Hybrid approach for anthracnose detection using intensity and size features</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>V., Patel, Venus; N., Srivastava, Noopur; M., Khare, Manish</t>
+          <t>K. Swetha; V. Venkataraman; G. D. Sadhana; R. Priyatharshini</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Lecture Notes in Electrical Engineering</t>
+          <t>2016 IEEE Technological Innovations in ICT for Agriculture and Rural Development (TIAR)</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G119" t="n">
-        <v>0.4259781837463379</v>
+        <v>0.5252072215080261</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Tópico 6: soybean, vegetable, learningbased</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>In agriculture, plant disease and its precise detection is an important task. Researchers have attempted several methods to automate disease detection using the latest tools and techniques of image processing and machine learning. In this paper, a semi-automatic system is designed to detect two diseases of soybean (glycine max) named mosaic virus and leaf spot. We used the k-means clustering approach to extract the combined colour and texture features from the diseased area of soybean leaves and classified it using the KNN algorithm. The observations are compared with the existing work to validate the efficacy of the proposed approach. Moreover, visual inspections of the leaf sample also prove the suitability of the proposed system for detection and classification. © 2022 Elsevier B.V., All rights reserved.</t>
+          <t>Anthracnose is a group of fungal diseases that affect a variety of plants in warm, humid areas. Commonly infecting the developing shoots and leaves, anthracnose fungi (usually Colletotrichum or Gloeosporium) produce spores in tiny, sunken, saucer-shaped fruiting bodies known as acervuli. Symptoms include sunken spots or lesions (blight) of various colors in leaves, stems, fruits, or flowers. This reduces the agricultural production significantly. Hence there is a need to detect this disease at the earliest. This paper is based on the determination of lesion areas affected by anthracnose by segmenting them using thresholding segmentation technique. The lesion areas are identified by dark spots on the surface of the leaf or the fruit. The percentage of affected area is determined by taking the size and intensity of the spots into consideration. We have considered three types of fruit namely mango, apple and tomato for our work. The developed methodology consists of two phases. In the first phase, the segmentation technique namely region growing is employed for separating anthracnose affected lesion areas from normal area. In the second phase, these affected areas are graded by calculating the percentage of affected area The work finds application in developing a machine vision system in horticulture field.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>10.1109/CCiCT56684.2022.00013</t>
+          <t>10.1109/ICBSII58188.2023.10181087</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Identification of Diseases in Cassava Leaves using Convolutional Neural Network</t>
+          <t>Classification of Cultivars Employing the Alexnet Technique Using Deep Learning</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>A.A., John, Ashwin Abraham</t>
+          <t>Gurunathan, K.; Bharathkumar, V.; Meeran, M.H.A.; Hariprasath, K.; Jidendiran, R.</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2022 Fifth International Conference on Computational Intelligence and Communication Technologies (CCICT)</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G120" t="n">
-        <v>0.495625376701355</v>
+        <v>0.5694220066070557</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Automating the detection of different types of diseases in plants is one of the most complex recent challenges faced by agricultural experts all over the world. Cassava is loaded with carbohydrates and is mostly cultivated by small farmers in Sub-Saharan Africa as a security crop as it is capable of growing amidst drought which affects mostly all the other crops directly and adversely. At present, farmers are completely dependent on plant health experts to come and have a weekly or bi-weekly random inspection of the plants. They collect leaf samples from 3 different parts of the plant - top, middle, and lower parts and send them to the lab for testing. This takes up a lot of time and does not leave enough time for farmers to find a solution once the plants get affected. Therefore, it is important for farmers to detect the diseases as early as possible. To tackle this problem, we propose a disease detection model for cassava plants using a Convolutional Neural Network (CNN). The features in the cassava plant images which signify the presence of disease will be automatically learned by the Neural Network. The farmers cannot detect these features manually. This research was conducted using a dataset of 21,397 labeled images collected during a regular survey in Uganda comprising four diseases namely Cassava Bacterial Blight (CBB), Cassava Brown Streak Disease (CBSD), Cassava Green Mottle (CGM), Cassava Mosaic Disease (CMD) and the dataset also contains healthy images of the plant. Most of the images in this dataset were taken by farmers in their gardens to provide a realistic representation of how farmers would diagnose these diseases in real life. These images were annotated by experts at the National Crops Resources Research Institute (NaCRRI) in collaboration with the AI lab at Makerere University, Kampala. © 2022 Elsevier B.V., All rights reserved.</t>
+          <t>The recognition of hybrid fruits by humans is considered a challenging task as fruits exist in various colors, sizes, shapes, and textures. In the marketplace, where prediction of fruits, vegetables, and pulses by retailers and the general public is very difficult. In this paper, we have recognised two different classes of fruits, vegetables, and pulses and categorised them based on the stages of their existence and maturity in a procedure called fruit maturity classification. Crop distribution, good fruit counts, crop harvesting, crop disease detection, weed management, and production forecasting are all aspects of managing water and soil and are just a few of the smart agricultural applications that employ robust learning (DL). The finest deep learning is what this project seeks to produce in algorithms for estimating fruit quality and ripeness in order to forecast fruit shelf life. Manual vegetable and fruit detection is a hard process when done in large numbers, but it becomes easy when done in small amounts. Automated detection of these is thus used. Fruit, crop, and pulse images served as the input for the first stage of processing, which included detection. Background removal, extraction of colour and texture properties, and categorization comprised the three steps of the process. The K-means clustering method was used for background subtraction. Statistical attributes were used to pinpoint colour characteristics. This research proposes a simple and effective method for detecting fruits and predicting their nutrition information using deep Alex networks (DAN). The datasets used in the investigation were obtained from the Fruit 360 library of image processing problems. Apples, berries, bananas, grapes, papaya, peaches, avocados, and various apple tastes are among the fruit groups. The trials are also carried out on a variety of additional fruit samples gathered from various Web archives. The network design consists of three fully linked layers, including the max pooling and RELU levels, and five convolution layers. 227∗227∗3 photos should be used as input for 96 filters that are 11∗11∗3 and have a stride length of 4. © 2023 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>10.37391/ijeer.100343</t>
+          <t>10.1109/ICCPCT65132.2025.11176616</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Lime Diseases Detection and Classification Using Spectroscopy and Computer Vision</t>
+          <t>AI-Driven Gardening Assistant: Intelligent Plant Care and Disease Detection Using AI</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>H.S., Jayswal, Hardikkumar Sudhirbhai; J.P., Chaudhari, Jitendra P.</t>
+          <t>K. Sumithra Devi; M. Santhosh</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>International Journal of Electrical and Electronics Research</t>
+          <t>2025 8th International Conference on Circuit, Power &amp; Computing Technologies (ICCPCT)</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G121" t="n">
-        <v>0.3966308832168579</v>
+        <v>0.7122525572776794</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 6: gardening, management, specie</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>In the agricultural industry, plant diseases and pests pose the greatest risks. Lime is rich 10 source of vitamin C which works as an immunity booster in human body. Because of the late and manually diseases detection in lime causes a vast loss in crop production worldwide. The most common diseases are found in limes are lime canker, lemon scab, brown rot, sooty mould and Armillaria. In this paper we used imaging and non-imaging (spectral based sensing) methods with the combination of machine learning technique to detect the lime canker and sooty mould diseases. Image acquirement, pre-processing, segmentation and classification are all steps in the imaging methodology, which is then followed by feature extraction. In non-imaging methodology a multispectral sensor (Spectrometer) is used with 400 nm to 1000 nm wavelength to detect the diseases. training set and test set ratio is fixed for both techniques are 75% and 25% respectively. When it comes to identifying and classifying lime disease, spectroscopy has a 99% efficiency rating compared to imaging methodology's 96%. © 2022 Elsevier B.V., All rights reserved.</t>
+          <t>The popularity of terrace and backyard gardening heightened the demand for smart, AI-enabled plant care and disease control. Here is presented the AI-Driven Gardening Assistant, an end-to-end solution that leverages computer vision and deep learning techniques for plant species identification, disease identification, and personalized care instructions. The assistant uses the YOLO algorithm, which is trained on a very large, augmented dataset covering multiple crop species, to ensure high-accuracy detection in diverse environmental conditions. A Retrieval-Augmented Generation (RAG) engine also powers an interactive chatbot through which users can ask expert, context-specific gardening advice from a highly curated knowledge base. Other than disease treatment, the assistant gives advice on terrace gardening methods and prevention. System implementation, deployment, and testing results are stated, and they indicate how the system can be applied to optimize terrace gardening using available AI-based assistance.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>10.13031/ja.14342</t>
+          <t>10.1109/ICAIQSA64000.2024.10882354</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>INTRA-CANOPY SENSING USING MULTI-ROTOR SUAS: A NEW APPROACH FOR CROP STRESS DETECTION AND DIAGNOSIS</t>
+          <t>Optimizing Vegetable Yield Forecasting with Machine Learning Using Soil and Weather Data</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>C.R., Wiegman, Christopher R.; R., Venkatesh, Ramarao; S.A., Shearer, Scott A.</t>
+          <t>S. Chavan; D. R. Ingle</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Journal of the ASABE</t>
+          <t>2024 International Conference on Artificial Intelligence and Quantum Computation-Based Sensor Application (ICAIQSA)</t>
         </is>
       </c>
       <c r="F122" t="n">
         <v>4</v>
       </c>
       <c r="G122" t="n">
-        <v>0.607199490070343</v>
+        <v>0.6457252502441406</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Remote sensing is a critical tool in precision agriculture, giving producers the ability to monitor field conditions throughout the growing season. Although several remote sensing platforms are in use today, small unmanned aerial systems (sUAS) provide the greatest flexibility with the highest resolution. As sUAS capabilities continue to increase (i.e., payload, flight time, and speed), their potential in commercial row crop production is substantial. However, like other forms of remote sensing, traditional sUAS are limited to a nadir view of the target and only capture the top of the crop canopy. Although disease epidemiology and stress origins vary, this limited view usually does not capture the impact of stress at the initial manifestation. For example, stresses such as macronutrient deficiencies in corn originate at the base of the plant and then move upward as nutrients translocate. By the time the stress is detectable at the top of the canopy, the opportunity to mitigate yield loss is limited. A new sUAS platform is needed for sensing beneath the upper portion of the canopy. The Stinger platform, developed to meet this need, consists of a 4.0 m fiberglass rod, custom sensor mount, communication network, and radio link. Using this platform, a variety of sensors can be inserted into the crop canopy from a hovering sUAS. The Stinger platform, when combined with artificial intelligence (AI), significantly expands the capabilities of sUAS for diagnosis of crop stress in row crop production. © 2022 Elsevier B.V., All rights reserved.</t>
+          <t>The majority of people in India depend mostly on agriculture for their livelihood, which also contributes substantially to the country's economy. However, there is still room for improvement and expansion in the agricultural sector's use of technology. Because they can handle huge datasets, recognize patterns, and make predictions or classifications without being specifically trained for each circumstance, machine learning and deep learning have transformed research in numerous domains Accurate and helpful information on many topics is also crucial in farming, in addition to improvements in agricultural apparatus and technology. Remote sensors, satellite photos, and surveys are used to gather this data. Vegetable farming plays a crucial role in meeting the growing global demand for nutritious food. However, unpredictable weather patterns and suboptimal soil conditions can often hinder crop yields, posing significant challenges for farmers. This study aims to address this issue by using machine learning techniques to analyze soil properties, weather patterns, and crop data to provide tailored suggestions for crop selection, which can ultimately increase vegetable yields and promote sustainable farming practices. The research methodology involved collecting extensive data from diverse vegetable farms, including soil samples, weather records, and crop performance metrics over multiple seasons. Using machine learning algorithms, this dataset was processed to develop predictive models that assess the impact of various soil characteristics and weather factors on crop growth and productivity. The developed models were validated on a separate dataset, and the results demonstrated their high accuracy and reliability. The findings of this study suggest that machine learning can be a valuable tool for vegetable farmers to make informed decisions about crop management, leading to increased yields and improved sustainability.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>10.7717/peerj.11683</t>
+          <t>10.1109/ISESD56103.2022.9980675</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>RFPDR: a random forest approach for plant disease resistance protein prediction</t>
+          <t>Detection of Begomovirus Disease for Identification of Disease Severity Level in Tomato Leaves Using Convolutional Neural Network (CNN)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>D., Simón, Diego; O., Borsani, Omar; C.V., Filippi, Carla Valeria</t>
+          <t>I. Mubarokah; P. Laksono; Cepy; R. Safitri; I. Idris</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -5457,368 +5473,368 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>PeerJ</t>
+          <t>2022 International Symposium on Electronics and Smart Devices (ISESD)</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G123" t="n">
-        <v>0.8716010451316833</v>
+        <v>0.9490697979927063</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Background. Plant innate immunity relies on a broad repertoire of receptor proteins that can detect pathogens and trigger an effective defense response. Bioinformatic tools based on conserved domain and sequence similarity are within the most popular strategies for protein identification and characterization. However, the multi-domain nature, high sequence diversity and complex evolutionary history of disease resistance (DR) proteins make their prediction a real challenge. Here we present RFPDR, which pioneers the application of Random Forest (RF) for Plant DR protein prediction. Methods. A recently published collection of experimentally validated DR proteins was used as a positive dataset, while 10x10 nested datasets, ranging from 400-4,000 non-DR proteins, were used as negative datasets. A total of 9,631 features were extracted from each protein sequence, and included in a full dimension (FD) RFPDR model. Sequence selection was performed, to generate a reduced-dimension (RD) RFPDR model. Model performances were evaluated using an 80/20 (training/testing) partition, with 10- cross fold validation, and compared to baseline, sequence-based and state-of-the-art strategies. To gain some insights into the underlying biology, the most discriminatory sequence-based features in the RF classifier were identified. Results and Discussion. RD-RFPDR showed to be sensitive (86.4 ± 4.0%) and specific (96.9 ± 1.5%) for identifying DR proteins, while robust to data imbalance. Its high performance and robustness, added to the fact that RD-RFPDR provides valuable information related to DR proteins underlying properties, make RD-RFPDR an interesting approach for DR protein prediction, complementing the state-of-the-art strategies. © 2022 Elsevier B.V., All rights reserved.</t>
+          <t>Tomato is one of the horticultural crops that have high demand in the community, which demands continuous increase in production and quality. On the other hand, cultivating and caring for tomato are not simple. The challenge frequently encountered by tomato farmers is the prevalence of diseases on tomato leave caused by bacteria, viruses, and fungus. If the diseases are not treated appropriately, these diseases will cause a decrease in production due to the poor quality of tomatoes. In this study, the optimized Convolutional Neural Network (CNN) model for classification and detection Begomovirus disease in tomato leave is proposed. The optimized model is obtained from the comparison of three types architectures: SSD Mobilenet V1 FPN, EfficientDet D1 and SSD Resnet 50 V1 FPN. For the purpose of this research, a dataset consisted of tomato leaves contracted with various stages of begomovirus has been collected and prepared to be used as training and validation. The dataset is grouped into 4 classes based on the severity level of the disease according to the scale of symptoms that occur in tomato leave. The Experimental results shows that the mAP value of SSD Mobilenet V1 FPN, SSD Resnet 50 V1 FPN and EfficientDet D1 model are 56.17%, 61.58% and 66.03%, respectively. The EfficientDet D1 model resulted in the highest mean Average Precision (mAP) value due to this model produced the lowest loss value of 0.1 compared to the other 2 models. The proposed model uses BiFPN method for feature extraction which resulted in higher accuracy compared to previous models which only used FPN. This performance was able to be achieved with much less number of layers.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>10.1109/DELCON54057.2022.9753210</t>
+          <t>10.1109/CONECCT57959.2023.10234771</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Early Detection of Casava Plant Leaf Diseases using EfficientNet-B0</t>
+          <t>Disease Detection In Pomegranate Plant Using Image Processing Techniques</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Y., Vijayalata, Y.; N., Billakanti, Nikhil; K., Veeravalli, Karthik; R.N., Ashlin Deepa, R. N.; L., Kota, Lokesh</t>
+          <t>Sahebgouda; M. Sumana</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2022 IEEE Delhi Section Conference (DELCON)</t>
+          <t>2023 IEEE International Conference on Electronics, Computing and Communication Technologies (CONECCT)</t>
         </is>
       </c>
       <c r="F124" t="n">
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.5131650567054749</v>
+        <v>0.9081897735595703</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Image recognition plays a major role in everyday life applications like medical image analysis, gaming, surveillance and security, industrial automation, and more recently it has gained massive backing in the agricultural industry to identify plant diseases in crops. Plant diseases are a huge problem in agriculture and incorporating machine learning algorithms for their early detection will help better yields and save the farmers from loses. This paper entails the use of such machine learning algorithms to detect leaf diseases in the cassava plant. Cassava is one of the largest sources of carbohydrates for the continent of Africa. It is also very vulnerable to several plant diseases; this in turn threatens the food security of the continent. The present study is based on four of such diseases that affect the cassava yield namely, Cassava Bacterial Blight (CBB), Cassava Brown Streak Disease (CBSD), Cassava Mosaic Disease (CMD), and Cassava Green Mottle (CGM). In this research work, EfficientNet-B0 is proposed for the early detection of these diseases. The EfficientNet-B0 models outperform existing CNNs in terms of accuracy and efficiency while reducing parameter size and FLOPS by an order of magnitude. It is easier to detect disease at an early stage without the assistance of professionals, saving farmers both time and money. And our proposed model gave an accuracy of 92.6%. © 2022 Elsevier B.V., All rights reserved.</t>
+          <t>The majority of the people in India is dependent on agriculture. Every crop the farmers cultivate has some sort of illness. The most successfully adopted subtropical fruit crop in India is the pomegranate. Pomegranates have the highest economic value of all the fruits. Pomegranate has very little immunity to infection during cultivation, especially in the early stages. As a result, it is particularly susceptible to the sickness. The detection of plant diseases is a beneficial use of image processing. Picture acquisition, picture pre-processing, Image segmentation, feature extraction, object recognition, and classification are all steps within the infection discovery handle.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-96634-8_37</t>
+          <t>10.1109/IDICAIEI61867.2024.10842864</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Design and Development of a CNN Model Based Android Application for Detection of Plant Leaf Diseases In-Home Grown Plants in Saudi Arabia</t>
+          <t>A Review: Citrus Disease Detection Using Machine Learning Approach</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>S.B.S., Imam, Sharmila Banu Sheik; R.O., Alsultan, Rawan Omar; D.A., Albdah, Dalal Abdulmohsen; G.K., Almulhim, Ghaliah Khalid; N.H., Alshaikhmubarak, Norah Hamed</t>
+          <t>S. C. Raut; N. N. Kasat</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Studies in Computational Intelligence</t>
+          <t>2024 2nd DMIHER International Conference on Artificial Intelligence in Healthcare, Education and Industry (IDICAIEI)</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.4154699444770813</v>
+        <v>0.7139562964439392</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>The growth of every country depends on its agricultural growth. Growing plants at home have become a hobby as well as a nutrient factor. It also ensures that the vegetables and plants are pesticide-free and contain nutrients like antioxidants, vitamins, and minerals as a whole. But growing plants at home is not that easy as they get affected by different diseases caused by bacteria, fungi, viruses which raise the need to identify them to prevent them from causing health issues to humans. This paper identifies the common diseases that affect vegetables like affect tomatoes, potatoes, corn, pepper leaves by using an android mobile application which is generally diagnosed by human visual confirmation. The Application allows gardeners to input the image of the diseased plant. The image is then converted and processed with the trained model against the common symptoms include water-soaked, gray-green spots, and dark circular spots. This process will be done by using a dataset which is a collection of all infected leaves images that will be processed through an image processing and train it by using CNN that extracts and learn the features. This project aims to help house-gardeners identify plant leaf diseases to ensure their health, raise the productivity and quality of plants. Deep learning is introduced to tackle this problem to raise the quality and quantity of plant production and to ensure public health. © 2022 Elsevier B.V., All rights reserved.</t>
+          <t>Citrus is an important fruit crops worldwide, and diseases are one of the major constraints affecting their production and quality. An early stage detection and precise classification of citrus diseases are very important for the disease management, effectively. Diseases can affect Leaves, Fruits and stem of citrus plant. Traditional methods for disease detection and classification are time-consuming and expensive. Various techniques are proposed for the classification and detection of citrus crop diseases. Use of Machine Learning algorithms like SVM, ANN, Fuzzy C-Means Classifier, KNN, and CNN classifier are proposed by many researchers worldwide after the investigation and validation of results. This work includes the study of various citrus crop diseases and the review of literature on automatic detection and identification of the diseases using machine learning and Deep learning approaches. It also includes the brief overview of the techniques in order to improve the detection accuracy using Data Augmentation and Transfer Learning.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>10.1109/ICSSIT53264.2022.9716430</t>
+          <t>10.1109/I2CACIS65476.2025.11101702</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ML Algorithm-Based Detection of Leaf Diseases</t>
+          <t>OrchiZen: Hybrid Integrated Smart Farming System for Orchid Plantations</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>M., Kathiravan, M.; K.H., Priya, K. Hari; S., Sreesubha, S.; A., Irumporai, A.; M.C., Vinoth Kumar, M. Chenthil; V.V., Reddy, Vishnu Vardhan</t>
+          <t>D. Wijendra; V. Jayasinghearachchi; O. A. P Dilshan; H. M. K. C. B Herath; Y. M. T. N. S Yapa; K. D. M. M Rathnasiri</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2022 4th International Conference on Smart Systems and Inventive Technology (ICSSIT)</t>
+          <t>2025 IEEE International Conference on Automatic Control and Intelligent Systems (I2CACIS)</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G126" t="n">
-        <v>0.6953845620155334</v>
+        <v>0.504813551902771</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Tópico 2: tomato, fruit, grape</t>
+          <t>Tópico 5: system, agriculture, soil</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>In day-to-day life, while the plant is important for every human being to get rich vitamins of vegetables, the plant disease rate is increasing proportionally. The disease on the plant causes severe suffering to farmers economically. So, the plant disease is either to be controlled or predicted before it leads to big damages. To solve this issue, machine learning algorithms have been proposed to analyze the root causes of the disease and to prescribe suitable pesticides to cure the plant. Though many methods have been encountered to detect the disease of a crop, the existing methods failed to give accurate results. While many existing methods failed to apply image processing techniques and databases to store the crop data, the proposed CNN algorithm adopted these features by creating web applications to know the different types of disease that have occurred on the plant. The result witnesses that the proposed algorithms have shown improved accuracy (93.3%) which helps the farmer to raise the productivity of a crop. The developed app also helps young farmers to read and select suitable image options to improve the good yielding of their agriculture. © 2022 Elsevier B.V., All rights reserved.</t>
+          <t>OrchiZen is a hybrid integrated smart farming system designed for orchid cultivation, leveraging Machine Learning (ML) and Internet of Things (IoT) technologies to address key horticultural challenges, including irrigation, disease treatment, choice of species, lighting, and nutrients. The OrchiZen has smart irrigation advisory, species recommendation, Ultraviolet (UV) based disease treatment, light optimization, and fertilizer advisory. The priorities are given to specific species such as Dendrobium, Vanda, and Phalaenopsis. The realities of telemonitoring, data processing, and forecasting increase organizational productivity and contribute to better environmental management. The outcomes illustrate that existing modern technologies can enhance the output and ecology of the orchid production to a significant extent, redefining the conventional technologies.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>10.13052/jmm1550-4646.18310</t>
+          <t>10.1109/ICCIT60459.2023.10441449</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Micronutrient Deficiency Detection with Fingernail Images Using Deep Learning Techniques</t>
+          <t>A vision transformer-based approach for recognizing seven prevalent mango leaf diseases</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>K., Tamil Selvi, K.; R., Thamilselvan, R.; R.J., Aarthi, R. J.; P.S., Priyadarsini, P. S.; T., Ranjani, T.</t>
+          <t>Rayed, M.E.; Abdullah-Al-Akib; Alfaz, N.; Niha, S.I.; Islam, S.M.S.</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Journal of Mobile Multimedia</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.5760210156440735</v>
+        <v>0.6686332821846008</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Micronutrient deficiencies have a significant impact on society's overall health and well-being, necessitating supplementation. Clinical equipment is required to measure micronutrients such as iron, zinc, and vitamins using existing clinical methods. In rural and low-income areas, there is a tradeoff between infrastructure, precision, invasiveness, and cost. Invasive blood sampling in paediatric patients is more uncomfortable, in addition to being cost prohibitive. There is a link between micronutrient deficiencies and subjective assessments of anatomical regions like finger nail beds. Artificial intelligence can detect micronutrient deficiency by looking at the colour and metadata of the fingernails. Convolutional neural network models are used in the proposed deep learning model to extract the features of the nails and predict the corresponding deficiencies. Various architectures such as ResNet, SqueezeNet, DenseNet, VGG and custom model are used to detect cutaneous abnormalities such as Melanonychia, Mycotic, and Buea's lines. The realtime images are used to train the model, which is then validated with sample images for increased accuracy. With images collected from web crawlers, the proposed non-invasive model has an accuracy of 94%, and performance can be further improved by training with large variants of data and data augmentation. This prediction mechanism is used in primary health care settings and is linked to frontline workers for quick and easy diagnosis © 2022 Elsevier B.V., All rights reserved.</t>
+          <t>Plant diseases, particularly affecting fruit crops, pose a significant challenge to the worldwide supply of fresh food due to their direct impact on the quality of fruits, resulting in an overall decline in agricultural production. The traditional approach of detecting leaf diseases in fruit plants requires farmers to undertake manual inspection which exhibits a lack of reliability and consistency. Moreover, the manual inspection procedure is prone to errors due to its reliance on the farmer's knowledge and skill. Mango referred to as the "king of all fruits", is renowned for its rich composition of various vitamins and vital nutrients. Mangoes are susceptible to many diseases that adversely damage their visual appeal, and flavor, and have significant implications on the overall economy. The identification of diseases affecting mango plant leaves using automated recognition remains a challenge due to the diverse range of symptoms and limited availability of data. There have been several deep learning-based research studies focused on identifying diseases in mango leaves; however, the majority of these studies have employed a convolutional neural network (CNN) trained on a small number of data. This study presents a Vision Transformer (ViT) based approach to detect diseases in mango leaves using publicly available data namely MangoLeafBD. The ViT model has been selected as the detection model due to its parameter efficiency compared to deep CNN models. The ViT has produced remarkable overall classification accuracy of 100%, precision of 100%, recall of 100%, and f1-score of 100% for disease detection on mango leaves which is better than the existing CNN approaches on the MangoLeafBD dataset. This demonstrates that our approach has the potential to assist farmers in the field by providing automated, simple, and more reliable mango leaf disease diagnosis. © 2023 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-84760-9_31</t>
+          <t>10.1109/I-SMAC61858.2024.10714657</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>A Diagnostic Classifier for Prediction of Vitamin and Mineral Deficiency Based on Symptoms and Profiling Its Impact During Pregnancy</t>
+          <t>A Mango Disease Prediction for Smart Agiculture using Machine Learning Algorithms</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>R., Sawant, Rupali; J.W., Bakal, Jagdish W.</t>
+          <t>L. K; A. Packialatha</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Lecture Notes in Networks and Systems</t>
+          <t>2024 8th International Conference on I-SMAC (IoT in Social, Mobile, Analytics and Cloud) (I-SMAC)</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.5894243121147156</v>
+        <v>0.4970059394836426</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Tópico 7: model, data, study</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Vitamins &amp; Minerals or Micronutrients from our daily diet has a huge significance for health maintenance irrespective of age. Research indicates that every single micronutrient benefits a human body when taken in a regulated manner. But inadequacy may lead to numerous health complications that has a possibility to turn into serious conditions in the long run if not treated in time. Pregnant women go through numerous developmental stages during which their dietary normalcy increases for the baby to develop a healthy immune system. This research aims to focus on various symptoms that can cause micronutrient deficiency and then using the findings to build a diagnostic classifier using machine learning techniques to identify and treat the deficiencies before aggravation. © 2021 Elsevier B.V., All rights reserved.</t>
+          <t>The country's economy relies heavily on agriculture, and the health of the crops is essential to its success. Crop diseases that go undetected can cost the agriculture industry. Thus early detection and identification are crucial. It is possible to avoid crop diseases from destroying the harvest if they are accurately diagnosed and detected. Because healthy and diseased plants appear identical in their early stages, farmers cannot distinguish between the two by watching the crop leaf. India exports vast mangoes, making it an economically and environmentally significant fruit. About 1500 mango species are grown in India, with over 1000 commercial types. There are a lot of diseases that harm mangoes, affecting their look, taste, and economy. The "Prediction of Disease in Mango Fruit Crops" A complex warning system that uses machine learning and IoT. One of the main objectives is to develop a system that can forecast disease outbreaks on mango fruit harvests using historical weather information and crop yield Mango trees in India are plagued by a fungus called Anthracnose, which is the most frequent disease of its kind. Anthracnose, a highly contagious fungus, requires a quick and accurate method of diagnosis. As a result, an in-depth examination of the plants is essential before initiating any control measures. This study examines machine learning(ML) and deep learning (DL) strategies for detecting and classifying mango plant diseases. The performance of ML and DL-based classification models for mango crops and their datasets and feature extraction approachesare examined in this work. Finally, a variety of issues involved in plant disease identification are explored.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>10.3389/fgene.2021.763915</t>
+          <t>10.1109/ICMNWC63764.2024.10872300</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Construction of sRNA Regulatory Network for Magnaporthe oryzae Infecting Rice Based on Multi-Omics Data</t>
+          <t>Classification of Downy Mildew Disease in Watermelon Plant Leaf using VGG-16 Convolutional Neural Network</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>E., Zhao, Enshuang; H., Zhang, Hao; X., Li, Xueqing; T., Zhao, Tianheng; H., Zhao, Hengyi</t>
+          <t>A. Khannum; D. R; K. Y</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Frontiers in Genetics</t>
+          <t>2024 4th International Conference on Mobile Networks and Wireless Communications (ICMNWC)</t>
         </is>
       </c>
       <c r="F129" t="n">
         <v>2</v>
       </c>
       <c r="G129" t="n">
-        <v>0.6878044009208679</v>
+        <v>0.5493067502975464</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 3: method, early, area</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Studies have shown that fungi cause plant diseases through cross-species RNA interference mechanism (RNAi) and secreted protein infection mechanism. The small RNAs (sRNAs) of Magnaporthe oryzae use the RNAi mechanism of rice to realize the infection process, and different effector proteins can increase the autotoxicity by inhibiting pathogen-associated molecular patterns triggered immunity (PTI) to achieve the purpose of infection. However, the coordination of sRNAs and proteins in the process of M. oryzae infecting rice is still poorly understood. Therefore, the combination of transcriptomics and proteomics to study the mechanism of M. oryzae infecting rice has important theoretical significance and practical value for controlling rice diseases and improving rice yields. In this paper, we used the high-throughput data of various omics before and after the M. oryzae infecting rice to screen differentially expressed genes and sRNAs and predict protein interaction pairs based on the interolog and the domain-domain methods. We were then used to construct a prediction model of the M. oryzae-rice interaction proteins according to the obtained proteins in the proteomic network. Finally, for the differentially expressed genes, differentially expressed sRNAs, the corresponding mRNAs of rice and M. oryzae, and the interacting protein molecules, the M. oryzae-rice sRNA regulatory network was built and analyzed, the core nodes were selected. The functional enrichment analysis was conducted to explore the potential effect pathways and the critical infection factors of M. oryzae sRNAs and proteins were mined and analyzed. The results showed that 22 sRNAs of M. oryzae, 77 secretory proteins of M. oryzae were used as effect factors to participate in the infection process of M. oryzae. And many significantly enriched GO modules were discovered, which were related to the infection mechanism of M. oryzae. © 2021 Elsevier B.V., All rights reserved.</t>
+          <t>Downy Mildew, caused by Pseudoperonospora cubensis, poses a serious threat to watermelon (Citrullus lanatus) crops, with the potential to drastically reduce yields and cause substantial economic losses in the agricultural sector. Early and accurate detection is essential for mitigating these impacts and maintaining crop productivity. An automatic detection system was developed using the VGG-16 Convolutional Neural Network (CNN) model, selected for its high accuracy. Trained and validated on a dataset of 585 images, split into 80% for training and 20% for validation, the model achieved 100% accuracy in both phases, with minimal losses of 0.0325 and 0.0098 respectively. These results underscore the model's potential for precise Downy Mildew detection, supporting improved disease management in precision agriculture.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>10.1094/MPMI-03-21-0071-R</t>
+          <t>10.1109/ICICI65870.2025.11069612</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Computational Structural Genomics Unravels Common Folds and Novel Families in the Secretome of Fungal Phytopathogen Magnaporthe oryzae</t>
+          <t>A Review on Deep Learning and Transfer Learning Models: Grape Leaf Disease Detection</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>K., Seong, Kyungyong; K.V., Krasileva, Ksenia V.</t>
+          <t>Dhavane, P.G.; Mangave, T.G.; Deshmukh, T.S.; Kajale, P.P.</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Molecular Plant-Microbe Interactions</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>0.9220969080924988</v>
+        <v>0.7491450309753418</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 2: approach, data, grape</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Structural biology has the potential to illuminate the evolution of pathogen effectors and their commonalities that cannot be readily detected at the primary sequence level. Recent breakthroughs in protein structure modeling have demonstrated the feasibility to predict the protein folds without depending on homologous templates. These advances enabled a genome-wide computational structural biology approach to help understand proteins based on their predicted folds. In this study, we employed structure prediction methods on the secretome of the destructive fungal pathogen Magnaporthe oryzae. Out of 1,854 secreted proteins, we predicted the folds of 1,295 proteins (70%). We showed that template-free modeling by TrRosetta captured 514 folds missed by homology modeling, including many known effectors and virulence factors, and that TrRosetta generally produced higher quality models for secreted proteins. Along with sensitive homology search, we employed structure-based clustering, defining not only homologous groups with divergent members but also sequence-unrelated structurally analogous groups. We demonstrate that this approach can reveal new putative members of structurally similar MAX effectors and novel analogous effector families present in M. oryzae and possibly in other phytopathogens. We also investigated the evolution of expanded putative ADP-ribose transferases with predicted structures. We suggest that the loss of catalytic activities of the enzymes might have led them to new evolutionary trajectories to be specialized as protein binders. Collectively, we propose that computational structural genomics approaches can be an integral part of studying effector biology and provide valuable resources that were inaccessible before the advent of machine learning-based structure prediction. © 2021 Elsevier B.V., All rights reserved.</t>
+          <t>Grapes are the most significant fruit crops which contain several vitamins and minerals such as vitamins K, and B, as well as copper. Grape plants can be greatly affected by different diseases including grape esca, isariopsis leaf spot, black rot, powdery mildew or downy mildew, and so on. These diseases impact the entire grape's quality and yield. Early detection of grape leaf disease is essential to reduce economic costs and disease progression. However, various existing approaches pose certain challenges including computational cost, real-time detection, illumination, and occlusion as well as misclassification. This survey analyzes recent works using the machine learning, deep learning, and transfer learning techniques for grape leaf disease diagnosis in the form of dataset availability, disease severity estimation, and computational resources. Among other techniques, deep learning shows superior performance results and a better capability to extract features. Additionally, this research analyzes various performance metrics and the limitations of existing approaches. © 2025 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>10.1093/bib/bbab037</t>
+          <t>10.1109/CASP.2016.7746160</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Machine learning for phytopathology: From the molecular scale towards the network scale</t>
+          <t>SVM classifier based grape leaf disease detection</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Y., Wang, Yansu; M., Zhou, Murong; Q., Zou, Quan; L., Xu, Lei</t>
+          <t>Padol, P.B.; Yadav, A.A.</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Briefings in Bioinformatics</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G131" t="n">
-        <v>0.9884282350540161</v>
+        <v>0.5589200854301453</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Tópico 3: protein, effector, sequence</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>With the increasing volume of high-Throughput sequencing data from a variety of omics techniques in the field of plant-pathogen interactions, sorting, retrieving, processing and visualizing biological information have become a great challenge. Within the explosion of data, machine learning offers powerful tools to process these complex omics data by various algorithms, such as Bayesian reasoning, support vector machine and random forest. Here, we introduce the basic frameworks of machine learning in dissecting plant-pathogen interactions and discuss the applications and advances of machine learning in plant-pathogen interactions from molecular to network biology, including the prediction of pathogen effectors, plant disease resistance protein monitoring and the discovery of protein-protein networks. The aim of this review is to provide a summary of advances in plant defense and pathogen infection and to indicate the important developments of machine learning in phytopathology. © 2021 Elsevier B.V., All rights reserved.</t>
+          <t>Grape constitutes one of the most widely grown fruit crops in the India. Productivity of grape decreases due to infections caused by various types of diseases on its fruit, stem and leaf. Leaf diseases are mainly caused by bacteria, fungi, virus etc. Diseases are a major factor limiting fruit production and diseases are often difficult to control. Without accurate disease diagnosis, proper control actions cannot be used at the appropriate time. Image Processing is one of the widely used technique is adopted for the plant leaf diseases detection and classification. This paper is intended to aid in the detection and classification leaf diseases of grape using SVM classification technique. First the diseased region is found using segmentation by K-means clustering, then both color and texture features are extracted. Finally classification technique is used to detect the type of leaf disease. The proposed system can successfully detect and classify the examined disease with accuracy of 88.89%. © 2016 IEEE.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>10.3390/su13158600</t>
+          <t>10.1109/SCSE53661.2021.9568308</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Frontiers in the solicitation of machine learning approaches in vegetable science research</t>
+          <t>Deep learning-based pesticides prescription system for leaf diseases of home garden crops in Sri Lanka</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>M., Sharma, Meenakshi; P., Kaushik, Prashant; A., Chawade, Aakash</t>
+          <t>S. Sangeevan</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5826,1778 +5842,187 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Sustainability (Switzerland)</t>
+          <t>2021 International Research Conference on Smart Computing and Systems Engineering (SCSE)</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G132" t="n">
-        <v>0.3617160618305206</v>
+        <v>0.474560558795929</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Tópico 6: soybean, vegetable, learningbased</t>
+          <t>Tópico 7: system, pesticide, solution</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Along with essential nutrients and trace elements, vegetables provide raw materials for the food processing industry. Despite this, plant diseases and unfavorable weather patterns continue to threaten the delicate balance between vegetable production and consumption. It is critical to utilize machine learning (ML) in this setting because it provides context for decision-making related to breeding goals. Cutting-edge technologies for crop genome sequencing and phenotyping, combined with advances in computer science, are currently fueling a revolution in vegetable science and technology. Additionally, various ML techniques such as prediction, classification, and clustering are frequently used to forecast vegetable crop production in the field. In the vegetable seed industry, machine learning algorithms are used to assess seed quality before germination and have the potential to improve vegetable production with desired features significantly; whereas, in plant disease detection and management, the ML approaches can improve decision-support systems that assist in converting massive amounts of data into valuable recommendations. On similar lines, in vegetable breeding, ML approaches are helpful in predicting treatment results, such as what will happen if a gene is silenced. Furthermore, ML approaches can be a saviour to insufficient coverage and noisy data generated using various omics platforms. This article examines ML models in the field of vegetable sciences, which encompasses breeding, biotechnology, and genome sequencing. © 2021 Elsevier B.V., All rights reserved.</t>
+          <t>The study proposes a deep learning-based pesticides prescription system for leaf diseases of home garden crops in Sri Lanka. It is an intelligent system to get suitable pesticides prescriptions for plant leaf diseases. Home gardening has become popular and is rapid because of the current pandemic situation. However, plant diseases are a major problem in gardening activities, even in a home garden or in a commercial garden. Identifying and finding a solution for the plant disease is a big challenge for home gardeners rather than commercial farmers. The proposed system of deep learning-based pesticides prescription system for leaf diseases of home garden crops in Sri Lanka will be the best solution for identifying and finding a solution to the plant diseases. The system is using a trained model for prescribing pesticides. The model was built using the deep learning method and trained in the supervised learning process. The convolutional neural network algorithm was used in the model. Transfer learning with AlexN et pre-trained model was used to increase the performance in the proposed solution and the best accuracy of 88.64 % was achieved in the experiments.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>10.3390/plants10081542</t>
+          <t>10.1109/IBSSC51096.2020.9332186</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Raman spectroscopy and machine-learning for early detection of bacterial canker of tomato: The asymptomatic disease condition</t>
+          <t>Cayenne based Plant Monitoring Control System</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>M.R., Vallejo-Pérez, Moisés Roberto; J.A., Sosa-Herrera, Jesús Antonio; H.R., Navarro, Hugo Ricardo; L.G., Álvarez-Preciado, Luz Gabriela; Á.G., Rodríguez-Vázquez, Ángel Gabriel; J.P., Lara-Ávila, José Pablo</t>
+          <t>K. Kolvekar; S. Lotlikar; M. Naik; A. Faldesai; Y. Muttu; M. Colaco</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Plants</t>
+          <t>2020 IEEE Bombay Section Signature Conference (IBSSC)</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G133" t="n">
-        <v>0.358305037021637</v>
+        <v>0.5484346151351929</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Tópico 1: cassava, blight, potato</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Bacterial canker of tomato is caused by Clavibacter michiganensis subsp. michiganensis (Cmm). The disease is highly destructive, because it produces latent asymptomatic infections that favor contagion rates. The present research aims consisted on the implementation of Raman spectroscopy (RS) and machine-learning spectral analysis as a method for the early disease detection. Raman spectra were obtained from infected asymptomatic tomato plants (BCTo) and healthy controls (HTo) with 785 nm excitation laser micro-Raman spectrometer. Spectral data were normalized and processed by principal component analysis (PCA), then the classifiers algorithms multilayer perceptron (PCA + MLP) and linear discriminant analysis (PCA + LDA) were implemented. Bacterial isolation and identification (16S rRNA gene sequencing) were realized of each plant studied. The Raman spectra obtained from tomato leaf samples of HTo and BCTo exhibited peaks associated to cellular components, and the most prominent vibrational bands were assigned to carbohydrates, carotenoids, chlorophyll, and phenolic compounds. Biochemical changes were also detectable in the Raman spectral patterns. Raman bands associated with triterpenoids and flavonoids compounds can be considered as indicators of Cmm infection during the asymptomatic stage. RS is an efficient, fast and reliable technology to differentiate the tomato health condition (BCTo or HTo). The analytical method showed high performance values of sensitivity, specificity and accuracy, among others. © 2021 Elsevier B.V., All rights reserved.</t>
+          <t>India is the world's major producer of various agricultural materials like fruits, vegetables, pulses, etc. Tomato is the most widely cultivated crop in India making it the most profitable agribusiness. Until industrial revolution, almost two-third of the human residents depends only on farming. For major development &amp; solidification of India's agriculture, research and extension system is one of the most vital needs for agricultural development. If agriculture is to be safe, healthy &amp; sustainable, it is essential to have healthy crops as they play an important role in generating sufficient quantities of healthy foods &amp; contribute to the quality of life. Hence, for the increased production, suitable evaluation of crop disease in the field is very critical. Tomato horticulture farmers face lots of problems out of which leaf disease is of major concern because it happens at the earlier stage of the plant growth and if not treated on time it can destroy the full cultivation. This paper focuses on monitoring the tomato crop plantation and tomato leaf disease classification using image processing techniques and artificial neural networks. With this system farmer will now be able to view his farm and will be able to take control actions based on the measured parameters stored onto the cloud making the system very efficient.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>10.1016/j.rse.2021.112420</t>
+          <t>10.1109/ICSIT65336.2025.11293878</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Detection of Xylella fastidiosa in almond orchards by synergic use of an epidemic spread model and remotely sensed plant traits</t>
+          <t>Image Processing in Crop Quality Assessment and Disease Detection of Okra Using CNN with U- NET</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>C., Camino, Carlos; R., Calderón, R.; S.S.R., Parnell, Stephen S.R.; H., Dierkes, H.; Y.H., Chemin, Yann H.; M., Román-Écija, Miguel; M., Montes-Borrego, Miguel; B.B., Landa, Blanca B.; J.A., Navas-Cortés, Juan A.; P.J., Zarco-Tejada, Pablo J.</t>
+          <t>P. Rawat; K. Gupta</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Remote Sensing of Environment</t>
+          <t>2025 International Conference on Sustainability, Innovation &amp; Technology (ICSIT)</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G134" t="n">
-        <v>0.5780991911888123</v>
+        <v>0.5525097250938416</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 4: tomato, used, vegetable</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>The early detection of Xylella fastidiosa (Xf) infections is critical to the management of this dangerous plan pathogen across the world. Recent studies with remote sensing (RS) sensors at different scales have shown that Xf-infected olive trees have distinct spectral features in the visible and infrared regions (VNIR). However, further work is needed to integrate remote sensing in the management of plant disease epidemics. Here, we research how the spectral changes picked up by different sets of RS plant traits (i.e., pigments, structural or leaf protein content), can help capture the spatial dynamics of Xf spread. We coupled a spatial spread model with the probability of Xf-infection predicted by a RS-driven support vector machine (RS-SVM) model. Furthermore, we analyzed which RS plant traits contribute most to the output of the prediction models. For that, in almond orchards affected by Xf (n = 1426 trees), we conducted a field campaign simultaneously with an airborne campaign to collect high-resolution thermal images and hyperspectral images in the visible-near-infrared (VNIR, 400–850 nm) and short-wave infrared regions (SWIR, 950–1700 nm). The best performing RS-SVM model (OA = 75%; kappa = 0.50) included as predictors leaf protein content, nitrogen indices (NIs), fluorescence and a thermal indicator (T&lt;inf&gt;c&lt;/inf&gt;), alongside pigments and structural parameters. Leaf protein content together with NIs contributed 28% to the explanatory power of the model, followed by chlorophyll (22%), structural parameters (LAI and LIDF&lt;inf&gt;a&lt;/inf&gt;), and chlorophyll indicators of photosynthetic efficiency. Coupling the RS model with an epidemic spread model increased the accuracy (OA = 80%; kappa = 0.48). In the almond trees where the presence of Xf was assayed by qPCR (n = 318 trees), the combined RS-spread model yielded an OA of 71% and kappa = 0.33, which is higher than the RS-only model and visual inspections (both OA = 64–65% and kappa = 0.26–31). Our work demonstrates how combining spatial epidemiological models and remote sensing can lead to highly accurate predictions of plant disease spatial distribution. © 2021 Elsevier B.V., All rights reserved.</t>
+          <t>Okra (Lady finger), an important vegetable crop in India, is frequently plagued by leaf diseases, which reduce yield and affect crop quality. Manual testimony of such diseases is time-taking and inclined to human error, particularly in rural locations where specialist resources are scarce. To solve this issue, this study presents a Custom CNN with U-Net for detecting and classifying okra leaf disease in high-resolution RGB images. A dataset of 1,500 images covering six classes, including healthy leaves and five major disease kinds, was used. The methodology covers data preparation, augmentation, and classification with custom CNN. The classifier achieved 0.99% AUC with overall test accuracy of 88%, with strong class-wise performance as evidenced by the confusion matrix and classification report. ROC analysis also revealed good separability across all classes, indicating the model's resilience. In addition to classification, a U-Net architecture was developed for segmentation and estimating future severity levels. Visualization of predictions revealed a close match between expected and real labels, confirming the model's reliability. This study emphasizes the utility of CNN and U-Net techniques. Future research will look into real-time deployment on edge devices and the integration of severity grading using lesion segmentation to better crop health management.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>10.1109/ICAI52203.2021.9445261</t>
+          <t>10.1109/ICRITO66076.2025.11241636</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Robust Optimization of MobileNet for Plant Disease Classification with Fine Tuned Parameters</t>
+          <t>A Hybrid Deep Learning-Machine Learning Pipeline for Precision Monitoring of Citrus Diseases</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>H., Younis, Haseeb; M.Z., Khan, Muhammad Zeeshan; M.U.G., Khan, Muhammand Usman Ghani; H., Mukhtar, Hamza</t>
+          <t>M. Vishnoi; V. Vashisht; A. K. Dubey; A. K. Dubey</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>2025 12th International Conference on Reliability, Infocom Technologies and Optimization (Trends and Future Directions) (ICRITO)</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.5713438391685486</v>
+        <v>0.6251786947250366</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Tópico 2: tomato, fruit, grape</t>
+          <t>Tópico 1: fruit, mango, citrus</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Vegetables are enriched with vitamins, essential for mental as well as physical health, are used in our routine life. Vegetable farming is one of the wide-scale businesses across the world. Many times, Vegetable plants are attacked by different diseases which consequences a heavy deficit for farmers. Early prognosis of these plant diseases can help to overcome this loss. Due to the variation of these diseases, it is difficult to identify the attacking disease. Deep learning models can be used for early detection of these diseased plants and appropriate measurements can be taken to minimize deficit. In this paper, we proposed a deep learning-based model for the early prognosis and classification of plant diseases. We have tuned a deep learning-based pretrained model in 2 folds over a publicly available dataset that contains images of different plants suffering from different diseases as well as healthy plants. We are envisioned to classify each instance as healthy or the name of the disease, the plant is being suffered. This transfer learning method has achieved remarkable results on this data-set of tomato plants and achieved 98.89% accuracy. To the best of our knowledge, this model is lightweight than other states of the art model with such significant results. This deep learning-based system can be used in real life for the detection of diseases of plants. © 2021 Elsevier B.V., All rights reserved.</t>
+          <t>Citrus is a globally cultivated fruit crop that plays a vital role in the economy. In India, citrus accounts for approximately $6-8 \%$ of horticulture sector. It ranks third among fruit categories and contributes for around $\mathbf{1 2 - 1 3} \boldsymbol{\%}$ of the country's overall fruit production. Citrus fruits are not only economically significant but also offer multiple benefits for both health and nutrition. However, a number of diseases can be a threat to citrus cultivation. Canker, greening, and black spot can greatly damage both productivity and marketability. Although several conventional methods have developed to improve fruit quality and detect diseases which are time-consuming and moderately effective. In contrast, deep learning and machine learning techniques have greatly improved the performance of disease identification. This study proposes a hybrid model that integrates both transfer learning and machine learning approaches in order to detect and classify citrus diseases. The proposed model localizes regions of interest (ROI) of an image, and the features extracted from ROI improves the model's detection capability. As a result, the model achieves an overall accuracy of greater than 95 % and the improved model shows strong performance across various validation metrics as compared to SVM model and YOLOV5 model. It stays effective on single labeled datasets and provides better computational efficiency than standard deep learning models.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>10.1109/I2CT51068.2021.9417926</t>
+          <t>https://doi.org/10.1016/j.pestbp.2025.106931</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>E-Agri Kit: Agricultural Aid using Deep Learning</t>
+          <t>Harnessing biological control and advanced technologies for sustainable wheat rust management: An integrated approach</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>A., Goyal, Anmolika; S., Ghose, Shreya; S., Das, Sheona; R., Chapaneri, Radhika; M., Desai, Maithili</t>
+          <t>Johannes Mapuranga; Wenxiang Yang</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>No especificado</t>
+          <t>Pesticide Biochemistry and Physiology</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G136" t="n">
-        <v>0.712571918964386</v>
+        <v>0.8251547813415527</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Tópico 5: crop, soil, system</t>
+          <t>Tópico 6: gardening, management, specie</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>This paper presents an agricultural aid application, developed and designed, to help farmers by utilizing Image Processing, Machine Learning and Deep Learning concepts. Our application provides features such as early detection of plant disease, implemented using various approaches. After evaluation, results showed that Convolutional Neural Network was performing better for plant disease detection with an accuracy of 97.94% at 20 epochs. It further helps the farmer to forecast the weather to decide the right time for agricultural activities like harvesting and plucking. To avoid reoccurrence of disease due to loss in soil minerals, a crop specific fertilizer calculator is incorporated which can calculate the amount of urea, diammonium phosphate and muriate of potash required for a given area. Since India is a multilingual country, the application has been designed to incorporate language translation in four languages: Marathi, Hindi, Punjabi and English. © 2021 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>10.14569/IJACSA.2021.0121087</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Using Transfer Learning for Nutrient Deficiency Prediction and Classification in Tomato Plant</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>V., Kusanur, Vrunda; V.S., Chakravarthi, Veena S.</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>2021</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>International Journal of Advanced Computer Science and Applications</t>
-        </is>
-      </c>
-      <c r="F137" t="n">
-        <v>4</v>
-      </c>
-      <c r="G137" t="n">
-        <v>0.4024023711681366</v>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Tópico 5: crop, soil, system</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>Plants need nutrients to develop normally. The essential nutrients like carbon, oxygen, and hydrogen are obtained from sunlight, air, and water to prepare food and plant growth. For healthy growth, plants also need macronutrients such as Potassium, Calcium, Nitrogen, Sulphur, Magnesium, and Phosphorus in relatively great quantities. When a plant doesn’t find necessary nutrients for its growth inadequate amount, deficiency of plant nutrients occur. Plants exhibit various symptoms to indicate the deficiency. Automatic identification and differentiation of these deficiencies are very important in the greenhouse environment. Deep Neural Networks are extremely efficient in image categorization problems. In this work, we used the part of the pre-trained deep learning model i.e. Transfer Learning model to detect the nutrient stress in the plant. We compared three different architectures including Inception-V3, ResNet50, and VGG16 with two classifiers: RF and SVM to improve, classification accuracy. A total of 880 images of Calcium and Magnesium deficiencies in the Tomato plant from the greenhouse were collected to form a dataset. For training, 704(80%) images are used and for testing, 176(20%) images are used to examine the model performance. Experimental results demonstrated that the largest accuracy of 99.14% has resulted for the VGG16 model with SVM classifier and 98.71% for Inception-V3 with Random Forest Classifier. For a batch size of 8 and epochs equal to 10, the Inception -V3 architecture attained the highest validation accuracy of 99.99% and the least validation loss of 0.0000384 on an average. © 2021 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>10.1007/978-981-15-9689-6_50</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Identification of Nutrition’s Deficiency in Plant and Prediction of Nutrition Requirement Using Image Processing</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>A., Patel, Ashish; P.R., Swaminarayan, Priya R.; M., Patel, Mukta</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>2021</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Lecture Notes in Networks and Systems</t>
-        </is>
-      </c>
-      <c r="F138" t="n">
-        <v>4</v>
-      </c>
-      <c r="G138" t="n">
-        <v>0.5912401080131531</v>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Tópico 5: crop, soil, system</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Agriculture plays a important role in the Indian economy. 70% of rural population is dependent on agriculture as well as 17% of total GDP is contributed from Agriculture sector and provides employment to over 60% of the population. As the Indian population increasing day by day, the demand of increasing food production is also increasing to. The total area to under cultivation decreasing over the past years. Thirteen essential minerals and nutrients are requiring to grow and survival of plants and crops. All this nutrient is supplied from the soil. If adequate nutrients are not supplied to the plant, it will affect the growth and quality of plant. Nutrients are very important for the plant growth, 13 essential nutrients required for plant survive and growth. These nutrients are taken from soil. Soil nutrients deficiency affects the quality and growth of the plants. Nutrients deficiency symptoms always visible in the plant leaves. These symptoms are like leaf colour and textures, interveinal chlorosis, uniform chlorosis, marginal chlorosis, necrosis, distorted edges, reduction in size of the leaf, etc. Nutrient deficiency symptoms seen on the old and new leaves are different for different nutrients. Mineral nutrients are classified into macro and micronutrients. For plant survival, large amount of macronutrients and small amount of micronutrients are required. Macronutrients and micronutrients nutrients are essential to the plant, but excessive use of nutrients harms the crop production as well as wastage of money. To increase crop production with proper amount of nutrition need to be feed up to the plant at hungry stage. Excessive use of fertilizer creates so many problems like soil pollution, soil hardness, loss of foreign currency, etc. Early stage nutritional detection system can give sufficient time to use organic fertilizer which helps in pH balance and land preparation cost. © 2021 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>10.1109/R10-HTC49770.2020.9356973</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Water Stress Identification in Chickpea Images using Machine Learning</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>S., Azimi, Shiva; T.K., Gandhi, Tapan Kumar</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>2020</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>IEEE Region 10 Humanitarian Technology Conference, R10-HTC</t>
-        </is>
-      </c>
-      <c r="F139" t="n">
-        <v>4</v>
-      </c>
-      <c r="G139" t="n">
-        <v>0.8651778101921082</v>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Tópico 5: crop, soil, system</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>Computer vision based plant phenotyping methods can be employed for plant health monitoring and plant disease detection. This can play a crucial role in precision farming, enabling increased crop outputs to meet the demands of a rising world population. In this work, we consider an important problem of quantifying the moisture stress levels in chickpea plants using the shoot images. Compared to leave images, using shoot images is non-destructive and provides more information. Pulses like chickpea, owing to their high protein and nutrition content, can play an important role towards ensuring food security in poor countries. In the present work, we have employed Machine Learning techniques to compare the performance of different descriptors for stress classification induced by water deficiency from chickpea shoot images. From the results, we found that the support vector machine classifier outperforms other classifiers using SIFT descriptors, achieving nearly 73% classification accuracy. © 2021 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>10.1016/j.micres.2020.126567</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Effector Biology of Biotrophic Plant Fungal Pathogens: Current Advances and Future Prospects</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>R., Jaswal, Rajdeep; K., Kiran, Kanti; S., Rajarammohan, Sivasubramanian; H., Dubey, Himanshu; P.K., Singh, Pankaj Kumar; Y., Sharma, Yogesh; R.K., Deshmukh, Rupesh Kailasrao; H., Sonah, Humira; N.K., Gupta, Naveen Kumar; T.R., Sharma, Tilak Raj</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>2020</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Microbiological Research</t>
-        </is>
-      </c>
-      <c r="F140" t="n">
-        <v>2</v>
-      </c>
-      <c r="G140" t="n">
-        <v>0.9772552847862244</v>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Tópico 3: protein, effector, sequence</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>The interaction of fungal pathogens with their host requires a novel invading mechanism and the presence of various virulence-associated components responsible for promoting the infection. The small secretory proteins, explicitly known as effector proteins, are one of the prime mechanisms of host manipulation utilized by the pathogen to disarm the host. Several effector proteins are known to translocate from fungus to the plant cell for host manipulation. Many fungal effectors have been identified using genomic, transcriptomic, and bioinformatics approaches. Most of the effector proteins are devoid of any conserved signatures, and their prediction based on sequence homology is very challenging, therefore by combining the sequence consensus based upon machine learning features, multiple tools have also been developed for predicting apoplastic and cytoplasmic effectors. Various post-genomics approaches like transcriptomics of virulent isolates have also been utilized for identifying active consortia of effectors. Significant progress has been made in understanding biotrophic effectors; however, most of it is underway due to their complex interaction with host and complicated recognition and signaling networks. This review discusses advances, and challenges in effector identification and highlighted various features of the potential effector proteins and approaches for understanding their genetics and strategies for regulation. © 2020 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>10.3390/ijms21165686</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Computational methods for predicting functions at the mRNA isoform level</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>S.K., Mishra, Sambit Kumar; V.R., Muthye, Viraj R.; G., Kandoi, Gaurav</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>2020</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>International Journal of Molecular Sciences</t>
-        </is>
-      </c>
-      <c r="F141" t="n">
-        <v>2</v>
-      </c>
-      <c r="G141" t="n">
-        <v>0.8838339447975159</v>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Tópico 3: protein, effector, sequence</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>Multiple mRNA isoforms of the same gene are produced via alternative splicing, a biological mechanism that regulates protein diversity while maintaining genome size. Alternatively spliced mRNA isoforms of the same gene may sometimes have very similar sequence, but they can have significantly diverse effects on cellular function and regulation. The products of alternative splicing have important and diverse functional roles, such as response to environmental stress, regulation of gene expression, human heritable, and plant diseases. The mRNA isoforms of the same gene can have dramatically different functions. Despite the functional importance of mRNA isoforms, very little has been done to annotate their functions. The recent years have however seen the development of several computational methods aimed at predicting mRNA isoform level biological functions. These methods use a wide array of proteo-genomic data to develop machine learning-based mRNA isoform function prediction tools. In this review, we discuss the computational methods developed for predicting the biological function at the individual mRNA isoform level. © 2020 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>10.1007/s12530-019-09289-2</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Artificial bee colony optimization (ABC) for grape leaves disease detection</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>A.D., Andrushia, A. Diana; A., Trephena Patricia, A.</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>2020</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Evolving Systems</t>
-        </is>
-      </c>
-      <c r="F142" t="n">
-        <v>1</v>
-      </c>
-      <c r="G142" t="n">
-        <v>0.6254897713661194</v>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Tópico 2: tomato, fruit, grape</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>Plants are one of the important sources of food to the mankind. Plant diseases affect the economy of the country and also reduce the quality of agricultural product. Throughout the world, grapes are treated as a major fruit source, which contains nutrients like vitamin C. Diseases in the grape plants seriously affect the quality and production of grapes. Computer vision-based techniques have been used successfully in the last decades, to detect and classify the plants diseases. This paper deals with the identification and classification of diseases in grape leaves by using artificial bee colony (ABC) based feature selection. Initially the input images are applied with pre-processing steps which eliminate noises and background of the images. The features of color, texture and shape are extracted. ABC based attribute selection is used to find the optimal feature set. The selected features are given to the support vector machine classifier for foliar disease detection of grapes. The proposed method is experimented and compared with the other feature selection algorithms. The comparison results depict, the efficacy of the proposed method through the performance metrics such as recall, precision and classification accuracy. © 2020 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>10.1016/j.cropro.2019.104885</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>High-throughput field phenotyping of Ascochyta blight disease severity in chickpea</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>C., Zhang, Chongyuan; W., Chen, Weidong; S., Sankaran, Sindhuja</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>2019</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Crop Protection</t>
-        </is>
-      </c>
-      <c r="F143" t="n">
-        <v>4</v>
-      </c>
-      <c r="G143" t="n">
-        <v>0.782441258430481</v>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Tópico 5: crop, soil, system</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>Pulse crops, such as chickpea (Cicer arietinum L.), serve as excellent food sources that provide proteins and minerals to humans and livestock. Additionally, pulses are important sources of soil nitrogen in rotational cropping systems. However, pulse production is limited by several biotic and abiotic stress factors. One such disease is Ascochyta blight (Ascochyta rabiei) in chickpea. To minimize the impact of Ascochyta blight, timely information on disease outbreak and epidemics is essential for implementing disease control methods. Thus, in this study, the feasibility of monitoring Ascochyta blight disease severity in chickpea using remote sensing techniques was evaluated. Disease severity was monitored using an unmanned aircraft system integrated with different types of sensors (3-band multispectral, 5-band multispectral, and thermal cameras). Results indicated that different flight altitudes (60 m and 90 m above ground level) that lead to different image resolutions did not influence disease detection efficiency, especially with the 3-band camera. Selected image features, including canopy area, percentage of canopy area, and vegetation indices (e.g., green normalized difference vegetation index) from multispectral cameras, and mean canopy temperature from the thermal camera, were significantly correlated with yield and visual ratings of disease severity. Moreover, hyperspectral sensing was found to be useful in predicting disease severity. In summary, this study demonstrated that disease severity of Ascochyta blight in chickpea can be monitored using remote sensing methods under active field conditions. With timely and accurate disease severity information from high-throughput phenotyping technologies, the effects of Ascochyta blight on chickpea yield and quality can be minimized with timely application of proper management techniques. © 2019 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>10.1016/j.dib.2019.104340</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>A citrus fruits and leaves dataset for detection and classification of citrus diseases through machine learning</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>H.T., Rauf, Hafiz Tayyab; B.A., Saleem, Basharat Ali; M.I.U., Lali, Muhammad Ikram Ullah; M.A., Khan, Muhammad Attique; M.I., Sharif, Muhammad Irfan; S.A.C., Bukhari, Syed Ahmad Chan</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>2019</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Data in Brief</t>
-        </is>
-      </c>
-      <c r="F144" t="n">
-        <v>1</v>
-      </c>
-      <c r="G144" t="n">
-        <v>0.4902197122573853</v>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Tópico 2: tomato, fruit, grape</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Plants are as vulnerable by diseases as animals. Citrus is a major plant grown mainly in the tropical areas of the world due to its richness in vitamin C and other important nutrients. The production of the citrus fruit has been widely affected by citrus diseases which ultimately degrades the fruit quality and causes financial loss to the growers. During the past decade, image processing and computer vision methods have been broadly adopted for the detection and classification of plant diseases. Early detection of diseases in citrus plants helps in preventing them to spread in the orchards which minimize the financial loss to the farmers. In this article, an image dataset citrus fruits, leaves, and stem is presented. The dataset holds citrus fruits and leaves images of healthy and infected plants with diseases such as Black spot, Canker, Scab, Greening, and Melanose. Most of the images were captured in December from the Orchards in Sargodha region of Pakistan when the fruit was about to ripen and maximum diseases were found on citrus plants. The dataset is hosted by the Department of Computer Science, University of Gujrat and acquired under the mutual cooperation of the University of Gujrat and the Citrus Research Center, Government of Punjab, Pakistan. The dataset would potentially be helpful to researchers who use machine learning and computer vision algorithms to develop computer applications to help farmers in early detection of plant diseases. The dataset is freely available at https://data.mendeley.com/datasets/3f83gxmv57/2. © 2022 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>10.3390/app9081601</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>A comparative study of deep CNN in forecasting and classifying the macronutrient deficiencies on development of tomato plant</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>T.T., Tran, Tin Trung; J., Choi, Jae-won; T.T.H., Le, Thien Tu Huynh; J., Kim, Jongwook</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>2019</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Applied Sciences (Switzerland)</t>
-        </is>
-      </c>
-      <c r="F145" t="n">
-        <v>6</v>
-      </c>
-      <c r="G145" t="n">
-        <v>0.5852974057197571</v>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Tópico 7: model, data, study</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>During the process of plant growth, such as during the flowering stages and fruit development, the plants need to be provided with the various minerals and nutrients to grow. Nutrient deficiency is the cause of serious diseases in plant growth, affecting crop yield. In this article, we employed artificial neural network models to recognize, classify, and predict the nutritional deficiencies occurring in tomato plants (Solanum lycopersicum L.). To classify and predict the different macronutrient deficiencies in the cropping process, this paper handles the captured images of the macronutrient deficiency. This deficiency during the fruiting and leafing phases of tomato plant are based on a deep convolutional neural network (CNN). A total of 571 images were captured with tomato leaves and fruits containing the crop species at the growth stage. Among all images, 80% (461 captured images) were used for the training dataset and 20% (110 captured images) were applied for the validation dataset. In this study, we provide an analysis of two different model architectures based on convolutional neural network for classifying and predicting the nutrient deficiency symptoms. For instance, Inception-ResNet v2 and Autoencoder with the captured images of tomato plant growth under the greenhouse conditions. Moreover, a major type of statistical structure, namely Ensemble Averaging, was applied with two aforementioned predictive models to increase the accuracy of predictive validation. Three mineral nutrients, i.e., Calcium/Ca2+, Potassium/K+, and Nitrogen/N, are considered for use in evaluating the nutrient status in the development of tomato plant with these models. The aim of this study is to predict the nutrient deficiency accurately in order to increase crop production and prevent the emergence of tomato pathology caused by lack of nutrients. The predictive performance of the three models in this paper are validated, with the accuracy rates of 87.273% and 79.091% for Inception-ResNet v2 and Autoencoder, respectively, and with 91% validity using Ensemble Averaging. © 2019 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>10.1093/bib/bbx123</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Critical assessment and performance improvement of plant-pathogen protein-protein interaction prediction methods</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>S., Yang, Shiping; H., Li, Hong; H., He, Huaqin; Y., Zhou, Yuan; Z., Zhang, Ziding</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>2019</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Briefings in Bioinformatics</t>
-        </is>
-      </c>
-      <c r="F146" t="n">
-        <v>2</v>
-      </c>
-      <c r="G146" t="n">
-        <v>0.9923004508018494</v>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Tópico 3: protein, effector, sequence</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>The identification of plant-pathogen protein-protein interactions (PPIs) is an attractive and challenging research topic for deciphering the complexmolecularmechanismof plant immunity and pathogen infection. Considering that the experimental identification of plant-pathogen PPIs is time-consuming and labor-intensive, computationalmethods are emerging as an important strategy to complement the experimentalmethods. In this work, we first evaluated the performance of traditional computationalmethods such as interolog, domain-domain interaction and domain-motif interaction in predicting known plant-pathogen PPIs. Owing to the low sensitivity of the traditionalmethods, we utilized RandomForest to build an interspecies PPI predictionmodel based onmultiple sequence encodings and novel network attributes in the established plant PPI network. Critical assessment of the features demonstrated that the integration of sequence information and network attributes resulted in significant and robust performance improvement. Additionally, we also discussed the influence of Gene Ontology and gene expression information on the prediction performance. TheWeb server implementing the integrated predictionmethod, named InterSPPI, has beenmade freely available at http://systbio.cau.edu.cn/intersppi/index.php. InterSPPI could achieve a reasonably high accuracy with a precision of 73.8% and a recall of 76.6% in the independent test. To examine the applicability of InterSPPI, we also conducted cross-species and proteome-wide plant-pathogen PPI prediction tests. Taken together, we hope this work can provide a comprehensive understanding of the current status of plant-pathogen PPI predictions, and the proposed InterSPPI can become a useful tool to accelerate the exploration of plant-pathogen interactions. © 2021 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>10.1007/978-981-13-1501-5_19</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>An analysis of various techniques for leaf disease prediction</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>P.R., Niveditha, P. R.; H.L., Gururaj, H. L.; V., Janhavi, V.</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>2019</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Advances in Intelligent Systems and Computing</t>
-        </is>
-      </c>
-      <c r="F147" t="n">
-        <v>5</v>
-      </c>
-      <c r="G147" t="n">
-        <v>0.4417244791984558</v>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Tópico 6: soybean, vegetable, learningbased</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>The detection of plant diseases at early stage can be the best precaution taken by any farmer to avoid great loss. If that work of detecting the plant is made automatic, then it would be the essential topic for discovery. Mainly, plant diseases are caused by fungi, bacteria, and virus. All three affect the plant in different way which can be identified. This feature helps in detecting the particular disease. When it comes to fungi, they can be classified with their morphology that is based on their reproductive structures. Bacteria have the unique property of increasing their number in short duration, the single cell dividing into two and hence multiplying in number, but compared to fungi, they have simple life cycle. Viruses are the smallest particle found. They are made up of proteins and genetic materials. The method for detecting involves five stages, in the first stage, the image is selected through the inputs, the second stage involves processing of image, the third involves dividing the image, the fourth involves finding unique attributes, and final step involves analysis. © 2018 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>10.1016/j.mib.2018.01.017</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Bioinformatic prediction of plant–pathogenicity effector proteins of fungi</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>D.A., Jones, Darcy A.B.; S., Bertazzoni, Stefania; C.J., Turo, Chala J.; R.A., Syme, Robert Andrew; J.K., Hane, James K.</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>2018</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Current Opinion in Microbiology</t>
-        </is>
-      </c>
-      <c r="F148" t="n">
-        <v>2</v>
-      </c>
-      <c r="G148" t="n">
-        <v>0.986865222454071</v>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Tópico 3: protein, effector, sequence</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Effector proteins are important virulence factors of fungal plant pathogens and their prediction largely relies on bioinformatic methods. In this review we outline the current methods for the prediction of fungal plant pathogenicity effector proteins. Some fungal effectors have been characterised and are represented by conserved motifs or in sequence repositories, however most fungal effectors do not generally exhibit high conservation of amino acid sequence. Therefore various predictive methods have been developed around: general properties, structure, position in the genomic landscape, and detection of mutations including repeat-induced point mutations and positive selection. A combinatorial approach incorporating several of these methods is often employed and candidates can be prioritised by either ranked scores or hierarchical clustering. © 2018 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>10.1109/iFUZZY.2018.8751688</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>A nutrient deficiency prediction method using deep learning on development of tomato fruits</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>J., Choi, Jae-won; T.T., Trung, Tin Tran; T.L., Huynh Thien, Thien Le; P., Geon-Soo, Park; C., van Dang, Chien; J., Kim, Jongwook</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>2018</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>No especificado</t>
-        </is>
-      </c>
-      <c r="F149" t="n">
-        <v>1</v>
-      </c>
-      <c r="G149" t="n">
-        <v>0.5071201324462891</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Tópico 2: tomato, fruit, grape</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>During the development of tomato (Solanum lycopersicum L.) crop, the mineral nutrients are the important elements in the process of plant growth. Therefore, the recognition and prediction of the nutrient deficiencies in the cropping process have been great interest. In this paper, we propose a method of recognition and prediction the nutrient deficiency occurs on fruiting phrase of tomato plant based on the deep neural network. Moreover, we decide to use two essential mineral nutrients (i.e. Calcium and Potassium) for evaluating the nutrient status in the development of tomato plant. Inception-ResNet v2 based-Convolution Neural Network (CNN) is applied to distinguish the above mineral nutrients with the captured images of tomato plant growth under the greenhouse conditions. The aim of this study is to improve the accurate prediction of the nutrient deficiency for increasing the crop production and prevent the emergence of tomato pathology caused by the lack of nutrient. The performance of the Inception-ResNet v2 is validated through the real fruit images that were captured on growth of tomato plant. © 2020 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>10.1007/s11120-017-0467-7</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Chlorophyll fluorescence as a tool for nutrient status identification in rapeseed plants</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>H.M., Kalaji, Hazem M.; W., Ba̧ba, Wojciech; K., Gediga, Krzysztof; V.N., Goltsev, Vasilij N.; I.A., Samborska, Izabela Anna; M.D., Cetner, Magdalena Danuta; S.G., Dimitrova, Stella G.; U., Piszcz, Urszula; K., Bielecki, Krzysztof; K., Karmowska, Kamila</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>2018</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Photosynthesis Research</t>
-        </is>
-      </c>
-      <c r="F150" t="n">
-        <v>5</v>
-      </c>
-      <c r="G150" t="n">
-        <v>0.5320999026298523</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Tópico 6: soybean, vegetable, learningbased</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>In natural conditions, plants growth and development depends on environmental conditions, including the availability of micro- and macroelements in the soil. Nutrient status should thus be examined not by establishing the effects of single nutrient deficiencies on the physiological state of the plant but by combinations of them. Differences in the nutrient content significantly affect the photochemical process of photosynthesis therefore playing a crucial role in plants growth and development. In this work, an attempt was made to find a connection between element content in (i) different soils, (ii) plant leaves, grown on these soils and (iii) changes in selected chlorophyll a fluorescence parameters, in order to find a method for early detection of plant stress resulting from the combination of nutrient status in natural conditions. To achieve this goal, a mathematical procedure was used which combines principal component analysis (a tool for the reduction of data complexity), hierarchical k-means (a classification method) and a machine-learning method—super-organising maps. Differences in the mineral content of soil and plant leaves resulted in functional changes in the photosynthetic machinery that can be measured by chlorophyll a fluorescent signals. Five groups of patterns in the chlorophyll fluorescent parameters were established: the ‘no deficiency’, Fe-specific deficiency, slight, moderate and strong deficiency. Unfavourable development in groups with nutrient deficiency of any kind was reflected by a strong increase in F&lt;inf&gt;o&lt;/inf&gt; and ΔV/Δt&lt;inf&gt;0&lt;/inf&gt; and decline in φ&lt;inf&gt;Po&lt;/inf&gt;, φ&lt;inf&gt;Eo&lt;/inf&gt;δ&lt;inf&gt;Ro&lt;/inf&gt; and φ&lt;inf&gt;Ro&lt;/inf&gt;. The strong deficiency group showed the suboptimal development of the photosynthetic machinery, which affects both PSII and PSI. The nutrient-deficient groups also differed in antenna complex organisation. Thus, our work suggests that the chlorophyll fluorescent method combined with machine-learning methods can be highly informative and in some cases, it can replace much more expensive and time-consuming procedures such as chemometric analyses. © 2018 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>10.3233/978-1-61499-822-8-94</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Advanced stevia disease detection using deep learning</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>S., Lakshmi, S.; R., Sivakumar, R.</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>2017</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Advances in parallel computing</t>
-        </is>
-      </c>
-      <c r="F151" t="n">
-        <v>1</v>
-      </c>
-      <c r="G151" t="n">
-        <v>0.5773987770080566</v>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Tópico 2: tomato, fruit, grape</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Almost all of us are tempted to take sweets due to its pleasant nature. When it is overused, it will affect our body entirely. Diabetic is a disease that occurs when the blood glucose level is high. According to the study of World Health Organization (WHO), the prevalence percentage of diabetic persons is doubled in the last 10 years. Life style, working environment, nature of the work, food habits and hereditary are few reasons for diabetic. Diabetic leads to various health problems like heart disease, stroke, kidney problems, nerves damage, eye and dental problems over time. Stevia is a sugar substitute which is available all over the world and it is proved to give more safety for diabetic patients. Stevia contains proteins, vitamins and minerals. Stevia plant may be affected by various diseases such as root rot, charcoal rot, wilt, leaf spot disease and so on. This chapter demonstrates the deep learning approach to enable the disease detection through image recognition. A deep convolutional neural network is trained to classify the disease affected leaves, achieving the accuracy of over 99%. © 2018 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>10.3389/fpls.2017.01852</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Deep learning for image-based cassava disease detection</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>A.M., Ramcharan, Amanda M.; K., Baranowski, Kelsee; P.C., McCloskey, Peter C.; B., Ahmed, Babuali; J.P., Legg, James P.; D.P., Hughes, David P.</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>2017</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Frontiers in Plant Science</t>
-        </is>
-      </c>
-      <c r="F152" t="n">
-        <v>0</v>
-      </c>
-      <c r="G152" t="n">
-        <v>0.9908394813537598</v>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Tópico 1: cassava, blight, potato</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Cassava is the third largest source of carbohydrates for human food in the world but is vulnerable to virus diseases, which threaten to destabilize food security in sub-Saharan Africa. Novel methods of cassava disease detection are needed to support improved control which will prevent this crisis. Image recognition offers both a cost effective and scalable technology for disease detection. New deep learning models offer an avenue for this technology to be easily deployed on mobile devices. Using a dataset of cassava disease images taken in the field in Tanzania, we applied transfer learning to train a deep convolutional neural network to identify three diseases and two types of pest damage (or lack thereof). The best trained model accuracies were 98% for brown leaf spot (BLS), 96% for red mite damage (RMD), 95% for green mite damage (GMD), 98% for cassava brown streak disease (CBSD), and 96% for cassava mosaic disease (CMD). The best model achieved an overall accuracy of 93% for data not used in the training process. Our results show that the transfer learning approach for image recognition of field images offers a fast, affordable, and easily deployable strategy for digital plant disease detection. © 2017 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>10.1016/j.compbiomed.2016.09.008</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>DRPPP: A machine learning based tool for prediction of disease resistance proteins in plants</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>T., Pal, Tarun; V.K., Jaiswal, Varun K.; R.S., Chauhan, Rajinder Singh</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>2016</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Computers in Biology and Medicine</t>
-        </is>
-      </c>
-      <c r="F153" t="n">
-        <v>2</v>
-      </c>
-      <c r="G153" t="n">
-        <v>0.7331138849258423</v>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Tópico 3: protein, effector, sequence</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Plant disease outbreak is increasing rapidly around the globe and is a major cause for crop loss worldwide. Plants, in turn, have developed diverse defense mechanisms to identify and evade different pathogenic microorganisms. Early identification of plant disease resistance genes (R genes) can be exploited for crop improvement programs. The present prediction methods are either based on sequence similarity/domain-based methods or electronically annotated sequences, which might miss existing unrecognized proteins or low similarity proteins. Therefore, there is an urgent need to devise a novel machine learning technique to address this problem. In the current study, a SVM-based tool was developed for prediction of disease resistance proteins in plants. All known disease resistance (R) proteins (112) were taken as a positive set, whereas manually curated negative dataset consisted of 119 R proteins. Feature extraction generated 10,270 features using 16 different methods. The ten-fold cross validation was performed to optimize SVM parameters using radial basis function. The model was derived using libSVM and achieved an overall accuracy of 91.11% on the test dataset. The tool was found to be robust and can be used for high-throughput datasets. The current study provides instant identification of R proteins using machine learning approach, in addition to the similarity or domain prediction methods. © 2017 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>10.1371/journal.pone.0097446</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Supervised learning classification models for prediction of plant virus encoded RNA silencing suppressors</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Z., Jagga, Zeenia; D.K., Gupta, Dinesh Kumar</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>2014</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>PLOS ONE</t>
-        </is>
-      </c>
-      <c r="F154" t="n">
-        <v>2</v>
-      </c>
-      <c r="G154" t="n">
-        <v>0.6445139646530151</v>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Tópico 3: protein, effector, sequence</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Viral encoded RNA silencing suppressor proteins interfere with the host RNA silencing machinery, facilitating viral infection by evading host immunity. In plant hosts, the viral proteins have several basic science implications and biotechnology applications. However in silico identification of these proteins is limited by their high sequence diversity. In this study we developed supervised learning based classification models for plant viral RNA silencing suppressor proteins in plant viruses. We developed four classifiers based on supervised learning algorithms: J48, Random Forest, LibSVM and Naïve Bayes algorithms, with enriched model learning by correlation based feature selection. Structural and physicochemical features calculated for experimentally verified primary protein sequences were used to train the classifiers. The training features include amino acid composition; auto correlation coefficients; composition, transition, and distribution of various physicochemical properties; and pseudo amino acid composition. Performance analysis of predictive models based on 10 fold cross-validation and independent data testing revealed that the Random Forest based model was the best and achieved 86.11% overall accuracy and 86.22% balanced accuracy with a remarkably high area under the Receivers Operating Characteristic curve of 0.95 to predict viral RNA silencing suppressor proteins. The prediction models for plant viral RNA silencing suppressors can potentially aid identification of novel viral RNA silencing suppressors, which will provide valuable insights into the mechanism of RNA silencing and could be further explored as potential targets for designing novel antiviral therapeutics. Also, the key subset of identified optimal features may help in determining compositional patterns in the viral proteins which are important determinants for RNA silencing suppressor activities. The best prediction model developed in the study is available as a freely accessible web server pVsupPred at http://bioinfo.icgeb.res.in/pvsup/. © 2014 Jagga, Gupta. © 2014 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>10.1371/journal.ppat.1003972</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Code-Assisted Discovery of TAL Effector Targets in Bacterial Leaf Streak of Rice Reveals Contrast with Bacterial Blight and a Novel Susceptibility Gene</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>R.A., Cernadas, Raúl Andrés; E.L., Doyle, Erin L.; D.O., Niño-Liu, David O.; K.E., Wilkins, Katherine E.; T.J., Bancroft, Tim J.; L., Wang, Li; C.L., Schmidt, Clarice L.; R.A., Caldo, Rico A.; B., Yang, Bing; F.F., White, Frank F.</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>2014</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>PLOS Pathogens</t>
-        </is>
-      </c>
-      <c r="F155" t="n">
-        <v>2</v>
-      </c>
-      <c r="G155" t="n">
-        <v>0.7025050520896912</v>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Tópico 3: protein, effector, sequence</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Bacterial leaf streak of rice, caused by Xanthomonas oryzae pv. oryzicola (Xoc) is an increasingly important yield constraint in this staple crop. A mesophyll colonizer, Xoc differs from X. oryzae pv. oryzae (Xoo), which invades xylem to cause bacterial blight of rice. Both produce multiple distinct TAL effectors, type III-delivered proteins that transactivate effector-specific host genes. A TAL effector finds its target(s) via a partially degenerate code whereby the modular effector amino acid sequence identifies nucleotide sequences to which the protein binds. Virulence contributions of some Xoo TAL effectors have been shown, and their relevant targets, susceptibility (S) genes, identified, but the role of TAL effectors in leaf streak is uncharacterized. We used host transcript profiling to compare leaf streak to blight and to probe functions of Xoc TAL effectors. We found that Xoc and Xoo induce almost completely different host transcriptional changes. Roughly one in three genes upregulated by the pathogens is preceded by a candidate TAL effector binding element. Experimental analysis of the 44 such genes predicted to be Xoc TAL effector targets verified nearly half, and identified most others as false predictions. None of the Xoc targets is a known bacterial blight S gene. Mutational analysis revealed that Tal2g, which activates two genes, contributes to lesion expansion and bacterial exudation. Use of designer TAL effectors discriminated a sulfate transporter gene as the S gene. Across all targets, basal expression tended to be higher than genome-average, and induction moderate. Finally, machine learning applied to real vs. falsely predicted targets yielded a classifier that recalled 92% of the real targets with 88% precision, providing a tool for better target prediction in the future. Our study expands the number of known TAL effector targets, identifies a new class of S gene, and improves our ability to predict functional targeting. © 2014 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>10.1007/978-1-4614-6372-6_8</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>In-silico approaches for studying the MAP kinase signaling pathways involved in resistance against Alternaria blight in Brassica</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>G., Taj, Gohar; S., Sharma, Sugandha; P., Giri, Priyanka; D., Pandey, Dinesh; A., Kumar, Anil</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>2013</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Springer eBooks</t>
-        </is>
-      </c>
-      <c r="F156" t="n">
-        <v>2</v>
-      </c>
-      <c r="G156" t="n">
-        <v>0.6064732670783997</v>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Tópico 3: protein, effector, sequence</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>The most devastating fungal disease of Brassica is Black spot or Alternaria blight caused by Alternaria brassicae. Alternaria brassicae causes the disease through the production of host specific toxin viz. chlorotic and necrotic toxins, which are responsible for the formation of chlorotic, necrotic and green islands like disease symptoms in susceptible Brassica leaves. Signal transduction is the means by which cells respond to extracellular information. Mitogen- activated protein kinase (MAPK) cascades are important signaling modules in eukaryotic cells. MAPK are important intermediates in signal transduction pathways that are initiated by many types of cell surface receptors. They function Downstream of sensors/receptors and regulate cellular responses to external and endogenous stimuli. Mitogen activated kinase, ensures their specificity of action by interacting with its different substrates through docking domains. Specific docking interactions between MAPKs and its substrate are crucial for efficient and accurate signal transmission. Recent studies have shown that disease resistance against any pathogen in plant is governed by combinatorial interaction between proteins. Therefore, now a day's much effort has gone into finding the complete set of interacting protein. Genome wide protein-protein interaction network have been realized by using high throughput methods like yeast two hybrid system and affinity immunochip based system. Some groups studied the partner of MAPK by using phosphoproteomics approach. However these methods are cost effective, require good infrastructure and contain high false positive result. The need of in silico methods for protein-protein interaction prediction is being driven by above listed limitation and also by the generation of sequences at a rate far beyond our ability to carry out experimental functional analysis. In this chapter we are trying to give insight about different in silico approaches e.g. Machine Learning Approaches viz., Hidden Markov Model (HMM), Neural Network (NN), Support Vector Machine (SVM) etc., Direct Sequence Analysis approach that takes into account surface information for predicting protein-protein interaction, Docking studies which attempts to use geometric and steric considerations to fit two proteins of known structure into a bound complex,(iv) through Phylogenetic profiling. By using some of these methods we studied the MAPK interaction with upstream or downstream proteins viz WRKY protein, Myb protein, bZIP, NAC, MAPKK, Phosphatases and some other defence proteins. The main advantages of these in-silico approaches are less expensive, provide result in less time and the precision and accuracy are also much better than the conventional wet lab methods. © 2016 Elsevier B.V., All rights reserved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>10.1109/MVIP62238.2024.10491178</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Tomato Leaf Disease Detection Using Transfer Learning: A Comparative Study</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>M. Bahrami; A. Pourhatami; M. Maboodi</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>2024 13th Iranian/3rd International Machine Vision and Image Processing Conference (MVIP)</t>
-        </is>
-      </c>
-      <c r="F157" t="n">
-        <v>6</v>
-      </c>
-      <c r="G157" t="n">
-        <v>0.697862982749939</v>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Tópico 7: model, data, study</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Tomato, a vital food crop enriched with essential minerals and vitamins, is widely used in various cuisines. Leaf disease is a common problem that significantly impacts the quantity and quality of tomato production. So, farmers should accurately surveil tomato farms to manufacture high-quality foods free from pests. In this regard, accurate and robust algorithms are needed to detect tomato leaf disease. Among various methods, deep learning algorithms provide automatic, accurate, and robust leaf disease detection algorithms. In this paper, a comprehensive analysis of different transfer learning algorithms, including VGG19, ResNet-101, and MobileNet-v2 was done on PlantVillage and CCMT datasets. The best performance was achieved by VGG19, where the best accuracy, precision, recall, and F1-score on the test set of PlantVillage and CCMT datasets were 99.48%, 99.27%, 99.28%, 99.27%, and 92.76%, 92.74%, 95.09%, 90.86%, respectively. The results demonstrate that VGG19 can detect tomato leaf disease precisely and robustly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>10.1109/ICOSEC61587.2024.10722678</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>A Detailed Investigation of Deep Learning and Machine Learning Approaches for Sugarcane Foliage Disorder Identification</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>R. T. Khatoon; D. Ashok; S. K. R. Mallidi; V. Gopikrishna; P. Srikanth; P. Bhaskar</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>2024 5th International Conference on Smart Electronics and Communication (ICOSEC)</t>
-        </is>
-      </c>
-      <c r="F158" t="n">
-        <v>4</v>
-      </c>
-      <c r="G158" t="n">
-        <v>0.598248302936554</v>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Tópico 5: crop, soil, system</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Our nation grows an enormous amount of sugarcane. Sugarcane is no exception to the rule that plants are susceptible to disease. One problem with the sugar industry is that small-scale farmers lose revenue when sugarcane diseases aren’t identified and addressed in time to save the growing crops. A popular way for a farmer to discover and diagnose sugarcane illnesses is by visual inspection. Using this method on large farms becomes more laborious and time-consuming. The farmers and sugarcane business are both put at risk if it is not handled sooner. This inquiry was motivated by the ever-increasing types of ailments and the fact that farmers have limited abilities when it comes to diagnosing and identifying these diseases. A combination of Deep Learning (DL), Computer Vision (CV), and Machine Learning (ML) can solve this challenge. To boost agricultural output and efficiency, specialists have taken an interest in prompt disease identification and diagnosis. Losses may be avoided by employing ML and DL algorithms for early disease detection in sugarcane crops. The purpose of this research was to quickly and accurately extract diagnostic information from sugarcane using a variety of image processing and DL methods. Additionally, the difficulties and potential future directions of computational methods for evaluating sugarcane infestations are brought to light.</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>10.1109/ICMLC.2010.21</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>SVM Model for Amino Acid Composition Based Prediction of MMPs and ADAMs</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>K. Pant; B. Pant; K. R. Pardasani</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>2010</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>2010 Second International Conference on Machine Learning and Computing</t>
-        </is>
-      </c>
-      <c r="F159" t="n">
-        <v>2</v>
-      </c>
-      <c r="G159" t="n">
-        <v>0.7592259049415588</v>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Tópico 3: protein, effector, sequence</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>The MMPs and ADAMs are cell surface proteases which belong to metalloprotease family. They play an important role in skin aging, skin disorders, anticancer therapy and other physiological disorders. Thus there arises the need to understand the relationships among various parameters of these proteins for prediction of their classes, structures and functionality. The computational approaches for prediction of their classes are fast and economical therefore can be used to complement the existing wet lab techniques. Realizing their importance, in this paper an attempt has been made to correlate them with their amino acid composition and predict them with fair accuracy. This is a novel method where ADAMs and MMPs have been classified on the basis of amino acid composition using Support Vector Machine. The SVM has been implemented using Lib SVM package. The method discriminates MMP subfamily from ADAM proteases with Matthew's correlation coefficient of 0.98 using amino acid composition. The performance of the method was evaluated using 5-fold cross-validation where accuracy of 98% was obtained.</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>10.1109/AECE59614.2023.10428363</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>A Novel Cloud-Based Framework for Leaf Disease Detection and Classification: Enhancing Plant Health Using Android Applications</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>A. Kiran; A. Namdev; R. R. Chandan; P. B. Waghmare; D. Dhabliya; A. Gupta</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>2023 3rd International Conference on Advancement in Electronics &amp; Communication Engineering (AECE)</t>
-        </is>
-      </c>
-      <c r="F160" t="n">
-        <v>6</v>
-      </c>
-      <c r="G160" t="n">
-        <v>0.4900111854076385</v>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Tópico 7: model, data, study</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>The difficult challenge of identifying the leaf disease in agriculture is employed to stop the dangerous epidemic. The majority of plant diseases are brought on by fungus, bacteria, and viruses, with the fungi often attached to the plant's reproductive organs. As a result, bacteria have simpler life cycles and are more dangerous than fungi. Similar to bacteria, viruses are microscopic particles that contain genetic information and protein but no additional protein. Therefore, it is crucial to spot illness in plant leaves. Therefore, the goal of this research is to identify leaf disease in a cloudy environment. The use of smartphones for many applications has increased recently. A brand-new operating system called Android is freely accessible in the Android Market. Thus, this study uses an Android application to develop a cloud-based illness categorization system.</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>10.1109/PDGC56933.2022.10053320</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Analysis of Apple Plant Leaf Diseases Detection and Classification: A Review</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>S. Kumar; R. Kumar; M. Gupta</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>2022 Seventh International Conference on Parallel, Distributed and Grid Computing (PDGC)</t>
-        </is>
-      </c>
-      <c r="F161" t="n">
-        <v>1</v>
-      </c>
-      <c r="G161" t="n">
-        <v>0.5088988542556763</v>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Tópico 2: tomato, fruit, grape</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Agriculture has a vital role in the development of any country like India where the majority of the population’s livelihood depends on agriculture. Every year, diseases and pests harm apple production by a significant amount of money. Farmers face a challenge in identifying distinct apple illnesses because the symptoms of different illnesses can be extremely similar and occur at the same time. Therefore, Leaf Disease Prediction (LDP) in apple cultivation is considerably important to overcome these problems. In this work, an overview of the taxonomy of apple plant diseases is discussed with their symptoms, cause, and effect. This study concluded that the method used for automatic detection and classification of apple plant diseases is still in its infancy. Hence, a new efficient model is required for the detection and classification of apple plant leaf disease that can save the farmer from loss as well as help them in increasing the production of apples.</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>10.1109/ICET54505.2021.9689807</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Identification of Leaf Diseases in Potato Crop Using Deep Convolutional Neural Networks (DCNNs)</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Z. Saeed; M. Urooj Khan; A. Raza; N. Sajjad; S. Naz; A. Salal</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>2021</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>2021 16th International Conference on Emerging Technologies (ICET)</t>
-        </is>
-      </c>
-      <c r="F162" t="n">
-        <v>0</v>
-      </c>
-      <c r="G162" t="n">
-        <v>0.5312085151672363</v>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Tópico 1: cassava, blight, potato</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Potatoes are used by a billion people globally as its intake per capita is 31.3 kilograms per month worldwide and its crop production surpasses 300 million metric tons. They have great nutritional potential and offer more protein and iron than other vegetables. Various diseases, such as early blight, late blight, and others, will attack potato plants and manifest their symptoms in the leaves. If these outbreaks are discovered early and appropriate treatment is taken, the farmer will not suffer significant economic losses. In this article, the suggested computer vision deep learning approach would significantly help in early identification and detection of different potato disease. Many plant diseases have different visual characteristics that may be utilized to accurately identify and classify them. This study describes a potato disease classification method based on computer vision-deep learning combination. The system trains deep convolutional neural networks such as ResNet-152 and InceptionV3 on the Kaggle potato dataset with an accuracy of 98.34% and 95.24% respectively at learning rate of 0.0005. This system successfully performs the classification of three categories: healthy, early, and late blight for potato leaves.</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>10.1109/ACCESS.2024.3407153</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Mulberry Leaf Disease Detection Using CNN-Based Smart Android Application</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>A. Salam; M. Naznine; N. Jahan; E. Nahid; M. Nahiduzzaman; M. E. H. Chowdhury</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>IEEE Access</t>
-        </is>
-      </c>
-      <c r="F163" t="n">
-        <v>4</v>
-      </c>
-      <c r="G163" t="n">
-        <v>0.5830755233764648</v>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Tópico 5: crop, soil, system</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Mulberry leaves serve as the primary food source for Bombyx mori silkworms, crucial for silk thread production. However, mulberry trees are highly susceptible to diseases, spreading rapidly and causing significant losses. Manual disease identification across large farms is arduous and time-consuming. Leveraging computer vision for early disease detection and classification can mitigate up to 90% of production losses. This study collected leaves from two regions of Bangladesh, categorized as healthy, leaf rust-affected, and leaf spot-affected. With a total of 1091 images, split into training (764), testing (218), and validation (109) sets for 5-fold cross-validation, preprocessing and augmentation yielded 6,000 images, including synthetics. This study compares ResNet50, VGG19, and MobileNetV3Small on a specific task following architecture modifications. Four convolutional layers with different output channels (512, 128, 64, and 32) were added to baseline models. We assessed how these architectural changes affected model correctness, computing efficiency, and convergence rates. Comparing three pretrained convolutional neural networks (CNNs) - MobileNetV3Small, ResNet50, and VGG19 - augmented with four additional layers, the modified MobileNetV3Small excelled in precision, recall, F1-score, and accuracy, achieving notable results of 97.0%, 96.4%, 96.4%, and 96.4%, respectively, across cross-validation folds. An efficient smartphone application employing the proposed model for mulberry leaf disease recognition was developed. Overall, the model outperformed existing State of the Art (SOTA) approaches, showcasing its effectiveness in disease identification. The interpretative Grad-CAM visualization images match sericulture specialists’ assessments, validating the model’s predictions. These results imply that, this eXplainable AI (XAI) approach with a modified deep learning architecture can appropriately classify mulberry leaves.</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>10.1109/ICEET56468.2022.10007133</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Federated learning-based UAVs for the diagnosis of Plant Diseases</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>F. S. Khan; S. Khan; M. N. H. Mohd; A. Waseem; M. N. A. Khan; S. Ali; R. Ahmed</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>2022 International Conference on Engineering and Emerging Technologies (ICEET)</t>
-        </is>
-      </c>
-      <c r="F164" t="n">
-        <v>4</v>
-      </c>
-      <c r="G164" t="n">
-        <v>0.7798483371734619</v>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Tópico 5: crop, soil, system</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>The technological revolution for farmers, especially for the safety of their crops from pests, plays an evident change and convenience for the agriculture industry. The current research presented the classification of different pests using federated learning-based UAVs. The designed scenarios comprise four different sites connected with a global model where different parameters for these sites are received from the local model. State-of-the-art EfficientNet deep model with B03 configurations provides the best accuracy for classifying nine types of pests. The system can achieve an accuracy of 99.55% with the augmentation of images into different angles. The federated learning designed UAVs are the most reliable connection with very less computation power during the classification of pests for the agricultural environment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>10.1109/INCET64471.2025.11140131</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Tomato Leaf Disease Detection Using a Convolutional Neural Network</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>K. K. Kumar; R. Jawwharlal; V. S; J. B. Naik; B. Suma; A. Gupta</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>2025</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>2025 6th International Conference for Emerging Technology (INCET)</t>
-        </is>
-      </c>
-      <c r="F165" t="n">
-        <v>1</v>
-      </c>
-      <c r="G165" t="n">
-        <v>0.7895268201828003</v>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Tópico 2: tomato, fruit, grape</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Tomatoes are one of the most widely farmed and consumed vegetables in the world, and they are essential to the agricultural industry. Tomato plants are unfortunately prone to a number of illnesses, which can result in decreased production and quality and substantial financial losses. Grey leaf spot is one of the most prevalent diseases affecting tomato plants. It damages and destroys the leaves, which eventually prevents the plant from bearing fruit. Contact, invasion, latency, and onset are the four stages of the infection that the pathogen that causes grey leaf spot in tomato plants goes through. Early illness detection can provide effective management strategies and potentially avert widespread pandemics. Solanum lycopersicum, often known as the South Indian tomato, is a widely used vegetable in cooking. The tomato plant is widely cultivated and regarded as a significant agricultural commodity due to its ability to adapt to a range of environmental conditions and its abundance in potassium, vitamins C and K, and other minerals. However, growing tomatoes is not without its difficulties. Leaf diseases, which can reduce yields by as much as 60%, are one major challenge. The likelihood that conventional detection methods won't be able to keep up with the quick trends in plant diseases underscores the urgent need for creative alternatives. NNs provide a new technique for identifying tomato leaf disease. An inventive technique that utilizes and accurately diagnoses tomato leaf diseases is presented in this study. neural networks with convolutions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>10.1109/ICSC64553.2025.10968949</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Population Nutrition-Driven Crop Recommendations: Addressing Regional Micronutrient Deficiencies for Improved Public Health</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>P. Seshanth Vishal; P. Subedi; S. R. Divakarla; A. Harini; L. S</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>2025</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>2025 10th International Conference on Signal Processing and Communication (ICSC)</t>
-        </is>
-      </c>
-      <c r="F166" t="n">
-        <v>4</v>
-      </c>
-      <c r="G166" t="n">
-        <v>0.9080201387405396</v>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Tópico 5: crop, soil, system</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Crop yield optimization is paramount for an agriculture-based economy such as India, particularly in rural areas, which account for 92.02% of the agricultural workforce. However rural areas suffer the most from nutritional deficiencies. The proposed work attempts to combat the malnutrition by recommending crops which not only leverages the soil conditions (N, P, K, pH) and environmental conditions (humidity, rain, temperature) but also the micronutrient deficiencies among the regional population (Sodium, Potassium, Vitamin C, Calcium, Iron, Vitamin B6, Magnesium per 100mg). A hybrid dataset combining the crop recommendation dataset and USDA nutritional values dataset was prepared and utilized Six Machine Learning models-Decision trees, Support Vector machine (SVM), Logistic regression (LR), XGBoost, Random Forest (RF), and Naive Bayes (NB)-were trained and evaluated to determine the most effective model. The Random Forest classifier demonstrates an accuracy of 100% for the dataset used. The implementation of precision farming techniques optimizes crop yield production and contributes to food security and sustainable agriculture. Furthermore, the proposed work addresses the previously overlooked issue of deficiencies and recommends crops containing nutrients based on regional requirements. This approach will significantly impact agricultural produce and the holistic health of the population.</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>10.1109/CSDGAIS64098.2024.11064829</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Personalized Nutrition Recommendations Using Machine Learning</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>K. Samy; A. Osheba; H. S. El-Din; R. M. Sallam; M. A. Elaziz</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>2024 International Conference on Smart-Digital-Green Technologies and Artificial Intelligence Sciences (CSDGAIS)</t>
-        </is>
-      </c>
-      <c r="F167" t="n">
-        <v>4</v>
-      </c>
-      <c r="G167" t="n">
-        <v>0.9889057278633118</v>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Tópico 5: crop, soil, system</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Human nutrition is essential for maintaining health, promoting growth and development, preventing chronic diseases, managing medical conditions, and improving mental well-being. Nutritional imbalances, due to inadequate or excessive dietary intake, can lead to significant health issues. This project focuses on developing an advanced AI-based system to provide personalized nutrition recommendations for individuals with specific medical conditions. Utilizing sophisticated algorithms, the system analyzes a wide range of data, including health metrics, dietary preferences, and medical restrictions, to create customized diet plans that meet each user's unique needs. By leveraging AI technology, the system offers enhanced capabilities in food nutrition analysis, caloric intake calculation, and prediction of nutrient deficiencies or toxicities. It will address various conditions such as diabetes, hypertension, and food allergies, aligning diet plans with medical guidelines.</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>10.1109/IGARSS.1990.688847</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Airborne Biochemical Mapping For Stress Detection In Coniferous Forests</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>C. Banninger</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>1990</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>10th Annual International Symposium on Geoscience and Remote Sensing</t>
-        </is>
-      </c>
-      <c r="F168" t="n">
-        <v>3</v>
-      </c>
-      <c r="G168" t="n">
-        <v>0.5456134080886841</v>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Tópico 4: yolov, increase, map</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>10.1109/IATMSI64286.2025.10985607</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Proposed Convolutional Neural Network for the Detection of Guava Leaf Diseases</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>R. Singh; S. Gupta; S. Aluvala; R. RiadHwsein; G. Sharma</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>2025</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>2025 IEEE International Conference on Interdisciplinary Approaches in Technology and Management for Social Innovation (IATMSI)</t>
-        </is>
-      </c>
-      <c r="F169" t="n">
-        <v>4</v>
-      </c>
-      <c r="G169" t="n">
-        <v>0.7081536054611206</v>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Tópico 5: crop, soil, system</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Fruit cultivation is essential for domestic consumption and global trade, as agriculture continues to be a fundamental pillar of numerous economies worldwide. Guava (Psidium guajava) is a highly regarded fruit for its nutritional benefits, including high levels of dietary fiber, antioxidants, and vitamins A and C. Nevertheless, guava cultivation is encountering substantial obstacles due to various leaf diseases, which can harm the quality of the fruit and the yield. It is imperative to effectively manage these diseases to guarantee the optimal fruit production and guava crops' health. Timely and precise disease identification is critical to conventional disease management strategies, including applying fungicides, cultivating resistant varieties, and implementing cultural practices. Recent developments in deep learning, particularly Convolutional Neural Networks (CNNs), present promising solutions for the automated detection and classification of plant diseases based on visual symptoms. A CNN model that is specifically designed for the classification of guava leaf diseases, such as Canker, Dot, Mummification, Rust, and Healthy leaves, is proposed in this study. The model was trained on a comprehensive dataset that included 2108 training images and 527 testing images, and it was subsequently evaluated over a period of 30 epochs. It achieved an overall accuracy of 86.91%, with high precision, recall, and F1 scores across various disease categories. The model's potential for practical applications in agriculture, such as mobile apps or field-based systems, to assist farmers in the timely and effective management of diseases is evident in its robustness and reliability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>10.1109/IATMSI64286.2025.10984798</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>AI-enabled Recapitulated Neuro Fuzzy Optimization (RNFO)algorithm for evaluating the food consumption and nutrition during COVID-19</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>H. M. Henrietta; A. Stanley Raj</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>2025</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>2025 IEEE International Conference on Interdisciplinary Approaches in Technology and Management for Social Innovation (IATMSI)</t>
-        </is>
-      </c>
-      <c r="F170" t="n">
-        <v>4</v>
-      </c>
-      <c r="G170" t="n">
-        <v>0.5573188066482544</v>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Tópico 5: crop, soil, system</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Food is essential for human survival and supports daily activities, energy production, and overall health. Adequate nutrient intake enables physiological and biochemical processes critical for energy conversion. Carbohydrates, among key nutrients, play a pivotal role in maintaining consistent energy levels. Malnutrition—marked by nutrient deficiencies or imbalances—is a pressing global health issue, with severe consequences for older adults who face age-related emotional and physical changes. Proper carbohydrate consumption helps regulate blood sugar and reduces the risk of chronic diseases. A balanced diet emphasizes natural foods while minimizing processed and high-fat animal products. This research explores the nutritional value of food, the impact of nutrient excess or deficiency, and carbohydrate’s health role. It employs an AI-driven Recapitulated Neuro-Fuzzy Optimization algorithm to analyze gender-based nutritional patterns during the COVID-19 pandemic.</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>10.1109/ECCE57851.2023.10101542</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>An Efficient Transfer Learning-based Approach for Apple Leaf Disease Classification</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>M. H. Ashmafee; T. Ahmed; S. Ahmed; M. B. Hasan; M. N. Jahan; A. B. M. Ashikur Rahman</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>2023 International Conference on Electrical, Computer and Communication Engineering (ECCE)</t>
-        </is>
-      </c>
-      <c r="F171" t="n">
-        <v>4</v>
-      </c>
-      <c r="G171" t="n">
-        <v>0.554876446723938</v>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Tópico 5: crop, soil, system</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Correct identification and categorization of plant diseases are crucial for ensuring the safety of the global food supply and the overall financial success of stakeholders. In this regard, a wide range of solutions has been made available by in-troducing deep learning-based classification systems for different staple crops. Despite being one of the most important commercial crops in many parts of the globe, research proposing a smart solution for automatically classifying apple leaf diseases remains relatively unexplored. This work proposes a transfer learning-based approach for identifying apple leaf diseases. The system extracts features using a pretrained EfficientNetV2S architecture and passes to a classifier block for effective prediction. The class imbalance issues are tackled by utilizing runtime data augmentation. The effect of various hyperparameters, such as input resolution, learning rate, number of epochs, etc., has been investigated carefully. The competence of the proposed pipeline has been evaluated on the apple leaf disease subset from the publicly available ‘PlantVillage’ dataset, where it achieved an accuracy of 99.21 %, outperforming the existing works.</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>10.1109/ICOSEC58147.2023.10276191</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Exploring a Novel Methodologies for Beetroot Leaf Disease Severity Prediction: Federated Learning and CNN</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>S. Mehta; V. Kukreja; V. Sharma; M. Manwal</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>2023 4th International Conference on Smart Electronics and Communication (ICOSEC)</t>
-        </is>
-      </c>
-      <c r="F172" t="n">
-        <v>4</v>
-      </c>
-      <c r="G172" t="n">
-        <v>0.5267233848571777</v>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Tópico 5: crop, soil, system</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>This study explains how a federated learning Convolutional Neural Network (CNN) model is used to diagnose the various degrees of beetroot leaf diseases. Beetroot crops are essential to the world's food systems, but several illnesses often affect their quality and productivity. To suggest a CNN model using federated learning to analyse data from several clients while preserving privacy for a quick and precise diagnosis. The method analyses the severity of the five stages of beetroot leaf diseases using a federated learning technique across several local clients to use precision, recall, F1-score, and accuracy as performance measurements. The review showed that performance had improved consistently for all customers. As an example, Client X had a prediction accuracy of 0.97, which increased gradually to 0.98 for both Client P and Client R. Additionally, as shown by the macro-average (94.15-94.17%), weighted average (94.67%), and micro-average (94.62%) scores for top-performing customers, the model's performance remained stable and resilient throughout all severity levels. The study's findings support using a CNN model built on federated learning for scalable, effective, and privacy-preserving disease control in agriculture. The promising results suggest the potential for extending such approaches to other agricultural products, considerably advancing efforts to ensure global food security. The research also showed that the CNN model could learn and develop continuously in a federated learning scenario, highlighting its usefulness as a dynamic tool that adapts to new illness patterns. A paradigm shift in the approach to combating agricultural illnesses and increasing food supply is heralded by this study, which reveals a potential junction between machine learning and agricultural disease management. The findings motivate more research into the model's adaptability to other crops and pests, enhancing its contribution to resilient and sustainable farming systems.</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.atech.2025.101406</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>A Review of the Application of UAV Multispectral Remote Sensing Technology in Precision Agriculture</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Shuang Zhang; Xiaorui Wang; Hong Lin; Zhenping Qiang</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>2025</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Smart Agricultural Technology</t>
-        </is>
-      </c>
-      <c r="F173" t="n">
-        <v>4</v>
-      </c>
-      <c r="G173" t="n">
-        <v>0.7627755999565125</v>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Tópico 5: crop, soil, system</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>With the growing demand for precision agriculture, which requires high spatial and temporal resolution crop information, unmanned aerial vehicles (UAVs) equipped with multispectral sensors have become increasingly vital tools for agricultural management due to their real-time monitoring capabilities, flexibility, and cost-effectiveness. This paper provides a scoping review of advances in UAV-based multispectral remote sensing applications in precision agriculture, focusing on four key domains: crop growth monitoring, pest and disease identification, nutrient status assessment, and yield prediction. We offer a comprehensive analysis of the relevant literature, evaluating the principal challenges and opportunities associated with deploying this technology in the field. Our review indicates that traditional vegetation indices (e.g., NDVI, GNDVI, SAVI) have achieved mature application across diverse crops. In contrast, integrating emerging indices (e.g., TCARI, RDVI, OSAVI) with intelligent algorithms can significantly enhance monitoring accuracy and operational efficiency. In addition, we recommend that future research prioritize improvements in algorithmic precision, optimizing the data-processing workflows, and interdisciplinary collaboration to promote deeper integration of UAV-based multispectral sensing and artificial intelligence methods. Finally, we outline several practical research directions to inform and guide subsequent investigations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1017/S2040470019000013</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Proceedings of the British Society of Animal Science</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Desconocido</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>2019</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Advances in Animal Biosciences</t>
-        </is>
-      </c>
-      <c r="F174" t="n">
-        <v>4</v>
-      </c>
-      <c r="G174" t="n">
-        <v>0.8107492327690125</v>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Tópico 5: crop, soil, system</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.rineng.2025.104507</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>The role of industry 4.0 technologies in the export flower industry: Insights from a systematic literature review and surveys in emerging economies</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Fernando Mantilla; Gonzalo Mejía; Diana Tascón</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>2025</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Results in Engineering</t>
-        </is>
-      </c>
-      <c r="F175" t="n">
-        <v>6</v>
-      </c>
-      <c r="G175" t="n">
-        <v>0.5198959112167358</v>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Tópico 7: model, data, study</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>This paper aims to investigate the application of Industry 4.0 technologies in the flower industry focusing on the export business. The flower export sector is a very important industry for developing countries with considerable potential for improvement with Industry 4.0 technologies. Despite this potential, the deployment of these technologies encounters numerous barriers especially in emerging countries. This paper also studies the influence of these technologies on the productivity and sustainability of flower farms, including the entire process from planting to post-harvest management and distribution. We use a mixed-method strategy to accomplish these objectives: we performed a systematic literature review and carried out exploratory surveys administered to flower farmers in Ecuador and Colombia. The findings indicate that while the application of smart agricultural technologies in floriculture is currently restricted in emerging countries, there exists potential for its implementation. This research also points out obstacles for their adoption, including expenses, technical difficulties, and insufficient specialist. This research discusses the opportunities and problems associated with the integration of Industry 4.0 technologies in floriculture by offering both theoretical and practical insights, while also giving recommendations for industry stakeholders in managing this transition.</t>
+          <t>Wheat rusts caused by biotrophic fungi of the genus Puccinia continuously threaten global wheat production and food security. The rapid evolution of virulent races, and the limitations of chemical fungicides, including environmental contamination, human health concerns, and resistance development, necessitate a shift towards integrated management strategies. This review explores biocontrol agents (BCAs), including fungal (Trichoderma spp., Cladosporium cladosporioides), bacterial (Bacillus subtilis, Pseudomonas spp.), and actinomycetes (Streptomyces spp.), as foundational components of wheat rusts management. We highlight their modes of action such as mycoparasitism, antibiosis, competition, and the induction of systemic resistance. Additionally, we explore how cutting-edge adjunct technologies can enhance the efficacy and sustainability of BCAs. These include nano-formulations, for targeted antimicrobial actions and plant defense potentiation; plant extracts and antimicrobial peptides as natural defense elicitors; and artificial intelligence (AI) tools, for presymptomatic detection, severity quantification, epidemic forecasting, and early warning systems that enable precise application of BCAs and nano-formulations. While BCAs, nanoformulations, plant extracts and AI-driven tools offer powerful, environmentally benign alternatives capable of significantly reducing reliance on synthetic chemicals, chemical fungicides remain an essential component of current wheat rusts management, particularly during severe epidemics or when rapid knockdown of inoculum is required. A truly integrated and sustainable strategy therefore combines these novel approaches with the judicious, resistance-management-oriented use of effective chemical fungicides applied according to economic thresholds and in rotation or mixture to delay resistance development, thereby maximizing durability and minimizing environmental impact. However, the successful translation of this strategy to the field hinges on overcoming key challenges in formulation stability, scalable production, and seamless integration into existing and chemical-based agricultural practices to mitigate the impact of wheat rusts and safeguard global wheat yields and food security.</t>
         </is>
       </c>
     </row>
